--- a/projetos/gestao-ia-planilhas/produto/kit-completo/09-horas-e-custo-por-projeto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/09-horas-e-custo-por-projeto.xlsx
@@ -2650,7 +2650,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="25">
-        <f>IF(OR(B5="",E5=""),"",E5*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B5,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B5="",E5=""),"",IFERROR(E5*INDEX(Config!$D$11:$D$20,MATCH(B5,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>420</v>
       </c>
       <c r="G5" s="24">
@@ -2690,7 +2690,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="25">
-        <f>IF(OR(B6="",E6=""),"",E6*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B6,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B6="",E6=""),"",IFERROR(E6*INDEX(Config!$D$11:$D$20,MATCH(B6,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G6" s="24">
@@ -2730,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="25">
-        <f>IF(OR(B7="",E7=""),"",E7*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B7,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B7="",E7=""),"",IFERROR(E7*INDEX(Config!$D$11:$D$20,MATCH(B7,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G7" s="24">
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="25">
-        <f>IF(OR(B8="",E8=""),"",E8*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B8,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B8="",E8=""),"",IFERROR(E8*INDEX(Config!$D$11:$D$20,MATCH(B8,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>308.571428571429</v>
       </c>
       <c r="G8" s="24">
@@ -2810,7 +2810,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="25">
-        <f>IF(OR(B9="",E9=""),"",E9*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B9,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B9="",E9=""),"",IFERROR(E9*INDEX(Config!$D$11:$D$20,MATCH(B9,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>232.142857142857</v>
       </c>
       <c r="G9" s="24">
@@ -2850,7 +2850,7 @@
         <v>0.5</v>
       </c>
       <c r="F10" s="25">
-        <f>IF(OR(B10="",E10=""),"",E10*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B10,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B10="",E10=""),"",IFERROR(E10*INDEX(Config!$D$11:$D$20,MATCH(B10,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>23.2142857142857</v>
       </c>
       <c r="G10" s="24">
@@ -2890,7 +2890,7 @@
         <v>3.5</v>
       </c>
       <c r="F11" s="25">
-        <f>IF(OR(B11="",E11=""),"",E11*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B11,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B11="",E11=""),"",IFERROR(E11*INDEX(Config!$D$11:$D$20,MATCH(B11,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G11" s="24">
@@ -2930,7 +2930,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="25">
-        <f>IF(OR(B12="",E12=""),"",E12*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B12,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B12="",E12=""),"",IFERROR(E12*INDEX(Config!$D$11:$D$20,MATCH(B12,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>241.666666666667</v>
       </c>
       <c r="G12" s="24">
@@ -2970,7 +2970,7 @@
         <v>5.5</v>
       </c>
       <c r="F13" s="25">
-        <f>IF(OR(B13="",E13=""),"",E13*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B13,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B13="",E13=""),"",IFERROR(E13*INDEX(Config!$D$11:$D$20,MATCH(B13,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>385</v>
       </c>
       <c r="G13" s="24">
@@ -3010,7 +3010,7 @@
         <v>3.5</v>
       </c>
       <c r="F14" s="25">
-        <f>IF(OR(B14="",E14=""),"",E14*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B14,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B14="",E14=""),"",IFERROR(E14*INDEX(Config!$D$11:$D$20,MATCH(B14,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G14" s="24">
@@ -3050,7 +3050,7 @@
         <v>0.5</v>
       </c>
       <c r="F15" s="25">
-        <f>IF(OR(B15="",E15=""),"",E15*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B15,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B15="",E15=""),"",IFERROR(E15*INDEX(Config!$D$11:$D$20,MATCH(B15,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>25.7142857142857</v>
       </c>
       <c r="G15" s="24">
@@ -3090,7 +3090,7 @@
         <v>6.5</v>
       </c>
       <c r="F16" s="25">
-        <f>IF(OR(B16="",E16=""),"",E16*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B16,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B16="",E16=""),"",IFERROR(E16*INDEX(Config!$D$11:$D$20,MATCH(B16,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>334.285714285714</v>
       </c>
       <c r="G16" s="24">
@@ -3130,7 +3130,7 @@
         <v>7.5</v>
       </c>
       <c r="F17" s="25">
-        <f>IF(OR(B17="",E17=""),"",E17*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B17,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B17="",E17=""),"",IFERROR(E17*INDEX(Config!$D$11:$D$20,MATCH(B17,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>348.214285714286</v>
       </c>
       <c r="G17" s="24">
@@ -3170,7 +3170,7 @@
         <v>1.5</v>
       </c>
       <c r="F18" s="25">
-        <f>IF(OR(B18="",E18=""),"",E18*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B18,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B18="",E18=""),"",IFERROR(E18*INDEX(Config!$D$11:$D$20,MATCH(B18,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G18" s="24">
@@ -3210,7 +3210,7 @@
         <v>3.5</v>
       </c>
       <c r="F19" s="25">
-        <f>IF(OR(B19="",E19=""),"",E19*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B19,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B19="",E19=""),"",IFERROR(E19*INDEX(Config!$D$11:$D$20,MATCH(B19,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G19" s="24">
@@ -3250,7 +3250,7 @@
         <v>3.5</v>
       </c>
       <c r="F20" s="25">
-        <f>IF(OR(B20="",E20=""),"",E20*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B20,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B20="",E20=""),"",IFERROR(E20*INDEX(Config!$D$11:$D$20,MATCH(B20,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G20" s="24">
@@ -3290,7 +3290,7 @@
         <v>3.5</v>
       </c>
       <c r="F21" s="25">
-        <f>IF(OR(B21="",E21=""),"",E21*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B21,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B21="",E21=""),"",IFERROR(E21*INDEX(Config!$D$11:$D$20,MATCH(B21,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G21" s="24">
@@ -3330,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="25">
-        <f>IF(OR(B22="",E22=""),"",E22*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B22,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B22="",E22=""),"",IFERROR(E22*INDEX(Config!$D$11:$D$20,MATCH(B22,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G22" s="24">
@@ -3370,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="25">
-        <f>IF(OR(B23="",E23=""),"",E23*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B23,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B23="",E23=""),"",IFERROR(E23*INDEX(Config!$D$11:$D$20,MATCH(B23,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G23" s="24">
@@ -3410,7 +3410,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="25">
-        <f>IF(OR(B24="",E24=""),"",E24*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B24,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B24="",E24=""),"",IFERROR(E24*INDEX(Config!$D$11:$D$20,MATCH(B24,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>360</v>
       </c>
       <c r="G24" s="24">
@@ -3450,7 +3450,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="25">
-        <f>IF(OR(B25="",E25=""),"",E25*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B25,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B25="",E25=""),"",IFERROR(E25*INDEX(Config!$D$11:$D$20,MATCH(B25,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>278.571428571429</v>
       </c>
       <c r="G25" s="24">
@@ -3490,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="25">
-        <f>IF(OR(B26="",E26=""),"",E26*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B26,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B26="",E26=""),"",IFERROR(E26*INDEX(Config!$D$11:$D$20,MATCH(B26,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G26" s="24">
@@ -3530,7 +3530,7 @@
         <v>3.5</v>
       </c>
       <c r="F27" s="25">
-        <f>IF(OR(B27="",E27=""),"",E27*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B27,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B27="",E27=""),"",IFERROR(E27*INDEX(Config!$D$11:$D$20,MATCH(B27,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G27" s="24">
@@ -3570,7 +3570,7 @@
         <v>3.5</v>
       </c>
       <c r="F28" s="25">
-        <f>IF(OR(B28="",E28=""),"",E28*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B28,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B28="",E28=""),"",IFERROR(E28*INDEX(Config!$D$11:$D$20,MATCH(B28,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G28" s="24">
@@ -3610,7 +3610,7 @@
         <v>6</v>
       </c>
       <c r="F29" s="25">
-        <f>IF(OR(B29="",E29=""),"",E29*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B29,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B29="",E29=""),"",IFERROR(E29*INDEX(Config!$D$11:$D$20,MATCH(B29,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>420</v>
       </c>
       <c r="G29" s="24">
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="25">
-        <f>IF(OR(B30="",E30=""),"",E30*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B30,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B30="",E30=""),"",IFERROR(E30*INDEX(Config!$D$11:$D$20,MATCH(B30,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G30" s="24">
@@ -3690,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="25">
-        <f>IF(OR(B31="",E31=""),"",E31*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B31,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B31="",E31=""),"",IFERROR(E31*INDEX(Config!$D$11:$D$20,MATCH(B31,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G31" s="24">
@@ -3730,7 +3730,7 @@
         <v>6.5</v>
       </c>
       <c r="F32" s="25">
-        <f>IF(OR(B32="",E32=""),"",E32*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B32,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B32="",E32=""),"",IFERROR(E32*INDEX(Config!$D$11:$D$20,MATCH(B32,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>334.285714285714</v>
       </c>
       <c r="G32" s="24">
@@ -3770,7 +3770,7 @@
         <v>7.5</v>
       </c>
       <c r="F33" s="25">
-        <f>IF(OR(B33="",E33=""),"",E33*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B33,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B33="",E33=""),"",IFERROR(E33*INDEX(Config!$D$11:$D$20,MATCH(B33,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>348.214285714286</v>
       </c>
       <c r="G33" s="24">
@@ -3810,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="25">
-        <f>IF(OR(B34="",E34=""),"",E34*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B34,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B34="",E34=""),"",IFERROR(E34*INDEX(Config!$D$11:$D$20,MATCH(B34,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G34" s="24">
@@ -3850,7 +3850,7 @@
         <v>2.5</v>
       </c>
       <c r="F35" s="25">
-        <f>IF(OR(B35="",E35=""),"",E35*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B35,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B35="",E35=""),"",IFERROR(E35*INDEX(Config!$D$11:$D$20,MATCH(B35,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G35" s="24">
@@ -3890,7 +3890,7 @@
         <v>3.5</v>
       </c>
       <c r="F36" s="25">
-        <f>IF(OR(B36="",E36=""),"",E36*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B36,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B36="",E36=""),"",IFERROR(E36*INDEX(Config!$D$11:$D$20,MATCH(B36,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G36" s="24">
@@ -3930,7 +3930,7 @@
         <v>3.5</v>
       </c>
       <c r="F37" s="25">
-        <f>IF(OR(B37="",E37=""),"",E37*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B37,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B37="",E37=""),"",IFERROR(E37*INDEX(Config!$D$11:$D$20,MATCH(B37,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G37" s="24">
@@ -3970,7 +3970,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="25">
-        <f>IF(OR(B38="",E38=""),"",E38*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B38,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B38="",E38=""),"",IFERROR(E38*INDEX(Config!$D$11:$D$20,MATCH(B38,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G38" s="24">
@@ -4010,7 +4010,7 @@
         <v>1.5</v>
       </c>
       <c r="F39" s="25">
-        <f>IF(OR(B39="",E39=""),"",E39*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B39,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B39="",E39=""),"",IFERROR(E39*INDEX(Config!$D$11:$D$20,MATCH(B39,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G39" s="24">
@@ -4050,7 +4050,7 @@
         <v>8</v>
       </c>
       <c r="F40" s="25">
-        <f>IF(OR(B40="",E40=""),"",E40*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B40,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B40="",E40=""),"",IFERROR(E40*INDEX(Config!$D$11:$D$20,MATCH(B40,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>411.428571428571</v>
       </c>
       <c r="G40" s="24">
@@ -4090,7 +4090,7 @@
         <v>5.5</v>
       </c>
       <c r="F41" s="25">
-        <f>IF(OR(B41="",E41=""),"",E41*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B41,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B41="",E41=""),"",IFERROR(E41*INDEX(Config!$D$11:$D$20,MATCH(B41,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>255.357142857143</v>
       </c>
       <c r="G41" s="24">
@@ -4130,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="25">
-        <f>IF(OR(B42="",E42=""),"",E42*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B42,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B42="",E42=""),"",IFERROR(E42*INDEX(Config!$D$11:$D$20,MATCH(B42,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G42" s="24">
@@ -4170,7 +4170,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="25">
-        <f>IF(OR(B43="",E43=""),"",E43*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B43,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B43="",E43=""),"",IFERROR(E43*INDEX(Config!$D$11:$D$20,MATCH(B43,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G43" s="24">
@@ -4210,7 +4210,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="25">
-        <f>IF(OR(B44="",E44=""),"",E44*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B44,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B44="",E44=""),"",IFERROR(E44*INDEX(Config!$D$11:$D$20,MATCH(B44,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G44" s="24">
@@ -4250,7 +4250,7 @@
         <v>5.5</v>
       </c>
       <c r="F45" s="25">
-        <f>IF(OR(B45="",E45=""),"",E45*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B45,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B45="",E45=""),"",IFERROR(E45*INDEX(Config!$D$11:$D$20,MATCH(B45,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>385</v>
       </c>
       <c r="G45" s="24">
@@ -4290,7 +4290,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="25">
-        <f>IF(OR(B46="",E46=""),"",E46*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B46,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B46="",E46=""),"",IFERROR(E46*INDEX(Config!$D$11:$D$20,MATCH(B46,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G46" s="24">
@@ -4330,7 +4330,7 @@
         <v>1.5</v>
       </c>
       <c r="F47" s="25">
-        <f>IF(OR(B47="",E47=""),"",E47*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B47,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B47="",E47=""),"",IFERROR(E47*INDEX(Config!$D$11:$D$20,MATCH(B47,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G47" s="24">
@@ -4370,7 +4370,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="25">
-        <f>IF(OR(B48="",E48=""),"",E48*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B48,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B48="",E48=""),"",IFERROR(E48*INDEX(Config!$D$11:$D$20,MATCH(B48,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>308.571428571429</v>
       </c>
       <c r="G48" s="24">
@@ -4410,7 +4410,7 @@
         <v>5.5</v>
       </c>
       <c r="F49" s="25">
-        <f>IF(OR(B49="",E49=""),"",E49*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B49,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B49="",E49=""),"",IFERROR(E49*INDEX(Config!$D$11:$D$20,MATCH(B49,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>255.357142857143</v>
       </c>
       <c r="G49" s="24">
@@ -4450,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="25">
-        <f>IF(OR(B50="",E50=""),"",E50*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B50,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B50="",E50=""),"",IFERROR(E50*INDEX(Config!$D$11:$D$20,MATCH(B50,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G50" s="24">
@@ -4490,7 +4490,7 @@
         <v>4.5</v>
       </c>
       <c r="F51" s="25">
-        <f>IF(OR(B51="",E51=""),"",E51*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B51,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B51="",E51=""),"",IFERROR(E51*INDEX(Config!$D$11:$D$20,MATCH(B51,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>217.5</v>
       </c>
       <c r="G51" s="24">
@@ -4530,7 +4530,7 @@
         <v>3</v>
       </c>
       <c r="F52" s="25">
-        <f>IF(OR(B52="",E52=""),"",E52*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B52,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B52="",E52=""),"",IFERROR(E52*INDEX(Config!$D$11:$D$20,MATCH(B52,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G52" s="24">
@@ -4570,7 +4570,7 @@
         <v>5.5</v>
       </c>
       <c r="F53" s="25">
-        <f>IF(OR(B53="",E53=""),"",E53*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B53,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B53="",E53=""),"",IFERROR(E53*INDEX(Config!$D$11:$D$20,MATCH(B53,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>385</v>
       </c>
       <c r="G53" s="24">
@@ -4610,7 +4610,7 @@
         <v>3</v>
       </c>
       <c r="F54" s="25">
-        <f>IF(OR(B54="",E54=""),"",E54*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B54,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B54="",E54=""),"",IFERROR(E54*INDEX(Config!$D$11:$D$20,MATCH(B54,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G54" s="24">
@@ -4650,7 +4650,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="25">
-        <f>IF(OR(B55="",E55=""),"",E55*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B55,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B55="",E55=""),"",IFERROR(E55*INDEX(Config!$D$11:$D$20,MATCH(B55,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G55" s="24">
@@ -4690,7 +4690,7 @@
         <v>6.5</v>
       </c>
       <c r="F56" s="25">
-        <f>IF(OR(B56="",E56=""),"",E56*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B56,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B56="",E56=""),"",IFERROR(E56*INDEX(Config!$D$11:$D$20,MATCH(B56,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>334.285714285714</v>
       </c>
       <c r="G56" s="24">
@@ -4730,7 +4730,7 @@
         <v>7</v>
       </c>
       <c r="F57" s="25">
-        <f>IF(OR(B57="",E57=""),"",E57*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B57,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B57="",E57=""),"",IFERROR(E57*INDEX(Config!$D$11:$D$20,MATCH(B57,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>325</v>
       </c>
       <c r="G57" s="24">
@@ -4770,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="F58" s="25">
-        <f>IF(OR(B58="",E58=""),"",E58*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B58,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B58="",E58=""),"",IFERROR(E58*INDEX(Config!$D$11:$D$20,MATCH(B58,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G58" s="24">
@@ -4810,7 +4810,7 @@
         <v>5.5</v>
       </c>
       <c r="F59" s="25">
-        <f>IF(OR(B59="",E59=""),"",E59*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B59,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B59="",E59=""),"",IFERROR(E59*INDEX(Config!$D$11:$D$20,MATCH(B59,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>265.833333333333</v>
       </c>
       <c r="G59" s="24">
@@ -4850,7 +4850,7 @@
         <v>3</v>
       </c>
       <c r="F60" s="25">
-        <f>IF(OR(B60="",E60=""),"",E60*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B60,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B60="",E60=""),"",IFERROR(E60*INDEX(Config!$D$11:$D$20,MATCH(B60,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G60" s="24">
@@ -4890,7 +4890,7 @@
         <v>4</v>
       </c>
       <c r="F61" s="25">
-        <f>IF(OR(B61="",E61=""),"",E61*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B61,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B61="",E61=""),"",IFERROR(E61*INDEX(Config!$D$11:$D$20,MATCH(B61,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>280</v>
       </c>
       <c r="G61" s="24">
@@ -4930,7 +4930,7 @@
         <v>3.5</v>
       </c>
       <c r="F62" s="25">
-        <f>IF(OR(B62="",E62=""),"",E62*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B62,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B62="",E62=""),"",IFERROR(E62*INDEX(Config!$D$11:$D$20,MATCH(B62,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G62" s="24">
@@ -4970,7 +4970,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="25">
-        <f>IF(OR(B63="",E63=""),"",E63*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B63,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B63="",E63=""),"",IFERROR(E63*INDEX(Config!$D$11:$D$20,MATCH(B63,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G63" s="24">
@@ -5010,7 +5010,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="25">
-        <f>IF(OR(B64="",E64=""),"",E64*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B64,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B64="",E64=""),"",IFERROR(E64*INDEX(Config!$D$11:$D$20,MATCH(B64,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>205.714285714286</v>
       </c>
       <c r="G64" s="24">
@@ -5050,7 +5050,7 @@
         <v>7</v>
       </c>
       <c r="F65" s="25">
-        <f>IF(OR(B65="",E65=""),"",E65*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B65,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B65="",E65=""),"",IFERROR(E65*INDEX(Config!$D$11:$D$20,MATCH(B65,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>325</v>
       </c>
       <c r="G65" s="24">
@@ -5090,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="25">
-        <f>IF(OR(B66="",E66=""),"",E66*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B66,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B66="",E66=""),"",IFERROR(E66*INDEX(Config!$D$11:$D$20,MATCH(B66,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G66" s="24">
@@ -5130,7 +5130,7 @@
         <v>4</v>
       </c>
       <c r="F67" s="25">
-        <f>IF(OR(B67="",E67=""),"",E67*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B67,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B67="",E67=""),"",IFERROR(E67*INDEX(Config!$D$11:$D$20,MATCH(B67,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G67" s="24">
@@ -5170,7 +5170,7 @@
         <v>4.5</v>
       </c>
       <c r="F68" s="25">
-        <f>IF(OR(B68="",E68=""),"",E68*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B68,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B68="",E68=""),"",IFERROR(E68*INDEX(Config!$D$11:$D$20,MATCH(B68,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>217.5</v>
       </c>
       <c r="G68" s="24">
@@ -5210,7 +5210,7 @@
         <v>3.5</v>
       </c>
       <c r="F69" s="25">
-        <f>IF(OR(B69="",E69=""),"",E69*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B69,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B69="",E69=""),"",IFERROR(E69*INDEX(Config!$D$11:$D$20,MATCH(B69,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G69" s="24">
@@ -5250,7 +5250,7 @@
         <v>2.5</v>
       </c>
       <c r="F70" s="25">
-        <f>IF(OR(B70="",E70=""),"",E70*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B70,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B70="",E70=""),"",IFERROR(E70*INDEX(Config!$D$11:$D$20,MATCH(B70,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G70" s="24">
@@ -5290,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="25">
-        <f>IF(OR(B71="",E71=""),"",E71*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B71,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B71="",E71=""),"",IFERROR(E71*INDEX(Config!$D$11:$D$20,MATCH(B71,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G71" s="24">
@@ -5330,7 +5330,7 @@
         <v>7</v>
       </c>
       <c r="F72" s="25">
-        <f>IF(OR(B72="",E72=""),"",E72*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B72,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B72="",E72=""),"",IFERROR(E72*INDEX(Config!$D$11:$D$20,MATCH(B72,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>360</v>
       </c>
       <c r="G72" s="24">
@@ -5370,7 +5370,7 @@
         <v>3.5</v>
       </c>
       <c r="F73" s="25">
-        <f>IF(OR(B73="",E73=""),"",E73*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B73,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B73="",E73=""),"",IFERROR(E73*INDEX(Config!$D$11:$D$20,MATCH(B73,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>162.5</v>
       </c>
       <c r="G73" s="24">
@@ -5410,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="25">
-        <f>IF(OR(B74="",E74=""),"",E74*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B74,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B74="",E74=""),"",IFERROR(E74*INDEX(Config!$D$11:$D$20,MATCH(B74,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G74" s="24">
@@ -5450,7 +5450,7 @@
         <v>3</v>
       </c>
       <c r="F75" s="25">
-        <f>IF(OR(B75="",E75=""),"",E75*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B75,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B75="",E75=""),"",IFERROR(E75*INDEX(Config!$D$11:$D$20,MATCH(B75,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G75" s="24">
@@ -5490,7 +5490,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="25">
-        <f>IF(OR(B76="",E76=""),"",E76*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B76,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B76="",E76=""),"",IFERROR(E76*INDEX(Config!$D$11:$D$20,MATCH(B76,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G76" s="24">
@@ -5530,7 +5530,7 @@
         <v>6</v>
       </c>
       <c r="F77" s="25">
-        <f>IF(OR(B77="",E77=""),"",E77*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B77,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B77="",E77=""),"",IFERROR(E77*INDEX(Config!$D$11:$D$20,MATCH(B77,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>420</v>
       </c>
       <c r="G77" s="24">
@@ -5570,7 +5570,7 @@
         <v>3.5</v>
       </c>
       <c r="F78" s="25">
-        <f>IF(OR(B78="",E78=""),"",E78*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B78,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B78="",E78=""),"",IFERROR(E78*INDEX(Config!$D$11:$D$20,MATCH(B78,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G78" s="24">
@@ -5610,7 +5610,7 @@
         <v>1.5</v>
       </c>
       <c r="F79" s="25">
-        <f>IF(OR(B79="",E79=""),"",E79*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B79,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B79="",E79=""),"",IFERROR(E79*INDEX(Config!$D$11:$D$20,MATCH(B79,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G79" s="24">
@@ -5650,7 +5650,7 @@
         <v>6</v>
       </c>
       <c r="F80" s="25">
-        <f>IF(OR(B80="",E80=""),"",E80*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B80,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B80="",E80=""),"",IFERROR(E80*INDEX(Config!$D$11:$D$20,MATCH(B80,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>308.571428571429</v>
       </c>
       <c r="G80" s="24">
@@ -5690,7 +5690,7 @@
         <v>5.5</v>
       </c>
       <c r="F81" s="25">
-        <f>IF(OR(B81="",E81=""),"",E81*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B81,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B81="",E81=""),"",IFERROR(E81*INDEX(Config!$D$11:$D$20,MATCH(B81,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>255.357142857143</v>
       </c>
       <c r="G81" s="24">
@@ -5730,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="25">
-        <f>IF(OR(B82="",E82=""),"",E82*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B82,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B82="",E82=""),"",IFERROR(E82*INDEX(Config!$D$11:$D$20,MATCH(B82,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G82" s="24">
@@ -5770,7 +5770,7 @@
         <v>3.5</v>
       </c>
       <c r="F83" s="25">
-        <f>IF(OR(B83="",E83=""),"",E83*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B83,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B83="",E83=""),"",IFERROR(E83*INDEX(Config!$D$11:$D$20,MATCH(B83,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G83" s="24">
@@ -5810,7 +5810,7 @@
         <v>2.5</v>
       </c>
       <c r="F84" s="25">
-        <f>IF(OR(B84="",E84=""),"",E84*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B84,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B84="",E84=""),"",IFERROR(E84*INDEX(Config!$D$11:$D$20,MATCH(B84,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G84" s="24">
@@ -5850,7 +5850,7 @@
         <v>5</v>
       </c>
       <c r="F85" s="25">
-        <f>IF(OR(B85="",E85=""),"",E85*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B85,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B85="",E85=""),"",IFERROR(E85*INDEX(Config!$D$11:$D$20,MATCH(B85,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>350</v>
       </c>
       <c r="G85" s="24">
@@ -5890,7 +5890,7 @@
         <v>3</v>
       </c>
       <c r="F86" s="25">
-        <f>IF(OR(B86="",E86=""),"",E86*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B86,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B86="",E86=""),"",IFERROR(E86*INDEX(Config!$D$11:$D$20,MATCH(B86,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G86" s="24">
@@ -5930,7 +5930,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="25">
-        <f>IF(OR(B87="",E87=""),"",E87*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B87,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B87="",E87=""),"",IFERROR(E87*INDEX(Config!$D$11:$D$20,MATCH(B87,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G87" s="24">
@@ -5970,7 +5970,7 @@
         <v>1.5</v>
       </c>
       <c r="F88" s="25">
-        <f>IF(OR(B88="",E88=""),"",E88*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B88,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B88="",E88=""),"",IFERROR(E88*INDEX(Config!$D$11:$D$20,MATCH(B88,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G88" s="24">
@@ -6010,7 +6010,7 @@
         <v>5.5</v>
       </c>
       <c r="F89" s="25">
-        <f>IF(OR(B89="",E89=""),"",E89*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B89,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B89="",E89=""),"",IFERROR(E89*INDEX(Config!$D$11:$D$20,MATCH(B89,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>282.857142857143</v>
       </c>
       <c r="G89" s="24">
@@ -6050,7 +6050,7 @@
         <v>7.5</v>
       </c>
       <c r="F90" s="25">
-        <f>IF(OR(B90="",E90=""),"",E90*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B90,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B90="",E90=""),"",IFERROR(E90*INDEX(Config!$D$11:$D$20,MATCH(B90,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>348.214285714286</v>
       </c>
       <c r="G90" s="24">
@@ -6090,7 +6090,7 @@
         <v>1.5</v>
       </c>
       <c r="F91" s="25">
-        <f>IF(OR(B91="",E91=""),"",E91*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B91,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B91="",E91=""),"",IFERROR(E91*INDEX(Config!$D$11:$D$20,MATCH(B91,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G91" s="24">
@@ -6130,7 +6130,7 @@
         <v>4.5</v>
       </c>
       <c r="F92" s="25">
-        <f>IF(OR(B92="",E92=""),"",E92*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B92,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B92="",E92=""),"",IFERROR(E92*INDEX(Config!$D$11:$D$20,MATCH(B92,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>217.5</v>
       </c>
       <c r="G92" s="24">
@@ -6170,7 +6170,7 @@
         <v>2.5</v>
       </c>
       <c r="F93" s="25">
-        <f>IF(OR(B93="",E93=""),"",E93*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B93,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B93="",E93=""),"",IFERROR(E93*INDEX(Config!$D$11:$D$20,MATCH(B93,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G93" s="24">
@@ -6210,7 +6210,7 @@
         <v>5</v>
       </c>
       <c r="F94" s="25">
-        <f>IF(OR(B94="",E94=""),"",E94*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B94,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B94="",E94=""),"",IFERROR(E94*INDEX(Config!$D$11:$D$20,MATCH(B94,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>350</v>
       </c>
       <c r="G94" s="24">
@@ -6250,7 +6250,7 @@
         <v>2.5</v>
       </c>
       <c r="F95" s="25">
-        <f>IF(OR(B95="",E95=""),"",E95*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B95,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B95="",E95=""),"",IFERROR(E95*INDEX(Config!$D$11:$D$20,MATCH(B95,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G95" s="24">
@@ -6290,7 +6290,7 @@
         <v>2</v>
       </c>
       <c r="F96" s="25">
-        <f>IF(OR(B96="",E96=""),"",E96*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B96,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B96="",E96=""),"",IFERROR(E96*INDEX(Config!$D$11:$D$20,MATCH(B96,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G96" s="24">
@@ -6330,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="25">
-        <f>IF(OR(B97="",E97=""),"",E97*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B97,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B97="",E97=""),"",IFERROR(E97*INDEX(Config!$D$11:$D$20,MATCH(B97,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G97" s="24">
@@ -6370,7 +6370,7 @@
         <v>4</v>
       </c>
       <c r="F98" s="25">
-        <f>IF(OR(B98="",E98=""),"",E98*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B98,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B98="",E98=""),"",IFERROR(E98*INDEX(Config!$D$11:$D$20,MATCH(B98,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>205.714285714286</v>
       </c>
       <c r="G98" s="24">
@@ -6410,7 +6410,7 @@
         <v>6.5</v>
       </c>
       <c r="F99" s="25">
-        <f>IF(OR(B99="",E99=""),"",E99*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B99,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B99="",E99=""),"",IFERROR(E99*INDEX(Config!$D$11:$D$20,MATCH(B99,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>301.785714285714</v>
       </c>
       <c r="G99" s="24">
@@ -6450,7 +6450,7 @@
         <v>0.5</v>
       </c>
       <c r="F100" s="25">
-        <f>IF(OR(B100="",E100=""),"",E100*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B100,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B100="",E100=""),"",IFERROR(E100*INDEX(Config!$D$11:$D$20,MATCH(B100,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>23.2142857142857</v>
       </c>
       <c r="G100" s="24">
@@ -6490,7 +6490,7 @@
         <v>3.5</v>
       </c>
       <c r="F101" s="25">
-        <f>IF(OR(B101="",E101=""),"",E101*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B101,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B101="",E101=""),"",IFERROR(E101*INDEX(Config!$D$11:$D$20,MATCH(B101,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G101" s="24">
@@ -6530,7 +6530,7 @@
         <v>2.5</v>
       </c>
       <c r="F102" s="25">
-        <f>IF(OR(B102="",E102=""),"",E102*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B102,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B102="",E102=""),"",IFERROR(E102*INDEX(Config!$D$11:$D$20,MATCH(B102,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G102" s="24">
@@ -6570,7 +6570,7 @@
         <v>4</v>
       </c>
       <c r="F103" s="25">
-        <f>IF(OR(B103="",E103=""),"",E103*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B103,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B103="",E103=""),"",IFERROR(E103*INDEX(Config!$D$11:$D$20,MATCH(B103,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>280</v>
       </c>
       <c r="G103" s="24">
@@ -6610,7 +6610,7 @@
         <v>2.5</v>
       </c>
       <c r="F104" s="25">
-        <f>IF(OR(B104="",E104=""),"",E104*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B104,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B104="",E104=""),"",IFERROR(E104*INDEX(Config!$D$11:$D$20,MATCH(B104,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G104" s="24">
@@ -6650,7 +6650,7 @@
         <v>2.5</v>
       </c>
       <c r="F105" s="25">
-        <f>IF(OR(B105="",E105=""),"",E105*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B105,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B105="",E105=""),"",IFERROR(E105*INDEX(Config!$D$11:$D$20,MATCH(B105,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>128.571428571429</v>
       </c>
       <c r="G105" s="24">
@@ -6690,7 +6690,7 @@
         <v>1.5</v>
       </c>
       <c r="F106" s="25">
-        <f>IF(OR(B106="",E106=""),"",E106*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B106,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B106="",E106=""),"",IFERROR(E106*INDEX(Config!$D$11:$D$20,MATCH(B106,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G106" s="24">
@@ -6730,7 +6730,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="25">
-        <f>IF(OR(B107="",E107=""),"",E107*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B107,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B107="",E107=""),"",IFERROR(E107*INDEX(Config!$D$11:$D$20,MATCH(B107,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>257.142857142857</v>
       </c>
       <c r="G107" s="24">
@@ -6770,7 +6770,7 @@
         <v>6.5</v>
       </c>
       <c r="F108" s="25">
-        <f>IF(OR(B108="",E108=""),"",E108*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B108,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B108="",E108=""),"",IFERROR(E108*INDEX(Config!$D$11:$D$20,MATCH(B108,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>301.785714285714</v>
       </c>
       <c r="G108" s="24">
@@ -6810,7 +6810,7 @@
         <v>1.5</v>
       </c>
       <c r="F109" s="25">
-        <f>IF(OR(B109="",E109=""),"",E109*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B109,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B109="",E109=""),"",IFERROR(E109*INDEX(Config!$D$11:$D$20,MATCH(B109,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G109" s="24">
@@ -6850,7 +6850,7 @@
         <v>4</v>
       </c>
       <c r="F110" s="25">
-        <f>IF(OR(B110="",E110=""),"",E110*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B110,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B110="",E110=""),"",IFERROR(E110*INDEX(Config!$D$11:$D$20,MATCH(B110,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G110" s="24">
@@ -6890,7 +6890,7 @@
         <v>2.5</v>
       </c>
       <c r="F111" s="25">
-        <f>IF(OR(B111="",E111=""),"",E111*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B111,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B111="",E111=""),"",IFERROR(E111*INDEX(Config!$D$11:$D$20,MATCH(B111,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G111" s="24">
@@ -6930,7 +6930,7 @@
         <v>4.5</v>
       </c>
       <c r="F112" s="25">
-        <f>IF(OR(B112="",E112=""),"",E112*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B112,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B112="",E112=""),"",IFERROR(E112*INDEX(Config!$D$11:$D$20,MATCH(B112,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>315</v>
       </c>
       <c r="G112" s="24">
@@ -6970,7 +6970,7 @@
         <v>3.5</v>
       </c>
       <c r="F113" s="25">
-        <f>IF(OR(B113="",E113=""),"",E113*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B113,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B113="",E113=""),"",IFERROR(E113*INDEX(Config!$D$11:$D$20,MATCH(B113,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G113" s="24">
@@ -7010,7 +7010,7 @@
         <v>1.5</v>
       </c>
       <c r="F114" s="25">
-        <f>IF(OR(B114="",E114=""),"",E114*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B114,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B114="",E114=""),"",IFERROR(E114*INDEX(Config!$D$11:$D$20,MATCH(B114,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G114" s="24">
@@ -7050,7 +7050,7 @@
         <v>1.5</v>
       </c>
       <c r="F115" s="25">
-        <f>IF(OR(B115="",E115=""),"",E115*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B115,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B115="",E115=""),"",IFERROR(E115*INDEX(Config!$D$11:$D$20,MATCH(B115,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G115" s="24">
@@ -7090,7 +7090,7 @@
         <v>6.5</v>
       </c>
       <c r="F116" s="25">
-        <f>IF(OR(B116="",E116=""),"",E116*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B116,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B116="",E116=""),"",IFERROR(E116*INDEX(Config!$D$11:$D$20,MATCH(B116,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>334.285714285714</v>
       </c>
       <c r="G116" s="24">
@@ -7130,7 +7130,7 @@
         <v>7.5</v>
       </c>
       <c r="F117" s="25">
-        <f>IF(OR(B117="",E117=""),"",E117*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B117,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B117="",E117=""),"",IFERROR(E117*INDEX(Config!$D$11:$D$20,MATCH(B117,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>348.214285714286</v>
       </c>
       <c r="G117" s="24">
@@ -7170,7 +7170,7 @@
         <v>1.5</v>
       </c>
       <c r="F118" s="25">
-        <f>IF(OR(B118="",E118=""),"",E118*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B118,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B118="",E118=""),"",IFERROR(E118*INDEX(Config!$D$11:$D$20,MATCH(B118,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G118" s="24">
@@ -7210,7 +7210,7 @@
         <v>4</v>
       </c>
       <c r="F119" s="25">
-        <f>IF(OR(B119="",E119=""),"",E119*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B119,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B119="",E119=""),"",IFERROR(E119*INDEX(Config!$D$11:$D$20,MATCH(B119,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G119" s="24">
@@ -7250,7 +7250,7 @@
         <v>3</v>
       </c>
       <c r="F120" s="25">
-        <f>IF(OR(B120="",E120=""),"",E120*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B120,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B120="",E120=""),"",IFERROR(E120*INDEX(Config!$D$11:$D$20,MATCH(B120,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G120" s="24">
@@ -7290,7 +7290,7 @@
         <v>4</v>
       </c>
       <c r="F121" s="25">
-        <f>IF(OR(B121="",E121=""),"",E121*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B121,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B121="",E121=""),"",IFERROR(E121*INDEX(Config!$D$11:$D$20,MATCH(B121,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>280</v>
       </c>
       <c r="G121" s="24">
@@ -7330,7 +7330,7 @@
         <v>2.5</v>
       </c>
       <c r="F122" s="25">
-        <f>IF(OR(B122="",E122=""),"",E122*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B122,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B122="",E122=""),"",IFERROR(E122*INDEX(Config!$D$11:$D$20,MATCH(B122,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G122" s="24">
@@ -7370,7 +7370,7 @@
         <v>2</v>
       </c>
       <c r="F123" s="25">
-        <f>IF(OR(B123="",E123=""),"",E123*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B123,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B123="",E123=""),"",IFERROR(E123*INDEX(Config!$D$11:$D$20,MATCH(B123,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G123" s="24">
@@ -7410,7 +7410,7 @@
         <v>1.5</v>
       </c>
       <c r="F124" s="25">
-        <f>IF(OR(B124="",E124=""),"",E124*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B124,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B124="",E124=""),"",IFERROR(E124*INDEX(Config!$D$11:$D$20,MATCH(B124,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G124" s="24">
@@ -7450,7 +7450,7 @@
         <v>5</v>
       </c>
       <c r="F125" s="25">
-        <f>IF(OR(B125="",E125=""),"",E125*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B125,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B125="",E125=""),"",IFERROR(E125*INDEX(Config!$D$11:$D$20,MATCH(B125,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>257.142857142857</v>
       </c>
       <c r="G125" s="24">
@@ -7490,7 +7490,7 @@
         <v>9</v>
       </c>
       <c r="F126" s="25">
-        <f>IF(OR(B126="",E126=""),"",E126*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B126,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B126="",E126=""),"",IFERROR(E126*INDEX(Config!$D$11:$D$20,MATCH(B126,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>417.857142857143</v>
       </c>
       <c r="G126" s="24">
@@ -7530,7 +7530,7 @@
         <v>1.5</v>
       </c>
       <c r="F127" s="25">
-        <f>IF(OR(B127="",E127=""),"",E127*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B127,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B127="",E127=""),"",IFERROR(E127*INDEX(Config!$D$11:$D$20,MATCH(B127,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G127" s="24">
@@ -7570,7 +7570,7 @@
         <v>3.5</v>
       </c>
       <c r="F128" s="25">
-        <f>IF(OR(B128="",E128=""),"",E128*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B128,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B128="",E128=""),"",IFERROR(E128*INDEX(Config!$D$11:$D$20,MATCH(B128,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G128" s="24">
@@ -7610,7 +7610,7 @@
         <v>4</v>
       </c>
       <c r="F129" s="25">
-        <f>IF(OR(B129="",E129=""),"",E129*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B129,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B129="",E129=""),"",IFERROR(E129*INDEX(Config!$D$11:$D$20,MATCH(B129,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G129" s="24">
@@ -7650,7 +7650,7 @@
         <v>6.5</v>
       </c>
       <c r="F130" s="25">
-        <f>IF(OR(B130="",E130=""),"",E130*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B130,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B130="",E130=""),"",IFERROR(E130*INDEX(Config!$D$11:$D$20,MATCH(B130,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>455</v>
       </c>
       <c r="G130" s="24">
@@ -7690,7 +7690,7 @@
         <v>3.5</v>
       </c>
       <c r="F131" s="25">
-        <f>IF(OR(B131="",E131=""),"",E131*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B131,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B131="",E131=""),"",IFERROR(E131*INDEX(Config!$D$11:$D$20,MATCH(B131,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G131" s="24">
@@ -7730,7 +7730,7 @@
         <v>2</v>
       </c>
       <c r="F132" s="25">
-        <f>IF(OR(B132="",E132=""),"",E132*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B132,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B132="",E132=""),"",IFERROR(E132*INDEX(Config!$D$11:$D$20,MATCH(B132,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G132" s="24">
@@ -7770,7 +7770,7 @@
         <v>1.5</v>
       </c>
       <c r="F133" s="25">
-        <f>IF(OR(B133="",E133=""),"",E133*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B133,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B133="",E133=""),"",IFERROR(E133*INDEX(Config!$D$11:$D$20,MATCH(B133,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G133" s="24">
@@ -7810,7 +7810,7 @@
         <v>5.5</v>
       </c>
       <c r="F134" s="25">
-        <f>IF(OR(B134="",E134=""),"",E134*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B134,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B134="",E134=""),"",IFERROR(E134*INDEX(Config!$D$11:$D$20,MATCH(B134,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>282.857142857143</v>
       </c>
       <c r="G134" s="24">
@@ -7850,7 +7850,7 @@
         <v>5</v>
       </c>
       <c r="F135" s="25">
-        <f>IF(OR(B135="",E135=""),"",E135*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B135,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B135="",E135=""),"",IFERROR(E135*INDEX(Config!$D$11:$D$20,MATCH(B135,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>232.142857142857</v>
       </c>
       <c r="G135" s="24">
@@ -7890,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="F136" s="25">
-        <f>IF(OR(B136="",E136=""),"",E136*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B136,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B136="",E136=""),"",IFERROR(E136*INDEX(Config!$D$11:$D$20,MATCH(B136,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G136" s="24">
@@ -7930,7 +7930,7 @@
         <v>4.5</v>
       </c>
       <c r="F137" s="25">
-        <f>IF(OR(B137="",E137=""),"",E137*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B137,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B137="",E137=""),"",IFERROR(E137*INDEX(Config!$D$11:$D$20,MATCH(B137,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>217.5</v>
       </c>
       <c r="G137" s="24">
@@ -7970,7 +7970,7 @@
         <v>3.5</v>
       </c>
       <c r="F138" s="25">
-        <f>IF(OR(B138="",E138=""),"",E138*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B138,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B138="",E138=""),"",IFERROR(E138*INDEX(Config!$D$11:$D$20,MATCH(B138,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G138" s="24">
@@ -8010,7 +8010,7 @@
         <v>3.5</v>
       </c>
       <c r="F139" s="25">
-        <f>IF(OR(B139="",E139=""),"",E139*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B139,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B139="",E139=""),"",IFERROR(E139*INDEX(Config!$D$11:$D$20,MATCH(B139,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G139" s="24">
@@ -8050,7 +8050,7 @@
         <v>2</v>
       </c>
       <c r="F140" s="25">
-        <f>IF(OR(B140="",E140=""),"",E140*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B140,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B140="",E140=""),"",IFERROR(E140*INDEX(Config!$D$11:$D$20,MATCH(B140,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G140" s="24">
@@ -8090,7 +8090,7 @@
         <v>1.5</v>
       </c>
       <c r="F141" s="25">
-        <f>IF(OR(B141="",E141=""),"",E141*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B141,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B141="",E141=""),"",IFERROR(E141*INDEX(Config!$D$11:$D$20,MATCH(B141,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G141" s="24">
@@ -8130,7 +8130,7 @@
         <v>1</v>
       </c>
       <c r="F142" s="25">
-        <f>IF(OR(B142="",E142=""),"",E142*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B142,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B142="",E142=""),"",IFERROR(E142*INDEX(Config!$D$11:$D$20,MATCH(B142,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G142" s="24">
@@ -8170,7 +8170,7 @@
         <v>5</v>
       </c>
       <c r="F143" s="25">
-        <f>IF(OR(B143="",E143=""),"",E143*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B143,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B143="",E143=""),"",IFERROR(E143*INDEX(Config!$D$11:$D$20,MATCH(B143,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>257.142857142857</v>
       </c>
       <c r="G143" s="24">
@@ -8210,7 +8210,7 @@
         <v>6</v>
       </c>
       <c r="F144" s="25">
-        <f>IF(OR(B144="",E144=""),"",E144*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B144,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B144="",E144=""),"",IFERROR(E144*INDEX(Config!$D$11:$D$20,MATCH(B144,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>278.571428571429</v>
       </c>
       <c r="G144" s="24">
@@ -8250,7 +8250,7 @@
         <v>1</v>
       </c>
       <c r="F145" s="25">
-        <f>IF(OR(B145="",E145=""),"",E145*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B145,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B145="",E145=""),"",IFERROR(E145*INDEX(Config!$D$11:$D$20,MATCH(B145,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G145" s="24">
@@ -8290,7 +8290,7 @@
         <v>3.5</v>
       </c>
       <c r="F146" s="25">
-        <f>IF(OR(B146="",E146=""),"",E146*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B146,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B146="",E146=""),"",IFERROR(E146*INDEX(Config!$D$11:$D$20,MATCH(B146,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G146" s="24">
@@ -8330,7 +8330,7 @@
         <v>4.5</v>
       </c>
       <c r="F147" s="25">
-        <f>IF(OR(B147="",E147=""),"",E147*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B147,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B147="",E147=""),"",IFERROR(E147*INDEX(Config!$D$11:$D$20,MATCH(B147,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>217.5</v>
       </c>
       <c r="G147" s="24">
@@ -8370,7 +8370,7 @@
         <v>4.5</v>
       </c>
       <c r="F148" s="25">
-        <f>IF(OR(B148="",E148=""),"",E148*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B148,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B148="",E148=""),"",IFERROR(E148*INDEX(Config!$D$11:$D$20,MATCH(B148,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>315</v>
       </c>
       <c r="G148" s="24">
@@ -8410,7 +8410,7 @@
         <v>2</v>
       </c>
       <c r="F149" s="25">
-        <f>IF(OR(B149="",E149=""),"",E149*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B149,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B149="",E149=""),"",IFERROR(E149*INDEX(Config!$D$11:$D$20,MATCH(B149,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G149" s="24">
@@ -8450,7 +8450,7 @@
         <v>1.5</v>
       </c>
       <c r="F150" s="25">
-        <f>IF(OR(B150="",E150=""),"",E150*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B150,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B150="",E150=""),"",IFERROR(E150*INDEX(Config!$D$11:$D$20,MATCH(B150,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G150" s="24">
@@ -8490,7 +8490,7 @@
         <v>1</v>
       </c>
       <c r="F151" s="25">
-        <f>IF(OR(B151="",E151=""),"",E151*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B151,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B151="",E151=""),"",IFERROR(E151*INDEX(Config!$D$11:$D$20,MATCH(B151,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G151" s="24">
@@ -8530,7 +8530,7 @@
         <v>5</v>
       </c>
       <c r="F152" s="25">
-        <f>IF(OR(B152="",E152=""),"",E152*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B152,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B152="",E152=""),"",IFERROR(E152*INDEX(Config!$D$11:$D$20,MATCH(B152,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>257.142857142857</v>
       </c>
       <c r="G152" s="24">
@@ -8570,7 +8570,7 @@
         <v>6.5</v>
       </c>
       <c r="F153" s="25">
-        <f>IF(OR(B153="",E153=""),"",E153*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B153,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B153="",E153=""),"",IFERROR(E153*INDEX(Config!$D$11:$D$20,MATCH(B153,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>301.785714285714</v>
       </c>
       <c r="G153" s="24">
@@ -8610,7 +8610,7 @@
         <v>1</v>
       </c>
       <c r="F154" s="25">
-        <f>IF(OR(B154="",E154=""),"",E154*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B154,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B154="",E154=""),"",IFERROR(E154*INDEX(Config!$D$11:$D$20,MATCH(B154,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G154" s="24">
@@ -8650,7 +8650,7 @@
         <v>5</v>
       </c>
       <c r="F155" s="25">
-        <f>IF(OR(B155="",E155=""),"",E155*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B155,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B155="",E155=""),"",IFERROR(E155*INDEX(Config!$D$11:$D$20,MATCH(B155,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>241.666666666667</v>
       </c>
       <c r="G155" s="24">
@@ -8690,7 +8690,7 @@
         <v>3.5</v>
       </c>
       <c r="F156" s="25">
-        <f>IF(OR(B156="",E156=""),"",E156*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B156,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B156="",E156=""),"",IFERROR(E156*INDEX(Config!$D$11:$D$20,MATCH(B156,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G156" s="24">
@@ -8730,7 +8730,7 @@
         <v>7</v>
       </c>
       <c r="F157" s="25">
-        <f>IF(OR(B157="",E157=""),"",E157*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B157,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B157="",E157=""),"",IFERROR(E157*INDEX(Config!$D$11:$D$20,MATCH(B157,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>490</v>
       </c>
       <c r="G157" s="24">
@@ -8770,7 +8770,7 @@
         <v>2.5</v>
       </c>
       <c r="F158" s="25">
-        <f>IF(OR(B158="",E158=""),"",E158*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B158,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B158="",E158=""),"",IFERROR(E158*INDEX(Config!$D$11:$D$20,MATCH(B158,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G158" s="24">
@@ -8810,7 +8810,7 @@
         <v>2</v>
       </c>
       <c r="F159" s="25">
-        <f>IF(OR(B159="",E159=""),"",E159*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B159,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B159="",E159=""),"",IFERROR(E159*INDEX(Config!$D$11:$D$20,MATCH(B159,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G159" s="24">
@@ -8850,7 +8850,7 @@
         <v>1.5</v>
       </c>
       <c r="F160" s="25">
-        <f>IF(OR(B160="",E160=""),"",E160*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B160,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B160="",E160=""),"",IFERROR(E160*INDEX(Config!$D$11:$D$20,MATCH(B160,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G160" s="24">
@@ -8890,7 +8890,7 @@
         <v>5.5</v>
       </c>
       <c r="F161" s="25">
-        <f>IF(OR(B161="",E161=""),"",E161*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B161,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B161="",E161=""),"",IFERROR(E161*INDEX(Config!$D$11:$D$20,MATCH(B161,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>282.857142857143</v>
       </c>
       <c r="G161" s="24">
@@ -8930,7 +8930,7 @@
         <v>6.5</v>
       </c>
       <c r="F162" s="25">
-        <f>IF(OR(B162="",E162=""),"",E162*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B162,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B162="",E162=""),"",IFERROR(E162*INDEX(Config!$D$11:$D$20,MATCH(B162,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>301.785714285714</v>
       </c>
       <c r="G162" s="24">
@@ -8970,7 +8970,7 @@
         <v>1.5</v>
       </c>
       <c r="F163" s="25">
-        <f>IF(OR(B163="",E163=""),"",E163*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B163,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B163="",E163=""),"",IFERROR(E163*INDEX(Config!$D$11:$D$20,MATCH(B163,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G163" s="24">
@@ -9010,7 +9010,7 @@
         <v>3.5</v>
       </c>
       <c r="F164" s="25">
-        <f>IF(OR(B164="",E164=""),"",E164*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B164,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B164="",E164=""),"",IFERROR(E164*INDEX(Config!$D$11:$D$20,MATCH(B164,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G164" s="24">
@@ -9050,7 +9050,7 @@
         <v>3.5</v>
       </c>
       <c r="F165" s="25">
-        <f>IF(OR(B165="",E165=""),"",E165*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B165,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B165="",E165=""),"",IFERROR(E165*INDEX(Config!$D$11:$D$20,MATCH(B165,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G165" s="24">
@@ -9090,7 +9090,7 @@
         <v>7</v>
       </c>
       <c r="F166" s="25">
-        <f>IF(OR(B166="",E166=""),"",E166*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B166,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B166="",E166=""),"",IFERROR(E166*INDEX(Config!$D$11:$D$20,MATCH(B166,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>490</v>
       </c>
       <c r="G166" s="24">
@@ -9130,7 +9130,7 @@
         <v>3</v>
       </c>
       <c r="F167" s="25">
-        <f>IF(OR(B167="",E167=""),"",E167*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B167,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B167="",E167=""),"",IFERROR(E167*INDEX(Config!$D$11:$D$20,MATCH(B167,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G167" s="24">
@@ -9170,7 +9170,7 @@
         <v>2</v>
       </c>
       <c r="F168" s="25">
-        <f>IF(OR(B168="",E168=""),"",E168*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B168,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B168="",E168=""),"",IFERROR(E168*INDEX(Config!$D$11:$D$20,MATCH(B168,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G168" s="24">
@@ -9210,7 +9210,7 @@
         <v>1</v>
       </c>
       <c r="F169" s="25">
-        <f>IF(OR(B169="",E169=""),"",E169*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B169,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B169="",E169=""),"",IFERROR(E169*INDEX(Config!$D$11:$D$20,MATCH(B169,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G169" s="24">
@@ -9250,7 +9250,7 @@
         <v>5</v>
       </c>
       <c r="F170" s="25">
-        <f>IF(OR(B170="",E170=""),"",E170*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B170,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B170="",E170=""),"",IFERROR(E170*INDEX(Config!$D$11:$D$20,MATCH(B170,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>257.142857142857</v>
       </c>
       <c r="G170" s="24">
@@ -9290,7 +9290,7 @@
         <v>6.5</v>
       </c>
       <c r="F171" s="25">
-        <f>IF(OR(B171="",E171=""),"",E171*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B171,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B171="",E171=""),"",IFERROR(E171*INDEX(Config!$D$11:$D$20,MATCH(B171,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>301.785714285714</v>
       </c>
       <c r="G171" s="24">
@@ -9330,7 +9330,7 @@
         <v>1</v>
       </c>
       <c r="F172" s="25">
-        <f>IF(OR(B172="",E172=""),"",E172*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B172,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B172="",E172=""),"",IFERROR(E172*INDEX(Config!$D$11:$D$20,MATCH(B172,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G172" s="24">
@@ -9370,7 +9370,7 @@
         <v>5</v>
       </c>
       <c r="F173" s="25">
-        <f>IF(OR(B173="",E173=""),"",E173*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B173,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B173="",E173=""),"",IFERROR(E173*INDEX(Config!$D$11:$D$20,MATCH(B173,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>241.666666666667</v>
       </c>
       <c r="G173" s="24">
@@ -9410,7 +9410,7 @@
         <v>3.5</v>
       </c>
       <c r="F174" s="25">
-        <f>IF(OR(B174="",E174=""),"",E174*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B174,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B174="",E174=""),"",IFERROR(E174*INDEX(Config!$D$11:$D$20,MATCH(B174,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G174" s="24">
@@ -9450,7 +9450,7 @@
         <v>3</v>
       </c>
       <c r="F175" s="25">
-        <f>IF(OR(B175="",E175=""),"",E175*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B175,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B175="",E175=""),"",IFERROR(E175*INDEX(Config!$D$11:$D$20,MATCH(B175,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G175" s="24">
@@ -9490,7 +9490,7 @@
         <v>2.5</v>
       </c>
       <c r="F176" s="25">
-        <f>IF(OR(B176="",E176=""),"",E176*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B176,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B176="",E176=""),"",IFERROR(E176*INDEX(Config!$D$11:$D$20,MATCH(B176,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G176" s="24">
@@ -9530,7 +9530,7 @@
         <v>1.5</v>
       </c>
       <c r="F177" s="25">
-        <f>IF(OR(B177="",E177=""),"",E177*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B177,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B177="",E177=""),"",IFERROR(E177*INDEX(Config!$D$11:$D$20,MATCH(B177,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G177" s="24">
@@ -9570,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="F178" s="25">
-        <f>IF(OR(B178="",E178=""),"",E178*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B178,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B178="",E178=""),"",IFERROR(E178*INDEX(Config!$D$11:$D$20,MATCH(B178,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G178" s="24">
@@ -9610,7 +9610,7 @@
         <v>5.5</v>
       </c>
       <c r="F179" s="25">
-        <f>IF(OR(B179="",E179=""),"",E179*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B179,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B179="",E179=""),"",IFERROR(E179*INDEX(Config!$D$11:$D$20,MATCH(B179,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>282.857142857143</v>
       </c>
       <c r="G179" s="24">
@@ -9650,7 +9650,7 @@
         <v>6</v>
       </c>
       <c r="F180" s="25">
-        <f>IF(OR(B180="",E180=""),"",E180*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B180,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B180="",E180=""),"",IFERROR(E180*INDEX(Config!$D$11:$D$20,MATCH(B180,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>278.571428571429</v>
       </c>
       <c r="G180" s="24">
@@ -9690,7 +9690,7 @@
         <v>1</v>
       </c>
       <c r="F181" s="25">
-        <f>IF(OR(B181="",E181=""),"",E181*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B181,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B181="",E181=""),"",IFERROR(E181*INDEX(Config!$D$11:$D$20,MATCH(B181,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G181" s="24">
@@ -9730,7 +9730,7 @@
         <v>3</v>
       </c>
       <c r="F182" s="25">
-        <f>IF(OR(B182="",E182=""),"",E182*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B182,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B182="",E182=""),"",IFERROR(E182*INDEX(Config!$D$11:$D$20,MATCH(B182,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G182" s="24">
@@ -9770,7 +9770,7 @@
         <v>2.5</v>
       </c>
       <c r="F183" s="25">
-        <f>IF(OR(B183="",E183=""),"",E183*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B183,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B183="",E183=""),"",IFERROR(E183*INDEX(Config!$D$11:$D$20,MATCH(B183,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G183" s="24">
@@ -9810,7 +9810,7 @@
         <v>3</v>
       </c>
       <c r="F184" s="25">
-        <f>IF(OR(B184="",E184=""),"",E184*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B184,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B184="",E184=""),"",IFERROR(E184*INDEX(Config!$D$11:$D$20,MATCH(B184,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G184" s="24">
@@ -9850,7 +9850,7 @@
         <v>2.5</v>
       </c>
       <c r="F185" s="25">
-        <f>IF(OR(B185="",E185=""),"",E185*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B185,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B185="",E185=""),"",IFERROR(E185*INDEX(Config!$D$11:$D$20,MATCH(B185,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G185" s="24">
@@ -9890,7 +9890,7 @@
         <v>1.5</v>
       </c>
       <c r="F186" s="25">
-        <f>IF(OR(B186="",E186=""),"",E186*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B186,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B186="",E186=""),"",IFERROR(E186*INDEX(Config!$D$11:$D$20,MATCH(B186,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G186" s="24">
@@ -9930,7 +9930,7 @@
         <v>1</v>
       </c>
       <c r="F187" s="25">
-        <f>IF(OR(B187="",E187=""),"",E187*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B187,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B187="",E187=""),"",IFERROR(E187*INDEX(Config!$D$11:$D$20,MATCH(B187,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G187" s="24">
@@ -9970,7 +9970,7 @@
         <v>3.5</v>
       </c>
       <c r="F188" s="25">
-        <f>IF(OR(B188="",E188=""),"",E188*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B188,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B188="",E188=""),"",IFERROR(E188*INDEX(Config!$D$11:$D$20,MATCH(B188,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>180</v>
       </c>
       <c r="G188" s="24">
@@ -10010,7 +10010,7 @@
         <v>6</v>
       </c>
       <c r="F189" s="25">
-        <f>IF(OR(B189="",E189=""),"",E189*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B189,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B189="",E189=""),"",IFERROR(E189*INDEX(Config!$D$11:$D$20,MATCH(B189,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>278.571428571429</v>
       </c>
       <c r="G189" s="24">
@@ -10050,7 +10050,7 @@
         <v>1</v>
       </c>
       <c r="F190" s="25">
-        <f>IF(OR(B190="",E190=""),"",E190*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B190,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B190="",E190=""),"",IFERROR(E190*INDEX(Config!$D$11:$D$20,MATCH(B190,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G190" s="24">
@@ -10090,7 +10090,7 @@
         <v>5.5</v>
       </c>
       <c r="F191" s="25">
-        <f>IF(OR(B191="",E191=""),"",E191*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B191,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B191="",E191=""),"",IFERROR(E191*INDEX(Config!$D$11:$D$20,MATCH(B191,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>265.833333333333</v>
       </c>
       <c r="G191" s="24">
@@ -10130,7 +10130,7 @@
         <v>3.5</v>
       </c>
       <c r="F192" s="25">
-        <f>IF(OR(B192="",E192=""),"",E192*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B192,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B192="",E192=""),"",IFERROR(E192*INDEX(Config!$D$11:$D$20,MATCH(B192,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G192" s="24">
@@ -10170,7 +10170,7 @@
         <v>5.5</v>
       </c>
       <c r="F193" s="25">
-        <f>IF(OR(B193="",E193=""),"",E193*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B193,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B193="",E193=""),"",IFERROR(E193*INDEX(Config!$D$11:$D$20,MATCH(B193,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>385</v>
       </c>
       <c r="G193" s="24">
@@ -10210,7 +10210,7 @@
         <v>3.5</v>
       </c>
       <c r="F194" s="25">
-        <f>IF(OR(B194="",E194=""),"",E194*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B194,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B194="",E194=""),"",IFERROR(E194*INDEX(Config!$D$11:$D$20,MATCH(B194,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G194" s="24">
@@ -10250,7 +10250,7 @@
         <v>2</v>
       </c>
       <c r="F195" s="25">
-        <f>IF(OR(B195="",E195=""),"",E195*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B195,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B195="",E195=""),"",IFERROR(E195*INDEX(Config!$D$11:$D$20,MATCH(B195,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G195" s="24">
@@ -10290,7 +10290,7 @@
         <v>1.5</v>
       </c>
       <c r="F196" s="25">
-        <f>IF(OR(B196="",E196=""),"",E196*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B196,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B196="",E196=""),"",IFERROR(E196*INDEX(Config!$D$11:$D$20,MATCH(B196,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G196" s="24">
@@ -10330,7 +10330,7 @@
         <v>6</v>
       </c>
       <c r="F197" s="25">
-        <f>IF(OR(B197="",E197=""),"",E197*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B197,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B197="",E197=""),"",IFERROR(E197*INDEX(Config!$D$11:$D$20,MATCH(B197,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>308.571428571429</v>
       </c>
       <c r="G197" s="24">
@@ -10370,7 +10370,7 @@
         <v>6.5</v>
       </c>
       <c r="F198" s="25">
-        <f>IF(OR(B198="",E198=""),"",E198*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B198,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B198="",E198=""),"",IFERROR(E198*INDEX(Config!$D$11:$D$20,MATCH(B198,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>301.785714285714</v>
       </c>
       <c r="G198" s="24">
@@ -10410,7 +10410,7 @@
         <v>1</v>
       </c>
       <c r="F199" s="25">
-        <f>IF(OR(B199="",E199=""),"",E199*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B199,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B199="",E199=""),"",IFERROR(E199*INDEX(Config!$D$11:$D$20,MATCH(B199,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G199" s="24">
@@ -10450,7 +10450,7 @@
         <v>2.5</v>
       </c>
       <c r="F200" s="25">
-        <f>IF(OR(B200="",E200=""),"",E200*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B200,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B200="",E200=""),"",IFERROR(E200*INDEX(Config!$D$11:$D$20,MATCH(B200,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G200" s="24">
@@ -10490,7 +10490,7 @@
         <v>2</v>
       </c>
       <c r="F201" s="25">
-        <f>IF(OR(B201="",E201=""),"",E201*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B201,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B201="",E201=""),"",IFERROR(E201*INDEX(Config!$D$11:$D$20,MATCH(B201,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G201" s="24">
@@ -10530,7 +10530,7 @@
         <v>4</v>
       </c>
       <c r="F202" s="25">
-        <f>IF(OR(B202="",E202=""),"",E202*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B202,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B202="",E202=""),"",IFERROR(E202*INDEX(Config!$D$11:$D$20,MATCH(B202,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>280</v>
       </c>
       <c r="G202" s="24">
@@ -10570,7 +10570,7 @@
         <v>3</v>
       </c>
       <c r="F203" s="25">
-        <f>IF(OR(B203="",E203=""),"",E203*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B203,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B203="",E203=""),"",IFERROR(E203*INDEX(Config!$D$11:$D$20,MATCH(B203,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G203" s="24">
@@ -10610,7 +10610,7 @@
         <v>2</v>
       </c>
       <c r="F204" s="25">
-        <f>IF(OR(B204="",E204=""),"",E204*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B204,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B204="",E204=""),"",IFERROR(E204*INDEX(Config!$D$11:$D$20,MATCH(B204,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G204" s="24">
@@ -10650,7 +10650,7 @@
         <v>1</v>
       </c>
       <c r="F205" s="25">
-        <f>IF(OR(B205="",E205=""),"",E205*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B205,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B205="",E205=""),"",IFERROR(E205*INDEX(Config!$D$11:$D$20,MATCH(B205,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G205" s="24">
@@ -10690,7 +10690,7 @@
         <v>5.5</v>
       </c>
       <c r="F206" s="25">
-        <f>IF(OR(B206="",E206=""),"",E206*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B206,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B206="",E206=""),"",IFERROR(E206*INDEX(Config!$D$11:$D$20,MATCH(B206,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>282.857142857143</v>
       </c>
       <c r="G206" s="24">
@@ -10730,7 +10730,7 @@
         <v>4</v>
       </c>
       <c r="F207" s="25">
-        <f>IF(OR(B207="",E207=""),"",E207*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B207,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B207="",E207=""),"",IFERROR(E207*INDEX(Config!$D$11:$D$20,MATCH(B207,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>185.714285714286</v>
       </c>
       <c r="G207" s="24">
@@ -10770,7 +10770,7 @@
         <v>1</v>
       </c>
       <c r="F208" s="25">
-        <f>IF(OR(B208="",E208=""),"",E208*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B208,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B208="",E208=""),"",IFERROR(E208*INDEX(Config!$D$11:$D$20,MATCH(B208,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G208" s="24">
@@ -10810,7 +10810,7 @@
         <v>3.5</v>
       </c>
       <c r="F209" s="25">
-        <f>IF(OR(B209="",E209=""),"",E209*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B209,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B209="",E209=""),"",IFERROR(E209*INDEX(Config!$D$11:$D$20,MATCH(B209,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G209" s="24">
@@ -10850,7 +10850,7 @@
         <v>2.5</v>
       </c>
       <c r="F210" s="25">
-        <f>IF(OR(B210="",E210=""),"",E210*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B210,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B210="",E210=""),"",IFERROR(E210*INDEX(Config!$D$11:$D$20,MATCH(B210,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G210" s="24">
@@ -10890,7 +10890,7 @@
         <v>4.5</v>
       </c>
       <c r="F211" s="25">
-        <f>IF(OR(B211="",E211=""),"",E211*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B211,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B211="",E211=""),"",IFERROR(E211*INDEX(Config!$D$11:$D$20,MATCH(B211,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>315</v>
       </c>
       <c r="G211" s="24">
@@ -10930,7 +10930,7 @@
         <v>3.5</v>
       </c>
       <c r="F212" s="25">
-        <f>IF(OR(B212="",E212=""),"",E212*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B212,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B212="",E212=""),"",IFERROR(E212*INDEX(Config!$D$11:$D$20,MATCH(B212,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G212" s="24">
@@ -10970,7 +10970,7 @@
         <v>1.5</v>
       </c>
       <c r="F213" s="25">
-        <f>IF(OR(B213="",E213=""),"",E213*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B213,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B213="",E213=""),"",IFERROR(E213*INDEX(Config!$D$11:$D$20,MATCH(B213,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G213" s="24">
@@ -11010,7 +11010,7 @@
         <v>1</v>
       </c>
       <c r="F214" s="25">
-        <f>IF(OR(B214="",E214=""),"",E214*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B214,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B214="",E214=""),"",IFERROR(E214*INDEX(Config!$D$11:$D$20,MATCH(B214,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G214" s="24">
@@ -11050,7 +11050,7 @@
         <v>3.5</v>
       </c>
       <c r="F215" s="25">
-        <f>IF(OR(B215="",E215=""),"",E215*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B215,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B215="",E215=""),"",IFERROR(E215*INDEX(Config!$D$11:$D$20,MATCH(B215,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>180</v>
       </c>
       <c r="G215" s="24">
@@ -11090,7 +11090,7 @@
         <v>4.5</v>
       </c>
       <c r="F216" s="25">
-        <f>IF(OR(B216="",E216=""),"",E216*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B216,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B216="",E216=""),"",IFERROR(E216*INDEX(Config!$D$11:$D$20,MATCH(B216,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>208.928571428571</v>
       </c>
       <c r="G216" s="24">
@@ -11130,7 +11130,7 @@
         <v>1.5</v>
       </c>
       <c r="F217" s="25">
-        <f>IF(OR(B217="",E217=""),"",E217*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B217,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B217="",E217=""),"",IFERROR(E217*INDEX(Config!$D$11:$D$20,MATCH(B217,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G217" s="24">
@@ -11170,7 +11170,7 @@
         <v>3.5</v>
       </c>
       <c r="F218" s="25">
-        <f>IF(OR(B218="",E218=""),"",E218*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B218,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B218="",E218=""),"",IFERROR(E218*INDEX(Config!$D$11:$D$20,MATCH(B218,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G218" s="24">
@@ -11210,7 +11210,7 @@
         <v>3</v>
       </c>
       <c r="F219" s="25">
-        <f>IF(OR(B219="",E219=""),"",E219*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B219,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B219="",E219=""),"",IFERROR(E219*INDEX(Config!$D$11:$D$20,MATCH(B219,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G219" s="24">
@@ -11250,7 +11250,7 @@
         <v>3.5</v>
       </c>
       <c r="F220" s="25">
-        <f>IF(OR(B220="",E220=""),"",E220*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B220,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B220="",E220=""),"",IFERROR(E220*INDEX(Config!$D$11:$D$20,MATCH(B220,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G220" s="24">
@@ -11290,7 +11290,7 @@
         <v>2.5</v>
       </c>
       <c r="F221" s="25">
-        <f>IF(OR(B221="",E221=""),"",E221*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B221,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B221="",E221=""),"",IFERROR(E221*INDEX(Config!$D$11:$D$20,MATCH(B221,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G221" s="24">
@@ -11330,7 +11330,7 @@
         <v>2</v>
       </c>
       <c r="F222" s="25">
-        <f>IF(OR(B222="",E222=""),"",E222*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B222,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B222="",E222=""),"",IFERROR(E222*INDEX(Config!$D$11:$D$20,MATCH(B222,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G222" s="24">
@@ -11370,7 +11370,7 @@
         <v>1</v>
       </c>
       <c r="F223" s="25">
-        <f>IF(OR(B223="",E223=""),"",E223*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B223,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B223="",E223=""),"",IFERROR(E223*INDEX(Config!$D$11:$D$20,MATCH(B223,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G223" s="24">
@@ -11410,7 +11410,7 @@
         <v>3.5</v>
       </c>
       <c r="F224" s="25">
-        <f>IF(OR(B224="",E224=""),"",E224*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B224,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B224="",E224=""),"",IFERROR(E224*INDEX(Config!$D$11:$D$20,MATCH(B224,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>180</v>
       </c>
       <c r="G224" s="24">
@@ -11450,7 +11450,7 @@
         <v>6.5</v>
       </c>
       <c r="F225" s="25">
-        <f>IF(OR(B225="",E225=""),"",E225*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B225,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B225="",E225=""),"",IFERROR(E225*INDEX(Config!$D$11:$D$20,MATCH(B225,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>301.785714285714</v>
       </c>
       <c r="G225" s="24">
@@ -11490,7 +11490,7 @@
         <v>1.5</v>
       </c>
       <c r="F226" s="25">
-        <f>IF(OR(B226="",E226=""),"",E226*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B226,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B226="",E226=""),"",IFERROR(E226*INDEX(Config!$D$11:$D$20,MATCH(B226,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G226" s="24">
@@ -11530,7 +11530,7 @@
         <v>3.5</v>
       </c>
       <c r="F227" s="25">
-        <f>IF(OR(B227="",E227=""),"",E227*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B227,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B227="",E227=""),"",IFERROR(E227*INDEX(Config!$D$11:$D$20,MATCH(B227,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G227" s="24">
@@ -11570,7 +11570,7 @@
         <v>3.5</v>
       </c>
       <c r="F228" s="25">
-        <f>IF(OR(B228="",E228=""),"",E228*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B228,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B228="",E228=""),"",IFERROR(E228*INDEX(Config!$D$11:$D$20,MATCH(B228,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G228" s="24">
@@ -11610,7 +11610,7 @@
         <v>6</v>
       </c>
       <c r="F229" s="25">
-        <f>IF(OR(B229="",E229=""),"",E229*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B229,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B229="",E229=""),"",IFERROR(E229*INDEX(Config!$D$11:$D$20,MATCH(B229,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>420</v>
       </c>
       <c r="G229" s="24">
@@ -11650,7 +11650,7 @@
         <v>3.5</v>
       </c>
       <c r="F230" s="25">
-        <f>IF(OR(B230="",E230=""),"",E230*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B230,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B230="",E230=""),"",IFERROR(E230*INDEX(Config!$D$11:$D$20,MATCH(B230,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G230" s="24">
@@ -11690,7 +11690,7 @@
         <v>2.5</v>
       </c>
       <c r="F231" s="25">
-        <f>IF(OR(B231="",E231=""),"",E231*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B231,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B231="",E231=""),"",IFERROR(E231*INDEX(Config!$D$11:$D$20,MATCH(B231,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>128.571428571429</v>
       </c>
       <c r="G231" s="24">
@@ -11730,7 +11730,7 @@
         <v>1.5</v>
       </c>
       <c r="F232" s="25">
-        <f>IF(OR(B232="",E232=""),"",E232*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B232,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B232="",E232=""),"",IFERROR(E232*INDEX(Config!$D$11:$D$20,MATCH(B232,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G232" s="24">
@@ -11770,7 +11770,7 @@
         <v>5.5</v>
       </c>
       <c r="F233" s="25">
-        <f>IF(OR(B233="",E233=""),"",E233*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B233,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B233="",E233=""),"",IFERROR(E233*INDEX(Config!$D$11:$D$20,MATCH(B233,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>282.857142857143</v>
       </c>
       <c r="G233" s="24">
@@ -11810,7 +11810,7 @@
         <v>9</v>
       </c>
       <c r="F234" s="25">
-        <f>IF(OR(B234="",E234=""),"",E234*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B234,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B234="",E234=""),"",IFERROR(E234*INDEX(Config!$D$11:$D$20,MATCH(B234,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>417.857142857143</v>
       </c>
       <c r="G234" s="24">
@@ -11850,7 +11850,7 @@
         <v>1.5</v>
       </c>
       <c r="F235" s="25">
-        <f>IF(OR(B235="",E235=""),"",E235*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B235,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B235="",E235=""),"",IFERROR(E235*INDEX(Config!$D$11:$D$20,MATCH(B235,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G235" s="24">
@@ -11890,7 +11890,7 @@
         <v>5.5</v>
       </c>
       <c r="F236" s="25">
-        <f>IF(OR(B236="",E236=""),"",E236*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B236,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B236="",E236=""),"",IFERROR(E236*INDEX(Config!$D$11:$D$20,MATCH(B236,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>265.833333333333</v>
       </c>
       <c r="G236" s="24">
@@ -11930,7 +11930,7 @@
         <v>3</v>
       </c>
       <c r="F237" s="25">
-        <f>IF(OR(B237="",E237=""),"",E237*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B237,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B237="",E237=""),"",IFERROR(E237*INDEX(Config!$D$11:$D$20,MATCH(B237,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G237" s="24">
@@ -11970,7 +11970,7 @@
         <v>5.5</v>
       </c>
       <c r="F238" s="25">
-        <f>IF(OR(B238="",E238=""),"",E238*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B238,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B238="",E238=""),"",IFERROR(E238*INDEX(Config!$D$11:$D$20,MATCH(B238,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>385</v>
       </c>
       <c r="G238" s="24">
@@ -12010,7 +12010,7 @@
         <v>3.5</v>
       </c>
       <c r="F239" s="25">
-        <f>IF(OR(B239="",E239=""),"",E239*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B239,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B239="",E239=""),"",IFERROR(E239*INDEX(Config!$D$11:$D$20,MATCH(B239,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G239" s="24">
@@ -12050,7 +12050,7 @@
         <v>2</v>
       </c>
       <c r="F240" s="25">
-        <f>IF(OR(B240="",E240=""),"",E240*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B240,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B240="",E240=""),"",IFERROR(E240*INDEX(Config!$D$11:$D$20,MATCH(B240,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G240" s="24">
@@ -12090,7 +12090,7 @@
         <v>1</v>
       </c>
       <c r="F241" s="25">
-        <f>IF(OR(B241="",E241=""),"",E241*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B241,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B241="",E241=""),"",IFERROR(E241*INDEX(Config!$D$11:$D$20,MATCH(B241,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G241" s="24">
@@ -12130,7 +12130,7 @@
         <v>4.5</v>
       </c>
       <c r="F242" s="25">
-        <f>IF(OR(B242="",E242=""),"",E242*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B242,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B242="",E242=""),"",IFERROR(E242*INDEX(Config!$D$11:$D$20,MATCH(B242,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>231.428571428571</v>
       </c>
       <c r="G242" s="24">
@@ -12170,7 +12170,7 @@
         <v>7.5</v>
       </c>
       <c r="F243" s="25">
-        <f>IF(OR(B243="",E243=""),"",E243*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B243,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B243="",E243=""),"",IFERROR(E243*INDEX(Config!$D$11:$D$20,MATCH(B243,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>348.214285714286</v>
       </c>
       <c r="G243" s="24">
@@ -12210,7 +12210,7 @@
         <v>1</v>
       </c>
       <c r="F244" s="25">
-        <f>IF(OR(B244="",E244=""),"",E244*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B244,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B244="",E244=""),"",IFERROR(E244*INDEX(Config!$D$11:$D$20,MATCH(B244,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G244" s="24">
@@ -12250,7 +12250,7 @@
         <v>3.5</v>
       </c>
       <c r="F245" s="25">
-        <f>IF(OR(B245="",E245=""),"",E245*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B245,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B245="",E245=""),"",IFERROR(E245*INDEX(Config!$D$11:$D$20,MATCH(B245,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G245" s="24">
@@ -12290,7 +12290,7 @@
         <v>3.5</v>
       </c>
       <c r="F246" s="25">
-        <f>IF(OR(B246="",E246=""),"",E246*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B246,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B246="",E246=""),"",IFERROR(E246*INDEX(Config!$D$11:$D$20,MATCH(B246,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G246" s="24">
@@ -12330,7 +12330,7 @@
         <v>1.5</v>
       </c>
       <c r="F247" s="25">
-        <f>IF(OR(B247="",E247=""),"",E247*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B247,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B247="",E247=""),"",IFERROR(E247*INDEX(Config!$D$11:$D$20,MATCH(B247,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>105</v>
       </c>
       <c r="G247" s="24">
@@ -12370,7 +12370,7 @@
         <v>2.5</v>
       </c>
       <c r="F248" s="25">
-        <f>IF(OR(B248="",E248=""),"",E248*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B248,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B248="",E248=""),"",IFERROR(E248*INDEX(Config!$D$11:$D$20,MATCH(B248,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G248" s="24">
@@ -12410,7 +12410,7 @@
         <v>2.5</v>
       </c>
       <c r="F249" s="25">
-        <f>IF(OR(B249="",E249=""),"",E249*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B249,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B249="",E249=""),"",IFERROR(E249*INDEX(Config!$D$11:$D$20,MATCH(B249,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G249" s="24">
@@ -12450,7 +12450,7 @@
         <v>3</v>
       </c>
       <c r="F250" s="25">
-        <f>IF(OR(B250="",E250=""),"",E250*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B250,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B250="",E250=""),"",IFERROR(E250*INDEX(Config!$D$11:$D$20,MATCH(B250,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>154.285714285714</v>
       </c>
       <c r="G250" s="24">
@@ -12490,7 +12490,7 @@
         <v>1.5</v>
       </c>
       <c r="F251" s="25">
-        <f>IF(OR(B251="",E251=""),"",E251*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B251,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B251="",E251=""),"",IFERROR(E251*INDEX(Config!$D$11:$D$20,MATCH(B251,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G251" s="24">
@@ -12530,7 +12530,7 @@
         <v>1</v>
       </c>
       <c r="F252" s="25">
-        <f>IF(OR(B252="",E252=""),"",E252*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B252,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B252="",E252=""),"",IFERROR(E252*INDEX(Config!$D$11:$D$20,MATCH(B252,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G252" s="24">
@@ -12570,7 +12570,7 @@
         <v>2</v>
       </c>
       <c r="F253" s="25">
-        <f>IF(OR(B253="",E253=""),"",E253*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B253,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B253="",E253=""),"",IFERROR(E253*INDEX(Config!$D$11:$D$20,MATCH(B253,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G253" s="24">
@@ -12610,7 +12610,7 @@
         <v>2.5</v>
       </c>
       <c r="F254" s="25">
-        <f>IF(OR(B254="",E254=""),"",E254*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B254,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B254="",E254=""),"",IFERROR(E254*INDEX(Config!$D$11:$D$20,MATCH(B254,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G254" s="24">
@@ -12650,7 +12650,7 @@
         <v>1</v>
       </c>
       <c r="F255" s="25">
-        <f>IF(OR(B255="",E255=""),"",E255*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B255,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B255="",E255=""),"",IFERROR(E255*INDEX(Config!$D$11:$D$20,MATCH(B255,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G255" s="24">
@@ -12690,7 +12690,7 @@
         <v>5</v>
       </c>
       <c r="F256" s="25">
-        <f>IF(OR(B256="",E256=""),"",E256*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B256,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B256="",E256=""),"",IFERROR(E256*INDEX(Config!$D$11:$D$20,MATCH(B256,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>241.666666666667</v>
       </c>
       <c r="G256" s="24">
@@ -12730,7 +12730,7 @@
         <v>1</v>
       </c>
       <c r="F257" s="25">
-        <f>IF(OR(B257="",E257=""),"",E257*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B257,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B257="",E257=""),"",IFERROR(E257*INDEX(Config!$D$11:$D$20,MATCH(B257,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G257" s="24">
@@ -12770,7 +12770,7 @@
         <v>2.5</v>
       </c>
       <c r="F258" s="25">
-        <f>IF(OR(B258="",E258=""),"",E258*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B258,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B258="",E258=""),"",IFERROR(E258*INDEX(Config!$D$11:$D$20,MATCH(B258,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G258" s="24">
@@ -12810,7 +12810,7 @@
         <v>2</v>
       </c>
       <c r="F259" s="25">
-        <f>IF(OR(B259="",E259=""),"",E259*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B259,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B259="",E259=""),"",IFERROR(E259*INDEX(Config!$D$11:$D$20,MATCH(B259,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G259" s="24">
@@ -12850,7 +12850,7 @@
         <v>2</v>
       </c>
       <c r="F260" s="25">
-        <f>IF(OR(B260="",E260=""),"",E260*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B260,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B260="",E260=""),"",IFERROR(E260*INDEX(Config!$D$11:$D$20,MATCH(B260,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G260" s="24">
@@ -12890,7 +12890,7 @@
         <v>2</v>
       </c>
       <c r="F261" s="25">
-        <f>IF(OR(B261="",E261=""),"",E261*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B261,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B261="",E261=""),"",IFERROR(E261*INDEX(Config!$D$11:$D$20,MATCH(B261,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G261" s="24">
@@ -12930,7 +12930,7 @@
         <v>6</v>
       </c>
       <c r="F262" s="25">
-        <f>IF(OR(B262="",E262=""),"",E262*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B262,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B262="",E262=""),"",IFERROR(E262*INDEX(Config!$D$11:$D$20,MATCH(B262,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>308.571428571429</v>
       </c>
       <c r="G262" s="24">
@@ -12970,7 +12970,7 @@
         <v>2</v>
       </c>
       <c r="F263" s="25">
-        <f>IF(OR(B263="",E263=""),"",E263*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B263,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B263="",E263=""),"",IFERROR(E263*INDEX(Config!$D$11:$D$20,MATCH(B263,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G263" s="24">
@@ -13010,7 +13010,7 @@
         <v>1.5</v>
       </c>
       <c r="F264" s="25">
-        <f>IF(OR(B264="",E264=""),"",E264*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B264,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B264="",E264=""),"",IFERROR(E264*INDEX(Config!$D$11:$D$20,MATCH(B264,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G264" s="24">
@@ -13050,7 +13050,7 @@
         <v>2</v>
       </c>
       <c r="F265" s="25">
-        <f>IF(OR(B265="",E265=""),"",E265*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B265,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B265="",E265=""),"",IFERROR(E265*INDEX(Config!$D$11:$D$20,MATCH(B265,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G265" s="24">
@@ -13090,7 +13090,7 @@
         <v>3.5</v>
       </c>
       <c r="F266" s="25">
-        <f>IF(OR(B266="",E266=""),"",E266*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B266,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B266="",E266=""),"",IFERROR(E266*INDEX(Config!$D$11:$D$20,MATCH(B266,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>162.5</v>
       </c>
       <c r="G266" s="24">
@@ -13130,7 +13130,7 @@
         <v>1</v>
       </c>
       <c r="F267" s="25">
-        <f>IF(OR(B267="",E267=""),"",E267*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B267,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B267="",E267=""),"",IFERROR(E267*INDEX(Config!$D$11:$D$20,MATCH(B267,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G267" s="24">
@@ -13170,7 +13170,7 @@
         <v>6</v>
       </c>
       <c r="F268" s="25">
-        <f>IF(OR(B268="",E268=""),"",E268*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B268,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B268="",E268=""),"",IFERROR(E268*INDEX(Config!$D$11:$D$20,MATCH(B268,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>290</v>
       </c>
       <c r="G268" s="24">
@@ -13210,7 +13210,7 @@
         <v>0.5</v>
       </c>
       <c r="F269" s="25">
-        <f>IF(OR(B269="",E269=""),"",E269*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B269,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B269="",E269=""),"",IFERROR(E269*INDEX(Config!$D$11:$D$20,MATCH(B269,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G269" s="24">
@@ -13250,7 +13250,7 @@
         <v>2.5</v>
       </c>
       <c r="F270" s="25">
-        <f>IF(OR(B270="",E270=""),"",E270*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B270,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B270="",E270=""),"",IFERROR(E270*INDEX(Config!$D$11:$D$20,MATCH(B270,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G270" s="24">
@@ -13290,7 +13290,7 @@
         <v>2</v>
       </c>
       <c r="F271" s="25">
-        <f>IF(OR(B271="",E271=""),"",E271*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B271,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B271="",E271=""),"",IFERROR(E271*INDEX(Config!$D$11:$D$20,MATCH(B271,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G271" s="24">
@@ -13330,7 +13330,7 @@
         <v>2</v>
       </c>
       <c r="F272" s="25">
-        <f>IF(OR(B272="",E272=""),"",E272*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B272,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B272="",E272=""),"",IFERROR(E272*INDEX(Config!$D$11:$D$20,MATCH(B272,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G272" s="24">
@@ -13370,7 +13370,7 @@
         <v>3</v>
       </c>
       <c r="F273" s="25">
-        <f>IF(OR(B273="",E273=""),"",E273*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B273,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B273="",E273=""),"",IFERROR(E273*INDEX(Config!$D$11:$D$20,MATCH(B273,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G273" s="24">
@@ -13410,7 +13410,7 @@
         <v>6.5</v>
       </c>
       <c r="F274" s="25">
-        <f>IF(OR(B274="",E274=""),"",E274*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B274,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B274="",E274=""),"",IFERROR(E274*INDEX(Config!$D$11:$D$20,MATCH(B274,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>334.285714285714</v>
       </c>
       <c r="G274" s="24">
@@ -13450,7 +13450,7 @@
         <v>1.5</v>
       </c>
       <c r="F275" s="25">
-        <f>IF(OR(B275="",E275=""),"",E275*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B275,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B275="",E275=""),"",IFERROR(E275*INDEX(Config!$D$11:$D$20,MATCH(B275,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G275" s="24">
@@ -13490,7 +13490,7 @@
         <v>1</v>
       </c>
       <c r="F276" s="25">
-        <f>IF(OR(B276="",E276=""),"",E276*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B276,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B276="",E276=""),"",IFERROR(E276*INDEX(Config!$D$11:$D$20,MATCH(B276,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G276" s="24">
@@ -13530,7 +13530,7 @@
         <v>2.5</v>
       </c>
       <c r="F277" s="25">
-        <f>IF(OR(B277="",E277=""),"",E277*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B277,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B277="",E277=""),"",IFERROR(E277*INDEX(Config!$D$11:$D$20,MATCH(B277,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G277" s="24">
@@ -13570,7 +13570,7 @@
         <v>3</v>
       </c>
       <c r="F278" s="25">
-        <f>IF(OR(B278="",E278=""),"",E278*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B278,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B278="",E278=""),"",IFERROR(E278*INDEX(Config!$D$11:$D$20,MATCH(B278,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>139.285714285714</v>
       </c>
       <c r="G278" s="24">
@@ -13610,7 +13610,7 @@
         <v>1.5</v>
       </c>
       <c r="F279" s="25">
-        <f>IF(OR(B279="",E279=""),"",E279*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B279,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B279="",E279=""),"",IFERROR(E279*INDEX(Config!$D$11:$D$20,MATCH(B279,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G279" s="24">
@@ -13650,7 +13650,7 @@
         <v>4</v>
       </c>
       <c r="F280" s="25">
-        <f>IF(OR(B280="",E280=""),"",E280*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B280,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B280="",E280=""),"",IFERROR(E280*INDEX(Config!$D$11:$D$20,MATCH(B280,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G280" s="24">
@@ -13690,7 +13690,7 @@
         <v>1</v>
       </c>
       <c r="F281" s="25">
-        <f>IF(OR(B281="",E281=""),"",E281*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B281,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B281="",E281=""),"",IFERROR(E281*INDEX(Config!$D$11:$D$20,MATCH(B281,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G281" s="24">
@@ -13730,7 +13730,7 @@
         <v>2</v>
       </c>
       <c r="F282" s="25">
-        <f>IF(OR(B282="",E282=""),"",E282*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B282,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B282="",E282=""),"",IFERROR(E282*INDEX(Config!$D$11:$D$20,MATCH(B282,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G282" s="24">
@@ -13770,7 +13770,7 @@
         <v>2</v>
       </c>
       <c r="F283" s="25">
-        <f>IF(OR(B283="",E283=""),"",E283*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B283,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B283="",E283=""),"",IFERROR(E283*INDEX(Config!$D$11:$D$20,MATCH(B283,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G283" s="24">
@@ -13810,7 +13810,7 @@
         <v>2.5</v>
       </c>
       <c r="F284" s="25">
-        <f>IF(OR(B284="",E284=""),"",E284*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B284,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B284="",E284=""),"",IFERROR(E284*INDEX(Config!$D$11:$D$20,MATCH(B284,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G284" s="24">
@@ -13850,7 +13850,7 @@
         <v>2</v>
       </c>
       <c r="F285" s="25">
-        <f>IF(OR(B285="",E285=""),"",E285*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B285,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B285="",E285=""),"",IFERROR(E285*INDEX(Config!$D$11:$D$20,MATCH(B285,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G285" s="24">
@@ -13890,7 +13890,7 @@
         <v>5</v>
       </c>
       <c r="F286" s="25">
-        <f>IF(OR(B286="",E286=""),"",E286*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B286,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B286="",E286=""),"",IFERROR(E286*INDEX(Config!$D$11:$D$20,MATCH(B286,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>257.142857142857</v>
       </c>
       <c r="G286" s="24">
@@ -13930,7 +13930,7 @@
         <v>1.5</v>
       </c>
       <c r="F287" s="25">
-        <f>IF(OR(B287="",E287=""),"",E287*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B287,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B287="",E287=""),"",IFERROR(E287*INDEX(Config!$D$11:$D$20,MATCH(B287,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G287" s="24">
@@ -13970,7 +13970,7 @@
         <v>1</v>
       </c>
       <c r="F288" s="25">
-        <f>IF(OR(B288="",E288=""),"",E288*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B288,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B288="",E288=""),"",IFERROR(E288*INDEX(Config!$D$11:$D$20,MATCH(B288,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G288" s="24">
@@ -14010,7 +14010,7 @@
         <v>2.5</v>
       </c>
       <c r="F289" s="25">
-        <f>IF(OR(B289="",E289=""),"",E289*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B289,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B289="",E289=""),"",IFERROR(E289*INDEX(Config!$D$11:$D$20,MATCH(B289,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G289" s="24">
@@ -14050,7 +14050,7 @@
         <v>4.5</v>
       </c>
       <c r="F290" s="25">
-        <f>IF(OR(B290="",E290=""),"",E290*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B290,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B290="",E290=""),"",IFERROR(E290*INDEX(Config!$D$11:$D$20,MATCH(B290,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>208.928571428571</v>
       </c>
       <c r="G290" s="24">
@@ -14090,7 +14090,7 @@
         <v>1.5</v>
       </c>
       <c r="F291" s="25">
-        <f>IF(OR(B291="",E291=""),"",E291*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B291,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B291="",E291=""),"",IFERROR(E291*INDEX(Config!$D$11:$D$20,MATCH(B291,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G291" s="24">
@@ -14130,7 +14130,7 @@
         <v>3.5</v>
       </c>
       <c r="F292" s="25">
-        <f>IF(OR(B292="",E292=""),"",E292*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B292,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B292="",E292=""),"",IFERROR(E292*INDEX(Config!$D$11:$D$20,MATCH(B292,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G292" s="24">
@@ -14170,7 +14170,7 @@
         <v>0.5</v>
       </c>
       <c r="F293" s="25">
-        <f>IF(OR(B293="",E293=""),"",E293*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B293,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B293="",E293=""),"",IFERROR(E293*INDEX(Config!$D$11:$D$20,MATCH(B293,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G293" s="24">
@@ -14210,7 +14210,7 @@
         <v>2.5</v>
       </c>
       <c r="F294" s="25">
-        <f>IF(OR(B294="",E294=""),"",E294*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B294,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B294="",E294=""),"",IFERROR(E294*INDEX(Config!$D$11:$D$20,MATCH(B294,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G294" s="24">
@@ -14250,7 +14250,7 @@
         <v>2.5</v>
       </c>
       <c r="F295" s="25">
-        <f>IF(OR(B295="",E295=""),"",E295*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B295,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B295="",E295=""),"",IFERROR(E295*INDEX(Config!$D$11:$D$20,MATCH(B295,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G295" s="24">
@@ -14290,7 +14290,7 @@
         <v>3.5</v>
       </c>
       <c r="F296" s="25">
-        <f>IF(OR(B296="",E296=""),"",E296*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B296,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B296="",E296=""),"",IFERROR(E296*INDEX(Config!$D$11:$D$20,MATCH(B296,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G296" s="24">
@@ -14330,7 +14330,7 @@
         <v>3.5</v>
       </c>
       <c r="F297" s="25">
-        <f>IF(OR(B297="",E297=""),"",E297*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B297,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B297="",E297=""),"",IFERROR(E297*INDEX(Config!$D$11:$D$20,MATCH(B297,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G297" s="24">
@@ -14370,7 +14370,7 @@
         <v>5.5</v>
       </c>
       <c r="F298" s="25">
-        <f>IF(OR(B298="",E298=""),"",E298*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B298,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B298="",E298=""),"",IFERROR(E298*INDEX(Config!$D$11:$D$20,MATCH(B298,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>282.857142857143</v>
       </c>
       <c r="G298" s="24">
@@ -14410,7 +14410,7 @@
         <v>2</v>
       </c>
       <c r="F299" s="25">
-        <f>IF(OR(B299="",E299=""),"",E299*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B299,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B299="",E299=""),"",IFERROR(E299*INDEX(Config!$D$11:$D$20,MATCH(B299,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G299" s="24">
@@ -14450,7 +14450,7 @@
         <v>1</v>
       </c>
       <c r="F300" s="25">
-        <f>IF(OR(B300="",E300=""),"",E300*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B300,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B300="",E300=""),"",IFERROR(E300*INDEX(Config!$D$11:$D$20,MATCH(B300,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G300" s="24">
@@ -14490,7 +14490,7 @@
         <v>2</v>
       </c>
       <c r="F301" s="25">
-        <f>IF(OR(B301="",E301=""),"",E301*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B301,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B301="",E301=""),"",IFERROR(E301*INDEX(Config!$D$11:$D$20,MATCH(B301,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G301" s="24">
@@ -14530,7 +14530,7 @@
         <v>4</v>
       </c>
       <c r="F302" s="25">
-        <f>IF(OR(B302="",E302=""),"",E302*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B302,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B302="",E302=""),"",IFERROR(E302*INDEX(Config!$D$11:$D$20,MATCH(B302,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>185.714285714286</v>
       </c>
       <c r="G302" s="24">
@@ -14570,7 +14570,7 @@
         <v>1.5</v>
       </c>
       <c r="F303" s="25">
-        <f>IF(OR(B303="",E303=""),"",E303*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B303,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B303="",E303=""),"",IFERROR(E303*INDEX(Config!$D$11:$D$20,MATCH(B303,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G303" s="24">
@@ -14610,7 +14610,7 @@
         <v>4.5</v>
       </c>
       <c r="F304" s="25">
-        <f>IF(OR(B304="",E304=""),"",E304*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B304,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B304="",E304=""),"",IFERROR(E304*INDEX(Config!$D$11:$D$20,MATCH(B304,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>217.5</v>
       </c>
       <c r="G304" s="24">
@@ -14650,7 +14650,7 @@
         <v>1</v>
       </c>
       <c r="F305" s="25">
-        <f>IF(OR(B305="",E305=""),"",E305*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B305,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B305="",E305=""),"",IFERROR(E305*INDEX(Config!$D$11:$D$20,MATCH(B305,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G305" s="24">
@@ -14690,7 +14690,7 @@
         <v>2</v>
       </c>
       <c r="F306" s="25">
-        <f>IF(OR(B306="",E306=""),"",E306*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B306,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B306="",E306=""),"",IFERROR(E306*INDEX(Config!$D$11:$D$20,MATCH(B306,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G306" s="24">
@@ -14730,7 +14730,7 @@
         <v>2</v>
       </c>
       <c r="F307" s="25">
-        <f>IF(OR(B307="",E307=""),"",E307*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B307,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B307="",E307=""),"",IFERROR(E307*INDEX(Config!$D$11:$D$20,MATCH(B307,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G307" s="24">
@@ -14770,7 +14770,7 @@
         <v>2</v>
       </c>
       <c r="F308" s="25">
-        <f>IF(OR(B308="",E308=""),"",E308*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B308,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B308="",E308=""),"",IFERROR(E308*INDEX(Config!$D$11:$D$20,MATCH(B308,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G308" s="24">
@@ -14810,7 +14810,7 @@
         <v>2.5</v>
       </c>
       <c r="F309" s="25">
-        <f>IF(OR(B309="",E309=""),"",E309*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B309,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B309="",E309=""),"",IFERROR(E309*INDEX(Config!$D$11:$D$20,MATCH(B309,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G309" s="24">
@@ -14850,7 +14850,7 @@
         <v>7</v>
       </c>
       <c r="F310" s="25">
-        <f>IF(OR(B310="",E310=""),"",E310*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B310,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B310="",E310=""),"",IFERROR(E310*INDEX(Config!$D$11:$D$20,MATCH(B310,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>360</v>
       </c>
       <c r="G310" s="24">
@@ -14890,7 +14890,7 @@
         <v>2</v>
       </c>
       <c r="F311" s="25">
-        <f>IF(OR(B311="",E311=""),"",E311*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B311,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B311="",E311=""),"",IFERROR(E311*INDEX(Config!$D$11:$D$20,MATCH(B311,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G311" s="24">
@@ -14930,7 +14930,7 @@
         <v>1.5</v>
       </c>
       <c r="F312" s="25">
-        <f>IF(OR(B312="",E312=""),"",E312*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B312,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B312="",E312=""),"",IFERROR(E312*INDEX(Config!$D$11:$D$20,MATCH(B312,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G312" s="24">
@@ -14970,7 +14970,7 @@
         <v>2.5</v>
       </c>
       <c r="F313" s="25">
-        <f>IF(OR(B313="",E313=""),"",E313*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B313,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B313="",E313=""),"",IFERROR(E313*INDEX(Config!$D$11:$D$20,MATCH(B313,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G313" s="24">
@@ -15010,7 +15010,7 @@
         <v>4</v>
       </c>
       <c r="F314" s="25">
-        <f>IF(OR(B314="",E314=""),"",E314*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B314,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B314="",E314=""),"",IFERROR(E314*INDEX(Config!$D$11:$D$20,MATCH(B314,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>185.714285714286</v>
       </c>
       <c r="G314" s="24">
@@ -15050,7 +15050,7 @@
         <v>1</v>
       </c>
       <c r="F315" s="25">
-        <f>IF(OR(B315="",E315=""),"",E315*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B315,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B315="",E315=""),"",IFERROR(E315*INDEX(Config!$D$11:$D$20,MATCH(B315,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G315" s="24">
@@ -15090,7 +15090,7 @@
         <v>7</v>
       </c>
       <c r="F316" s="25">
-        <f>IF(OR(B316="",E316=""),"",E316*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B316,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B316="",E316=""),"",IFERROR(E316*INDEX(Config!$D$11:$D$20,MATCH(B316,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>338.333333333333</v>
       </c>
       <c r="G316" s="24">
@@ -15130,7 +15130,7 @@
         <v>1</v>
       </c>
       <c r="F317" s="25">
-        <f>IF(OR(B317="",E317=""),"",E317*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B317,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B317="",E317=""),"",IFERROR(E317*INDEX(Config!$D$11:$D$20,MATCH(B317,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G317" s="24">
@@ -15170,7 +15170,7 @@
         <v>2.5</v>
       </c>
       <c r="F318" s="25">
-        <f>IF(OR(B318="",E318=""),"",E318*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B318,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B318="",E318=""),"",IFERROR(E318*INDEX(Config!$D$11:$D$20,MATCH(B318,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G318" s="24">
@@ -15210,7 +15210,7 @@
         <v>1.5</v>
       </c>
       <c r="F319" s="25">
-        <f>IF(OR(B319="",E319=""),"",E319*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B319,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B319="",E319=""),"",IFERROR(E319*INDEX(Config!$D$11:$D$20,MATCH(B319,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>105</v>
       </c>
       <c r="G319" s="24">
@@ -15250,7 +15250,7 @@
         <v>2</v>
       </c>
       <c r="F320" s="25">
-        <f>IF(OR(B320="",E320=""),"",E320*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B320,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B320="",E320=""),"",IFERROR(E320*INDEX(Config!$D$11:$D$20,MATCH(B320,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G320" s="24">
@@ -15290,7 +15290,7 @@
         <v>2.5</v>
       </c>
       <c r="F321" s="25">
-        <f>IF(OR(B321="",E321=""),"",E321*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B321,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B321="",E321=""),"",IFERROR(E321*INDEX(Config!$D$11:$D$20,MATCH(B321,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G321" s="24">
@@ -15330,7 +15330,7 @@
         <v>6</v>
       </c>
       <c r="F322" s="25">
-        <f>IF(OR(B322="",E322=""),"",E322*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B322,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B322="",E322=""),"",IFERROR(E322*INDEX(Config!$D$11:$D$20,MATCH(B322,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>308.571428571429</v>
       </c>
       <c r="G322" s="24">
@@ -15370,7 +15370,7 @@
         <v>1.5</v>
       </c>
       <c r="F323" s="25">
-        <f>IF(OR(B323="",E323=""),"",E323*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B323,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B323="",E323=""),"",IFERROR(E323*INDEX(Config!$D$11:$D$20,MATCH(B323,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G323" s="24">
@@ -15410,7 +15410,7 @@
         <v>1</v>
       </c>
       <c r="F324" s="25">
-        <f>IF(OR(B324="",E324=""),"",E324*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B324,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B324="",E324=""),"",IFERROR(E324*INDEX(Config!$D$11:$D$20,MATCH(B324,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G324" s="24">
@@ -15450,7 +15450,7 @@
         <v>2.5</v>
       </c>
       <c r="F325" s="25">
-        <f>IF(OR(B325="",E325=""),"",E325*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B325,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B325="",E325=""),"",IFERROR(E325*INDEX(Config!$D$11:$D$20,MATCH(B325,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G325" s="24">
@@ -15490,7 +15490,7 @@
         <v>4.5</v>
       </c>
       <c r="F326" s="25">
-        <f>IF(OR(B326="",E326=""),"",E326*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B326,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B326="",E326=""),"",IFERROR(E326*INDEX(Config!$D$11:$D$20,MATCH(B326,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>208.928571428571</v>
       </c>
       <c r="G326" s="24">
@@ -15530,7 +15530,7 @@
         <v>1</v>
       </c>
       <c r="F327" s="25">
-        <f>IF(OR(B327="",E327=""),"",E327*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B327,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B327="",E327=""),"",IFERROR(E327*INDEX(Config!$D$11:$D$20,MATCH(B327,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G327" s="24">
@@ -15570,7 +15570,7 @@
         <v>4</v>
       </c>
       <c r="F328" s="25">
-        <f>IF(OR(B328="",E328=""),"",E328*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B328,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B328="",E328=""),"",IFERROR(E328*INDEX(Config!$D$11:$D$20,MATCH(B328,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G328" s="24">
@@ -15610,7 +15610,7 @@
         <v>0.5</v>
       </c>
       <c r="F329" s="25">
-        <f>IF(OR(B329="",E329=""),"",E329*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B329,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B329="",E329=""),"",IFERROR(E329*INDEX(Config!$D$11:$D$20,MATCH(B329,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G329" s="24">
@@ -15650,7 +15650,7 @@
         <v>2</v>
       </c>
       <c r="F330" s="25">
-        <f>IF(OR(B330="",E330=""),"",E330*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B330,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B330="",E330=""),"",IFERROR(E330*INDEX(Config!$D$11:$D$20,MATCH(B330,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G330" s="24">
@@ -15690,7 +15690,7 @@
         <v>2.5</v>
       </c>
       <c r="F331" s="25">
-        <f>IF(OR(B331="",E331=""),"",E331*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B331,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B331="",E331=""),"",IFERROR(E331*INDEX(Config!$D$11:$D$20,MATCH(B331,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G331" s="24">
@@ -15730,7 +15730,7 @@
         <v>3</v>
       </c>
       <c r="F332" s="25">
-        <f>IF(OR(B332="",E332=""),"",E332*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B332,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B332="",E332=""),"",IFERROR(E332*INDEX(Config!$D$11:$D$20,MATCH(B332,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G332" s="24">
@@ -15770,7 +15770,7 @@
         <v>3</v>
       </c>
       <c r="F333" s="25">
-        <f>IF(OR(B333="",E333=""),"",E333*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B333,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B333="",E333=""),"",IFERROR(E333*INDEX(Config!$D$11:$D$20,MATCH(B333,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G333" s="24">
@@ -15810,7 +15810,7 @@
         <v>6.5</v>
       </c>
       <c r="F334" s="25">
-        <f>IF(OR(B334="",E334=""),"",E334*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B334,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B334="",E334=""),"",IFERROR(E334*INDEX(Config!$D$11:$D$20,MATCH(B334,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>334.285714285714</v>
       </c>
       <c r="G334" s="24">
@@ -15850,7 +15850,7 @@
         <v>1.5</v>
       </c>
       <c r="F335" s="25">
-        <f>IF(OR(B335="",E335=""),"",E335*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B335,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B335="",E335=""),"",IFERROR(E335*INDEX(Config!$D$11:$D$20,MATCH(B335,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G335" s="24">
@@ -15890,7 +15890,7 @@
         <v>1.5</v>
       </c>
       <c r="F336" s="25">
-        <f>IF(OR(B336="",E336=""),"",E336*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B336,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B336="",E336=""),"",IFERROR(E336*INDEX(Config!$D$11:$D$20,MATCH(B336,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G336" s="24">
@@ -15930,7 +15930,7 @@
         <v>2.5</v>
       </c>
       <c r="F337" s="25">
-        <f>IF(OR(B337="",E337=""),"",E337*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B337,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B337="",E337=""),"",IFERROR(E337*INDEX(Config!$D$11:$D$20,MATCH(B337,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G337" s="24">
@@ -15970,7 +15970,7 @@
         <v>3.5</v>
       </c>
       <c r="F338" s="25">
-        <f>IF(OR(B338="",E338=""),"",E338*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B338,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B338="",E338=""),"",IFERROR(E338*INDEX(Config!$D$11:$D$20,MATCH(B338,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>162.5</v>
       </c>
       <c r="G338" s="24">
@@ -16010,7 +16010,7 @@
         <v>1</v>
       </c>
       <c r="F339" s="25">
-        <f>IF(OR(B339="",E339=""),"",E339*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B339,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B339="",E339=""),"",IFERROR(E339*INDEX(Config!$D$11:$D$20,MATCH(B339,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G339" s="24">
@@ -16050,7 +16050,7 @@
         <v>5</v>
       </c>
       <c r="F340" s="25">
-        <f>IF(OR(B340="",E340=""),"",E340*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B340,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B340="",E340=""),"",IFERROR(E340*INDEX(Config!$D$11:$D$20,MATCH(B340,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>241.666666666667</v>
       </c>
       <c r="G340" s="24">
@@ -16090,7 +16090,7 @@
         <v>1</v>
       </c>
       <c r="F341" s="25">
-        <f>IF(OR(B341="",E341=""),"",E341*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B341,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B341="",E341=""),"",IFERROR(E341*INDEX(Config!$D$11:$D$20,MATCH(B341,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G341" s="24">
@@ -16130,7 +16130,7 @@
         <v>2</v>
       </c>
       <c r="F342" s="25">
-        <f>IF(OR(B342="",E342=""),"",E342*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B342,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B342="",E342=""),"",IFERROR(E342*INDEX(Config!$D$11:$D$20,MATCH(B342,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G342" s="24">
@@ -16170,7 +16170,7 @@
         <v>2</v>
       </c>
       <c r="F343" s="25">
-        <f>IF(OR(B343="",E343=""),"",E343*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B343,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B343="",E343=""),"",IFERROR(E343*INDEX(Config!$D$11:$D$20,MATCH(B343,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G343" s="24">
@@ -16210,7 +16210,7 @@
         <v>2.5</v>
       </c>
       <c r="F344" s="25">
-        <f>IF(OR(B344="",E344=""),"",E344*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B344,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B344="",E344=""),"",IFERROR(E344*INDEX(Config!$D$11:$D$20,MATCH(B344,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G344" s="24">
@@ -16250,7 +16250,7 @@
         <v>3.5</v>
       </c>
       <c r="F345" s="25">
-        <f>IF(OR(B345="",E345=""),"",E345*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B345,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B345="",E345=""),"",IFERROR(E345*INDEX(Config!$D$11:$D$20,MATCH(B345,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G345" s="24">
@@ -16290,7 +16290,7 @@
         <v>6</v>
       </c>
       <c r="F346" s="25">
-        <f>IF(OR(B346="",E346=""),"",E346*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B346,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B346="",E346=""),"",IFERROR(E346*INDEX(Config!$D$11:$D$20,MATCH(B346,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>308.571428571429</v>
       </c>
       <c r="G346" s="24">
@@ -16330,7 +16330,7 @@
         <v>1</v>
       </c>
       <c r="F347" s="25">
-        <f>IF(OR(B347="",E347=""),"",E347*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B347,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B347="",E347=""),"",IFERROR(E347*INDEX(Config!$D$11:$D$20,MATCH(B347,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G347" s="24">
@@ -16370,7 +16370,7 @@
         <v>1</v>
       </c>
       <c r="F348" s="25">
-        <f>IF(OR(B348="",E348=""),"",E348*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B348,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B348="",E348=""),"",IFERROR(E348*INDEX(Config!$D$11:$D$20,MATCH(B348,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G348" s="24">
@@ -16410,7 +16410,7 @@
         <v>1.5</v>
       </c>
       <c r="F349" s="25">
-        <f>IF(OR(B349="",E349=""),"",E349*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B349,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B349="",E349=""),"",IFERROR(E349*INDEX(Config!$D$11:$D$20,MATCH(B349,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G349" s="24">
@@ -16450,7 +16450,7 @@
         <v>4</v>
       </c>
       <c r="F350" s="25">
-        <f>IF(OR(B350="",E350=""),"",E350*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B350,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B350="",E350=""),"",IFERROR(E350*INDEX(Config!$D$11:$D$20,MATCH(B350,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>185.714285714286</v>
       </c>
       <c r="G350" s="24">
@@ -16490,7 +16490,7 @@
         <v>0.5</v>
       </c>
       <c r="F351" s="25">
-        <f>IF(OR(B351="",E351=""),"",E351*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B351,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B351="",E351=""),"",IFERROR(E351*INDEX(Config!$D$11:$D$20,MATCH(B351,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>23.2142857142857</v>
       </c>
       <c r="G351" s="24">
@@ -16530,7 +16530,7 @@
         <v>4</v>
       </c>
       <c r="F352" s="25">
-        <f>IF(OR(B352="",E352=""),"",E352*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B352,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B352="",E352=""),"",IFERROR(E352*INDEX(Config!$D$11:$D$20,MATCH(B352,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G352" s="24">
@@ -16570,7 +16570,7 @@
         <v>0.5</v>
       </c>
       <c r="F353" s="25">
-        <f>IF(OR(B353="",E353=""),"",E353*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B353,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B353="",E353=""),"",IFERROR(E353*INDEX(Config!$D$11:$D$20,MATCH(B353,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G353" s="24">
@@ -16610,7 +16610,7 @@
         <v>2.5</v>
       </c>
       <c r="F354" s="25">
-        <f>IF(OR(B354="",E354=""),"",E354*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B354,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B354="",E354=""),"",IFERROR(E354*INDEX(Config!$D$11:$D$20,MATCH(B354,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G354" s="24">
@@ -16650,7 +16650,7 @@
         <v>2.5</v>
       </c>
       <c r="F355" s="25">
-        <f>IF(OR(B355="",E355=""),"",E355*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B355,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B355="",E355=""),"",IFERROR(E355*INDEX(Config!$D$11:$D$20,MATCH(B355,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G355" s="24">
@@ -16690,7 +16690,7 @@
         <v>2.5</v>
       </c>
       <c r="F356" s="25">
-        <f>IF(OR(B356="",E356=""),"",E356*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B356,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B356="",E356=""),"",IFERROR(E356*INDEX(Config!$D$11:$D$20,MATCH(B356,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G356" s="24">
@@ -16730,7 +16730,7 @@
         <v>3</v>
       </c>
       <c r="F357" s="25">
-        <f>IF(OR(B357="",E357=""),"",E357*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B357,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B357="",E357=""),"",IFERROR(E357*INDEX(Config!$D$11:$D$20,MATCH(B357,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G357" s="24">
@@ -16770,7 +16770,7 @@
         <v>5.5</v>
       </c>
       <c r="F358" s="25">
-        <f>IF(OR(B358="",E358=""),"",E358*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B358,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B358="",E358=""),"",IFERROR(E358*INDEX(Config!$D$11:$D$20,MATCH(B358,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>282.857142857143</v>
       </c>
       <c r="G358" s="24">
@@ -16810,7 +16810,7 @@
         <v>2</v>
       </c>
       <c r="F359" s="25">
-        <f>IF(OR(B359="",E359=""),"",E359*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B359,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B359="",E359=""),"",IFERROR(E359*INDEX(Config!$D$11:$D$20,MATCH(B359,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G359" s="24">
@@ -16850,7 +16850,7 @@
         <v>1</v>
       </c>
       <c r="F360" s="25">
-        <f>IF(OR(B360="",E360=""),"",E360*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B360,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B360="",E360=""),"",IFERROR(E360*INDEX(Config!$D$11:$D$20,MATCH(B360,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G360" s="24">
@@ -16890,7 +16890,7 @@
         <v>2.5</v>
       </c>
       <c r="F361" s="25">
-        <f>IF(OR(B361="",E361=""),"",E361*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B361,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B361="",E361=""),"",IFERROR(E361*INDEX(Config!$D$11:$D$20,MATCH(B361,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G361" s="24">
@@ -16930,7 +16930,7 @@
         <v>4.5</v>
       </c>
       <c r="F362" s="25">
-        <f>IF(OR(B362="",E362=""),"",E362*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B362,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B362="",E362=""),"",IFERROR(E362*INDEX(Config!$D$11:$D$20,MATCH(B362,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>208.928571428571</v>
       </c>
       <c r="G362" s="24">
@@ -16970,7 +16970,7 @@
         <v>1.5</v>
       </c>
       <c r="F363" s="25">
-        <f>IF(OR(B363="",E363=""),"",E363*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B363,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B363="",E363=""),"",IFERROR(E363*INDEX(Config!$D$11:$D$20,MATCH(B363,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G363" s="24">
@@ -17010,7 +17010,7 @@
         <v>3.5</v>
       </c>
       <c r="F364" s="25">
-        <f>IF(OR(B364="",E364=""),"",E364*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B364,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B364="",E364=""),"",IFERROR(E364*INDEX(Config!$D$11:$D$20,MATCH(B364,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G364" s="24">
@@ -17050,7 +17050,7 @@
         <v>0.5</v>
       </c>
       <c r="F365" s="25">
-        <f>IF(OR(B365="",E365=""),"",E365*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B365,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B365="",E365=""),"",IFERROR(E365*INDEX(Config!$D$11:$D$20,MATCH(B365,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G365" s="24">
@@ -17090,7 +17090,7 @@
         <v>2.5</v>
       </c>
       <c r="F366" s="25">
-        <f>IF(OR(B366="",E366=""),"",E366*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B366,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B366="",E366=""),"",IFERROR(E366*INDEX(Config!$D$11:$D$20,MATCH(B366,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G366" s="24">
@@ -17130,7 +17130,7 @@
         <v>2.5</v>
       </c>
       <c r="F367" s="25">
-        <f>IF(OR(B367="",E367=""),"",E367*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B367,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B367="",E367=""),"",IFERROR(E367*INDEX(Config!$D$11:$D$20,MATCH(B367,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G367" s="24">
@@ -17170,7 +17170,7 @@
         <v>3</v>
       </c>
       <c r="F368" s="25">
-        <f>IF(OR(B368="",E368=""),"",E368*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B368,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B368="",E368=""),"",IFERROR(E368*INDEX(Config!$D$11:$D$20,MATCH(B368,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G368" s="24">
@@ -17210,7 +17210,7 @@
         <v>2</v>
       </c>
       <c r="F369" s="25">
-        <f>IF(OR(B369="",E369=""),"",E369*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B369,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B369="",E369=""),"",IFERROR(E369*INDEX(Config!$D$11:$D$20,MATCH(B369,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G369" s="24">
@@ -17250,7 +17250,7 @@
         <v>4.5</v>
       </c>
       <c r="F370" s="25">
-        <f>IF(OR(B370="",E370=""),"",E370*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B370,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B370="",E370=""),"",IFERROR(E370*INDEX(Config!$D$11:$D$20,MATCH(B370,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>231.428571428571</v>
       </c>
       <c r="G370" s="24">
@@ -17290,7 +17290,7 @@
         <v>1.5</v>
       </c>
       <c r="F371" s="25">
-        <f>IF(OR(B371="",E371=""),"",E371*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B371,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B371="",E371=""),"",IFERROR(E371*INDEX(Config!$D$11:$D$20,MATCH(B371,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G371" s="24">
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="F372" s="25">
-        <f>IF(OR(B372="",E372=""),"",E372*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B372,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B372="",E372=""),"",IFERROR(E372*INDEX(Config!$D$11:$D$20,MATCH(B372,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G372" s="24">
@@ -17370,7 +17370,7 @@
         <v>2.5</v>
       </c>
       <c r="F373" s="25">
-        <f>IF(OR(B373="",E373=""),"",E373*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B373,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B373="",E373=""),"",IFERROR(E373*INDEX(Config!$D$11:$D$20,MATCH(B373,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G373" s="24">
@@ -17410,7 +17410,7 @@
         <v>5</v>
       </c>
       <c r="F374" s="25">
-        <f>IF(OR(B374="",E374=""),"",E374*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B374,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B374="",E374=""),"",IFERROR(E374*INDEX(Config!$D$11:$D$20,MATCH(B374,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>232.142857142857</v>
       </c>
       <c r="G374" s="24">
@@ -17450,7 +17450,7 @@
         <v>0.5</v>
       </c>
       <c r="F375" s="25">
-        <f>IF(OR(B375="",E375=""),"",E375*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B375,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B375="",E375=""),"",IFERROR(E375*INDEX(Config!$D$11:$D$20,MATCH(B375,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>23.2142857142857</v>
       </c>
       <c r="G375" s="24">
@@ -17490,7 +17490,7 @@
         <v>4</v>
       </c>
       <c r="F376" s="25">
-        <f>IF(OR(B376="",E376=""),"",E376*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B376,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B376="",E376=""),"",IFERROR(E376*INDEX(Config!$D$11:$D$20,MATCH(B376,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G376" s="24">
@@ -17530,7 +17530,7 @@
         <v>0.5</v>
       </c>
       <c r="F377" s="25">
-        <f>IF(OR(B377="",E377=""),"",E377*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B377,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B377="",E377=""),"",IFERROR(E377*INDEX(Config!$D$11:$D$20,MATCH(B377,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G377" s="24">
@@ -17570,7 +17570,7 @@
         <v>2</v>
       </c>
       <c r="F378" s="25">
-        <f>IF(OR(B378="",E378=""),"",E378*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B378,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B378="",E378=""),"",IFERROR(E378*INDEX(Config!$D$11:$D$20,MATCH(B378,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G378" s="24">
@@ -17610,7 +17610,7 @@
         <v>2.5</v>
       </c>
       <c r="F379" s="25">
-        <f>IF(OR(B379="",E379=""),"",E379*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B379,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B379="",E379=""),"",IFERROR(E379*INDEX(Config!$D$11:$D$20,MATCH(B379,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G379" s="24">
@@ -17650,7 +17650,7 @@
         <v>3</v>
       </c>
       <c r="F380" s="25">
-        <f>IF(OR(B380="",E380=""),"",E380*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B380,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B380="",E380=""),"",IFERROR(E380*INDEX(Config!$D$11:$D$20,MATCH(B380,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G380" s="24">
@@ -17690,7 +17690,7 @@
         <v>2.5</v>
       </c>
       <c r="F381" s="25">
-        <f>IF(OR(B381="",E381=""),"",E381*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B381,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B381="",E381=""),"",IFERROR(E381*INDEX(Config!$D$11:$D$20,MATCH(B381,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G381" s="24">
@@ -17730,7 +17730,7 @@
         <v>4</v>
       </c>
       <c r="F382" s="25">
-        <f>IF(OR(B382="",E382=""),"",E382*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B382,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B382="",E382=""),"",IFERROR(E382*INDEX(Config!$D$11:$D$20,MATCH(B382,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>205.714285714286</v>
       </c>
       <c r="G382" s="24">
@@ -17770,7 +17770,7 @@
         <v>2</v>
       </c>
       <c r="F383" s="25">
-        <f>IF(OR(B383="",E383=""),"",E383*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B383,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B383="",E383=""),"",IFERROR(E383*INDEX(Config!$D$11:$D$20,MATCH(B383,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G383" s="24">
@@ -17810,7 +17810,7 @@
         <v>1</v>
       </c>
       <c r="F384" s="25">
-        <f>IF(OR(B384="",E384=""),"",E384*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B384,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B384="",E384=""),"",IFERROR(E384*INDEX(Config!$D$11:$D$20,MATCH(B384,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G384" s="24">
@@ -17850,7 +17850,7 @@
         <v>3</v>
       </c>
       <c r="F385" s="25">
-        <f>IF(OR(B385="",E385=""),"",E385*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B385,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B385="",E385=""),"",IFERROR(E385*INDEX(Config!$D$11:$D$20,MATCH(B385,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>139.285714285714</v>
       </c>
       <c r="G385" s="24">
@@ -17890,7 +17890,7 @@
         <v>5</v>
       </c>
       <c r="F386" s="25">
-        <f>IF(OR(B386="",E386=""),"",E386*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B386,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B386="",E386=""),"",IFERROR(E386*INDEX(Config!$D$11:$D$20,MATCH(B386,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>232.142857142857</v>
       </c>
       <c r="G386" s="24">
@@ -17930,7 +17930,7 @@
         <v>1</v>
       </c>
       <c r="F387" s="25">
-        <f>IF(OR(B387="",E387=""),"",E387*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B387,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B387="",E387=""),"",IFERROR(E387*INDEX(Config!$D$11:$D$20,MATCH(B387,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G387" s="24">
@@ -17970,7 +17970,7 @@
         <v>3.5</v>
       </c>
       <c r="F388" s="25">
-        <f>IF(OR(B388="",E388=""),"",E388*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B388,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B388="",E388=""),"",IFERROR(E388*INDEX(Config!$D$11:$D$20,MATCH(B388,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G388" s="24">
@@ -18010,7 +18010,7 @@
         <v>1</v>
       </c>
       <c r="F389" s="25">
-        <f>IF(OR(B389="",E389=""),"",E389*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B389,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B389="",E389=""),"",IFERROR(E389*INDEX(Config!$D$11:$D$20,MATCH(B389,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G389" s="24">
@@ -18050,7 +18050,7 @@
         <v>3</v>
       </c>
       <c r="F390" s="25">
-        <f>IF(OR(B390="",E390=""),"",E390*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B390,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B390="",E390=""),"",IFERROR(E390*INDEX(Config!$D$11:$D$20,MATCH(B390,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G390" s="24">
@@ -18090,7 +18090,7 @@
         <v>2</v>
       </c>
       <c r="F391" s="25">
-        <f>IF(OR(B391="",E391=""),"",E391*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B391,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B391="",E391=""),"",IFERROR(E391*INDEX(Config!$D$11:$D$20,MATCH(B391,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G391" s="24">
@@ -18130,7 +18130,7 @@
         <v>3.5</v>
       </c>
       <c r="F392" s="25">
-        <f>IF(OR(B392="",E392=""),"",E392*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B392,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B392="",E392=""),"",IFERROR(E392*INDEX(Config!$D$11:$D$20,MATCH(B392,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G392" s="24">
@@ -18170,7 +18170,7 @@
         <v>4</v>
       </c>
       <c r="F393" s="25">
-        <f>IF(OR(B393="",E393=""),"",E393*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B393,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B393="",E393=""),"",IFERROR(E393*INDEX(Config!$D$11:$D$20,MATCH(B393,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>280</v>
       </c>
       <c r="G393" s="24">
@@ -18210,7 +18210,7 @@
         <v>4.5</v>
       </c>
       <c r="F394" s="25">
-        <f>IF(OR(B394="",E394=""),"",E394*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B394,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B394="",E394=""),"",IFERROR(E394*INDEX(Config!$D$11:$D$20,MATCH(B394,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>231.428571428571</v>
       </c>
       <c r="G394" s="24">
@@ -18250,7 +18250,7 @@
         <v>1.5</v>
       </c>
       <c r="F395" s="25">
-        <f>IF(OR(B395="",E395=""),"",E395*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B395,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B395="",E395=""),"",IFERROR(E395*INDEX(Config!$D$11:$D$20,MATCH(B395,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G395" s="24">
@@ -18290,7 +18290,7 @@
         <v>1</v>
       </c>
       <c r="F396" s="25">
-        <f>IF(OR(B396="",E396=""),"",E396*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B396,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B396="",E396=""),"",IFERROR(E396*INDEX(Config!$D$11:$D$20,MATCH(B396,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G396" s="24">
@@ -18330,7 +18330,7 @@
         <v>2.5</v>
       </c>
       <c r="F397" s="25">
-        <f>IF(OR(B397="",E397=""),"",E397*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B397,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B397="",E397=""),"",IFERROR(E397*INDEX(Config!$D$11:$D$20,MATCH(B397,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G397" s="24">
@@ -18370,7 +18370,7 @@
         <v>3.5</v>
       </c>
       <c r="F398" s="25">
-        <f>IF(OR(B398="",E398=""),"",E398*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B398,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B398="",E398=""),"",IFERROR(E398*INDEX(Config!$D$11:$D$20,MATCH(B398,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>162.5</v>
       </c>
       <c r="G398" s="24">
@@ -18410,7 +18410,7 @@
         <v>1</v>
       </c>
       <c r="F399" s="25">
-        <f>IF(OR(B399="",E399=""),"",E399*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B399,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B399="",E399=""),"",IFERROR(E399*INDEX(Config!$D$11:$D$20,MATCH(B399,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G399" s="24">
@@ -18450,7 +18450,7 @@
         <v>4</v>
       </c>
       <c r="F400" s="25">
-        <f>IF(OR(B400="",E400=""),"",E400*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B400,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B400="",E400=""),"",IFERROR(E400*INDEX(Config!$D$11:$D$20,MATCH(B400,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G400" s="24">
@@ -18490,7 +18490,7 @@
         <v>0.5</v>
       </c>
       <c r="F401" s="25">
-        <f>IF(OR(B401="",E401=""),"",E401*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B401,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B401="",E401=""),"",IFERROR(E401*INDEX(Config!$D$11:$D$20,MATCH(B401,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G401" s="24">
@@ -18530,7 +18530,7 @@
         <v>1.5</v>
       </c>
       <c r="F402" s="25">
-        <f>IF(OR(B402="",E402=""),"",E402*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B402,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B402="",E402=""),"",IFERROR(E402*INDEX(Config!$D$11:$D$20,MATCH(B402,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>72.5</v>
       </c>
       <c r="G402" s="24">
@@ -18570,7 +18570,7 @@
         <v>2</v>
       </c>
       <c r="F403" s="25">
-        <f>IF(OR(B403="",E403=""),"",E403*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B403,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B403="",E403=""),"",IFERROR(E403*INDEX(Config!$D$11:$D$20,MATCH(B403,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G403" s="24">
@@ -18610,7 +18610,7 @@
         <v>3</v>
       </c>
       <c r="F404" s="25">
-        <f>IF(OR(B404="",E404=""),"",E404*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B404,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B404="",E404=""),"",IFERROR(E404*INDEX(Config!$D$11:$D$20,MATCH(B404,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G404" s="24">
@@ -18650,7 +18650,7 @@
         <v>4</v>
       </c>
       <c r="F405" s="25">
-        <f>IF(OR(B405="",E405=""),"",E405*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B405,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B405="",E405=""),"",IFERROR(E405*INDEX(Config!$D$11:$D$20,MATCH(B405,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>280</v>
       </c>
       <c r="G405" s="24">
@@ -18690,7 +18690,7 @@
         <v>4</v>
       </c>
       <c r="F406" s="25">
-        <f>IF(OR(B406="",E406=""),"",E406*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B406,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B406="",E406=""),"",IFERROR(E406*INDEX(Config!$D$11:$D$20,MATCH(B406,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>205.714285714286</v>
       </c>
       <c r="G406" s="24">
@@ -18730,7 +18730,7 @@
         <v>2</v>
       </c>
       <c r="F407" s="25">
-        <f>IF(OR(B407="",E407=""),"",E407*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B407,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B407="",E407=""),"",IFERROR(E407*INDEX(Config!$D$11:$D$20,MATCH(B407,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G407" s="24">
@@ -18770,7 +18770,7 @@
         <v>1</v>
       </c>
       <c r="F408" s="25">
-        <f>IF(OR(B408="",E408=""),"",E408*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B408,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B408="",E408=""),"",IFERROR(E408*INDEX(Config!$D$11:$D$20,MATCH(B408,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G408" s="24">
@@ -18810,7 +18810,7 @@
         <v>2</v>
       </c>
       <c r="F409" s="25">
-        <f>IF(OR(B409="",E409=""),"",E409*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B409,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B409="",E409=""),"",IFERROR(E409*INDEX(Config!$D$11:$D$20,MATCH(B409,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G409" s="24">
@@ -18850,7 +18850,7 @@
         <v>5</v>
       </c>
       <c r="F410" s="25">
-        <f>IF(OR(B410="",E410=""),"",E410*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B410,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B410="",E410=""),"",IFERROR(E410*INDEX(Config!$D$11:$D$20,MATCH(B410,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>232.142857142857</v>
       </c>
       <c r="G410" s="24">
@@ -18890,7 +18890,7 @@
         <v>1</v>
       </c>
       <c r="F411" s="25">
-        <f>IF(OR(B411="",E411=""),"",E411*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B411,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B411="",E411=""),"",IFERROR(E411*INDEX(Config!$D$11:$D$20,MATCH(B411,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G411" s="24">
@@ -18930,7 +18930,7 @@
         <v>5</v>
       </c>
       <c r="F412" s="25">
-        <f>IF(OR(B412="",E412=""),"",E412*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B412,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B412="",E412=""),"",IFERROR(E412*INDEX(Config!$D$11:$D$20,MATCH(B412,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>241.666666666667</v>
       </c>
       <c r="G412" s="24">
@@ -18970,7 +18970,7 @@
         <v>1</v>
       </c>
       <c r="F413" s="25">
-        <f>IF(OR(B413="",E413=""),"",E413*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B413,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B413="",E413=""),"",IFERROR(E413*INDEX(Config!$D$11:$D$20,MATCH(B413,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G413" s="24">
@@ -19010,7 +19010,7 @@
         <v>2</v>
       </c>
       <c r="F414" s="25">
-        <f>IF(OR(B414="",E414=""),"",E414*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B414,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B414="",E414=""),"",IFERROR(E414*INDEX(Config!$D$11:$D$20,MATCH(B414,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G414" s="24">
@@ -19050,7 +19050,7 @@
         <v>2</v>
       </c>
       <c r="F415" s="25">
-        <f>IF(OR(B415="",E415=""),"",E415*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B415,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B415="",E415=""),"",IFERROR(E415*INDEX(Config!$D$11:$D$20,MATCH(B415,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G415" s="24">
@@ -19090,7 +19090,7 @@
         <v>2.5</v>
       </c>
       <c r="F416" s="25">
-        <f>IF(OR(B416="",E416=""),"",E416*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B416,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B416="",E416=""),"",IFERROR(E416*INDEX(Config!$D$11:$D$20,MATCH(B416,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G416" s="24">
@@ -19130,7 +19130,7 @@
         <v>2</v>
       </c>
       <c r="F417" s="25">
-        <f>IF(OR(B417="",E417=""),"",E417*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B417,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B417="",E417=""),"",IFERROR(E417*INDEX(Config!$D$11:$D$20,MATCH(B417,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G417" s="24">
@@ -19170,7 +19170,7 @@
         <v>3.5</v>
       </c>
       <c r="F418" s="25">
-        <f>IF(OR(B418="",E418=""),"",E418*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B418,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B418="",E418=""),"",IFERROR(E418*INDEX(Config!$D$11:$D$20,MATCH(B418,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>180</v>
       </c>
       <c r="G418" s="24">
@@ -19210,7 +19210,7 @@
         <v>1.5</v>
       </c>
       <c r="F419" s="25">
-        <f>IF(OR(B419="",E419=""),"",E419*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B419,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B419="",E419=""),"",IFERROR(E419*INDEX(Config!$D$11:$D$20,MATCH(B419,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G419" s="24">
@@ -19250,7 +19250,7 @@
         <v>1.5</v>
       </c>
       <c r="F420" s="25">
-        <f>IF(OR(B420="",E420=""),"",E420*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B420,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B420="",E420=""),"",IFERROR(E420*INDEX(Config!$D$11:$D$20,MATCH(B420,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G420" s="24">
@@ -19290,7 +19290,7 @@
         <v>2.5</v>
       </c>
       <c r="F421" s="25">
-        <f>IF(OR(B421="",E421=""),"",E421*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B421,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B421="",E421=""),"",IFERROR(E421*INDEX(Config!$D$11:$D$20,MATCH(B421,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G421" s="24">
@@ -19330,7 +19330,7 @@
         <v>5.5</v>
       </c>
       <c r="F422" s="25">
-        <f>IF(OR(B422="",E422=""),"",E422*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B422,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B422="",E422=""),"",IFERROR(E422*INDEX(Config!$D$11:$D$20,MATCH(B422,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>255.357142857143</v>
       </c>
       <c r="G422" s="24">
@@ -19370,7 +19370,7 @@
         <v>1</v>
       </c>
       <c r="F423" s="25">
-        <f>IF(OR(B423="",E423=""),"",E423*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B423,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B423="",E423=""),"",IFERROR(E423*INDEX(Config!$D$11:$D$20,MATCH(B423,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G423" s="24">
@@ -19410,7 +19410,7 @@
         <v>3.5</v>
       </c>
       <c r="F424" s="25">
-        <f>IF(OR(B424="",E424=""),"",E424*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B424,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B424="",E424=""),"",IFERROR(E424*INDEX(Config!$D$11:$D$20,MATCH(B424,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G424" s="24">
@@ -19450,7 +19450,7 @@
         <v>0.5</v>
       </c>
       <c r="F425" s="25">
-        <f>IF(OR(B425="",E425=""),"",E425*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B425,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B425="",E425=""),"",IFERROR(E425*INDEX(Config!$D$11:$D$20,MATCH(B425,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G425" s="24">
@@ -19490,7 +19490,7 @@
         <v>2</v>
       </c>
       <c r="F426" s="25">
-        <f>IF(OR(B426="",E426=""),"",E426*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B426,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B426="",E426=""),"",IFERROR(E426*INDEX(Config!$D$11:$D$20,MATCH(B426,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G426" s="24">
@@ -19530,7 +19530,7 @@
         <v>2</v>
       </c>
       <c r="F427" s="25">
-        <f>IF(OR(B427="",E427=""),"",E427*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B427,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B427="",E427=""),"",IFERROR(E427*INDEX(Config!$D$11:$D$20,MATCH(B427,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G427" s="24">
@@ -19570,7 +19570,7 @@
         <v>3</v>
       </c>
       <c r="F428" s="25">
-        <f>IF(OR(B428="",E428=""),"",E428*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B428,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B428="",E428=""),"",IFERROR(E428*INDEX(Config!$D$11:$D$20,MATCH(B428,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G428" s="24">
@@ -19610,7 +19610,7 @@
         <v>3</v>
       </c>
       <c r="F429" s="25">
-        <f>IF(OR(B429="",E429=""),"",E429*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B429,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B429="",E429=""),"",IFERROR(E429*INDEX(Config!$D$11:$D$20,MATCH(B429,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G429" s="24">
@@ -19650,7 +19650,7 @@
         <v>4</v>
       </c>
       <c r="F430" s="25">
-        <f>IF(OR(B430="",E430=""),"",E430*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B430,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B430="",E430=""),"",IFERROR(E430*INDEX(Config!$D$11:$D$20,MATCH(B430,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>205.714285714286</v>
       </c>
       <c r="G430" s="24">
@@ -19690,7 +19690,7 @@
         <v>1.5</v>
       </c>
       <c r="F431" s="25">
-        <f>IF(OR(B431="",E431=""),"",E431*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B431,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B431="",E431=""),"",IFERROR(E431*INDEX(Config!$D$11:$D$20,MATCH(B431,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G431" s="24">
@@ -19730,7 +19730,7 @@
         <v>1</v>
       </c>
       <c r="F432" s="25">
-        <f>IF(OR(B432="",E432=""),"",E432*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B432,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B432="",E432=""),"",IFERROR(E432*INDEX(Config!$D$11:$D$20,MATCH(B432,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G432" s="24">
@@ -19770,7 +19770,7 @@
         <v>2</v>
       </c>
       <c r="F433" s="25">
-        <f>IF(OR(B433="",E433=""),"",E433*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B433,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B433="",E433=""),"",IFERROR(E433*INDEX(Config!$D$11:$D$20,MATCH(B433,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G433" s="24">
@@ -19810,7 +19810,7 @@
         <v>3.5</v>
       </c>
       <c r="F434" s="25">
-        <f>IF(OR(B434="",E434=""),"",E434*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B434,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B434="",E434=""),"",IFERROR(E434*INDEX(Config!$D$11:$D$20,MATCH(B434,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>162.5</v>
       </c>
       <c r="G434" s="24">
@@ -19850,7 +19850,7 @@
         <v>1</v>
       </c>
       <c r="F435" s="25">
-        <f>IF(OR(B435="",E435=""),"",E435*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B435,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B435="",E435=""),"",IFERROR(E435*INDEX(Config!$D$11:$D$20,MATCH(B435,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G435" s="24">
@@ -19890,7 +19890,7 @@
         <v>3.5</v>
       </c>
       <c r="F436" s="25">
-        <f>IF(OR(B436="",E436=""),"",E436*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B436,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B436="",E436=""),"",IFERROR(E436*INDEX(Config!$D$11:$D$20,MATCH(B436,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G436" s="24">
@@ -19930,7 +19930,7 @@
         <v>0.5</v>
       </c>
       <c r="F437" s="25">
-        <f>IF(OR(B437="",E437=""),"",E437*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B437,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B437="",E437=""),"",IFERROR(E437*INDEX(Config!$D$11:$D$20,MATCH(B437,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G437" s="24">
@@ -19970,7 +19970,7 @@
         <v>1.5</v>
       </c>
       <c r="F438" s="25">
-        <f>IF(OR(B438="",E438=""),"",E438*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B438,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B438="",E438=""),"",IFERROR(E438*INDEX(Config!$D$11:$D$20,MATCH(B438,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>72.5</v>
       </c>
       <c r="G438" s="24">
@@ -20010,7 +20010,7 @@
         <v>2.5</v>
       </c>
       <c r="F439" s="25">
-        <f>IF(OR(B439="",E439=""),"",E439*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B439,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B439="",E439=""),"",IFERROR(E439*INDEX(Config!$D$11:$D$20,MATCH(B439,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G439" s="24">
@@ -20050,7 +20050,7 @@
         <v>2.5</v>
       </c>
       <c r="F440" s="25">
-        <f>IF(OR(B440="",E440=""),"",E440*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B440,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B440="",E440=""),"",IFERROR(E440*INDEX(Config!$D$11:$D$20,MATCH(B440,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G440" s="24">
@@ -20090,7 +20090,7 @@
         <v>3.5</v>
       </c>
       <c r="F441" s="25">
-        <f>IF(OR(B441="",E441=""),"",E441*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B441,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B441="",E441=""),"",IFERROR(E441*INDEX(Config!$D$11:$D$20,MATCH(B441,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G441" s="24">
@@ -20130,7 +20130,7 @@
         <v>4</v>
       </c>
       <c r="F442" s="25">
-        <f>IF(OR(B442="",E442=""),"",E442*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B442,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B442="",E442=""),"",IFERROR(E442*INDEX(Config!$D$11:$D$20,MATCH(B442,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>205.714285714286</v>
       </c>
       <c r="G442" s="24">
@@ -20170,7 +20170,7 @@
         <v>3</v>
       </c>
       <c r="F443" s="25">
-        <f>IF(OR(B443="",E443=""),"",E443*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B443,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B443="",E443=""),"",IFERROR(E443*INDEX(Config!$D$11:$D$20,MATCH(B443,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>154.285714285714</v>
       </c>
       <c r="G443" s="24">
@@ -20210,7 +20210,7 @@
         <v>1.5</v>
       </c>
       <c r="F444" s="25">
-        <f>IF(OR(B444="",E444=""),"",E444*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B444,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B444="",E444=""),"",IFERROR(E444*INDEX(Config!$D$11:$D$20,MATCH(B444,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G444" s="24">
@@ -20250,7 +20250,7 @@
         <v>1</v>
       </c>
       <c r="F445" s="25">
-        <f>IF(OR(B445="",E445=""),"",E445*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B445,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B445="",E445=""),"",IFERROR(E445*INDEX(Config!$D$11:$D$20,MATCH(B445,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G445" s="24">
@@ -20290,7 +20290,7 @@
         <v>4</v>
       </c>
       <c r="F446" s="25">
-        <f>IF(OR(B446="",E446=""),"",E446*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B446,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B446="",E446=""),"",IFERROR(E446*INDEX(Config!$D$11:$D$20,MATCH(B446,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>185.714285714286</v>
       </c>
       <c r="G446" s="24">
@@ -20330,7 +20330,7 @@
         <v>1.5</v>
       </c>
       <c r="F447" s="25">
-        <f>IF(OR(B447="",E447=""),"",E447*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B447,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B447="",E447=""),"",IFERROR(E447*INDEX(Config!$D$11:$D$20,MATCH(B447,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G447" s="24">
@@ -20370,7 +20370,7 @@
         <v>3</v>
       </c>
       <c r="F448" s="25">
-        <f>IF(OR(B448="",E448=""),"",E448*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B448,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B448="",E448=""),"",IFERROR(E448*INDEX(Config!$D$11:$D$20,MATCH(B448,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>139.285714285714</v>
       </c>
       <c r="G448" s="24">
@@ -20410,7 +20410,7 @@
         <v>1</v>
       </c>
       <c r="F449" s="25">
-        <f>IF(OR(B449="",E449=""),"",E449*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B449,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B449="",E449=""),"",IFERROR(E449*INDEX(Config!$D$11:$D$20,MATCH(B449,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G449" s="24">
@@ -20450,7 +20450,7 @@
         <v>6.5</v>
       </c>
       <c r="F450" s="25">
-        <f>IF(OR(B450="",E450=""),"",E450*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B450,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B450="",E450=""),"",IFERROR(E450*INDEX(Config!$D$11:$D$20,MATCH(B450,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>314.166666666667</v>
       </c>
       <c r="G450" s="24">
@@ -20490,7 +20490,7 @@
         <v>1</v>
       </c>
       <c r="F451" s="25">
-        <f>IF(OR(B451="",E451=""),"",E451*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B451,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B451="",E451=""),"",IFERROR(E451*INDEX(Config!$D$11:$D$20,MATCH(B451,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G451" s="24">
@@ -20530,7 +20530,7 @@
         <v>2.5</v>
       </c>
       <c r="F452" s="25">
-        <f>IF(OR(B452="",E452=""),"",E452*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B452,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B452="",E452=""),"",IFERROR(E452*INDEX(Config!$D$11:$D$20,MATCH(B452,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G452" s="24">
@@ -20570,7 +20570,7 @@
         <v>2</v>
       </c>
       <c r="F453" s="25">
-        <f>IF(OR(B453="",E453=""),"",E453*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B453,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B453="",E453=""),"",IFERROR(E453*INDEX(Config!$D$11:$D$20,MATCH(B453,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G453" s="24">
@@ -20610,7 +20610,7 @@
         <v>2.5</v>
       </c>
       <c r="F454" s="25">
-        <f>IF(OR(B454="",E454=""),"",E454*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B454,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B454="",E454=""),"",IFERROR(E454*INDEX(Config!$D$11:$D$20,MATCH(B454,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G454" s="24">
@@ -20650,7 +20650,7 @@
         <v>2.5</v>
       </c>
       <c r="F455" s="25">
-        <f>IF(OR(B455="",E455=""),"",E455*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B455,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B455="",E455=""),"",IFERROR(E455*INDEX(Config!$D$11:$D$20,MATCH(B455,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G455" s="24">
@@ -20690,7 +20690,7 @@
         <v>3</v>
       </c>
       <c r="F456" s="25">
-        <f>IF(OR(B456="",E456=""),"",E456*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B456,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B456="",E456=""),"",IFERROR(E456*INDEX(Config!$D$11:$D$20,MATCH(B456,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>154.285714285714</v>
       </c>
       <c r="G456" s="24">
@@ -20730,7 +20730,7 @@
         <v>2.5</v>
       </c>
       <c r="F457" s="25">
-        <f>IF(OR(B457="",E457=""),"",E457*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B457,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B457="",E457=""),"",IFERROR(E457*INDEX(Config!$D$11:$D$20,MATCH(B457,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>128.571428571429</v>
       </c>
       <c r="G457" s="24">
@@ -20770,7 +20770,7 @@
         <v>1.5</v>
       </c>
       <c r="F458" s="25">
-        <f>IF(OR(B458="",E458=""),"",E458*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B458,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B458="",E458=""),"",IFERROR(E458*INDEX(Config!$D$11:$D$20,MATCH(B458,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>77.1428571428571</v>
       </c>
       <c r="G458" s="24">
@@ -20810,7 +20810,7 @@
         <v>1</v>
       </c>
       <c r="F459" s="25">
-        <f>IF(OR(B459="",E459=""),"",E459*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B459,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B459="",E459=""),"",IFERROR(E459*INDEX(Config!$D$11:$D$20,MATCH(B459,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G459" s="24">
@@ -20850,7 +20850,7 @@
         <v>3</v>
       </c>
       <c r="F460" s="25">
-        <f>IF(OR(B460="",E460=""),"",E460*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B460,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B460="",E460=""),"",IFERROR(E460*INDEX(Config!$D$11:$D$20,MATCH(B460,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>139.285714285714</v>
       </c>
       <c r="G460" s="24">
@@ -20890,7 +20890,7 @@
         <v>2</v>
       </c>
       <c r="F461" s="25">
-        <f>IF(OR(B461="",E461=""),"",E461*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B461,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B461="",E461=""),"",IFERROR(E461*INDEX(Config!$D$11:$D$20,MATCH(B461,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G461" s="24">
@@ -20930,7 +20930,7 @@
         <v>2.5</v>
       </c>
       <c r="F462" s="25">
-        <f>IF(OR(B462="",E462=""),"",E462*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B462,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B462="",E462=""),"",IFERROR(E462*INDEX(Config!$D$11:$D$20,MATCH(B462,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G462" s="24">
@@ -20970,7 +20970,7 @@
         <v>0.5</v>
       </c>
       <c r="F463" s="25">
-        <f>IF(OR(B463="",E463=""),"",E463*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B463,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B463="",E463=""),"",IFERROR(E463*INDEX(Config!$D$11:$D$20,MATCH(B463,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>23.2142857142857</v>
       </c>
       <c r="G463" s="24">
@@ -21010,7 +21010,7 @@
         <v>5.5</v>
       </c>
       <c r="F464" s="25">
-        <f>IF(OR(B464="",E464=""),"",E464*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B464,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B464="",E464=""),"",IFERROR(E464*INDEX(Config!$D$11:$D$20,MATCH(B464,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>265.833333333333</v>
       </c>
       <c r="G464" s="24">
@@ -21050,7 +21050,7 @@
         <v>0.5</v>
       </c>
       <c r="F465" s="25">
-        <f>IF(OR(B465="",E465=""),"",E465*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B465,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B465="",E465=""),"",IFERROR(E465*INDEX(Config!$D$11:$D$20,MATCH(B465,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G465" s="24">
@@ -21090,7 +21090,7 @@
         <v>2.5</v>
       </c>
       <c r="F466" s="25">
-        <f>IF(OR(B466="",E466=""),"",E466*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B466,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B466="",E466=""),"",IFERROR(E466*INDEX(Config!$D$11:$D$20,MATCH(B466,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G466" s="24">
@@ -21130,7 +21130,7 @@
         <v>2</v>
       </c>
       <c r="F467" s="25">
-        <f>IF(OR(B467="",E467=""),"",E467*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B467,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B467="",E467=""),"",IFERROR(E467*INDEX(Config!$D$11:$D$20,MATCH(B467,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G467" s="24">
@@ -21170,7 +21170,7 @@
         <v>2</v>
       </c>
       <c r="F468" s="25">
-        <f>IF(OR(B468="",E468=""),"",E468*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B468,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B468="",E468=""),"",IFERROR(E468*INDEX(Config!$D$11:$D$20,MATCH(B468,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G468" s="24">
@@ -21210,7 +21210,7 @@
         <v>2.5</v>
       </c>
       <c r="F469" s="25">
-        <f>IF(OR(B469="",E469=""),"",E469*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B469,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B469="",E469=""),"",IFERROR(E469*INDEX(Config!$D$11:$D$20,MATCH(B469,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G469" s="24">
@@ -21250,7 +21250,7 @@
         <v>2.5</v>
       </c>
       <c r="F470" s="25">
-        <f>IF(OR(B470="",E470=""),"",E470*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B470,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B470="",E470=""),"",IFERROR(E470*INDEX(Config!$D$11:$D$20,MATCH(B470,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>128.571428571429</v>
       </c>
       <c r="G470" s="24">
@@ -21290,7 +21290,7 @@
         <v>2</v>
       </c>
       <c r="F471" s="25">
-        <f>IF(OR(B471="",E471=""),"",E471*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B471,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B471="",E471=""),"",IFERROR(E471*INDEX(Config!$D$11:$D$20,MATCH(B471,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G471" s="24">
@@ -21330,7 +21330,7 @@
         <v>1</v>
       </c>
       <c r="F472" s="25">
-        <f>IF(OR(B472="",E472=""),"",E472*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B472,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B472="",E472=""),"",IFERROR(E472*INDEX(Config!$D$11:$D$20,MATCH(B472,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G472" s="24">
@@ -21370,7 +21370,7 @@
         <v>0.5</v>
       </c>
       <c r="F473" s="25">
-        <f>IF(OR(B473="",E473=""),"",E473*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B473,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B473="",E473=""),"",IFERROR(E473*INDEX(Config!$D$11:$D$20,MATCH(B473,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>25.7142857142857</v>
       </c>
       <c r="G473" s="24">
@@ -21410,7 +21410,7 @@
         <v>3</v>
       </c>
       <c r="F474" s="25">
-        <f>IF(OR(B474="",E474=""),"",E474*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B474,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B474="",E474=""),"",IFERROR(E474*INDEX(Config!$D$11:$D$20,MATCH(B474,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>139.285714285714</v>
       </c>
       <c r="G474" s="24">
@@ -21450,7 +21450,7 @@
         <v>1.5</v>
       </c>
       <c r="F475" s="25">
-        <f>IF(OR(B475="",E475=""),"",E475*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B475,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B475="",E475=""),"",IFERROR(E475*INDEX(Config!$D$11:$D$20,MATCH(B475,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G475" s="24">
@@ -21490,7 +21490,7 @@
         <v>2.5</v>
       </c>
       <c r="F476" s="25">
-        <f>IF(OR(B476="",E476=""),"",E476*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B476,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B476="",E476=""),"",IFERROR(E476*INDEX(Config!$D$11:$D$20,MATCH(B476,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G476" s="24">
@@ -21530,7 +21530,7 @@
         <v>1</v>
       </c>
       <c r="F477" s="25">
-        <f>IF(OR(B477="",E477=""),"",E477*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B477,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B477="",E477=""),"",IFERROR(E477*INDEX(Config!$D$11:$D$20,MATCH(B477,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G477" s="24">
@@ -21570,7 +21570,7 @@
         <v>5</v>
       </c>
       <c r="F478" s="25">
-        <f>IF(OR(B478="",E478=""),"",E478*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B478,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B478="",E478=""),"",IFERROR(E478*INDEX(Config!$D$11:$D$20,MATCH(B478,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>241.666666666667</v>
       </c>
       <c r="G478" s="24">
@@ -21610,7 +21610,7 @@
         <v>0.5</v>
       </c>
       <c r="F479" s="25">
-        <f>IF(OR(B479="",E479=""),"",E479*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B479,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B479="",E479=""),"",IFERROR(E479*INDEX(Config!$D$11:$D$20,MATCH(B479,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G479" s="24">
@@ -21650,7 +21650,7 @@
         <v>2</v>
       </c>
       <c r="F480" s="25">
-        <f>IF(OR(B480="",E480=""),"",E480*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B480,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B480="",E480=""),"",IFERROR(E480*INDEX(Config!$D$11:$D$20,MATCH(B480,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G480" s="24">
@@ -21690,7 +21690,7 @@
         <v>2.5</v>
       </c>
       <c r="F481" s="25">
-        <f>IF(OR(B481="",E481=""),"",E481*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B481,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B481="",E481=""),"",IFERROR(E481*INDEX(Config!$D$11:$D$20,MATCH(B481,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G481" s="24">
@@ -21730,7 +21730,7 @@
         <v>2</v>
       </c>
       <c r="F482" s="25">
-        <f>IF(OR(B482="",E482=""),"",E482*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B482,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B482="",E482=""),"",IFERROR(E482*INDEX(Config!$D$11:$D$20,MATCH(B482,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G482" s="24">
@@ -21770,7 +21770,7 @@
         <v>2.5</v>
       </c>
       <c r="F483" s="25">
-        <f>IF(OR(B483="",E483=""),"",E483*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B483,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B483="",E483=""),"",IFERROR(E483*INDEX(Config!$D$11:$D$20,MATCH(B483,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G483" s="24">
@@ -21810,7 +21810,7 @@
         <v>4.5</v>
       </c>
       <c r="F484" s="25">
-        <f>IF(OR(B484="",E484=""),"",E484*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B484,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B484="",E484=""),"",IFERROR(E484*INDEX(Config!$D$11:$D$20,MATCH(B484,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>231.428571428571</v>
       </c>
       <c r="G484" s="24">
@@ -21850,7 +21850,7 @@
         <v>2</v>
       </c>
       <c r="F485" s="25">
-        <f>IF(OR(B485="",E485=""),"",E485*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B485,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B485="",E485=""),"",IFERROR(E485*INDEX(Config!$D$11:$D$20,MATCH(B485,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G485" s="24">
@@ -21890,7 +21890,7 @@
         <v>1</v>
       </c>
       <c r="F486" s="25">
-        <f>IF(OR(B486="",E486=""),"",E486*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B486,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B486="",E486=""),"",IFERROR(E486*INDEX(Config!$D$11:$D$20,MATCH(B486,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G486" s="24">
@@ -21930,7 +21930,7 @@
         <v>1</v>
       </c>
       <c r="F487" s="25">
-        <f>IF(OR(B487="",E487=""),"",E487*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B487,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B487="",E487=""),"",IFERROR(E487*INDEX(Config!$D$11:$D$20,MATCH(B487,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G487" s="24">
@@ -21970,7 +21970,7 @@
         <v>2.5</v>
       </c>
       <c r="F488" s="25">
-        <f>IF(OR(B488="",E488=""),"",E488*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B488,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B488="",E488=""),"",IFERROR(E488*INDEX(Config!$D$11:$D$20,MATCH(B488,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G488" s="24">
@@ -22010,7 +22010,7 @@
         <v>1.5</v>
       </c>
       <c r="F489" s="25">
-        <f>IF(OR(B489="",E489=""),"",E489*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B489,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B489="",E489=""),"",IFERROR(E489*INDEX(Config!$D$11:$D$20,MATCH(B489,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G489" s="24">
@@ -22050,7 +22050,7 @@
         <v>3</v>
       </c>
       <c r="F490" s="25">
-        <f>IF(OR(B490="",E490=""),"",E490*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B490,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B490="",E490=""),"",IFERROR(E490*INDEX(Config!$D$11:$D$20,MATCH(B490,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>139.285714285714</v>
       </c>
       <c r="G490" s="24">
@@ -22090,7 +22090,7 @@
         <v>1</v>
       </c>
       <c r="F491" s="25">
-        <f>IF(OR(B491="",E491=""),"",E491*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B491,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B491="",E491=""),"",IFERROR(E491*INDEX(Config!$D$11:$D$20,MATCH(B491,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G491" s="24">
@@ -22130,7 +22130,7 @@
         <v>5.5</v>
       </c>
       <c r="F492" s="25">
-        <f>IF(OR(B492="",E492=""),"",E492*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B492,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B492="",E492=""),"",IFERROR(E492*INDEX(Config!$D$11:$D$20,MATCH(B492,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>265.833333333333</v>
       </c>
       <c r="G492" s="24">
@@ -22170,7 +22170,7 @@
         <v>1</v>
       </c>
       <c r="F493" s="25">
-        <f>IF(OR(B493="",E493=""),"",E493*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B493,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B493="",E493=""),"",IFERROR(E493*INDEX(Config!$D$11:$D$20,MATCH(B493,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G493" s="24">
@@ -22210,7 +22210,7 @@
         <v>2.5</v>
       </c>
       <c r="F494" s="25">
-        <f>IF(OR(B494="",E494=""),"",E494*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B494,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B494="",E494=""),"",IFERROR(E494*INDEX(Config!$D$11:$D$20,MATCH(B494,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>120.833333333333</v>
       </c>
       <c r="G494" s="24">
@@ -22250,7 +22250,7 @@
         <v>2</v>
       </c>
       <c r="F495" s="25">
-        <f>IF(OR(B495="",E495=""),"",E495*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B495,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B495="",E495=""),"",IFERROR(E495*INDEX(Config!$D$11:$D$20,MATCH(B495,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G495" s="24">
@@ -22290,7 +22290,7 @@
         <v>3</v>
       </c>
       <c r="F496" s="25">
-        <f>IF(OR(B496="",E496=""),"",E496*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B496,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B496="",E496=""),"",IFERROR(E496*INDEX(Config!$D$11:$D$20,MATCH(B496,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G496" s="24">
@@ -22330,7 +22330,7 @@
         <v>3</v>
       </c>
       <c r="F497" s="25">
-        <f>IF(OR(B497="",E497=""),"",E497*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B497,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B497="",E497=""),"",IFERROR(E497*INDEX(Config!$D$11:$D$20,MATCH(B497,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>210</v>
       </c>
       <c r="G497" s="24">
@@ -22370,7 +22370,7 @@
         <v>5</v>
       </c>
       <c r="F498" s="25">
-        <f>IF(OR(B498="",E498=""),"",E498*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B498,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B498="",E498=""),"",IFERROR(E498*INDEX(Config!$D$11:$D$20,MATCH(B498,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>257.142857142857</v>
       </c>
       <c r="G498" s="24">
@@ -22410,7 +22410,7 @@
         <v>3.5</v>
       </c>
       <c r="F499" s="25">
-        <f>IF(OR(B499="",E499=""),"",E499*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B499,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B499="",E499=""),"",IFERROR(E499*INDEX(Config!$D$11:$D$20,MATCH(B499,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>180</v>
       </c>
       <c r="G499" s="24">
@@ -22450,7 +22450,7 @@
         <v>1</v>
       </c>
       <c r="F500" s="25">
-        <f>IF(OR(B500="",E500=""),"",E500*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B500,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B500="",E500=""),"",IFERROR(E500*INDEX(Config!$D$11:$D$20,MATCH(B500,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G500" s="24">
@@ -22490,7 +22490,7 @@
         <v>3</v>
       </c>
       <c r="F501" s="25">
-        <f>IF(OR(B501="",E501=""),"",E501*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B501,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B501="",E501=""),"",IFERROR(E501*INDEX(Config!$D$11:$D$20,MATCH(B501,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>139.285714285714</v>
       </c>
       <c r="G501" s="24">
@@ -22530,7 +22530,7 @@
         <v>1.5</v>
       </c>
       <c r="F502" s="25">
-        <f>IF(OR(B502="",E502=""),"",E502*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B502,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B502="",E502=""),"",IFERROR(E502*INDEX(Config!$D$11:$D$20,MATCH(B502,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G502" s="24">
@@ -22570,7 +22570,7 @@
         <v>2</v>
       </c>
       <c r="F503" s="25">
-        <f>IF(OR(B503="",E503=""),"",E503*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B503,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B503="",E503=""),"",IFERROR(E503*INDEX(Config!$D$11:$D$20,MATCH(B503,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G503" s="24">
@@ -22610,7 +22610,7 @@
         <v>0.5</v>
       </c>
       <c r="F504" s="25">
-        <f>IF(OR(B504="",E504=""),"",E504*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B504,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B504="",E504=""),"",IFERROR(E504*INDEX(Config!$D$11:$D$20,MATCH(B504,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>23.2142857142857</v>
       </c>
       <c r="G504" s="24">
@@ -22650,7 +22650,7 @@
         <v>5.5</v>
       </c>
       <c r="F505" s="25">
-        <f>IF(OR(B505="",E505=""),"",E505*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B505,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B505="",E505=""),"",IFERROR(E505*INDEX(Config!$D$11:$D$20,MATCH(B505,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>265.833333333333</v>
       </c>
       <c r="G505" s="24">
@@ -22690,7 +22690,7 @@
         <v>0.5</v>
       </c>
       <c r="F506" s="25">
-        <f>IF(OR(B506="",E506=""),"",E506*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B506,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B506="",E506=""),"",IFERROR(E506*INDEX(Config!$D$11:$D$20,MATCH(B506,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G506" s="24">
@@ -22730,7 +22730,7 @@
         <v>3</v>
       </c>
       <c r="F507" s="25">
-        <f>IF(OR(B507="",E507=""),"",E507*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B507,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B507="",E507=""),"",IFERROR(E507*INDEX(Config!$D$11:$D$20,MATCH(B507,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>145</v>
       </c>
       <c r="G507" s="24">
@@ -22770,7 +22770,7 @@
         <v>1</v>
       </c>
       <c r="F508" s="25">
-        <f>IF(OR(B508="",E508=""),"",E508*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B508,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B508="",E508=""),"",IFERROR(E508*INDEX(Config!$D$11:$D$20,MATCH(B508,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>70</v>
       </c>
       <c r="G508" s="24">
@@ -22810,7 +22810,7 @@
         <v>2</v>
       </c>
       <c r="F509" s="25">
-        <f>IF(OR(B509="",E509=""),"",E509*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B509,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B509="",E509=""),"",IFERROR(E509*INDEX(Config!$D$11:$D$20,MATCH(B509,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G509" s="24">
@@ -22850,7 +22850,7 @@
         <v>2</v>
       </c>
       <c r="F510" s="25">
-        <f>IF(OR(B510="",E510=""),"",E510*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B510,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B510="",E510=""),"",IFERROR(E510*INDEX(Config!$D$11:$D$20,MATCH(B510,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G510" s="24">
@@ -22890,7 +22890,7 @@
         <v>2</v>
       </c>
       <c r="F511" s="25">
-        <f>IF(OR(B511="",E511=""),"",E511*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B511,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B511="",E511=""),"",IFERROR(E511*INDEX(Config!$D$11:$D$20,MATCH(B511,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G511" s="24">
@@ -22930,7 +22930,7 @@
         <v>4</v>
       </c>
       <c r="F512" s="25">
-        <f>IF(OR(B512="",E512=""),"",E512*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B512,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B512="",E512=""),"",IFERROR(E512*INDEX(Config!$D$11:$D$20,MATCH(B512,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>205.714285714286</v>
       </c>
       <c r="G512" s="24">
@@ -22970,7 +22970,7 @@
         <v>3</v>
       </c>
       <c r="F513" s="25">
-        <f>IF(OR(B513="",E513=""),"",E513*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B513,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B513="",E513=""),"",IFERROR(E513*INDEX(Config!$D$11:$D$20,MATCH(B513,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>154.285714285714</v>
       </c>
       <c r="G513" s="24">
@@ -23010,7 +23010,7 @@
         <v>1</v>
       </c>
       <c r="F514" s="25">
-        <f>IF(OR(B514="",E514=""),"",E514*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B514,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B514="",E514=""),"",IFERROR(E514*INDEX(Config!$D$11:$D$20,MATCH(B514,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G514" s="24">
@@ -23050,7 +23050,7 @@
         <v>4</v>
       </c>
       <c r="F515" s="25">
-        <f>IF(OR(B515="",E515=""),"",E515*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B515,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B515="",E515=""),"",IFERROR(E515*INDEX(Config!$D$11:$D$20,MATCH(B515,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>185.714285714286</v>
       </c>
       <c r="G515" s="24">
@@ -23090,7 +23090,7 @@
         <v>2</v>
       </c>
       <c r="F516" s="25">
-        <f>IF(OR(B516="",E516=""),"",E516*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B516,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B516="",E516=""),"",IFERROR(E516*INDEX(Config!$D$11:$D$20,MATCH(B516,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G516" s="24">
@@ -23130,7 +23130,7 @@
         <v>2</v>
       </c>
       <c r="F517" s="25">
-        <f>IF(OR(B517="",E517=""),"",E517*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B517,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B517="",E517=""),"",IFERROR(E517*INDEX(Config!$D$11:$D$20,MATCH(B517,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G517" s="24">
@@ -23170,7 +23170,7 @@
         <v>1</v>
       </c>
       <c r="F518" s="25">
-        <f>IF(OR(B518="",E518=""),"",E518*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B518,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B518="",E518=""),"",IFERROR(E518*INDEX(Config!$D$11:$D$20,MATCH(B518,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G518" s="24">
@@ -23210,7 +23210,7 @@
         <v>3.5</v>
       </c>
       <c r="F519" s="25">
-        <f>IF(OR(B519="",E519=""),"",E519*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B519,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B519="",E519=""),"",IFERROR(E519*INDEX(Config!$D$11:$D$20,MATCH(B519,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G519" s="24">
@@ -23250,7 +23250,7 @@
         <v>0.5</v>
       </c>
       <c r="F520" s="25">
-        <f>IF(OR(B520="",E520=""),"",E520*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B520,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B520="",E520=""),"",IFERROR(E520*INDEX(Config!$D$11:$D$20,MATCH(B520,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G520" s="24">
@@ -23290,7 +23290,7 @@
         <v>1.5</v>
       </c>
       <c r="F521" s="25">
-        <f>IF(OR(B521="",E521=""),"",E521*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B521,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B521="",E521=""),"",IFERROR(E521*INDEX(Config!$D$11:$D$20,MATCH(B521,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>72.5</v>
       </c>
       <c r="G521" s="24">
@@ -23330,7 +23330,7 @@
         <v>1.5</v>
       </c>
       <c r="F522" s="25">
-        <f>IF(OR(B522="",E522=""),"",E522*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B522,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B522="",E522=""),"",IFERROR(E522*INDEX(Config!$D$11:$D$20,MATCH(B522,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>105</v>
       </c>
       <c r="G522" s="24">
@@ -23370,7 +23370,7 @@
         <v>2</v>
       </c>
       <c r="F523" s="25">
-        <f>IF(OR(B523="",E523=""),"",E523*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B523,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B523="",E523=""),"",IFERROR(E523*INDEX(Config!$D$11:$D$20,MATCH(B523,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G523" s="24">
@@ -23410,7 +23410,7 @@
         <v>2.5</v>
       </c>
       <c r="F524" s="25">
-        <f>IF(OR(B524="",E524=""),"",E524*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B524,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B524="",E524=""),"",IFERROR(E524*INDEX(Config!$D$11:$D$20,MATCH(B524,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G524" s="24">
@@ -23450,7 +23450,7 @@
         <v>1.5</v>
       </c>
       <c r="F525" s="25">
-        <f>IF(OR(B525="",E525=""),"",E525*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B525,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B525="",E525=""),"",IFERROR(E525*INDEX(Config!$D$11:$D$20,MATCH(B525,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>105</v>
       </c>
       <c r="G525" s="24">
@@ -23490,7 +23490,7 @@
         <v>3.5</v>
       </c>
       <c r="F526" s="25">
-        <f>IF(OR(B526="",E526=""),"",E526*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B526,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B526="",E526=""),"",IFERROR(E526*INDEX(Config!$D$11:$D$20,MATCH(B526,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>180</v>
       </c>
       <c r="G526" s="24">
@@ -23530,7 +23530,7 @@
         <v>2</v>
       </c>
       <c r="F527" s="25">
-        <f>IF(OR(B527="",E527=""),"",E527*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B527,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B527="",E527=""),"",IFERROR(E527*INDEX(Config!$D$11:$D$20,MATCH(B527,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G527" s="24">
@@ -23570,7 +23570,7 @@
         <v>1</v>
       </c>
       <c r="F528" s="25">
-        <f>IF(OR(B528="",E528=""),"",E528*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B528,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B528="",E528=""),"",IFERROR(E528*INDEX(Config!$D$11:$D$20,MATCH(B528,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G528" s="24">
@@ -23610,7 +23610,7 @@
         <v>3.5</v>
       </c>
       <c r="F529" s="25">
-        <f>IF(OR(B529="",E529=""),"",E529*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B529,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B529="",E529=""),"",IFERROR(E529*INDEX(Config!$D$11:$D$20,MATCH(B529,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>162.5</v>
       </c>
       <c r="G529" s="24">
@@ -23650,7 +23650,7 @@
         <v>1.5</v>
       </c>
       <c r="F530" s="25">
-        <f>IF(OR(B530="",E530=""),"",E530*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B530,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B530="",E530=""),"",IFERROR(E530*INDEX(Config!$D$11:$D$20,MATCH(B530,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G530" s="24">
@@ -23690,7 +23690,7 @@
         <v>2</v>
       </c>
       <c r="F531" s="25">
-        <f>IF(OR(B531="",E531=""),"",E531*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B531,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B531="",E531=""),"",IFERROR(E531*INDEX(Config!$D$11:$D$20,MATCH(B531,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>92.8571428571429</v>
       </c>
       <c r="G531" s="24">
@@ -23730,7 +23730,7 @@
         <v>0.5</v>
       </c>
       <c r="F532" s="25">
-        <f>IF(OR(B532="",E532=""),"",E532*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B532,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B532="",E532=""),"",IFERROR(E532*INDEX(Config!$D$11:$D$20,MATCH(B532,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>23.2142857142857</v>
       </c>
       <c r="G532" s="24">
@@ -23770,7 +23770,7 @@
         <v>3.5</v>
       </c>
       <c r="F533" s="25">
-        <f>IF(OR(B533="",E533=""),"",E533*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B533,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B533="",E533=""),"",IFERROR(E533*INDEX(Config!$D$11:$D$20,MATCH(B533,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>169.166666666667</v>
       </c>
       <c r="G533" s="24">
@@ -23810,7 +23810,7 @@
         <v>0.5</v>
       </c>
       <c r="F534" s="25">
-        <f>IF(OR(B534="",E534=""),"",E534*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B534,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B534="",E534=""),"",IFERROR(E534*INDEX(Config!$D$11:$D$20,MATCH(B534,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G534" s="24">
@@ -23850,7 +23850,7 @@
         <v>2</v>
       </c>
       <c r="F535" s="25">
-        <f>IF(OR(B535="",E535=""),"",E535*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B535,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B535="",E535=""),"",IFERROR(E535*INDEX(Config!$D$11:$D$20,MATCH(B535,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G535" s="24">
@@ -23890,7 +23890,7 @@
         <v>1.5</v>
       </c>
       <c r="F536" s="25">
-        <f>IF(OR(B536="",E536=""),"",E536*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B536,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B536="",E536=""),"",IFERROR(E536*INDEX(Config!$D$11:$D$20,MATCH(B536,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>105</v>
       </c>
       <c r="G536" s="24">
@@ -23930,7 +23930,7 @@
         <v>3.5</v>
       </c>
       <c r="F537" s="25">
-        <f>IF(OR(B537="",E537=""),"",E537*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B537,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B537="",E537=""),"",IFERROR(E537*INDEX(Config!$D$11:$D$20,MATCH(B537,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>245</v>
       </c>
       <c r="G537" s="24">
@@ -23970,7 +23970,7 @@
         <v>2.5</v>
       </c>
       <c r="F538" s="25">
-        <f>IF(OR(B538="",E538=""),"",E538*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B538,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B538="",E538=""),"",IFERROR(E538*INDEX(Config!$D$11:$D$20,MATCH(B538,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>175</v>
       </c>
       <c r="G538" s="24">
@@ -24010,7 +24010,7 @@
         <v>2</v>
       </c>
       <c r="F539" s="25">
-        <f>IF(OR(B539="",E539=""),"",E539*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B539,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B539="",E539=""),"",IFERROR(E539*INDEX(Config!$D$11:$D$20,MATCH(B539,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G539" s="24">
@@ -24050,7 +24050,7 @@
         <v>3</v>
       </c>
       <c r="F540" s="25">
-        <f>IF(OR(B540="",E540=""),"",E540*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B540,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B540="",E540=""),"",IFERROR(E540*INDEX(Config!$D$11:$D$20,MATCH(B540,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>154.285714285714</v>
       </c>
       <c r="G540" s="24">
@@ -24090,7 +24090,7 @@
         <v>3.5</v>
       </c>
       <c r="F541" s="25">
-        <f>IF(OR(B541="",E541=""),"",E541*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B541,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B541="",E541=""),"",IFERROR(E541*INDEX(Config!$D$11:$D$20,MATCH(B541,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>180</v>
       </c>
       <c r="G541" s="24">
@@ -24130,7 +24130,7 @@
         <v>1</v>
       </c>
       <c r="F542" s="25">
-        <f>IF(OR(B542="",E542=""),"",E542*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B542,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B542="",E542=""),"",IFERROR(E542*INDEX(Config!$D$11:$D$20,MATCH(B542,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G542" s="24">
@@ -24170,7 +24170,7 @@
         <v>2.5</v>
       </c>
       <c r="F543" s="25">
-        <f>IF(OR(B543="",E543=""),"",E543*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B543,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B543="",E543=""),"",IFERROR(E543*INDEX(Config!$D$11:$D$20,MATCH(B543,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G543" s="24">
@@ -24210,7 +24210,7 @@
         <v>1.5</v>
       </c>
       <c r="F544" s="25">
-        <f>IF(OR(B544="",E544=""),"",E544*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B544,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B544="",E544=""),"",IFERROR(E544*INDEX(Config!$D$11:$D$20,MATCH(B544,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>69.6428571428571</v>
       </c>
       <c r="G544" s="24">
@@ -24250,7 +24250,7 @@
         <v>2.5</v>
       </c>
       <c r="F545" s="25">
-        <f>IF(OR(B545="",E545=""),"",E545*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B545,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B545="",E545=""),"",IFERROR(E545*INDEX(Config!$D$11:$D$20,MATCH(B545,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G545" s="24">
@@ -24290,7 +24290,7 @@
         <v>1</v>
       </c>
       <c r="F546" s="25">
-        <f>IF(OR(B546="",E546=""),"",E546*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B546,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B546="",E546=""),"",IFERROR(E546*INDEX(Config!$D$11:$D$20,MATCH(B546,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G546" s="24">
@@ -24330,7 +24330,7 @@
         <v>4</v>
       </c>
       <c r="F547" s="25">
-        <f>IF(OR(B547="",E547=""),"",E547*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B547,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B547="",E547=""),"",IFERROR(E547*INDEX(Config!$D$11:$D$20,MATCH(B547,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G547" s="24">
@@ -24370,7 +24370,7 @@
         <v>1</v>
       </c>
       <c r="F548" s="25">
-        <f>IF(OR(B548="",E548=""),"",E548*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B548,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B548="",E548=""),"",IFERROR(E548*INDEX(Config!$D$11:$D$20,MATCH(B548,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>48.3333333333333</v>
       </c>
       <c r="G548" s="24">
@@ -24410,7 +24410,7 @@
         <v>2</v>
       </c>
       <c r="F549" s="25">
-        <f>IF(OR(B549="",E549=""),"",E549*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B549,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B549="",E549=""),"",IFERROR(E549*INDEX(Config!$D$11:$D$20,MATCH(B549,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>96.6666666666667</v>
       </c>
       <c r="G549" s="24">
@@ -24450,7 +24450,7 @@
         <v>1.5</v>
       </c>
       <c r="F550" s="25">
-        <f>IF(OR(B550="",E550=""),"",E550*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B550,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B550="",E550=""),"",IFERROR(E550*INDEX(Config!$D$11:$D$20,MATCH(B550,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>105</v>
       </c>
       <c r="G550" s="24">
@@ -24490,7 +24490,7 @@
         <v>2</v>
       </c>
       <c r="F551" s="25">
-        <f>IF(OR(B551="",E551=""),"",E551*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B551,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B551="",E551=""),"",IFERROR(E551*INDEX(Config!$D$11:$D$20,MATCH(B551,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G551" s="24">
@@ -24530,7 +24530,7 @@
         <v>1.5</v>
       </c>
       <c r="F552" s="25">
-        <f>IF(OR(B552="",E552=""),"",E552*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B552,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B552="",E552=""),"",IFERROR(E552*INDEX(Config!$D$11:$D$20,MATCH(B552,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>105</v>
       </c>
       <c r="G552" s="24">
@@ -24570,7 +24570,7 @@
         <v>2</v>
       </c>
       <c r="F553" s="25">
-        <f>IF(OR(B553="",E553=""),"",E553*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B553,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B553="",E553=""),"",IFERROR(E553*INDEX(Config!$D$11:$D$20,MATCH(B553,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>140</v>
       </c>
       <c r="G553" s="24">
@@ -24610,7 +24610,7 @@
         <v>3.5</v>
       </c>
       <c r="F554" s="25">
-        <f>IF(OR(B554="",E554=""),"",E554*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B554,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B554="",E554=""),"",IFERROR(E554*INDEX(Config!$D$11:$D$20,MATCH(B554,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>180</v>
       </c>
       <c r="G554" s="24">
@@ -24650,7 +24650,7 @@
         <v>2</v>
       </c>
       <c r="F555" s="25">
-        <f>IF(OR(B555="",E555=""),"",E555*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B555,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B555="",E555=""),"",IFERROR(E555*INDEX(Config!$D$11:$D$20,MATCH(B555,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>102.857142857143</v>
       </c>
       <c r="G555" s="24">
@@ -24690,7 +24690,7 @@
         <v>1</v>
       </c>
       <c r="F556" s="25">
-        <f>IF(OR(B556="",E556=""),"",E556*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B556,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B556="",E556=""),"",IFERROR(E556*INDEX(Config!$D$11:$D$20,MATCH(B556,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>51.4285714285714</v>
       </c>
       <c r="G556" s="24">
@@ -24730,7 +24730,7 @@
         <v>2.5</v>
       </c>
       <c r="F557" s="25">
-        <f>IF(OR(B557="",E557=""),"",E557*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B557,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B557="",E557=""),"",IFERROR(E557*INDEX(Config!$D$11:$D$20,MATCH(B557,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G557" s="24">
@@ -24770,7 +24770,7 @@
         <v>1</v>
       </c>
       <c r="F558" s="25">
-        <f>IF(OR(B558="",E558=""),"",E558*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B558,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B558="",E558=""),"",IFERROR(E558*INDEX(Config!$D$11:$D$20,MATCH(B558,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>46.4285714285714</v>
       </c>
       <c r="G558" s="24">
@@ -24810,7 +24810,7 @@
         <v>2.5</v>
       </c>
       <c r="F559" s="25">
-        <f>IF(OR(B559="",E559=""),"",E559*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B559,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B559="",E559=""),"",IFERROR(E559*INDEX(Config!$D$11:$D$20,MATCH(B559,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>116.071428571429</v>
       </c>
       <c r="G559" s="24">
@@ -24850,7 +24850,7 @@
         <v>0.5</v>
       </c>
       <c r="F560" s="25">
-        <f>IF(OR(B560="",E560=""),"",E560*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B560,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B560="",E560=""),"",IFERROR(E560*INDEX(Config!$D$11:$D$20,MATCH(B560,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>23.2142857142857</v>
       </c>
       <c r="G560" s="24">
@@ -24890,7 +24890,7 @@
         <v>4</v>
       </c>
       <c r="F561" s="25">
-        <f>IF(OR(B561="",E561=""),"",E561*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B561,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B561="",E561=""),"",IFERROR(E561*INDEX(Config!$D$11:$D$20,MATCH(B561,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>193.333333333333</v>
       </c>
       <c r="G561" s="24">
@@ -24930,7 +24930,7 @@
         <v>0.5</v>
       </c>
       <c r="F562" s="25">
-        <f>IF(OR(B562="",E562=""),"",E562*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B562,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B562="",E562=""),"",IFERROR(E562*INDEX(Config!$D$11:$D$20,MATCH(B562,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>24.1666666666667</v>
       </c>
       <c r="G562" s="24">
@@ -24970,7 +24970,7 @@
         <v>1.5</v>
       </c>
       <c r="F563" s="25">
-        <f>IF(OR(B563="",E563=""),"",E563*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B563,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B563="",E563=""),"",IFERROR(E563*INDEX(Config!$D$11:$D$20,MATCH(B563,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v>72.5</v>
       </c>
       <c r="G563" s="24">
@@ -24994,7 +24994,7 @@
       <c r="D564" s="28" t="n"/>
       <c r="E564" s="34" t="n"/>
       <c r="F564" s="25">
-        <f>IF(OR(B564="",E564=""),"",E564*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B564,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B564="",E564=""),"",IFERROR(E564*INDEX(Config!$D$11:$D$20,MATCH(B564,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G564" s="24">
@@ -25014,7 +25014,7 @@
       <c r="D565" s="28" t="n"/>
       <c r="E565" s="34" t="n"/>
       <c r="F565" s="25">
-        <f>IF(OR(B565="",E565=""),"",E565*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B565,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B565="",E565=""),"",IFERROR(E565*INDEX(Config!$D$11:$D$20,MATCH(B565,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G565" s="24">
@@ -25034,7 +25034,7 @@
       <c r="D566" s="28" t="n"/>
       <c r="E566" s="34" t="n"/>
       <c r="F566" s="25">
-        <f>IF(OR(B566="",E566=""),"",E566*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B566,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B566="",E566=""),"",IFERROR(E566*INDEX(Config!$D$11:$D$20,MATCH(B566,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G566" s="24">
@@ -25054,7 +25054,7 @@
       <c r="D567" s="28" t="n"/>
       <c r="E567" s="34" t="n"/>
       <c r="F567" s="25">
-        <f>IF(OR(B567="",E567=""),"",E567*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B567,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B567="",E567=""),"",IFERROR(E567*INDEX(Config!$D$11:$D$20,MATCH(B567,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G567" s="24">
@@ -25074,7 +25074,7 @@
       <c r="D568" s="28" t="n"/>
       <c r="E568" s="34" t="n"/>
       <c r="F568" s="25">
-        <f>IF(OR(B568="",E568=""),"",E568*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B568,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B568="",E568=""),"",IFERROR(E568*INDEX(Config!$D$11:$D$20,MATCH(B568,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G568" s="24">
@@ -25094,7 +25094,7 @@
       <c r="D569" s="28" t="n"/>
       <c r="E569" s="34" t="n"/>
       <c r="F569" s="25">
-        <f>IF(OR(B569="",E569=""),"",E569*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B569,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B569="",E569=""),"",IFERROR(E569*INDEX(Config!$D$11:$D$20,MATCH(B569,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G569" s="24">
@@ -25114,7 +25114,7 @@
       <c r="D570" s="28" t="n"/>
       <c r="E570" s="34" t="n"/>
       <c r="F570" s="25">
-        <f>IF(OR(B570="",E570=""),"",E570*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B570,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B570="",E570=""),"",IFERROR(E570*INDEX(Config!$D$11:$D$20,MATCH(B570,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G570" s="24">
@@ -25134,7 +25134,7 @@
       <c r="D571" s="28" t="n"/>
       <c r="E571" s="34" t="n"/>
       <c r="F571" s="25">
-        <f>IF(OR(B571="",E571=""),"",E571*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B571,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B571="",E571=""),"",IFERROR(E571*INDEX(Config!$D$11:$D$20,MATCH(B571,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G571" s="24">
@@ -25154,7 +25154,7 @@
       <c r="D572" s="28" t="n"/>
       <c r="E572" s="34" t="n"/>
       <c r="F572" s="25">
-        <f>IF(OR(B572="",E572=""),"",E572*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B572,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B572="",E572=""),"",IFERROR(E572*INDEX(Config!$D$11:$D$20,MATCH(B572,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G572" s="24">
@@ -25174,7 +25174,7 @@
       <c r="D573" s="28" t="n"/>
       <c r="E573" s="34" t="n"/>
       <c r="F573" s="25">
-        <f>IF(OR(B573="",E573=""),"",E573*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B573,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B573="",E573=""),"",IFERROR(E573*INDEX(Config!$D$11:$D$20,MATCH(B573,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G573" s="24">
@@ -25194,7 +25194,7 @@
       <c r="D574" s="28" t="n"/>
       <c r="E574" s="34" t="n"/>
       <c r="F574" s="25">
-        <f>IF(OR(B574="",E574=""),"",E574*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B574,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B574="",E574=""),"",IFERROR(E574*INDEX(Config!$D$11:$D$20,MATCH(B574,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G574" s="24">
@@ -25214,7 +25214,7 @@
       <c r="D575" s="28" t="n"/>
       <c r="E575" s="34" t="n"/>
       <c r="F575" s="25">
-        <f>IF(OR(B575="",E575=""),"",E575*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B575,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B575="",E575=""),"",IFERROR(E575*INDEX(Config!$D$11:$D$20,MATCH(B575,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G575" s="24">
@@ -25234,7 +25234,7 @@
       <c r="D576" s="28" t="n"/>
       <c r="E576" s="34" t="n"/>
       <c r="F576" s="25">
-        <f>IF(OR(B576="",E576=""),"",E576*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B576,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B576="",E576=""),"",IFERROR(E576*INDEX(Config!$D$11:$D$20,MATCH(B576,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G576" s="24">
@@ -25254,7 +25254,7 @@
       <c r="D577" s="28" t="n"/>
       <c r="E577" s="34" t="n"/>
       <c r="F577" s="25">
-        <f>IF(OR(B577="",E577=""),"",E577*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B577,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B577="",E577=""),"",IFERROR(E577*INDEX(Config!$D$11:$D$20,MATCH(B577,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G577" s="24">
@@ -25274,7 +25274,7 @@
       <c r="D578" s="28" t="n"/>
       <c r="E578" s="34" t="n"/>
       <c r="F578" s="25">
-        <f>IF(OR(B578="",E578=""),"",E578*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B578,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B578="",E578=""),"",IFERROR(E578*INDEX(Config!$D$11:$D$20,MATCH(B578,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G578" s="24">
@@ -25294,7 +25294,7 @@
       <c r="D579" s="28" t="n"/>
       <c r="E579" s="34" t="n"/>
       <c r="F579" s="25">
-        <f>IF(OR(B579="",E579=""),"",E579*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B579,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B579="",E579=""),"",IFERROR(E579*INDEX(Config!$D$11:$D$20,MATCH(B579,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G579" s="24">
@@ -25314,7 +25314,7 @@
       <c r="D580" s="28" t="n"/>
       <c r="E580" s="34" t="n"/>
       <c r="F580" s="25">
-        <f>IF(OR(B580="",E580=""),"",E580*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B580,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B580="",E580=""),"",IFERROR(E580*INDEX(Config!$D$11:$D$20,MATCH(B580,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G580" s="24">
@@ -25334,7 +25334,7 @@
       <c r="D581" s="28" t="n"/>
       <c r="E581" s="34" t="n"/>
       <c r="F581" s="25">
-        <f>IF(OR(B581="",E581=""),"",E581*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B581,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B581="",E581=""),"",IFERROR(E581*INDEX(Config!$D$11:$D$20,MATCH(B581,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G581" s="24">
@@ -25354,7 +25354,7 @@
       <c r="D582" s="28" t="n"/>
       <c r="E582" s="34" t="n"/>
       <c r="F582" s="25">
-        <f>IF(OR(B582="",E582=""),"",E582*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B582,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B582="",E582=""),"",IFERROR(E582*INDEX(Config!$D$11:$D$20,MATCH(B582,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G582" s="24">
@@ -25374,7 +25374,7 @@
       <c r="D583" s="28" t="n"/>
       <c r="E583" s="34" t="n"/>
       <c r="F583" s="25">
-        <f>IF(OR(B583="",E583=""),"",E583*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B583,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B583="",E583=""),"",IFERROR(E583*INDEX(Config!$D$11:$D$20,MATCH(B583,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G583" s="24">
@@ -25394,7 +25394,7 @@
       <c r="D584" s="28" t="n"/>
       <c r="E584" s="34" t="n"/>
       <c r="F584" s="25">
-        <f>IF(OR(B584="",E584=""),"",E584*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B584,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B584="",E584=""),"",IFERROR(E584*INDEX(Config!$D$11:$D$20,MATCH(B584,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G584" s="24">
@@ -25414,7 +25414,7 @@
       <c r="D585" s="28" t="n"/>
       <c r="E585" s="34" t="n"/>
       <c r="F585" s="25">
-        <f>IF(OR(B585="",E585=""),"",E585*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B585,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B585="",E585=""),"",IFERROR(E585*INDEX(Config!$D$11:$D$20,MATCH(B585,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G585" s="24">
@@ -25434,7 +25434,7 @@
       <c r="D586" s="28" t="n"/>
       <c r="E586" s="34" t="n"/>
       <c r="F586" s="25">
-        <f>IF(OR(B586="",E586=""),"",E586*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B586,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B586="",E586=""),"",IFERROR(E586*INDEX(Config!$D$11:$D$20,MATCH(B586,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G586" s="24">
@@ -25454,7 +25454,7 @@
       <c r="D587" s="28" t="n"/>
       <c r="E587" s="34" t="n"/>
       <c r="F587" s="25">
-        <f>IF(OR(B587="",E587=""),"",E587*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B587,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B587="",E587=""),"",IFERROR(E587*INDEX(Config!$D$11:$D$20,MATCH(B587,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G587" s="24">
@@ -25474,7 +25474,7 @@
       <c r="D588" s="28" t="n"/>
       <c r="E588" s="34" t="n"/>
       <c r="F588" s="25">
-        <f>IF(OR(B588="",E588=""),"",E588*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B588,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B588="",E588=""),"",IFERROR(E588*INDEX(Config!$D$11:$D$20,MATCH(B588,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G588" s="24">
@@ -25494,7 +25494,7 @@
       <c r="D589" s="28" t="n"/>
       <c r="E589" s="34" t="n"/>
       <c r="F589" s="25">
-        <f>IF(OR(B589="",E589=""),"",E589*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B589,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B589="",E589=""),"",IFERROR(E589*INDEX(Config!$D$11:$D$20,MATCH(B589,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G589" s="24">
@@ -25514,7 +25514,7 @@
       <c r="D590" s="28" t="n"/>
       <c r="E590" s="34" t="n"/>
       <c r="F590" s="25">
-        <f>IF(OR(B590="",E590=""),"",E590*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B590,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B590="",E590=""),"",IFERROR(E590*INDEX(Config!$D$11:$D$20,MATCH(B590,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G590" s="24">
@@ -25534,7 +25534,7 @@
       <c r="D591" s="28" t="n"/>
       <c r="E591" s="34" t="n"/>
       <c r="F591" s="25">
-        <f>IF(OR(B591="",E591=""),"",E591*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B591,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B591="",E591=""),"",IFERROR(E591*INDEX(Config!$D$11:$D$20,MATCH(B591,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G591" s="24">
@@ -25554,7 +25554,7 @@
       <c r="D592" s="28" t="n"/>
       <c r="E592" s="34" t="n"/>
       <c r="F592" s="25">
-        <f>IF(OR(B592="",E592=""),"",E592*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B592,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B592="",E592=""),"",IFERROR(E592*INDEX(Config!$D$11:$D$20,MATCH(B592,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G592" s="24">
@@ -25574,7 +25574,7 @@
       <c r="D593" s="28" t="n"/>
       <c r="E593" s="34" t="n"/>
       <c r="F593" s="25">
-        <f>IF(OR(B593="",E593=""),"",E593*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B593,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B593="",E593=""),"",IFERROR(E593*INDEX(Config!$D$11:$D$20,MATCH(B593,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G593" s="24">
@@ -25594,7 +25594,7 @@
       <c r="D594" s="28" t="n"/>
       <c r="E594" s="34" t="n"/>
       <c r="F594" s="25">
-        <f>IF(OR(B594="",E594=""),"",E594*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B594,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B594="",E594=""),"",IFERROR(E594*INDEX(Config!$D$11:$D$20,MATCH(B594,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G594" s="24">
@@ -25614,7 +25614,7 @@
       <c r="D595" s="28" t="n"/>
       <c r="E595" s="34" t="n"/>
       <c r="F595" s="25">
-        <f>IF(OR(B595="",E595=""),"",E595*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B595,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B595="",E595=""),"",IFERROR(E595*INDEX(Config!$D$11:$D$20,MATCH(B595,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G595" s="24">
@@ -25634,7 +25634,7 @@
       <c r="D596" s="28" t="n"/>
       <c r="E596" s="34" t="n"/>
       <c r="F596" s="25">
-        <f>IF(OR(B596="",E596=""),"",E596*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B596,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B596="",E596=""),"",IFERROR(E596*INDEX(Config!$D$11:$D$20,MATCH(B596,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G596" s="24">
@@ -25654,7 +25654,7 @@
       <c r="D597" s="28" t="n"/>
       <c r="E597" s="34" t="n"/>
       <c r="F597" s="25">
-        <f>IF(OR(B597="",E597=""),"",E597*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B597,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B597="",E597=""),"",IFERROR(E597*INDEX(Config!$D$11:$D$20,MATCH(B597,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G597" s="24">
@@ -25674,7 +25674,7 @@
       <c r="D598" s="28" t="n"/>
       <c r="E598" s="34" t="n"/>
       <c r="F598" s="25">
-        <f>IF(OR(B598="",E598=""),"",E598*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B598,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B598="",E598=""),"",IFERROR(E598*INDEX(Config!$D$11:$D$20,MATCH(B598,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G598" s="24">
@@ -25694,7 +25694,7 @@
       <c r="D599" s="28" t="n"/>
       <c r="E599" s="34" t="n"/>
       <c r="F599" s="25">
-        <f>IF(OR(B599="",E599=""),"",E599*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B599,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B599="",E599=""),"",IFERROR(E599*INDEX(Config!$D$11:$D$20,MATCH(B599,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G599" s="24">
@@ -25714,7 +25714,7 @@
       <c r="D600" s="28" t="n"/>
       <c r="E600" s="34" t="n"/>
       <c r="F600" s="25">
-        <f>IF(OR(B600="",E600=""),"",E600*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B600,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B600="",E600=""),"",IFERROR(E600*INDEX(Config!$D$11:$D$20,MATCH(B600,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G600" s="24">
@@ -25734,7 +25734,7 @@
       <c r="D601" s="28" t="n"/>
       <c r="E601" s="34" t="n"/>
       <c r="F601" s="25">
-        <f>IF(OR(B601="",E601=""),"",E601*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B601,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B601="",E601=""),"",IFERROR(E601*INDEX(Config!$D$11:$D$20,MATCH(B601,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G601" s="24">
@@ -25754,7 +25754,7 @@
       <c r="D602" s="28" t="n"/>
       <c r="E602" s="34" t="n"/>
       <c r="F602" s="25">
-        <f>IF(OR(B602="",E602=""),"",E602*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B602,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B602="",E602=""),"",IFERROR(E602*INDEX(Config!$D$11:$D$20,MATCH(B602,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G602" s="24">
@@ -25774,7 +25774,7 @@
       <c r="D603" s="28" t="n"/>
       <c r="E603" s="34" t="n"/>
       <c r="F603" s="25">
-        <f>IF(OR(B603="",E603=""),"",E603*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B603,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B603="",E603=""),"",IFERROR(E603*INDEX(Config!$D$11:$D$20,MATCH(B603,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G603" s="24">
@@ -25794,7 +25794,7 @@
       <c r="D604" s="28" t="n"/>
       <c r="E604" s="34" t="n"/>
       <c r="F604" s="25">
-        <f>IF(OR(B604="",E604=""),"",E604*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B604,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B604="",E604=""),"",IFERROR(E604*INDEX(Config!$D$11:$D$20,MATCH(B604,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G604" s="24">
@@ -25814,7 +25814,7 @@
       <c r="D605" s="28" t="n"/>
       <c r="E605" s="34" t="n"/>
       <c r="F605" s="25">
-        <f>IF(OR(B605="",E605=""),"",E605*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B605,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B605="",E605=""),"",IFERROR(E605*INDEX(Config!$D$11:$D$20,MATCH(B605,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G605" s="24">
@@ -25834,7 +25834,7 @@
       <c r="D606" s="28" t="n"/>
       <c r="E606" s="34" t="n"/>
       <c r="F606" s="25">
-        <f>IF(OR(B606="",E606=""),"",E606*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B606,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B606="",E606=""),"",IFERROR(E606*INDEX(Config!$D$11:$D$20,MATCH(B606,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G606" s="24">
@@ -25854,7 +25854,7 @@
       <c r="D607" s="28" t="n"/>
       <c r="E607" s="34" t="n"/>
       <c r="F607" s="25">
-        <f>IF(OR(B607="",E607=""),"",E607*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B607,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B607="",E607=""),"",IFERROR(E607*INDEX(Config!$D$11:$D$20,MATCH(B607,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G607" s="24">
@@ -25874,7 +25874,7 @@
       <c r="D608" s="28" t="n"/>
       <c r="E608" s="34" t="n"/>
       <c r="F608" s="25">
-        <f>IF(OR(B608="",E608=""),"",E608*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B608,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B608="",E608=""),"",IFERROR(E608*INDEX(Config!$D$11:$D$20,MATCH(B608,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G608" s="24">
@@ -25894,7 +25894,7 @@
       <c r="D609" s="28" t="n"/>
       <c r="E609" s="34" t="n"/>
       <c r="F609" s="25">
-        <f>IF(OR(B609="",E609=""),"",E609*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B609,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B609="",E609=""),"",IFERROR(E609*INDEX(Config!$D$11:$D$20,MATCH(B609,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G609" s="24">
@@ -25914,7 +25914,7 @@
       <c r="D610" s="28" t="n"/>
       <c r="E610" s="34" t="n"/>
       <c r="F610" s="25">
-        <f>IF(OR(B610="",E610=""),"",E610*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B610,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B610="",E610=""),"",IFERROR(E610*INDEX(Config!$D$11:$D$20,MATCH(B610,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G610" s="24">
@@ -25934,7 +25934,7 @@
       <c r="D611" s="28" t="n"/>
       <c r="E611" s="34" t="n"/>
       <c r="F611" s="25">
-        <f>IF(OR(B611="",E611=""),"",E611*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B611,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B611="",E611=""),"",IFERROR(E611*INDEX(Config!$D$11:$D$20,MATCH(B611,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G611" s="24">
@@ -25954,7 +25954,7 @@
       <c r="D612" s="28" t="n"/>
       <c r="E612" s="34" t="n"/>
       <c r="F612" s="25">
-        <f>IF(OR(B612="",E612=""),"",E612*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B612,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B612="",E612=""),"",IFERROR(E612*INDEX(Config!$D$11:$D$20,MATCH(B612,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G612" s="24">
@@ -25974,7 +25974,7 @@
       <c r="D613" s="28" t="n"/>
       <c r="E613" s="34" t="n"/>
       <c r="F613" s="25">
-        <f>IF(OR(B613="",E613=""),"",E613*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B613,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B613="",E613=""),"",IFERROR(E613*INDEX(Config!$D$11:$D$20,MATCH(B613,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G613" s="24">
@@ -25994,7 +25994,7 @@
       <c r="D614" s="28" t="n"/>
       <c r="E614" s="34" t="n"/>
       <c r="F614" s="25">
-        <f>IF(OR(B614="",E614=""),"",E614*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B614,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B614="",E614=""),"",IFERROR(E614*INDEX(Config!$D$11:$D$20,MATCH(B614,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G614" s="24">
@@ -26014,7 +26014,7 @@
       <c r="D615" s="28" t="n"/>
       <c r="E615" s="34" t="n"/>
       <c r="F615" s="25">
-        <f>IF(OR(B615="",E615=""),"",E615*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B615,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B615="",E615=""),"",IFERROR(E615*INDEX(Config!$D$11:$D$20,MATCH(B615,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G615" s="24">
@@ -26034,7 +26034,7 @@
       <c r="D616" s="28" t="n"/>
       <c r="E616" s="34" t="n"/>
       <c r="F616" s="25">
-        <f>IF(OR(B616="",E616=""),"",E616*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B616,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B616="",E616=""),"",IFERROR(E616*INDEX(Config!$D$11:$D$20,MATCH(B616,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G616" s="24">
@@ -26054,7 +26054,7 @@
       <c r="D617" s="28" t="n"/>
       <c r="E617" s="34" t="n"/>
       <c r="F617" s="25">
-        <f>IF(OR(B617="",E617=""),"",E617*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B617,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B617="",E617=""),"",IFERROR(E617*INDEX(Config!$D$11:$D$20,MATCH(B617,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G617" s="24">
@@ -26074,7 +26074,7 @@
       <c r="D618" s="28" t="n"/>
       <c r="E618" s="34" t="n"/>
       <c r="F618" s="25">
-        <f>IF(OR(B618="",E618=""),"",E618*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B618,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B618="",E618=""),"",IFERROR(E618*INDEX(Config!$D$11:$D$20,MATCH(B618,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G618" s="24">
@@ -26094,7 +26094,7 @@
       <c r="D619" s="28" t="n"/>
       <c r="E619" s="34" t="n"/>
       <c r="F619" s="25">
-        <f>IF(OR(B619="",E619=""),"",E619*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B619,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B619="",E619=""),"",IFERROR(E619*INDEX(Config!$D$11:$D$20,MATCH(B619,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G619" s="24">
@@ -26114,7 +26114,7 @@
       <c r="D620" s="28" t="n"/>
       <c r="E620" s="34" t="n"/>
       <c r="F620" s="25">
-        <f>IF(OR(B620="",E620=""),"",E620*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B620,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B620="",E620=""),"",IFERROR(E620*INDEX(Config!$D$11:$D$20,MATCH(B620,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G620" s="24">
@@ -26134,7 +26134,7 @@
       <c r="D621" s="28" t="n"/>
       <c r="E621" s="34" t="n"/>
       <c r="F621" s="25">
-        <f>IF(OR(B621="",E621=""),"",E621*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B621,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B621="",E621=""),"",IFERROR(E621*INDEX(Config!$D$11:$D$20,MATCH(B621,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G621" s="24">
@@ -26154,7 +26154,7 @@
       <c r="D622" s="28" t="n"/>
       <c r="E622" s="34" t="n"/>
       <c r="F622" s="25">
-        <f>IF(OR(B622="",E622=""),"",E622*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B622,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B622="",E622=""),"",IFERROR(E622*INDEX(Config!$D$11:$D$20,MATCH(B622,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G622" s="24">
@@ -26174,7 +26174,7 @@
       <c r="D623" s="28" t="n"/>
       <c r="E623" s="34" t="n"/>
       <c r="F623" s="25">
-        <f>IF(OR(B623="",E623=""),"",E623*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B623,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B623="",E623=""),"",IFERROR(E623*INDEX(Config!$D$11:$D$20,MATCH(B623,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G623" s="24">
@@ -26194,7 +26194,7 @@
       <c r="D624" s="28" t="n"/>
       <c r="E624" s="34" t="n"/>
       <c r="F624" s="25">
-        <f>IF(OR(B624="",E624=""),"",E624*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B624,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B624="",E624=""),"",IFERROR(E624*INDEX(Config!$D$11:$D$20,MATCH(B624,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G624" s="24">
@@ -26214,7 +26214,7 @@
       <c r="D625" s="28" t="n"/>
       <c r="E625" s="34" t="n"/>
       <c r="F625" s="25">
-        <f>IF(OR(B625="",E625=""),"",E625*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B625,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B625="",E625=""),"",IFERROR(E625*INDEX(Config!$D$11:$D$20,MATCH(B625,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G625" s="24">
@@ -26234,7 +26234,7 @@
       <c r="D626" s="28" t="n"/>
       <c r="E626" s="34" t="n"/>
       <c r="F626" s="25">
-        <f>IF(OR(B626="",E626=""),"",E626*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B626,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B626="",E626=""),"",IFERROR(E626*INDEX(Config!$D$11:$D$20,MATCH(B626,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G626" s="24">
@@ -26254,7 +26254,7 @@
       <c r="D627" s="28" t="n"/>
       <c r="E627" s="34" t="n"/>
       <c r="F627" s="25">
-        <f>IF(OR(B627="",E627=""),"",E627*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B627,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B627="",E627=""),"",IFERROR(E627*INDEX(Config!$D$11:$D$20,MATCH(B627,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G627" s="24">
@@ -26274,7 +26274,7 @@
       <c r="D628" s="28" t="n"/>
       <c r="E628" s="34" t="n"/>
       <c r="F628" s="25">
-        <f>IF(OR(B628="",E628=""),"",E628*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B628,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B628="",E628=""),"",IFERROR(E628*INDEX(Config!$D$11:$D$20,MATCH(B628,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G628" s="24">
@@ -26294,7 +26294,7 @@
       <c r="D629" s="28" t="n"/>
       <c r="E629" s="34" t="n"/>
       <c r="F629" s="25">
-        <f>IF(OR(B629="",E629=""),"",E629*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B629,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B629="",E629=""),"",IFERROR(E629*INDEX(Config!$D$11:$D$20,MATCH(B629,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G629" s="24">
@@ -26314,7 +26314,7 @@
       <c r="D630" s="28" t="n"/>
       <c r="E630" s="34" t="n"/>
       <c r="F630" s="25">
-        <f>IF(OR(B630="",E630=""),"",E630*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B630,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B630="",E630=""),"",IFERROR(E630*INDEX(Config!$D$11:$D$20,MATCH(B630,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G630" s="24">
@@ -26334,7 +26334,7 @@
       <c r="D631" s="28" t="n"/>
       <c r="E631" s="34" t="n"/>
       <c r="F631" s="25">
-        <f>IF(OR(B631="",E631=""),"",E631*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B631,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B631="",E631=""),"",IFERROR(E631*INDEX(Config!$D$11:$D$20,MATCH(B631,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G631" s="24">
@@ -26354,7 +26354,7 @@
       <c r="D632" s="28" t="n"/>
       <c r="E632" s="34" t="n"/>
       <c r="F632" s="25">
-        <f>IF(OR(B632="",E632=""),"",E632*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B632,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B632="",E632=""),"",IFERROR(E632*INDEX(Config!$D$11:$D$20,MATCH(B632,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G632" s="24">
@@ -26374,7 +26374,7 @@
       <c r="D633" s="28" t="n"/>
       <c r="E633" s="34" t="n"/>
       <c r="F633" s="25">
-        <f>IF(OR(B633="",E633=""),"",E633*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B633,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B633="",E633=""),"",IFERROR(E633*INDEX(Config!$D$11:$D$20,MATCH(B633,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G633" s="24">
@@ -26394,7 +26394,7 @@
       <c r="D634" s="28" t="n"/>
       <c r="E634" s="34" t="n"/>
       <c r="F634" s="25">
-        <f>IF(OR(B634="",E634=""),"",E634*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B634,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B634="",E634=""),"",IFERROR(E634*INDEX(Config!$D$11:$D$20,MATCH(B634,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G634" s="24">
@@ -26414,7 +26414,7 @@
       <c r="D635" s="28" t="n"/>
       <c r="E635" s="34" t="n"/>
       <c r="F635" s="25">
-        <f>IF(OR(B635="",E635=""),"",E635*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B635,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B635="",E635=""),"",IFERROR(E635*INDEX(Config!$D$11:$D$20,MATCH(B635,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G635" s="24">
@@ -26434,7 +26434,7 @@
       <c r="D636" s="28" t="n"/>
       <c r="E636" s="34" t="n"/>
       <c r="F636" s="25">
-        <f>IF(OR(B636="",E636=""),"",E636*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B636,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B636="",E636=""),"",IFERROR(E636*INDEX(Config!$D$11:$D$20,MATCH(B636,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G636" s="24">
@@ -26454,7 +26454,7 @@
       <c r="D637" s="28" t="n"/>
       <c r="E637" s="34" t="n"/>
       <c r="F637" s="25">
-        <f>IF(OR(B637="",E637=""),"",E637*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B637,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B637="",E637=""),"",IFERROR(E637*INDEX(Config!$D$11:$D$20,MATCH(B637,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G637" s="24">
@@ -26474,7 +26474,7 @@
       <c r="D638" s="28" t="n"/>
       <c r="E638" s="34" t="n"/>
       <c r="F638" s="25">
-        <f>IF(OR(B638="",E638=""),"",E638*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B638,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B638="",E638=""),"",IFERROR(E638*INDEX(Config!$D$11:$D$20,MATCH(B638,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G638" s="24">
@@ -26494,7 +26494,7 @@
       <c r="D639" s="28" t="n"/>
       <c r="E639" s="34" t="n"/>
       <c r="F639" s="25">
-        <f>IF(OR(B639="",E639=""),"",E639*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B639,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B639="",E639=""),"",IFERROR(E639*INDEX(Config!$D$11:$D$20,MATCH(B639,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G639" s="24">
@@ -26514,7 +26514,7 @@
       <c r="D640" s="28" t="n"/>
       <c r="E640" s="34" t="n"/>
       <c r="F640" s="25">
-        <f>IF(OR(B640="",E640=""),"",E640*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B640,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B640="",E640=""),"",IFERROR(E640*INDEX(Config!$D$11:$D$20,MATCH(B640,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G640" s="24">
@@ -26534,7 +26534,7 @@
       <c r="D641" s="28" t="n"/>
       <c r="E641" s="34" t="n"/>
       <c r="F641" s="25">
-        <f>IF(OR(B641="",E641=""),"",E641*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B641,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B641="",E641=""),"",IFERROR(E641*INDEX(Config!$D$11:$D$20,MATCH(B641,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G641" s="24">
@@ -26554,7 +26554,7 @@
       <c r="D642" s="28" t="n"/>
       <c r="E642" s="34" t="n"/>
       <c r="F642" s="25">
-        <f>IF(OR(B642="",E642=""),"",E642*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B642,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B642="",E642=""),"",IFERROR(E642*INDEX(Config!$D$11:$D$20,MATCH(B642,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G642" s="24">
@@ -26574,7 +26574,7 @@
       <c r="D643" s="28" t="n"/>
       <c r="E643" s="34" t="n"/>
       <c r="F643" s="25">
-        <f>IF(OR(B643="",E643=""),"",E643*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B643,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B643="",E643=""),"",IFERROR(E643*INDEX(Config!$D$11:$D$20,MATCH(B643,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G643" s="24">
@@ -26594,7 +26594,7 @@
       <c r="D644" s="28" t="n"/>
       <c r="E644" s="34" t="n"/>
       <c r="F644" s="25">
-        <f>IF(OR(B644="",E644=""),"",E644*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B644,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B644="",E644=""),"",IFERROR(E644*INDEX(Config!$D$11:$D$20,MATCH(B644,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G644" s="24">
@@ -26614,7 +26614,7 @@
       <c r="D645" s="28" t="n"/>
       <c r="E645" s="34" t="n"/>
       <c r="F645" s="25">
-        <f>IF(OR(B645="",E645=""),"",E645*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B645,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B645="",E645=""),"",IFERROR(E645*INDEX(Config!$D$11:$D$20,MATCH(B645,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G645" s="24">
@@ -26634,7 +26634,7 @@
       <c r="D646" s="28" t="n"/>
       <c r="E646" s="34" t="n"/>
       <c r="F646" s="25">
-        <f>IF(OR(B646="",E646=""),"",E646*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B646,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B646="",E646=""),"",IFERROR(E646*INDEX(Config!$D$11:$D$20,MATCH(B646,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G646" s="24">
@@ -26654,7 +26654,7 @@
       <c r="D647" s="28" t="n"/>
       <c r="E647" s="34" t="n"/>
       <c r="F647" s="25">
-        <f>IF(OR(B647="",E647=""),"",E647*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B647,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B647="",E647=""),"",IFERROR(E647*INDEX(Config!$D$11:$D$20,MATCH(B647,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G647" s="24">
@@ -26674,7 +26674,7 @@
       <c r="D648" s="28" t="n"/>
       <c r="E648" s="34" t="n"/>
       <c r="F648" s="25">
-        <f>IF(OR(B648="",E648=""),"",E648*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B648,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B648="",E648=""),"",IFERROR(E648*INDEX(Config!$D$11:$D$20,MATCH(B648,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G648" s="24">
@@ -26694,7 +26694,7 @@
       <c r="D649" s="28" t="n"/>
       <c r="E649" s="34" t="n"/>
       <c r="F649" s="25">
-        <f>IF(OR(B649="",E649=""),"",E649*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B649,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B649="",E649=""),"",IFERROR(E649*INDEX(Config!$D$11:$D$20,MATCH(B649,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G649" s="24">
@@ -26714,7 +26714,7 @@
       <c r="D650" s="28" t="n"/>
       <c r="E650" s="34" t="n"/>
       <c r="F650" s="25">
-        <f>IF(OR(B650="",E650=""),"",E650*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B650,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B650="",E650=""),"",IFERROR(E650*INDEX(Config!$D$11:$D$20,MATCH(B650,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G650" s="24">
@@ -26734,7 +26734,7 @@
       <c r="D651" s="28" t="n"/>
       <c r="E651" s="34" t="n"/>
       <c r="F651" s="25">
-        <f>IF(OR(B651="",E651=""),"",E651*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B651,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B651="",E651=""),"",IFERROR(E651*INDEX(Config!$D$11:$D$20,MATCH(B651,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G651" s="24">
@@ -26754,7 +26754,7 @@
       <c r="D652" s="28" t="n"/>
       <c r="E652" s="34" t="n"/>
       <c r="F652" s="25">
-        <f>IF(OR(B652="",E652=""),"",E652*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B652,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B652="",E652=""),"",IFERROR(E652*INDEX(Config!$D$11:$D$20,MATCH(B652,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G652" s="24">
@@ -26774,7 +26774,7 @@
       <c r="D653" s="28" t="n"/>
       <c r="E653" s="34" t="n"/>
       <c r="F653" s="25">
-        <f>IF(OR(B653="",E653=""),"",E653*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B653,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B653="",E653=""),"",IFERROR(E653*INDEX(Config!$D$11:$D$20,MATCH(B653,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G653" s="24">
@@ -26794,7 +26794,7 @@
       <c r="D654" s="28" t="n"/>
       <c r="E654" s="34" t="n"/>
       <c r="F654" s="25">
-        <f>IF(OR(B654="",E654=""),"",E654*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B654,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B654="",E654=""),"",IFERROR(E654*INDEX(Config!$D$11:$D$20,MATCH(B654,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G654" s="24">
@@ -26814,7 +26814,7 @@
       <c r="D655" s="28" t="n"/>
       <c r="E655" s="34" t="n"/>
       <c r="F655" s="25">
-        <f>IF(OR(B655="",E655=""),"",E655*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B655,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B655="",E655=""),"",IFERROR(E655*INDEX(Config!$D$11:$D$20,MATCH(B655,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G655" s="24">
@@ -26834,7 +26834,7 @@
       <c r="D656" s="28" t="n"/>
       <c r="E656" s="34" t="n"/>
       <c r="F656" s="25">
-        <f>IF(OR(B656="",E656=""),"",E656*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B656,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B656="",E656=""),"",IFERROR(E656*INDEX(Config!$D$11:$D$20,MATCH(B656,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G656" s="24">
@@ -26854,7 +26854,7 @@
       <c r="D657" s="28" t="n"/>
       <c r="E657" s="34" t="n"/>
       <c r="F657" s="25">
-        <f>IF(OR(B657="",E657=""),"",E657*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B657,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B657="",E657=""),"",IFERROR(E657*INDEX(Config!$D$11:$D$20,MATCH(B657,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G657" s="24">
@@ -26874,7 +26874,7 @@
       <c r="D658" s="28" t="n"/>
       <c r="E658" s="34" t="n"/>
       <c r="F658" s="25">
-        <f>IF(OR(B658="",E658=""),"",E658*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B658,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B658="",E658=""),"",IFERROR(E658*INDEX(Config!$D$11:$D$20,MATCH(B658,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G658" s="24">
@@ -26894,7 +26894,7 @@
       <c r="D659" s="28" t="n"/>
       <c r="E659" s="34" t="n"/>
       <c r="F659" s="25">
-        <f>IF(OR(B659="",E659=""),"",E659*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B659,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B659="",E659=""),"",IFERROR(E659*INDEX(Config!$D$11:$D$20,MATCH(B659,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G659" s="24">
@@ -26914,7 +26914,7 @@
       <c r="D660" s="28" t="n"/>
       <c r="E660" s="34" t="n"/>
       <c r="F660" s="25">
-        <f>IF(OR(B660="",E660=""),"",E660*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B660,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B660="",E660=""),"",IFERROR(E660*INDEX(Config!$D$11:$D$20,MATCH(B660,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G660" s="24">
@@ -26934,7 +26934,7 @@
       <c r="D661" s="28" t="n"/>
       <c r="E661" s="34" t="n"/>
       <c r="F661" s="25">
-        <f>IF(OR(B661="",E661=""),"",E661*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B661,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B661="",E661=""),"",IFERROR(E661*INDEX(Config!$D$11:$D$20,MATCH(B661,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G661" s="24">
@@ -26954,7 +26954,7 @@
       <c r="D662" s="28" t="n"/>
       <c r="E662" s="34" t="n"/>
       <c r="F662" s="25">
-        <f>IF(OR(B662="",E662=""),"",E662*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B662,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B662="",E662=""),"",IFERROR(E662*INDEX(Config!$D$11:$D$20,MATCH(B662,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G662" s="24">
@@ -26974,7 +26974,7 @@
       <c r="D663" s="28" t="n"/>
       <c r="E663" s="34" t="n"/>
       <c r="F663" s="25">
-        <f>IF(OR(B663="",E663=""),"",E663*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B663,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B663="",E663=""),"",IFERROR(E663*INDEX(Config!$D$11:$D$20,MATCH(B663,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G663" s="24">
@@ -26994,7 +26994,7 @@
       <c r="D664" s="28" t="n"/>
       <c r="E664" s="34" t="n"/>
       <c r="F664" s="25">
-        <f>IF(OR(B664="",E664=""),"",E664*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B664,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B664="",E664=""),"",IFERROR(E664*INDEX(Config!$D$11:$D$20,MATCH(B664,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G664" s="24">
@@ -27014,7 +27014,7 @@
       <c r="D665" s="28" t="n"/>
       <c r="E665" s="34" t="n"/>
       <c r="F665" s="25">
-        <f>IF(OR(B665="",E665=""),"",E665*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B665,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B665="",E665=""),"",IFERROR(E665*INDEX(Config!$D$11:$D$20,MATCH(B665,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G665" s="24">
@@ -27034,7 +27034,7 @@
       <c r="D666" s="28" t="n"/>
       <c r="E666" s="34" t="n"/>
       <c r="F666" s="25">
-        <f>IF(OR(B666="",E666=""),"",E666*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B666,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B666="",E666=""),"",IFERROR(E666*INDEX(Config!$D$11:$D$20,MATCH(B666,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G666" s="24">
@@ -27054,7 +27054,7 @@
       <c r="D667" s="28" t="n"/>
       <c r="E667" s="34" t="n"/>
       <c r="F667" s="25">
-        <f>IF(OR(B667="",E667=""),"",E667*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B667,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B667="",E667=""),"",IFERROR(E667*INDEX(Config!$D$11:$D$20,MATCH(B667,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G667" s="24">
@@ -27074,7 +27074,7 @@
       <c r="D668" s="28" t="n"/>
       <c r="E668" s="34" t="n"/>
       <c r="F668" s="25">
-        <f>IF(OR(B668="",E668=""),"",E668*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B668,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B668="",E668=""),"",IFERROR(E668*INDEX(Config!$D$11:$D$20,MATCH(B668,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G668" s="24">
@@ -27094,7 +27094,7 @@
       <c r="D669" s="28" t="n"/>
       <c r="E669" s="34" t="n"/>
       <c r="F669" s="25">
-        <f>IF(OR(B669="",E669=""),"",E669*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B669,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B669="",E669=""),"",IFERROR(E669*INDEX(Config!$D$11:$D$20,MATCH(B669,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G669" s="24">
@@ -27114,7 +27114,7 @@
       <c r="D670" s="28" t="n"/>
       <c r="E670" s="34" t="n"/>
       <c r="F670" s="25">
-        <f>IF(OR(B670="",E670=""),"",E670*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B670,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B670="",E670=""),"",IFERROR(E670*INDEX(Config!$D$11:$D$20,MATCH(B670,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G670" s="24">
@@ -27134,7 +27134,7 @@
       <c r="D671" s="28" t="n"/>
       <c r="E671" s="34" t="n"/>
       <c r="F671" s="25">
-        <f>IF(OR(B671="",E671=""),"",E671*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B671,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B671="",E671=""),"",IFERROR(E671*INDEX(Config!$D$11:$D$20,MATCH(B671,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G671" s="24">
@@ -27154,7 +27154,7 @@
       <c r="D672" s="28" t="n"/>
       <c r="E672" s="34" t="n"/>
       <c r="F672" s="25">
-        <f>IF(OR(B672="",E672=""),"",E672*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B672,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B672="",E672=""),"",IFERROR(E672*INDEX(Config!$D$11:$D$20,MATCH(B672,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G672" s="24">
@@ -27174,7 +27174,7 @@
       <c r="D673" s="28" t="n"/>
       <c r="E673" s="34" t="n"/>
       <c r="F673" s="25">
-        <f>IF(OR(B673="",E673=""),"",E673*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B673,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B673="",E673=""),"",IFERROR(E673*INDEX(Config!$D$11:$D$20,MATCH(B673,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G673" s="24">
@@ -27194,7 +27194,7 @@
       <c r="D674" s="28" t="n"/>
       <c r="E674" s="34" t="n"/>
       <c r="F674" s="25">
-        <f>IF(OR(B674="",E674=""),"",E674*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B674,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B674="",E674=""),"",IFERROR(E674*INDEX(Config!$D$11:$D$20,MATCH(B674,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G674" s="24">
@@ -27214,7 +27214,7 @@
       <c r="D675" s="28" t="n"/>
       <c r="E675" s="34" t="n"/>
       <c r="F675" s="25">
-        <f>IF(OR(B675="",E675=""),"",E675*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B675,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B675="",E675=""),"",IFERROR(E675*INDEX(Config!$D$11:$D$20,MATCH(B675,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G675" s="24">
@@ -27234,7 +27234,7 @@
       <c r="D676" s="28" t="n"/>
       <c r="E676" s="34" t="n"/>
       <c r="F676" s="25">
-        <f>IF(OR(B676="",E676=""),"",E676*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B676,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B676="",E676=""),"",IFERROR(E676*INDEX(Config!$D$11:$D$20,MATCH(B676,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G676" s="24">
@@ -27254,7 +27254,7 @@
       <c r="D677" s="28" t="n"/>
       <c r="E677" s="34" t="n"/>
       <c r="F677" s="25">
-        <f>IF(OR(B677="",E677=""),"",E677*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B677,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B677="",E677=""),"",IFERROR(E677*INDEX(Config!$D$11:$D$20,MATCH(B677,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G677" s="24">
@@ -27274,7 +27274,7 @@
       <c r="D678" s="28" t="n"/>
       <c r="E678" s="34" t="n"/>
       <c r="F678" s="25">
-        <f>IF(OR(B678="",E678=""),"",E678*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B678,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B678="",E678=""),"",IFERROR(E678*INDEX(Config!$D$11:$D$20,MATCH(B678,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G678" s="24">
@@ -27294,7 +27294,7 @@
       <c r="D679" s="28" t="n"/>
       <c r="E679" s="34" t="n"/>
       <c r="F679" s="25">
-        <f>IF(OR(B679="",E679=""),"",E679*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B679,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B679="",E679=""),"",IFERROR(E679*INDEX(Config!$D$11:$D$20,MATCH(B679,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G679" s="24">
@@ -27314,7 +27314,7 @@
       <c r="D680" s="28" t="n"/>
       <c r="E680" s="34" t="n"/>
       <c r="F680" s="25">
-        <f>IF(OR(B680="",E680=""),"",E680*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B680,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B680="",E680=""),"",IFERROR(E680*INDEX(Config!$D$11:$D$20,MATCH(B680,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G680" s="24">
@@ -27334,7 +27334,7 @@
       <c r="D681" s="28" t="n"/>
       <c r="E681" s="34" t="n"/>
       <c r="F681" s="25">
-        <f>IF(OR(B681="",E681=""),"",E681*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B681,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B681="",E681=""),"",IFERROR(E681*INDEX(Config!$D$11:$D$20,MATCH(B681,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G681" s="24">
@@ -27354,7 +27354,7 @@
       <c r="D682" s="28" t="n"/>
       <c r="E682" s="34" t="n"/>
       <c r="F682" s="25">
-        <f>IF(OR(B682="",E682=""),"",E682*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B682,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B682="",E682=""),"",IFERROR(E682*INDEX(Config!$D$11:$D$20,MATCH(B682,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G682" s="24">
@@ -27374,7 +27374,7 @@
       <c r="D683" s="28" t="n"/>
       <c r="E683" s="34" t="n"/>
       <c r="F683" s="25">
-        <f>IF(OR(B683="",E683=""),"",E683*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B683,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B683="",E683=""),"",IFERROR(E683*INDEX(Config!$D$11:$D$20,MATCH(B683,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G683" s="24">
@@ -27394,7 +27394,7 @@
       <c r="D684" s="28" t="n"/>
       <c r="E684" s="34" t="n"/>
       <c r="F684" s="25">
-        <f>IF(OR(B684="",E684=""),"",E684*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B684,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B684="",E684=""),"",IFERROR(E684*INDEX(Config!$D$11:$D$20,MATCH(B684,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G684" s="24">
@@ -27414,7 +27414,7 @@
       <c r="D685" s="28" t="n"/>
       <c r="E685" s="34" t="n"/>
       <c r="F685" s="25">
-        <f>IF(OR(B685="",E685=""),"",E685*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B685,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B685="",E685=""),"",IFERROR(E685*INDEX(Config!$D$11:$D$20,MATCH(B685,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G685" s="24">
@@ -27434,7 +27434,7 @@
       <c r="D686" s="28" t="n"/>
       <c r="E686" s="34" t="n"/>
       <c r="F686" s="25">
-        <f>IF(OR(B686="",E686=""),"",E686*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B686,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B686="",E686=""),"",IFERROR(E686*INDEX(Config!$D$11:$D$20,MATCH(B686,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G686" s="24">
@@ -27454,7 +27454,7 @@
       <c r="D687" s="28" t="n"/>
       <c r="E687" s="34" t="n"/>
       <c r="F687" s="25">
-        <f>IF(OR(B687="",E687=""),"",E687*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B687,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B687="",E687=""),"",IFERROR(E687*INDEX(Config!$D$11:$D$20,MATCH(B687,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G687" s="24">
@@ -27474,7 +27474,7 @@
       <c r="D688" s="28" t="n"/>
       <c r="E688" s="34" t="n"/>
       <c r="F688" s="25">
-        <f>IF(OR(B688="",E688=""),"",E688*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B688,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B688="",E688=""),"",IFERROR(E688*INDEX(Config!$D$11:$D$20,MATCH(B688,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G688" s="24">
@@ -27494,7 +27494,7 @@
       <c r="D689" s="28" t="n"/>
       <c r="E689" s="34" t="n"/>
       <c r="F689" s="25">
-        <f>IF(OR(B689="",E689=""),"",E689*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B689,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B689="",E689=""),"",IFERROR(E689*INDEX(Config!$D$11:$D$20,MATCH(B689,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G689" s="24">
@@ -27514,7 +27514,7 @@
       <c r="D690" s="28" t="n"/>
       <c r="E690" s="34" t="n"/>
       <c r="F690" s="25">
-        <f>IF(OR(B690="",E690=""),"",E690*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B690,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B690="",E690=""),"",IFERROR(E690*INDEX(Config!$D$11:$D$20,MATCH(B690,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G690" s="24">
@@ -27534,7 +27534,7 @@
       <c r="D691" s="28" t="n"/>
       <c r="E691" s="34" t="n"/>
       <c r="F691" s="25">
-        <f>IF(OR(B691="",E691=""),"",E691*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B691,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B691="",E691=""),"",IFERROR(E691*INDEX(Config!$D$11:$D$20,MATCH(B691,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G691" s="24">
@@ -27554,7 +27554,7 @@
       <c r="D692" s="28" t="n"/>
       <c r="E692" s="34" t="n"/>
       <c r="F692" s="25">
-        <f>IF(OR(B692="",E692=""),"",E692*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B692,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B692="",E692=""),"",IFERROR(E692*INDEX(Config!$D$11:$D$20,MATCH(B692,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G692" s="24">
@@ -27574,7 +27574,7 @@
       <c r="D693" s="28" t="n"/>
       <c r="E693" s="34" t="n"/>
       <c r="F693" s="25">
-        <f>IF(OR(B693="",E693=""),"",E693*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B693,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B693="",E693=""),"",IFERROR(E693*INDEX(Config!$D$11:$D$20,MATCH(B693,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G693" s="24">
@@ -27594,7 +27594,7 @@
       <c r="D694" s="28" t="n"/>
       <c r="E694" s="34" t="n"/>
       <c r="F694" s="25">
-        <f>IF(OR(B694="",E694=""),"",E694*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B694,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B694="",E694=""),"",IFERROR(E694*INDEX(Config!$D$11:$D$20,MATCH(B694,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G694" s="24">
@@ -27614,7 +27614,7 @@
       <c r="D695" s="28" t="n"/>
       <c r="E695" s="34" t="n"/>
       <c r="F695" s="25">
-        <f>IF(OR(B695="",E695=""),"",E695*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B695,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B695="",E695=""),"",IFERROR(E695*INDEX(Config!$D$11:$D$20,MATCH(B695,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G695" s="24">
@@ -27634,7 +27634,7 @@
       <c r="D696" s="28" t="n"/>
       <c r="E696" s="34" t="n"/>
       <c r="F696" s="25">
-        <f>IF(OR(B696="",E696=""),"",E696*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B696,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B696="",E696=""),"",IFERROR(E696*INDEX(Config!$D$11:$D$20,MATCH(B696,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G696" s="24">
@@ -27654,7 +27654,7 @@
       <c r="D697" s="28" t="n"/>
       <c r="E697" s="34" t="n"/>
       <c r="F697" s="25">
-        <f>IF(OR(B697="",E697=""),"",E697*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B697,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B697="",E697=""),"",IFERROR(E697*INDEX(Config!$D$11:$D$20,MATCH(B697,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G697" s="24">
@@ -27674,7 +27674,7 @@
       <c r="D698" s="28" t="n"/>
       <c r="E698" s="34" t="n"/>
       <c r="F698" s="25">
-        <f>IF(OR(B698="",E698=""),"",E698*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B698,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B698="",E698=""),"",IFERROR(E698*INDEX(Config!$D$11:$D$20,MATCH(B698,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G698" s="24">
@@ -27694,7 +27694,7 @@
       <c r="D699" s="28" t="n"/>
       <c r="E699" s="34" t="n"/>
       <c r="F699" s="25">
-        <f>IF(OR(B699="",E699=""),"",E699*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B699,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B699="",E699=""),"",IFERROR(E699*INDEX(Config!$D$11:$D$20,MATCH(B699,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G699" s="24">
@@ -27714,7 +27714,7 @@
       <c r="D700" s="28" t="n"/>
       <c r="E700" s="34" t="n"/>
       <c r="F700" s="25">
-        <f>IF(OR(B700="",E700=""),"",E700*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B700,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B700="",E700=""),"",IFERROR(E700*INDEX(Config!$D$11:$D$20,MATCH(B700,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G700" s="24">
@@ -27734,7 +27734,7 @@
       <c r="D701" s="28" t="n"/>
       <c r="E701" s="34" t="n"/>
       <c r="F701" s="25">
-        <f>IF(OR(B701="",E701=""),"",E701*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B701,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B701="",E701=""),"",IFERROR(E701*INDEX(Config!$D$11:$D$20,MATCH(B701,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G701" s="24">
@@ -27754,7 +27754,7 @@
       <c r="D702" s="28" t="n"/>
       <c r="E702" s="34" t="n"/>
       <c r="F702" s="25">
-        <f>IF(OR(B702="",E702=""),"",E702*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B702,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B702="",E702=""),"",IFERROR(E702*INDEX(Config!$D$11:$D$20,MATCH(B702,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G702" s="24">
@@ -27774,7 +27774,7 @@
       <c r="D703" s="28" t="n"/>
       <c r="E703" s="34" t="n"/>
       <c r="F703" s="25">
-        <f>IF(OR(B703="",E703=""),"",E703*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B703,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B703="",E703=""),"",IFERROR(E703*INDEX(Config!$D$11:$D$20,MATCH(B703,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G703" s="24">
@@ -27794,7 +27794,7 @@
       <c r="D704" s="28" t="n"/>
       <c r="E704" s="34" t="n"/>
       <c r="F704" s="25">
-        <f>IF(OR(B704="",E704=""),"",E704*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B704,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B704="",E704=""),"",IFERROR(E704*INDEX(Config!$D$11:$D$20,MATCH(B704,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G704" s="24">
@@ -27814,7 +27814,7 @@
       <c r="D705" s="28" t="n"/>
       <c r="E705" s="34" t="n"/>
       <c r="F705" s="25">
-        <f>IF(OR(B705="",E705=""),"",E705*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B705,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B705="",E705=""),"",IFERROR(E705*INDEX(Config!$D$11:$D$20,MATCH(B705,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G705" s="24">
@@ -27834,7 +27834,7 @@
       <c r="D706" s="28" t="n"/>
       <c r="E706" s="34" t="n"/>
       <c r="F706" s="25">
-        <f>IF(OR(B706="",E706=""),"",E706*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B706,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B706="",E706=""),"",IFERROR(E706*INDEX(Config!$D$11:$D$20,MATCH(B706,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G706" s="24">
@@ -27854,7 +27854,7 @@
       <c r="D707" s="28" t="n"/>
       <c r="E707" s="34" t="n"/>
       <c r="F707" s="25">
-        <f>IF(OR(B707="",E707=""),"",E707*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B707,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B707="",E707=""),"",IFERROR(E707*INDEX(Config!$D$11:$D$20,MATCH(B707,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G707" s="24">
@@ -27874,7 +27874,7 @@
       <c r="D708" s="28" t="n"/>
       <c r="E708" s="34" t="n"/>
       <c r="F708" s="25">
-        <f>IF(OR(B708="",E708=""),"",E708*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B708,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B708="",E708=""),"",IFERROR(E708*INDEX(Config!$D$11:$D$20,MATCH(B708,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G708" s="24">
@@ -27894,7 +27894,7 @@
       <c r="D709" s="28" t="n"/>
       <c r="E709" s="34" t="n"/>
       <c r="F709" s="25">
-        <f>IF(OR(B709="",E709=""),"",E709*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B709,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B709="",E709=""),"",IFERROR(E709*INDEX(Config!$D$11:$D$20,MATCH(B709,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G709" s="24">
@@ -27914,7 +27914,7 @@
       <c r="D710" s="28" t="n"/>
       <c r="E710" s="34" t="n"/>
       <c r="F710" s="25">
-        <f>IF(OR(B710="",E710=""),"",E710*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B710,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B710="",E710=""),"",IFERROR(E710*INDEX(Config!$D$11:$D$20,MATCH(B710,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G710" s="24">
@@ -27934,7 +27934,7 @@
       <c r="D711" s="28" t="n"/>
       <c r="E711" s="34" t="n"/>
       <c r="F711" s="25">
-        <f>IF(OR(B711="",E711=""),"",E711*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B711,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B711="",E711=""),"",IFERROR(E711*INDEX(Config!$D$11:$D$20,MATCH(B711,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G711" s="24">
@@ -27954,7 +27954,7 @@
       <c r="D712" s="28" t="n"/>
       <c r="E712" s="34" t="n"/>
       <c r="F712" s="25">
-        <f>IF(OR(B712="",E712=""),"",E712*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B712,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B712="",E712=""),"",IFERROR(E712*INDEX(Config!$D$11:$D$20,MATCH(B712,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G712" s="24">
@@ -27974,7 +27974,7 @@
       <c r="D713" s="28" t="n"/>
       <c r="E713" s="34" t="n"/>
       <c r="F713" s="25">
-        <f>IF(OR(B713="",E713=""),"",E713*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B713,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B713="",E713=""),"",IFERROR(E713*INDEX(Config!$D$11:$D$20,MATCH(B713,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G713" s="24">
@@ -27994,7 +27994,7 @@
       <c r="D714" s="28" t="n"/>
       <c r="E714" s="34" t="n"/>
       <c r="F714" s="25">
-        <f>IF(OR(B714="",E714=""),"",E714*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B714,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B714="",E714=""),"",IFERROR(E714*INDEX(Config!$D$11:$D$20,MATCH(B714,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G714" s="24">
@@ -28014,7 +28014,7 @@
       <c r="D715" s="28" t="n"/>
       <c r="E715" s="34" t="n"/>
       <c r="F715" s="25">
-        <f>IF(OR(B715="",E715=""),"",E715*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B715,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B715="",E715=""),"",IFERROR(E715*INDEX(Config!$D$11:$D$20,MATCH(B715,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G715" s="24">
@@ -28034,7 +28034,7 @@
       <c r="D716" s="28" t="n"/>
       <c r="E716" s="34" t="n"/>
       <c r="F716" s="25">
-        <f>IF(OR(B716="",E716=""),"",E716*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B716,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B716="",E716=""),"",IFERROR(E716*INDEX(Config!$D$11:$D$20,MATCH(B716,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G716" s="24">
@@ -28054,7 +28054,7 @@
       <c r="D717" s="28" t="n"/>
       <c r="E717" s="34" t="n"/>
       <c r="F717" s="25">
-        <f>IF(OR(B717="",E717=""),"",E717*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B717,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B717="",E717=""),"",IFERROR(E717*INDEX(Config!$D$11:$D$20,MATCH(B717,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G717" s="24">
@@ -28074,7 +28074,7 @@
       <c r="D718" s="28" t="n"/>
       <c r="E718" s="34" t="n"/>
       <c r="F718" s="25">
-        <f>IF(OR(B718="",E718=""),"",E718*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B718,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B718="",E718=""),"",IFERROR(E718*INDEX(Config!$D$11:$D$20,MATCH(B718,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G718" s="24">
@@ -28094,7 +28094,7 @@
       <c r="D719" s="28" t="n"/>
       <c r="E719" s="34" t="n"/>
       <c r="F719" s="25">
-        <f>IF(OR(B719="",E719=""),"",E719*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B719,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B719="",E719=""),"",IFERROR(E719*INDEX(Config!$D$11:$D$20,MATCH(B719,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G719" s="24">
@@ -28114,7 +28114,7 @@
       <c r="D720" s="28" t="n"/>
       <c r="E720" s="34" t="n"/>
       <c r="F720" s="25">
-        <f>IF(OR(B720="",E720=""),"",E720*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B720,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B720="",E720=""),"",IFERROR(E720*INDEX(Config!$D$11:$D$20,MATCH(B720,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G720" s="24">
@@ -28134,7 +28134,7 @@
       <c r="D721" s="28" t="n"/>
       <c r="E721" s="34" t="n"/>
       <c r="F721" s="25">
-        <f>IF(OR(B721="",E721=""),"",E721*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B721,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B721="",E721=""),"",IFERROR(E721*INDEX(Config!$D$11:$D$20,MATCH(B721,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G721" s="24">
@@ -28154,7 +28154,7 @@
       <c r="D722" s="28" t="n"/>
       <c r="E722" s="34" t="n"/>
       <c r="F722" s="25">
-        <f>IF(OR(B722="",E722=""),"",E722*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B722,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B722="",E722=""),"",IFERROR(E722*INDEX(Config!$D$11:$D$20,MATCH(B722,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G722" s="24">
@@ -28174,7 +28174,7 @@
       <c r="D723" s="28" t="n"/>
       <c r="E723" s="34" t="n"/>
       <c r="F723" s="25">
-        <f>IF(OR(B723="",E723=""),"",E723*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B723,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B723="",E723=""),"",IFERROR(E723*INDEX(Config!$D$11:$D$20,MATCH(B723,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G723" s="24">
@@ -28194,7 +28194,7 @@
       <c r="D724" s="28" t="n"/>
       <c r="E724" s="34" t="n"/>
       <c r="F724" s="25">
-        <f>IF(OR(B724="",E724=""),"",E724*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B724,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B724="",E724=""),"",IFERROR(E724*INDEX(Config!$D$11:$D$20,MATCH(B724,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G724" s="24">
@@ -28214,7 +28214,7 @@
       <c r="D725" s="28" t="n"/>
       <c r="E725" s="34" t="n"/>
       <c r="F725" s="25">
-        <f>IF(OR(B725="",E725=""),"",E725*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B725,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B725="",E725=""),"",IFERROR(E725*INDEX(Config!$D$11:$D$20,MATCH(B725,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G725" s="24">
@@ -28234,7 +28234,7 @@
       <c r="D726" s="28" t="n"/>
       <c r="E726" s="34" t="n"/>
       <c r="F726" s="25">
-        <f>IF(OR(B726="",E726=""),"",E726*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B726,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B726="",E726=""),"",IFERROR(E726*INDEX(Config!$D$11:$D$20,MATCH(B726,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G726" s="24">
@@ -28254,7 +28254,7 @@
       <c r="D727" s="28" t="n"/>
       <c r="E727" s="34" t="n"/>
       <c r="F727" s="25">
-        <f>IF(OR(B727="",E727=""),"",E727*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B727,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B727="",E727=""),"",IFERROR(E727*INDEX(Config!$D$11:$D$20,MATCH(B727,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G727" s="24">
@@ -28274,7 +28274,7 @@
       <c r="D728" s="28" t="n"/>
       <c r="E728" s="34" t="n"/>
       <c r="F728" s="25">
-        <f>IF(OR(B728="",E728=""),"",E728*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B728,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B728="",E728=""),"",IFERROR(E728*INDEX(Config!$D$11:$D$20,MATCH(B728,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G728" s="24">
@@ -28294,7 +28294,7 @@
       <c r="D729" s="28" t="n"/>
       <c r="E729" s="34" t="n"/>
       <c r="F729" s="25">
-        <f>IF(OR(B729="",E729=""),"",E729*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B729,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B729="",E729=""),"",IFERROR(E729*INDEX(Config!$D$11:$D$20,MATCH(B729,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G729" s="24">
@@ -28314,7 +28314,7 @@
       <c r="D730" s="28" t="n"/>
       <c r="E730" s="34" t="n"/>
       <c r="F730" s="25">
-        <f>IF(OR(B730="",E730=""),"",E730*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B730,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B730="",E730=""),"",IFERROR(E730*INDEX(Config!$D$11:$D$20,MATCH(B730,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G730" s="24">
@@ -28334,7 +28334,7 @@
       <c r="D731" s="28" t="n"/>
       <c r="E731" s="34" t="n"/>
       <c r="F731" s="25">
-        <f>IF(OR(B731="",E731=""),"",E731*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B731,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B731="",E731=""),"",IFERROR(E731*INDEX(Config!$D$11:$D$20,MATCH(B731,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G731" s="24">
@@ -28354,7 +28354,7 @@
       <c r="D732" s="28" t="n"/>
       <c r="E732" s="34" t="n"/>
       <c r="F732" s="25">
-        <f>IF(OR(B732="",E732=""),"",E732*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B732,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B732="",E732=""),"",IFERROR(E732*INDEX(Config!$D$11:$D$20,MATCH(B732,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G732" s="24">
@@ -28374,7 +28374,7 @@
       <c r="D733" s="28" t="n"/>
       <c r="E733" s="34" t="n"/>
       <c r="F733" s="25">
-        <f>IF(OR(B733="",E733=""),"",E733*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B733,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B733="",E733=""),"",IFERROR(E733*INDEX(Config!$D$11:$D$20,MATCH(B733,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G733" s="24">
@@ -28394,7 +28394,7 @@
       <c r="D734" s="28" t="n"/>
       <c r="E734" s="34" t="n"/>
       <c r="F734" s="25">
-        <f>IF(OR(B734="",E734=""),"",E734*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B734,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B734="",E734=""),"",IFERROR(E734*INDEX(Config!$D$11:$D$20,MATCH(B734,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G734" s="24">
@@ -28414,7 +28414,7 @@
       <c r="D735" s="28" t="n"/>
       <c r="E735" s="34" t="n"/>
       <c r="F735" s="25">
-        <f>IF(OR(B735="",E735=""),"",E735*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B735,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B735="",E735=""),"",IFERROR(E735*INDEX(Config!$D$11:$D$20,MATCH(B735,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G735" s="24">
@@ -28434,7 +28434,7 @@
       <c r="D736" s="28" t="n"/>
       <c r="E736" s="34" t="n"/>
       <c r="F736" s="25">
-        <f>IF(OR(B736="",E736=""),"",E736*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B736,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B736="",E736=""),"",IFERROR(E736*INDEX(Config!$D$11:$D$20,MATCH(B736,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G736" s="24">
@@ -28454,7 +28454,7 @@
       <c r="D737" s="28" t="n"/>
       <c r="E737" s="34" t="n"/>
       <c r="F737" s="25">
-        <f>IF(OR(B737="",E737=""),"",E737*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B737,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B737="",E737=""),"",IFERROR(E737*INDEX(Config!$D$11:$D$20,MATCH(B737,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G737" s="24">
@@ -28474,7 +28474,7 @@
       <c r="D738" s="28" t="n"/>
       <c r="E738" s="34" t="n"/>
       <c r="F738" s="25">
-        <f>IF(OR(B738="",E738=""),"",E738*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B738,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B738="",E738=""),"",IFERROR(E738*INDEX(Config!$D$11:$D$20,MATCH(B738,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G738" s="24">
@@ -28494,7 +28494,7 @@
       <c r="D739" s="28" t="n"/>
       <c r="E739" s="34" t="n"/>
       <c r="F739" s="25">
-        <f>IF(OR(B739="",E739=""),"",E739*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B739,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B739="",E739=""),"",IFERROR(E739*INDEX(Config!$D$11:$D$20,MATCH(B739,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G739" s="24">
@@ -28514,7 +28514,7 @@
       <c r="D740" s="28" t="n"/>
       <c r="E740" s="34" t="n"/>
       <c r="F740" s="25">
-        <f>IF(OR(B740="",E740=""),"",E740*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B740,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B740="",E740=""),"",IFERROR(E740*INDEX(Config!$D$11:$D$20,MATCH(B740,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G740" s="24">
@@ -28534,7 +28534,7 @@
       <c r="D741" s="28" t="n"/>
       <c r="E741" s="34" t="n"/>
       <c r="F741" s="25">
-        <f>IF(OR(B741="",E741=""),"",E741*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B741,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B741="",E741=""),"",IFERROR(E741*INDEX(Config!$D$11:$D$20,MATCH(B741,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G741" s="24">
@@ -28554,7 +28554,7 @@
       <c r="D742" s="28" t="n"/>
       <c r="E742" s="34" t="n"/>
       <c r="F742" s="25">
-        <f>IF(OR(B742="",E742=""),"",E742*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B742,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B742="",E742=""),"",IFERROR(E742*INDEX(Config!$D$11:$D$20,MATCH(B742,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G742" s="24">
@@ -28574,7 +28574,7 @@
       <c r="D743" s="28" t="n"/>
       <c r="E743" s="34" t="n"/>
       <c r="F743" s="25">
-        <f>IF(OR(B743="",E743=""),"",E743*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B743,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B743="",E743=""),"",IFERROR(E743*INDEX(Config!$D$11:$D$20,MATCH(B743,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G743" s="24">
@@ -28594,7 +28594,7 @@
       <c r="D744" s="28" t="n"/>
       <c r="E744" s="34" t="n"/>
       <c r="F744" s="25">
-        <f>IF(OR(B744="",E744=""),"",E744*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B744,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B744="",E744=""),"",IFERROR(E744*INDEX(Config!$D$11:$D$20,MATCH(B744,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G744" s="24">
@@ -28614,7 +28614,7 @@
       <c r="D745" s="28" t="n"/>
       <c r="E745" s="34" t="n"/>
       <c r="F745" s="25">
-        <f>IF(OR(B745="",E745=""),"",E745*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B745,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B745="",E745=""),"",IFERROR(E745*INDEX(Config!$D$11:$D$20,MATCH(B745,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G745" s="24">
@@ -28634,7 +28634,7 @@
       <c r="D746" s="28" t="n"/>
       <c r="E746" s="34" t="n"/>
       <c r="F746" s="25">
-        <f>IF(OR(B746="",E746=""),"",E746*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B746,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B746="",E746=""),"",IFERROR(E746*INDEX(Config!$D$11:$D$20,MATCH(B746,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G746" s="24">
@@ -28654,7 +28654,7 @@
       <c r="D747" s="28" t="n"/>
       <c r="E747" s="34" t="n"/>
       <c r="F747" s="25">
-        <f>IF(OR(B747="",E747=""),"",E747*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B747,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B747="",E747=""),"",IFERROR(E747*INDEX(Config!$D$11:$D$20,MATCH(B747,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G747" s="24">
@@ -28674,7 +28674,7 @@
       <c r="D748" s="28" t="n"/>
       <c r="E748" s="34" t="n"/>
       <c r="F748" s="25">
-        <f>IF(OR(B748="",E748=""),"",E748*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B748,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B748="",E748=""),"",IFERROR(E748*INDEX(Config!$D$11:$D$20,MATCH(B748,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G748" s="24">
@@ -28694,7 +28694,7 @@
       <c r="D749" s="28" t="n"/>
       <c r="E749" s="34" t="n"/>
       <c r="F749" s="25">
-        <f>IF(OR(B749="",E749=""),"",E749*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B749,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B749="",E749=""),"",IFERROR(E749*INDEX(Config!$D$11:$D$20,MATCH(B749,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G749" s="24">
@@ -28714,7 +28714,7 @@
       <c r="D750" s="28" t="n"/>
       <c r="E750" s="34" t="n"/>
       <c r="F750" s="25">
-        <f>IF(OR(B750="",E750=""),"",E750*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B750,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B750="",E750=""),"",IFERROR(E750*INDEX(Config!$D$11:$D$20,MATCH(B750,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G750" s="24">
@@ -28734,7 +28734,7 @@
       <c r="D751" s="28" t="n"/>
       <c r="E751" s="34" t="n"/>
       <c r="F751" s="25">
-        <f>IF(OR(B751="",E751=""),"",E751*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B751,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B751="",E751=""),"",IFERROR(E751*INDEX(Config!$D$11:$D$20,MATCH(B751,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G751" s="24">
@@ -28754,7 +28754,7 @@
       <c r="D752" s="28" t="n"/>
       <c r="E752" s="34" t="n"/>
       <c r="F752" s="25">
-        <f>IF(OR(B752="",E752=""),"",E752*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B752,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B752="",E752=""),"",IFERROR(E752*INDEX(Config!$D$11:$D$20,MATCH(B752,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G752" s="24">
@@ -28774,7 +28774,7 @@
       <c r="D753" s="28" t="n"/>
       <c r="E753" s="34" t="n"/>
       <c r="F753" s="25">
-        <f>IF(OR(B753="",E753=""),"",E753*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B753,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B753="",E753=""),"",IFERROR(E753*INDEX(Config!$D$11:$D$20,MATCH(B753,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G753" s="24">
@@ -28794,7 +28794,7 @@
       <c r="D754" s="28" t="n"/>
       <c r="E754" s="34" t="n"/>
       <c r="F754" s="25">
-        <f>IF(OR(B754="",E754=""),"",E754*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B754,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B754="",E754=""),"",IFERROR(E754*INDEX(Config!$D$11:$D$20,MATCH(B754,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G754" s="24">
@@ -28814,7 +28814,7 @@
       <c r="D755" s="28" t="n"/>
       <c r="E755" s="34" t="n"/>
       <c r="F755" s="25">
-        <f>IF(OR(B755="",E755=""),"",E755*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B755,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B755="",E755=""),"",IFERROR(E755*INDEX(Config!$D$11:$D$20,MATCH(B755,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G755" s="24">
@@ -28834,7 +28834,7 @@
       <c r="D756" s="28" t="n"/>
       <c r="E756" s="34" t="n"/>
       <c r="F756" s="25">
-        <f>IF(OR(B756="",E756=""),"",E756*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B756,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B756="",E756=""),"",IFERROR(E756*INDEX(Config!$D$11:$D$20,MATCH(B756,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G756" s="24">
@@ -28854,7 +28854,7 @@
       <c r="D757" s="28" t="n"/>
       <c r="E757" s="34" t="n"/>
       <c r="F757" s="25">
-        <f>IF(OR(B757="",E757=""),"",E757*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B757,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B757="",E757=""),"",IFERROR(E757*INDEX(Config!$D$11:$D$20,MATCH(B757,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G757" s="24">
@@ -28874,7 +28874,7 @@
       <c r="D758" s="28" t="n"/>
       <c r="E758" s="34" t="n"/>
       <c r="F758" s="25">
-        <f>IF(OR(B758="",E758=""),"",E758*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B758,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B758="",E758=""),"",IFERROR(E758*INDEX(Config!$D$11:$D$20,MATCH(B758,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G758" s="24">
@@ -28894,7 +28894,7 @@
       <c r="D759" s="28" t="n"/>
       <c r="E759" s="34" t="n"/>
       <c r="F759" s="25">
-        <f>IF(OR(B759="",E759=""),"",E759*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B759,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B759="",E759=""),"",IFERROR(E759*INDEX(Config!$D$11:$D$20,MATCH(B759,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G759" s="24">
@@ -28914,7 +28914,7 @@
       <c r="D760" s="28" t="n"/>
       <c r="E760" s="34" t="n"/>
       <c r="F760" s="25">
-        <f>IF(OR(B760="",E760=""),"",E760*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B760,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B760="",E760=""),"",IFERROR(E760*INDEX(Config!$D$11:$D$20,MATCH(B760,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G760" s="24">
@@ -28934,7 +28934,7 @@
       <c r="D761" s="28" t="n"/>
       <c r="E761" s="34" t="n"/>
       <c r="F761" s="25">
-        <f>IF(OR(B761="",E761=""),"",E761*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B761,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B761="",E761=""),"",IFERROR(E761*INDEX(Config!$D$11:$D$20,MATCH(B761,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G761" s="24">
@@ -28954,7 +28954,7 @@
       <c r="D762" s="28" t="n"/>
       <c r="E762" s="34" t="n"/>
       <c r="F762" s="25">
-        <f>IF(OR(B762="",E762=""),"",E762*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B762,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B762="",E762=""),"",IFERROR(E762*INDEX(Config!$D$11:$D$20,MATCH(B762,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G762" s="24">
@@ -28974,7 +28974,7 @@
       <c r="D763" s="28" t="n"/>
       <c r="E763" s="34" t="n"/>
       <c r="F763" s="25">
-        <f>IF(OR(B763="",E763=""),"",E763*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B763,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B763="",E763=""),"",IFERROR(E763*INDEX(Config!$D$11:$D$20,MATCH(B763,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G763" s="24">
@@ -28994,7 +28994,7 @@
       <c r="D764" s="28" t="n"/>
       <c r="E764" s="34" t="n"/>
       <c r="F764" s="25">
-        <f>IF(OR(B764="",E764=""),"",E764*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B764,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B764="",E764=""),"",IFERROR(E764*INDEX(Config!$D$11:$D$20,MATCH(B764,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G764" s="24">
@@ -29014,7 +29014,7 @@
       <c r="D765" s="28" t="n"/>
       <c r="E765" s="34" t="n"/>
       <c r="F765" s="25">
-        <f>IF(OR(B765="",E765=""),"",E765*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B765,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B765="",E765=""),"",IFERROR(E765*INDEX(Config!$D$11:$D$20,MATCH(B765,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G765" s="24">
@@ -29034,7 +29034,7 @@
       <c r="D766" s="28" t="n"/>
       <c r="E766" s="34" t="n"/>
       <c r="F766" s="25">
-        <f>IF(OR(B766="",E766=""),"",E766*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B766,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B766="",E766=""),"",IFERROR(E766*INDEX(Config!$D$11:$D$20,MATCH(B766,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G766" s="24">
@@ -29054,7 +29054,7 @@
       <c r="D767" s="28" t="n"/>
       <c r="E767" s="34" t="n"/>
       <c r="F767" s="25">
-        <f>IF(OR(B767="",E767=""),"",E767*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B767,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B767="",E767=""),"",IFERROR(E767*INDEX(Config!$D$11:$D$20,MATCH(B767,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G767" s="24">
@@ -29074,7 +29074,7 @@
       <c r="D768" s="28" t="n"/>
       <c r="E768" s="34" t="n"/>
       <c r="F768" s="25">
-        <f>IF(OR(B768="",E768=""),"",E768*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B768,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B768="",E768=""),"",IFERROR(E768*INDEX(Config!$D$11:$D$20,MATCH(B768,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G768" s="24">
@@ -29094,7 +29094,7 @@
       <c r="D769" s="28" t="n"/>
       <c r="E769" s="34" t="n"/>
       <c r="F769" s="25">
-        <f>IF(OR(B769="",E769=""),"",E769*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B769,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B769="",E769=""),"",IFERROR(E769*INDEX(Config!$D$11:$D$20,MATCH(B769,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G769" s="24">
@@ -29114,7 +29114,7 @@
       <c r="D770" s="28" t="n"/>
       <c r="E770" s="34" t="n"/>
       <c r="F770" s="25">
-        <f>IF(OR(B770="",E770=""),"",E770*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B770,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B770="",E770=""),"",IFERROR(E770*INDEX(Config!$D$11:$D$20,MATCH(B770,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G770" s="24">
@@ -29134,7 +29134,7 @@
       <c r="D771" s="28" t="n"/>
       <c r="E771" s="34" t="n"/>
       <c r="F771" s="25">
-        <f>IF(OR(B771="",E771=""),"",E771*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B771,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B771="",E771=""),"",IFERROR(E771*INDEX(Config!$D$11:$D$20,MATCH(B771,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G771" s="24">
@@ -29154,7 +29154,7 @@
       <c r="D772" s="28" t="n"/>
       <c r="E772" s="34" t="n"/>
       <c r="F772" s="25">
-        <f>IF(OR(B772="",E772=""),"",E772*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B772,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B772="",E772=""),"",IFERROR(E772*INDEX(Config!$D$11:$D$20,MATCH(B772,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G772" s="24">
@@ -29174,7 +29174,7 @@
       <c r="D773" s="28" t="n"/>
       <c r="E773" s="34" t="n"/>
       <c r="F773" s="25">
-        <f>IF(OR(B773="",E773=""),"",E773*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B773,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B773="",E773=""),"",IFERROR(E773*INDEX(Config!$D$11:$D$20,MATCH(B773,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G773" s="24">
@@ -29194,7 +29194,7 @@
       <c r="D774" s="28" t="n"/>
       <c r="E774" s="34" t="n"/>
       <c r="F774" s="25">
-        <f>IF(OR(B774="",E774=""),"",E774*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B774,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B774="",E774=""),"",IFERROR(E774*INDEX(Config!$D$11:$D$20,MATCH(B774,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G774" s="24">
@@ -29214,7 +29214,7 @@
       <c r="D775" s="28" t="n"/>
       <c r="E775" s="34" t="n"/>
       <c r="F775" s="25">
-        <f>IF(OR(B775="",E775=""),"",E775*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B775,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B775="",E775=""),"",IFERROR(E775*INDEX(Config!$D$11:$D$20,MATCH(B775,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G775" s="24">
@@ -29234,7 +29234,7 @@
       <c r="D776" s="28" t="n"/>
       <c r="E776" s="34" t="n"/>
       <c r="F776" s="25">
-        <f>IF(OR(B776="",E776=""),"",E776*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B776,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B776="",E776=""),"",IFERROR(E776*INDEX(Config!$D$11:$D$20,MATCH(B776,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G776" s="24">
@@ -29254,7 +29254,7 @@
       <c r="D777" s="28" t="n"/>
       <c r="E777" s="34" t="n"/>
       <c r="F777" s="25">
-        <f>IF(OR(B777="",E777=""),"",E777*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B777,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B777="",E777=""),"",IFERROR(E777*INDEX(Config!$D$11:$D$20,MATCH(B777,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G777" s="24">
@@ -29274,7 +29274,7 @@
       <c r="D778" s="28" t="n"/>
       <c r="E778" s="34" t="n"/>
       <c r="F778" s="25">
-        <f>IF(OR(B778="",E778=""),"",E778*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B778,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B778="",E778=""),"",IFERROR(E778*INDEX(Config!$D$11:$D$20,MATCH(B778,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G778" s="24">
@@ -29294,7 +29294,7 @@
       <c r="D779" s="28" t="n"/>
       <c r="E779" s="34" t="n"/>
       <c r="F779" s="25">
-        <f>IF(OR(B779="",E779=""),"",E779*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B779,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B779="",E779=""),"",IFERROR(E779*INDEX(Config!$D$11:$D$20,MATCH(B779,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G779" s="24">
@@ -29314,7 +29314,7 @@
       <c r="D780" s="28" t="n"/>
       <c r="E780" s="34" t="n"/>
       <c r="F780" s="25">
-        <f>IF(OR(B780="",E780=""),"",E780*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B780,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B780="",E780=""),"",IFERROR(E780*INDEX(Config!$D$11:$D$20,MATCH(B780,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G780" s="24">
@@ -29334,7 +29334,7 @@
       <c r="D781" s="28" t="n"/>
       <c r="E781" s="34" t="n"/>
       <c r="F781" s="25">
-        <f>IF(OR(B781="",E781=""),"",E781*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B781,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B781="",E781=""),"",IFERROR(E781*INDEX(Config!$D$11:$D$20,MATCH(B781,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G781" s="24">
@@ -29354,7 +29354,7 @@
       <c r="D782" s="28" t="n"/>
       <c r="E782" s="34" t="n"/>
       <c r="F782" s="25">
-        <f>IF(OR(B782="",E782=""),"",E782*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B782,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B782="",E782=""),"",IFERROR(E782*INDEX(Config!$D$11:$D$20,MATCH(B782,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G782" s="24">
@@ -29374,7 +29374,7 @@
       <c r="D783" s="28" t="n"/>
       <c r="E783" s="34" t="n"/>
       <c r="F783" s="25">
-        <f>IF(OR(B783="",E783=""),"",E783*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B783,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B783="",E783=""),"",IFERROR(E783*INDEX(Config!$D$11:$D$20,MATCH(B783,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G783" s="24">
@@ -29394,7 +29394,7 @@
       <c r="D784" s="28" t="n"/>
       <c r="E784" s="34" t="n"/>
       <c r="F784" s="25">
-        <f>IF(OR(B784="",E784=""),"",E784*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B784,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B784="",E784=""),"",IFERROR(E784*INDEX(Config!$D$11:$D$20,MATCH(B784,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G784" s="24">
@@ -29414,7 +29414,7 @@
       <c r="D785" s="28" t="n"/>
       <c r="E785" s="34" t="n"/>
       <c r="F785" s="25">
-        <f>IF(OR(B785="",E785=""),"",E785*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B785,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B785="",E785=""),"",IFERROR(E785*INDEX(Config!$D$11:$D$20,MATCH(B785,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G785" s="24">
@@ -29434,7 +29434,7 @@
       <c r="D786" s="28" t="n"/>
       <c r="E786" s="34" t="n"/>
       <c r="F786" s="25">
-        <f>IF(OR(B786="",E786=""),"",E786*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B786,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B786="",E786=""),"",IFERROR(E786*INDEX(Config!$D$11:$D$20,MATCH(B786,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G786" s="24">
@@ -29454,7 +29454,7 @@
       <c r="D787" s="28" t="n"/>
       <c r="E787" s="34" t="n"/>
       <c r="F787" s="25">
-        <f>IF(OR(B787="",E787=""),"",E787*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B787,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B787="",E787=""),"",IFERROR(E787*INDEX(Config!$D$11:$D$20,MATCH(B787,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G787" s="24">
@@ -29474,7 +29474,7 @@
       <c r="D788" s="28" t="n"/>
       <c r="E788" s="34" t="n"/>
       <c r="F788" s="25">
-        <f>IF(OR(B788="",E788=""),"",E788*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B788,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B788="",E788=""),"",IFERROR(E788*INDEX(Config!$D$11:$D$20,MATCH(B788,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G788" s="24">
@@ -29494,7 +29494,7 @@
       <c r="D789" s="28" t="n"/>
       <c r="E789" s="34" t="n"/>
       <c r="F789" s="25">
-        <f>IF(OR(B789="",E789=""),"",E789*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B789,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B789="",E789=""),"",IFERROR(E789*INDEX(Config!$D$11:$D$20,MATCH(B789,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G789" s="24">
@@ -29514,7 +29514,7 @@
       <c r="D790" s="28" t="n"/>
       <c r="E790" s="34" t="n"/>
       <c r="F790" s="25">
-        <f>IF(OR(B790="",E790=""),"",E790*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B790,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B790="",E790=""),"",IFERROR(E790*INDEX(Config!$D$11:$D$20,MATCH(B790,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G790" s="24">
@@ -29534,7 +29534,7 @@
       <c r="D791" s="28" t="n"/>
       <c r="E791" s="34" t="n"/>
       <c r="F791" s="25">
-        <f>IF(OR(B791="",E791=""),"",E791*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B791,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B791="",E791=""),"",IFERROR(E791*INDEX(Config!$D$11:$D$20,MATCH(B791,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G791" s="24">
@@ -29554,7 +29554,7 @@
       <c r="D792" s="28" t="n"/>
       <c r="E792" s="34" t="n"/>
       <c r="F792" s="25">
-        <f>IF(OR(B792="",E792=""),"",E792*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B792,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B792="",E792=""),"",IFERROR(E792*INDEX(Config!$D$11:$D$20,MATCH(B792,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G792" s="24">
@@ -29574,7 +29574,7 @@
       <c r="D793" s="28" t="n"/>
       <c r="E793" s="34" t="n"/>
       <c r="F793" s="25">
-        <f>IF(OR(B793="",E793=""),"",E793*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B793,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B793="",E793=""),"",IFERROR(E793*INDEX(Config!$D$11:$D$20,MATCH(B793,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G793" s="24">
@@ -29594,7 +29594,7 @@
       <c r="D794" s="28" t="n"/>
       <c r="E794" s="34" t="n"/>
       <c r="F794" s="25">
-        <f>IF(OR(B794="",E794=""),"",E794*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B794,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B794="",E794=""),"",IFERROR(E794*INDEX(Config!$D$11:$D$20,MATCH(B794,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G794" s="24">
@@ -29614,7 +29614,7 @@
       <c r="D795" s="28" t="n"/>
       <c r="E795" s="34" t="n"/>
       <c r="F795" s="25">
-        <f>IF(OR(B795="",E795=""),"",E795*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B795,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B795="",E795=""),"",IFERROR(E795*INDEX(Config!$D$11:$D$20,MATCH(B795,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G795" s="24">
@@ -29634,7 +29634,7 @@
       <c r="D796" s="28" t="n"/>
       <c r="E796" s="34" t="n"/>
       <c r="F796" s="25">
-        <f>IF(OR(B796="",E796=""),"",E796*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B796,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B796="",E796=""),"",IFERROR(E796*INDEX(Config!$D$11:$D$20,MATCH(B796,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G796" s="24">
@@ -29654,7 +29654,7 @@
       <c r="D797" s="28" t="n"/>
       <c r="E797" s="34" t="n"/>
       <c r="F797" s="25">
-        <f>IF(OR(B797="",E797=""),"",E797*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B797,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B797="",E797=""),"",IFERROR(E797*INDEX(Config!$D$11:$D$20,MATCH(B797,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G797" s="24">
@@ -29674,7 +29674,7 @@
       <c r="D798" s="28" t="n"/>
       <c r="E798" s="34" t="n"/>
       <c r="F798" s="25">
-        <f>IF(OR(B798="",E798=""),"",E798*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B798,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B798="",E798=""),"",IFERROR(E798*INDEX(Config!$D$11:$D$20,MATCH(B798,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G798" s="24">
@@ -29694,7 +29694,7 @@
       <c r="D799" s="28" t="n"/>
       <c r="E799" s="34" t="n"/>
       <c r="F799" s="25">
-        <f>IF(OR(B799="",E799=""),"",E799*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B799,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B799="",E799=""),"",IFERROR(E799*INDEX(Config!$D$11:$D$20,MATCH(B799,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G799" s="24">
@@ -29714,7 +29714,7 @@
       <c r="D800" s="28" t="n"/>
       <c r="E800" s="34" t="n"/>
       <c r="F800" s="25">
-        <f>IF(OR(B800="",E800=""),"",E800*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B800,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B800="",E800=""),"",IFERROR(E800*INDEX(Config!$D$11:$D$20,MATCH(B800,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G800" s="24">
@@ -29734,7 +29734,7 @@
       <c r="D801" s="28" t="n"/>
       <c r="E801" s="34" t="n"/>
       <c r="F801" s="25">
-        <f>IF(OR(B801="",E801=""),"",E801*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B801,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B801="",E801=""),"",IFERROR(E801*INDEX(Config!$D$11:$D$20,MATCH(B801,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G801" s="24">
@@ -29754,7 +29754,7 @@
       <c r="D802" s="28" t="n"/>
       <c r="E802" s="34" t="n"/>
       <c r="F802" s="25">
-        <f>IF(OR(B802="",E802=""),"",E802*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B802,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B802="",E802=""),"",IFERROR(E802*INDEX(Config!$D$11:$D$20,MATCH(B802,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G802" s="24">
@@ -29774,7 +29774,7 @@
       <c r="D803" s="28" t="n"/>
       <c r="E803" s="34" t="n"/>
       <c r="F803" s="25">
-        <f>IF(OR(B803="",E803=""),"",E803*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B803,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B803="",E803=""),"",IFERROR(E803*INDEX(Config!$D$11:$D$20,MATCH(B803,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G803" s="24">
@@ -29794,7 +29794,7 @@
       <c r="D804" s="28" t="n"/>
       <c r="E804" s="34" t="n"/>
       <c r="F804" s="25">
-        <f>IF(OR(B804="",E804=""),"",E804*IFERROR(INDEX(Config!$D$11:$D$20,MATCH(B804,Config!$A$11:$A$20,0)),0))</f>
+        <f>IF(OR(B804="",E804=""),"",IFERROR(E804*INDEX(Config!$D$11:$D$20,MATCH(B804,Config!$A$11:$A$20,0)),"pessoa sem custo-hora em Config"))</f>
         <v/>
       </c>
       <c r="G804" s="24">
@@ -29814,19 +29814,19 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="B5:B804" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:B804" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$A$11:$A$20</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C804" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C804" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$A$24:$A$35</formula1>
     </dataValidation>
     <dataValidation sqref="I5:I804" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A804" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A804" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E804" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="E5:E804" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>24</formula2>
     </dataValidation>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/09-horas-e-custo-por-projeto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/09-horas-e-custo-por-projeto.xlsx
@@ -805,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -925,34 +925,58 @@
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/09-horas-e-custo-por-projeto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/09-horas-e-custo-por-projeto.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,11 @@
     <font>
       <name val="Arial"/>
       <color rgb="007A5AA8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B0A6C4"/>
       <sz val="9"/>
     </font>
     <font>
@@ -180,27 +185,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,16 +215,16 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -267,6 +272,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -855,7 +861,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, cadastre as pessoas com custo mensal E horas disponíveis: os dois são obrigatórios, porque o custo-hora sai da divisão. Faltando um, a planilha escreve o que falta em vez de calcular um custo zerado, e os projetos com horas orçadas, valor cobrado e status. Projetos internos (comercial, gestão) entram com status Interno; proposta ainda não fechada pode entrar como Proposta, sem horas.</t>
+          <t>Em Config, cadastre as pessoas com custo mensal E horas disponíveis: os dois são obrigatórios, porque o custo-hora sai da divisão. Faltando um, a planilha escreve o que falta em vez de calcular um custo zerado, e o custo e a margem dos projetos e pessoas com horas dessa pessoa aparecem como "cadastro incompleto" no Painel (uma soma parcial mentiria para menos). Cadastre também os projetos com horas orçadas, valor cobrado e status. Projetos internos (comercial, gestão) entram com status Interno; proposta ainda não fechada pode entrar como Proposta, sem horas.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1070,7 @@
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="14">
-        <f>SUMIFS(Horas!$F$5:$F$804,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)</f>
+        <f>IF(SUMIFS(Horas!$J$5:$J$804,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
         <v>14967.2619047619</v>
       </c>
       <c r="D5" s="8" t="n"/>
@@ -1081,7 +1087,7 @@
     </row>
     <row r="7">
       <c r="A7" s="17">
-        <f>IF(COUNTIF(Horas!$F$5:$F$804,"*Config*")=0,"","Atenção: "&amp;COUNTIF(Horas!$F$5:$F$804,"*Config*")&amp;" lançamento(s) de hora sem custo-hora (cadastro incompleto em Config). O custo e a margem dos projetos abaixo estão MENORES do que a realidade até você completar o custo mensal e as horas disponíveis da pessoa.")</f>
+        <f>IF(SUM(Horas!$J$5:$J$804)=0,"","Atenção: "&amp;SUM(Horas!$J$5:$J$804)&amp;" lançamento(s) de hora sem custo-hora (cadastro incompleto em Config). O custo desses lançamentos não está contado: o custo real é MAIOR e a margem real é MENOR do que qualquer soma parcial, por isso custo e margem dos projetos e pessoas afetados aparecem como 'cadastro incompleto' até você completar o custo mensal e as horas disponíveis da pessoa.")</f>
         <v/>
       </c>
     </row>
@@ -1166,7 +1172,7 @@
         <v>0.586607142857143</v>
       </c>
       <c r="F10" s="24">
-        <f>IF(Config!$A$24="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$24))</f>
+        <f>IF(Config!$A$24="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$24)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$24)))</f>
         <v>17218.0952380952</v>
       </c>
       <c r="G10" s="24">
@@ -1174,15 +1180,15 @@
         <v>24000</v>
       </c>
       <c r="H10" s="24">
-        <f>IF(OR(Config!$A$24="",G10=""),"",G10-F10)</f>
+        <f>IF(OR(Config!$A$24="",G10=""),"",IF(ISNUMBER(F10),G10-F10,"cadastro incompleto"))</f>
         <v>6781.90476190476</v>
       </c>
       <c r="I10" s="23">
-        <f>IF(OR(Config!$A$24="",G10="",G10=0),"",H10/G10)</f>
+        <f>IF(OR(Config!$A$24="",G10="",G10=0,NOT(ISNUMBER(H10))),"",H10/G10)</f>
         <v>0.282579365079365</v>
       </c>
       <c r="J10" s="25" t="str">
-        <f>IF(Config!$A$24="","",IF(Config!$E$24="Interno","Interno",IF(Config!$E$24="Proposta","Proposta",IF(AND(E10&lt;&gt;"",E10&gt;1),"Estourou as horas",IF(AND(I10&lt;&gt;"",I10&lt;0.2),"Margem baixa",IF(AND(E10&lt;&gt;"",E10&gt;0.85,Config!$E$24="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$24="","",IF(Config!$E$24="Interno","Interno",IF(Config!$E$24="Proposta","Proposta",IF(NOT(ISNUMBER(F10)),"Custo incompleto",IF(AND(E10&lt;&gt;"",E10&gt;1),"Estourou as horas",IF(AND(I10&lt;&gt;"",I10&lt;0.2),"Margem baixa",IF(AND(E10&lt;&gt;"",E10&gt;0.85,Config!$E$24="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v>Saudável</v>
       </c>
     </row>
@@ -1208,7 +1214,7 @@
         <v>0.171666666666667</v>
       </c>
       <c r="F11" s="24">
-        <f>IF(Config!$A$25="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$25))</f>
+        <f>IF(Config!$A$25="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$25)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$25)))</f>
         <v>2508.57142857143</v>
       </c>
       <c r="G11" s="24">
@@ -1216,15 +1222,15 @@
         <v>38000</v>
       </c>
       <c r="H11" s="24">
-        <f>IF(OR(Config!$A$25="",G11=""),"",G11-F11)</f>
+        <f>IF(OR(Config!$A$25="",G11=""),"",IF(ISNUMBER(F11),G11-F11,"cadastro incompleto"))</f>
         <v>35491.4285714286</v>
       </c>
       <c r="I11" s="23">
-        <f>IF(OR(Config!$A$25="",G11="",G11=0),"",H11/G11)</f>
+        <f>IF(OR(Config!$A$25="",G11="",G11=0,NOT(ISNUMBER(H11))),"",H11/G11)</f>
         <v>0.933984962406015</v>
       </c>
       <c r="J11" s="25" t="str">
-        <f>IF(Config!$A$25="","",IF(Config!$E$25="Interno","Interno",IF(Config!$E$25="Proposta","Proposta",IF(AND(E11&lt;&gt;"",E11&gt;1),"Estourou as horas",IF(AND(I11&lt;&gt;"",I11&lt;0.2),"Margem baixa",IF(AND(E11&lt;&gt;"",E11&gt;0.85,Config!$E$25="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$25="","",IF(Config!$E$25="Interno","Interno",IF(Config!$E$25="Proposta","Proposta",IF(NOT(ISNUMBER(F11)),"Custo incompleto",IF(AND(E11&lt;&gt;"",E11&gt;1),"Estourou as horas",IF(AND(I11&lt;&gt;"",I11&lt;0.2),"Margem baixa",IF(AND(E11&lt;&gt;"",E11&gt;0.85,Config!$E$25="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v>Saudável</v>
       </c>
     </row>
@@ -1250,7 +1256,7 @@
         <v>0.0730769230769231</v>
       </c>
       <c r="F12" s="24">
-        <f>IF(Config!$A$26="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$26))</f>
+        <f>IF(Config!$A$26="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$26)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$26)))</f>
         <v>665</v>
       </c>
       <c r="G12" s="24">
@@ -1258,15 +1264,15 @@
         <v>16000</v>
       </c>
       <c r="H12" s="24">
-        <f>IF(OR(Config!$A$26="",G12=""),"",G12-F12)</f>
+        <f>IF(OR(Config!$A$26="",G12=""),"",IF(ISNUMBER(F12),G12-F12,"cadastro incompleto"))</f>
         <v>15335</v>
       </c>
       <c r="I12" s="23">
-        <f>IF(OR(Config!$A$26="",G12="",G12=0),"",H12/G12)</f>
+        <f>IF(OR(Config!$A$26="",G12="",G12=0,NOT(ISNUMBER(H12))),"",H12/G12)</f>
         <v>0.9584375</v>
       </c>
       <c r="J12" s="25" t="str">
-        <f>IF(Config!$A$26="","",IF(Config!$E$26="Interno","Interno",IF(Config!$E$26="Proposta","Proposta",IF(AND(E12&lt;&gt;"",E12&gt;1),"Estourou as horas",IF(AND(I12&lt;&gt;"",I12&lt;0.2),"Margem baixa",IF(AND(E12&lt;&gt;"",E12&gt;0.85,Config!$E$26="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$26="","",IF(Config!$E$26="Interno","Interno",IF(Config!$E$26="Proposta","Proposta",IF(NOT(ISNUMBER(F12)),"Custo incompleto",IF(AND(E12&lt;&gt;"",E12&gt;1),"Estourou as horas",IF(AND(I12&lt;&gt;"",I12&lt;0.2),"Margem baixa",IF(AND(E12&lt;&gt;"",E12&gt;0.85,Config!$E$26="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v>Saudável</v>
       </c>
     </row>
@@ -1292,7 +1298,7 @@
         <v>0.921428571428571</v>
       </c>
       <c r="F13" s="24">
-        <f>IF(Config!$A$27="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$27))</f>
+        <f>IF(Config!$A$27="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$27)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$27)))</f>
         <v>3317.14285714286</v>
       </c>
       <c r="G13" s="24">
@@ -1300,15 +1306,15 @@
         <v>9500</v>
       </c>
       <c r="H13" s="24">
-        <f>IF(OR(Config!$A$27="",G13=""),"",G13-F13)</f>
+        <f>IF(OR(Config!$A$27="",G13=""),"",IF(ISNUMBER(F13),G13-F13,"cadastro incompleto"))</f>
         <v>6182.85714285714</v>
       </c>
       <c r="I13" s="23">
-        <f>IF(OR(Config!$A$27="",G13="",G13=0),"",H13/G13)</f>
+        <f>IF(OR(Config!$A$27="",G13="",G13=0,NOT(ISNUMBER(H13))),"",H13/G13)</f>
         <v>0.650827067669173</v>
       </c>
       <c r="J13" s="25" t="str">
-        <f>IF(Config!$A$27="","",IF(Config!$E$27="Interno","Interno",IF(Config!$E$27="Proposta","Proposta",IF(AND(E13&lt;&gt;"",E13&gt;1),"Estourou as horas",IF(AND(I13&lt;&gt;"",I13&lt;0.2),"Margem baixa",IF(AND(E13&lt;&gt;"",E13&gt;0.85,Config!$E$27="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$27="","",IF(Config!$E$27="Interno","Interno",IF(Config!$E$27="Proposta","Proposta",IF(NOT(ISNUMBER(F13)),"Custo incompleto",IF(AND(E13&lt;&gt;"",E13&gt;1),"Estourou as horas",IF(AND(I13&lt;&gt;"",I13&lt;0.2),"Margem baixa",IF(AND(E13&lt;&gt;"",E13&gt;0.85,Config!$E$27="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v>Saudável</v>
       </c>
     </row>
@@ -1334,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24">
-        <f>IF(Config!$A$28="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$28))</f>
+        <f>IF(Config!$A$28="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$28)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$28)))</f>
         <v>0</v>
       </c>
       <c r="G14" s="24">
@@ -1342,15 +1348,15 @@
         <v>4500</v>
       </c>
       <c r="H14" s="24">
-        <f>IF(OR(Config!$A$28="",G14=""),"",G14-F14)</f>
+        <f>IF(OR(Config!$A$28="",G14=""),"",IF(ISNUMBER(F14),G14-F14,"cadastro incompleto"))</f>
         <v>4500</v>
       </c>
       <c r="I14" s="23">
-        <f>IF(OR(Config!$A$28="",G14="",G14=0),"",H14/G14)</f>
+        <f>IF(OR(Config!$A$28="",G14="",G14=0,NOT(ISNUMBER(H14))),"",H14/G14)</f>
         <v>1</v>
       </c>
       <c r="J14" s="25" t="str">
-        <f>IF(Config!$A$28="","",IF(Config!$E$28="Interno","Interno",IF(Config!$E$28="Proposta","Proposta",IF(AND(E14&lt;&gt;"",E14&gt;1),"Estourou as horas",IF(AND(I14&lt;&gt;"",I14&lt;0.2),"Margem baixa",IF(AND(E14&lt;&gt;"",E14&gt;0.85,Config!$E$28="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$28="","",IF(Config!$E$28="Interno","Interno",IF(Config!$E$28="Proposta","Proposta",IF(NOT(ISNUMBER(F14)),"Custo incompleto",IF(AND(E14&lt;&gt;"",E14&gt;1),"Estourou as horas",IF(AND(I14&lt;&gt;"",I14&lt;0.2),"Margem baixa",IF(AND(E14&lt;&gt;"",E14&gt;0.85,Config!$E$28="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v>Proposta</v>
       </c>
     </row>
@@ -1376,7 +1382,7 @@
         <v/>
       </c>
       <c r="F15" s="24">
-        <f>IF(Config!$A$29="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$29))</f>
+        <f>IF(Config!$A$29="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$29)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$29)))</f>
         <v>40097.9761904762</v>
       </c>
       <c r="G15" s="24">
@@ -1384,15 +1390,15 @@
         <v>0</v>
       </c>
       <c r="H15" s="24">
-        <f>IF(OR(Config!$A$29="",G15=""),"",G15-F15)</f>
+        <f>IF(OR(Config!$A$29="",G15=""),"",IF(ISNUMBER(F15),G15-F15,"cadastro incompleto"))</f>
         <v>-40097.9761904762</v>
       </c>
       <c r="I15" s="23">
-        <f>IF(OR(Config!$A$29="",G15="",G15=0),"",H15/G15)</f>
+        <f>IF(OR(Config!$A$29="",G15="",G15=0,NOT(ISNUMBER(H15))),"",H15/G15)</f>
         <v/>
       </c>
       <c r="J15" s="25" t="str">
-        <f>IF(Config!$A$29="","",IF(Config!$E$29="Interno","Interno",IF(Config!$E$29="Proposta","Proposta",IF(AND(E15&lt;&gt;"",E15&gt;1),"Estourou as horas",IF(AND(I15&lt;&gt;"",I15&lt;0.2),"Margem baixa",IF(AND(E15&lt;&gt;"",E15&gt;0.85,Config!$E$29="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$29="","",IF(Config!$E$29="Interno","Interno",IF(Config!$E$29="Proposta","Proposta",IF(NOT(ISNUMBER(F15)),"Custo incompleto",IF(AND(E15&lt;&gt;"",E15&gt;1),"Estourou as horas",IF(AND(I15&lt;&gt;"",I15&lt;0.2),"Margem baixa",IF(AND(E15&lt;&gt;"",E15&gt;0.85,Config!$E$29="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v>Interno</v>
       </c>
     </row>
@@ -1418,7 +1424,7 @@
         <v/>
       </c>
       <c r="F16" s="24">
-        <f>IF(Config!$A$30="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$30))</f>
+        <f>IF(Config!$A$30="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$30)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$30)))</f>
         <v>22889.2857142857</v>
       </c>
       <c r="G16" s="24">
@@ -1426,15 +1432,15 @@
         <v>0</v>
       </c>
       <c r="H16" s="24">
-        <f>IF(OR(Config!$A$30="",G16=""),"",G16-F16)</f>
+        <f>IF(OR(Config!$A$30="",G16=""),"",IF(ISNUMBER(F16),G16-F16,"cadastro incompleto"))</f>
         <v>-22889.2857142857</v>
       </c>
       <c r="I16" s="23">
-        <f>IF(OR(Config!$A$30="",G16="",G16=0),"",H16/G16)</f>
+        <f>IF(OR(Config!$A$30="",G16="",G16=0,NOT(ISNUMBER(H16))),"",H16/G16)</f>
         <v/>
       </c>
       <c r="J16" s="25" t="str">
-        <f>IF(Config!$A$30="","",IF(Config!$E$30="Interno","Interno",IF(Config!$E$30="Proposta","Proposta",IF(AND(E16&lt;&gt;"",E16&gt;1),"Estourou as horas",IF(AND(I16&lt;&gt;"",I16&lt;0.2),"Margem baixa",IF(AND(E16&lt;&gt;"",E16&gt;0.85,Config!$E$30="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$30="","",IF(Config!$E$30="Interno","Interno",IF(Config!$E$30="Proposta","Proposta",IF(NOT(ISNUMBER(F16)),"Custo incompleto",IF(AND(E16&lt;&gt;"",E16&gt;1),"Estourou as horas",IF(AND(I16&lt;&gt;"",I16&lt;0.2),"Margem baixa",IF(AND(E16&lt;&gt;"",E16&gt;0.85,Config!$E$30="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v>Interno</v>
       </c>
     </row>
@@ -1460,7 +1466,7 @@
         <v/>
       </c>
       <c r="F17" s="24">
-        <f>IF(Config!$A$31="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$31))</f>
+        <f>IF(Config!$A$31="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$31)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$31)))</f>
         <v/>
       </c>
       <c r="G17" s="24">
@@ -1468,15 +1474,15 @@
         <v/>
       </c>
       <c r="H17" s="24">
-        <f>IF(OR(Config!$A$31="",G17=""),"",G17-F17)</f>
+        <f>IF(OR(Config!$A$31="",G17=""),"",IF(ISNUMBER(F17),G17-F17,"cadastro incompleto"))</f>
         <v/>
       </c>
       <c r="I17" s="23">
-        <f>IF(OR(Config!$A$31="",G17="",G17=0),"",H17/G17)</f>
+        <f>IF(OR(Config!$A$31="",G17="",G17=0,NOT(ISNUMBER(H17))),"",H17/G17)</f>
         <v/>
       </c>
       <c r="J17" s="25">
-        <f>IF(Config!$A$31="","",IF(Config!$E$31="Interno","Interno",IF(Config!$E$31="Proposta","Proposta",IF(AND(E17&lt;&gt;"",E17&gt;1),"Estourou as horas",IF(AND(I17&lt;&gt;"",I17&lt;0.2),"Margem baixa",IF(AND(E17&lt;&gt;"",E17&gt;0.85,Config!$E$31="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$31="","",IF(Config!$E$31="Interno","Interno",IF(Config!$E$31="Proposta","Proposta",IF(NOT(ISNUMBER(F17)),"Custo incompleto",IF(AND(E17&lt;&gt;"",E17&gt;1),"Estourou as horas",IF(AND(I17&lt;&gt;"",I17&lt;0.2),"Margem baixa",IF(AND(E17&lt;&gt;"",E17&gt;0.85,Config!$E$31="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v/>
       </c>
     </row>
@@ -1502,7 +1508,7 @@
         <v/>
       </c>
       <c r="F18" s="24">
-        <f>IF(Config!$A$32="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$32))</f>
+        <f>IF(Config!$A$32="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$32)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$32)))</f>
         <v/>
       </c>
       <c r="G18" s="24">
@@ -1510,15 +1516,15 @@
         <v/>
       </c>
       <c r="H18" s="24">
-        <f>IF(OR(Config!$A$32="",G18=""),"",G18-F18)</f>
+        <f>IF(OR(Config!$A$32="",G18=""),"",IF(ISNUMBER(F18),G18-F18,"cadastro incompleto"))</f>
         <v/>
       </c>
       <c r="I18" s="23">
-        <f>IF(OR(Config!$A$32="",G18="",G18=0),"",H18/G18)</f>
+        <f>IF(OR(Config!$A$32="",G18="",G18=0,NOT(ISNUMBER(H18))),"",H18/G18)</f>
         <v/>
       </c>
       <c r="J18" s="25">
-        <f>IF(Config!$A$32="","",IF(Config!$E$32="Interno","Interno",IF(Config!$E$32="Proposta","Proposta",IF(AND(E18&lt;&gt;"",E18&gt;1),"Estourou as horas",IF(AND(I18&lt;&gt;"",I18&lt;0.2),"Margem baixa",IF(AND(E18&lt;&gt;"",E18&gt;0.85,Config!$E$32="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$32="","",IF(Config!$E$32="Interno","Interno",IF(Config!$E$32="Proposta","Proposta",IF(NOT(ISNUMBER(F18)),"Custo incompleto",IF(AND(E18&lt;&gt;"",E18&gt;1),"Estourou as horas",IF(AND(I18&lt;&gt;"",I18&lt;0.2),"Margem baixa",IF(AND(E18&lt;&gt;"",E18&gt;0.85,Config!$E$32="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v/>
       </c>
     </row>
@@ -1544,7 +1550,7 @@
         <v/>
       </c>
       <c r="F19" s="24">
-        <f>IF(Config!$A$33="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$33))</f>
+        <f>IF(Config!$A$33="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$33)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$33)))</f>
         <v/>
       </c>
       <c r="G19" s="24">
@@ -1552,15 +1558,15 @@
         <v/>
       </c>
       <c r="H19" s="24">
-        <f>IF(OR(Config!$A$33="",G19=""),"",G19-F19)</f>
+        <f>IF(OR(Config!$A$33="",G19=""),"",IF(ISNUMBER(F19),G19-F19,"cadastro incompleto"))</f>
         <v/>
       </c>
       <c r="I19" s="23">
-        <f>IF(OR(Config!$A$33="",G19="",G19=0),"",H19/G19)</f>
+        <f>IF(OR(Config!$A$33="",G19="",G19=0,NOT(ISNUMBER(H19))),"",H19/G19)</f>
         <v/>
       </c>
       <c r="J19" s="25">
-        <f>IF(Config!$A$33="","",IF(Config!$E$33="Interno","Interno",IF(Config!$E$33="Proposta","Proposta",IF(AND(E19&lt;&gt;"",E19&gt;1),"Estourou as horas",IF(AND(I19&lt;&gt;"",I19&lt;0.2),"Margem baixa",IF(AND(E19&lt;&gt;"",E19&gt;0.85,Config!$E$33="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$33="","",IF(Config!$E$33="Interno","Interno",IF(Config!$E$33="Proposta","Proposta",IF(NOT(ISNUMBER(F19)),"Custo incompleto",IF(AND(E19&lt;&gt;"",E19&gt;1),"Estourou as horas",IF(AND(I19&lt;&gt;"",I19&lt;0.2),"Margem baixa",IF(AND(E19&lt;&gt;"",E19&gt;0.85,Config!$E$33="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v/>
       </c>
     </row>
@@ -1586,7 +1592,7 @@
         <v/>
       </c>
       <c r="F20" s="24">
-        <f>IF(Config!$A$34="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$34))</f>
+        <f>IF(Config!$A$34="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$34)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$34)))</f>
         <v/>
       </c>
       <c r="G20" s="24">
@@ -1594,15 +1600,15 @@
         <v/>
       </c>
       <c r="H20" s="24">
-        <f>IF(OR(Config!$A$34="",G20=""),"",G20-F20)</f>
+        <f>IF(OR(Config!$A$34="",G20=""),"",IF(ISNUMBER(F20),G20-F20,"cadastro incompleto"))</f>
         <v/>
       </c>
       <c r="I20" s="23">
-        <f>IF(OR(Config!$A$34="",G20="",G20=0),"",H20/G20)</f>
+        <f>IF(OR(Config!$A$34="",G20="",G20=0,NOT(ISNUMBER(H20))),"",H20/G20)</f>
         <v/>
       </c>
       <c r="J20" s="25">
-        <f>IF(Config!$A$34="","",IF(Config!$E$34="Interno","Interno",IF(Config!$E$34="Proposta","Proposta",IF(AND(E20&lt;&gt;"",E20&gt;1),"Estourou as horas",IF(AND(I20&lt;&gt;"",I20&lt;0.2),"Margem baixa",IF(AND(E20&lt;&gt;"",E20&gt;0.85,Config!$E$34="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$34="","",IF(Config!$E$34="Interno","Interno",IF(Config!$E$34="Proposta","Proposta",IF(NOT(ISNUMBER(F20)),"Custo incompleto",IF(AND(E20&lt;&gt;"",E20&gt;1),"Estourou as horas",IF(AND(I20&lt;&gt;"",I20&lt;0.2),"Margem baixa",IF(AND(E20&lt;&gt;"",E20&gt;0.85,Config!$E$34="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v/>
       </c>
     </row>
@@ -1628,7 +1634,7 @@
         <v/>
       </c>
       <c r="F21" s="24">
-        <f>IF(Config!$A$35="","",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$35))</f>
+        <f>IF(Config!$A$35="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$C$5:$C$804,Config!$A$35)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$C$5:$C$804,Config!$A$35)))</f>
         <v/>
       </c>
       <c r="G21" s="24">
@@ -1636,15 +1642,15 @@
         <v/>
       </c>
       <c r="H21" s="24">
-        <f>IF(OR(Config!$A$35="",G21=""),"",G21-F21)</f>
+        <f>IF(OR(Config!$A$35="",G21=""),"",IF(ISNUMBER(F21),G21-F21,"cadastro incompleto"))</f>
         <v/>
       </c>
       <c r="I21" s="23">
-        <f>IF(OR(Config!$A$35="",G21="",G21=0),"",H21/G21)</f>
+        <f>IF(OR(Config!$A$35="",G21="",G21=0,NOT(ISNUMBER(H21))),"",H21/G21)</f>
         <v/>
       </c>
       <c r="J21" s="25">
-        <f>IF(Config!$A$35="","",IF(Config!$E$35="Interno","Interno",IF(Config!$E$35="Proposta","Proposta",IF(AND(E21&lt;&gt;"",E21&gt;1),"Estourou as horas",IF(AND(I21&lt;&gt;"",I21&lt;0.2),"Margem baixa",IF(AND(E21&lt;&gt;"",E21&gt;0.85,Config!$E$35="Em andamento"),"Perto do limite","Saudável"))))))</f>
+        <f>IF(Config!$A$35="","",IF(Config!$E$35="Interno","Interno",IF(Config!$E$35="Proposta","Proposta",IF(NOT(ISNUMBER(F21)),"Custo incompleto",IF(AND(E21&lt;&gt;"",E21&gt;1),"Estourou as horas",IF(AND(I21&lt;&gt;"",I21&lt;0.2),"Margem baixa",IF(AND(E21&lt;&gt;"",E21&gt;0.85,Config!$E$35="Em andamento"),"Perto do limite","Saudável")))))))</f>
         <v/>
       </c>
     </row>
@@ -1714,7 +1720,7 @@
         <v>0.382352941176471</v>
       </c>
       <c r="F25" s="24">
-        <f>IF(Config!$A$11="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$11,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$11="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$11,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$11,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v>4760</v>
       </c>
       <c r="G25" s="26">
@@ -1744,7 +1750,7 @@
         <v>0.878571428571429</v>
       </c>
       <c r="F26" s="24">
-        <f>IF(Config!$A$12="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$12,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$12="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$12,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$12,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v>3600</v>
       </c>
       <c r="G26" s="26">
@@ -1774,7 +1780,7 @@
         <v>0.591549295774648</v>
       </c>
       <c r="F27" s="24">
-        <f>IF(Config!$A$13="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$13,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$13="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$13,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$13,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v>3296.42857142857</v>
       </c>
       <c r="G27" s="26">
@@ -1804,7 +1810,7 @@
         <v>0.627737226277372</v>
       </c>
       <c r="F28" s="24">
-        <f>IF(Config!$A$14="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$14,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$14="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$14,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$14,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v>3310.83333333333</v>
       </c>
       <c r="G28" s="26">
@@ -1834,7 +1840,7 @@
         <v/>
       </c>
       <c r="F29" s="24">
-        <f>IF(Config!$A$15="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$15,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$15="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$15,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$15,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v/>
       </c>
       <c r="G29" s="26">
@@ -1864,7 +1870,7 @@
         <v/>
       </c>
       <c r="F30" s="24">
-        <f>IF(Config!$A$16="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$16,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$16="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$16,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$16,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v/>
       </c>
       <c r="G30" s="26">
@@ -1894,7 +1900,7 @@
         <v/>
       </c>
       <c r="F31" s="24">
-        <f>IF(Config!$A$17="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$17,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$17="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$17,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$17,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v/>
       </c>
       <c r="G31" s="26">
@@ -1924,7 +1930,7 @@
         <v/>
       </c>
       <c r="F32" s="24">
-        <f>IF(Config!$A$18="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$18,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$18="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$18,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$18,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v/>
       </c>
       <c r="G32" s="26">
@@ -1954,7 +1960,7 @@
         <v/>
       </c>
       <c r="F33" s="24">
-        <f>IF(Config!$A$19="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$19,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$19="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$19,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$19,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v/>
       </c>
       <c r="G33" s="26">
@@ -1984,7 +1990,7 @@
         <v/>
       </c>
       <c r="F34" s="24">
-        <f>IF(Config!$A$20="","",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$20,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5))</f>
+        <f>IF(Config!$A$20="","",IF(SUMIFS(Horas!$J$5:$J$804,Horas!$B$5:$B$804,Config!$A$20,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)&gt;0,"cadastro incompleto",SUMIFS(Horas!$F$5:$F$804,Horas!$B$5:$B$804,Config!$A$20,Horas!$G$5:$G$804,Config!$B$7,Horas!$H$5:$H$804,Config!$B$5)))</f>
         <v/>
       </c>
       <c r="G34" s="26">
@@ -2009,7 +2015,7 @@
   </mergeCells>
   <conditionalFormatting sqref="J10:J21">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(J10="Estourou as horas",J9="Margem baixa")</formula>
+      <formula>OR(J10="Estourou as horas",J10="Margem baixa",J10="Custo incompleto")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>J10="Perto do limite"</formula>
@@ -2592,7 +2598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I804"/>
+  <dimension ref="A1:J804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2604,6 +2610,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2706,6 +2713,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J5" s="36">
+        <f>IF(AND(B5&lt;&gt;"",E5&lt;&gt;"",NOT(ISNUMBER(F5))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="34" t="n">
@@ -2746,6 +2757,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J6" s="36">
+        <f>IF(AND(B6&lt;&gt;"",E6&lt;&gt;"",NOT(ISNUMBER(F6))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="34" t="n">
@@ -2786,6 +2801,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J7" s="36">
+        <f>IF(AND(B7&lt;&gt;"",E7&lt;&gt;"",NOT(ISNUMBER(F7))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="34" t="n">
@@ -2826,6 +2845,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J8" s="36">
+        <f>IF(AND(B8&lt;&gt;"",E8&lt;&gt;"",NOT(ISNUMBER(F8))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="34" t="n">
@@ -2866,6 +2889,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J9" s="36">
+        <f>IF(AND(B9&lt;&gt;"",E9&lt;&gt;"",NOT(ISNUMBER(F9))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="34" t="n">
@@ -2906,6 +2933,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J10" s="36">
+        <f>IF(AND(B10&lt;&gt;"",E10&lt;&gt;"",NOT(ISNUMBER(F10))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="34" t="n">
@@ -2946,6 +2977,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J11" s="36">
+        <f>IF(AND(B11&lt;&gt;"",E11&lt;&gt;"",NOT(ISNUMBER(F11))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="34" t="n">
@@ -2986,6 +3021,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J12" s="36">
+        <f>IF(AND(B12&lt;&gt;"",E12&lt;&gt;"",NOT(ISNUMBER(F12))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="n">
@@ -3026,6 +3065,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J13" s="36">
+        <f>IF(AND(B13&lt;&gt;"",E13&lt;&gt;"",NOT(ISNUMBER(F13))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="34" t="n">
@@ -3066,6 +3109,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J14" s="36">
+        <f>IF(AND(B14&lt;&gt;"",E14&lt;&gt;"",NOT(ISNUMBER(F14))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="34" t="n">
@@ -3106,6 +3153,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J15" s="36">
+        <f>IF(AND(B15&lt;&gt;"",E15&lt;&gt;"",NOT(ISNUMBER(F15))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="34" t="n">
@@ -3146,6 +3197,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J16" s="36">
+        <f>IF(AND(B16&lt;&gt;"",E16&lt;&gt;"",NOT(ISNUMBER(F16))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="34" t="n">
@@ -3186,6 +3241,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J17" s="36">
+        <f>IF(AND(B17&lt;&gt;"",E17&lt;&gt;"",NOT(ISNUMBER(F17))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="n">
@@ -3226,6 +3285,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J18" s="36">
+        <f>IF(AND(B18&lt;&gt;"",E18&lt;&gt;"",NOT(ISNUMBER(F18))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="34" t="n">
@@ -3266,6 +3329,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J19" s="36">
+        <f>IF(AND(B19&lt;&gt;"",E19&lt;&gt;"",NOT(ISNUMBER(F19))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="34" t="n">
@@ -3306,6 +3373,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J20" s="36">
+        <f>IF(AND(B20&lt;&gt;"",E20&lt;&gt;"",NOT(ISNUMBER(F20))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="34" t="n">
@@ -3346,6 +3417,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J21" s="36">
+        <f>IF(AND(B21&lt;&gt;"",E21&lt;&gt;"",NOT(ISNUMBER(F21))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="34" t="n">
@@ -3386,6 +3461,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J22" s="36">
+        <f>IF(AND(B22&lt;&gt;"",E22&lt;&gt;"",NOT(ISNUMBER(F22))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="34" t="n">
@@ -3426,6 +3505,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J23" s="36">
+        <f>IF(AND(B23&lt;&gt;"",E23&lt;&gt;"",NOT(ISNUMBER(F23))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="34" t="n">
@@ -3466,6 +3549,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J24" s="36">
+        <f>IF(AND(B24&lt;&gt;"",E24&lt;&gt;"",NOT(ISNUMBER(F24))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="34" t="n">
@@ -3506,6 +3593,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J25" s="36">
+        <f>IF(AND(B25&lt;&gt;"",E25&lt;&gt;"",NOT(ISNUMBER(F25))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="34" t="n">
@@ -3546,6 +3637,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J26" s="36">
+        <f>IF(AND(B26&lt;&gt;"",E26&lt;&gt;"",NOT(ISNUMBER(F26))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="34" t="n">
@@ -3586,6 +3681,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J27" s="36">
+        <f>IF(AND(B27&lt;&gt;"",E27&lt;&gt;"",NOT(ISNUMBER(F27))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="34" t="n">
@@ -3626,6 +3725,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J28" s="36">
+        <f>IF(AND(B28&lt;&gt;"",E28&lt;&gt;"",NOT(ISNUMBER(F28))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="34" t="n">
@@ -3666,6 +3769,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J29" s="36">
+        <f>IF(AND(B29&lt;&gt;"",E29&lt;&gt;"",NOT(ISNUMBER(F29))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="34" t="n">
@@ -3706,6 +3813,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J30" s="36">
+        <f>IF(AND(B30&lt;&gt;"",E30&lt;&gt;"",NOT(ISNUMBER(F30))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="34" t="n">
@@ -3746,6 +3857,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J31" s="36">
+        <f>IF(AND(B31&lt;&gt;"",E31&lt;&gt;"",NOT(ISNUMBER(F31))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="34" t="n">
@@ -3786,6 +3901,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J32" s="36">
+        <f>IF(AND(B32&lt;&gt;"",E32&lt;&gt;"",NOT(ISNUMBER(F32))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="34" t="n">
@@ -3826,6 +3945,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J33" s="36">
+        <f>IF(AND(B33&lt;&gt;"",E33&lt;&gt;"",NOT(ISNUMBER(F33))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="34" t="n">
@@ -3866,6 +3989,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J34" s="36">
+        <f>IF(AND(B34&lt;&gt;"",E34&lt;&gt;"",NOT(ISNUMBER(F34))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="34" t="n">
@@ -3906,6 +4033,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J35" s="36">
+        <f>IF(AND(B35&lt;&gt;"",E35&lt;&gt;"",NOT(ISNUMBER(F35))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="34" t="n">
@@ -3946,6 +4077,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J36" s="36">
+        <f>IF(AND(B36&lt;&gt;"",E36&lt;&gt;"",NOT(ISNUMBER(F36))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="34" t="n">
@@ -3986,6 +4121,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J37" s="36">
+        <f>IF(AND(B37&lt;&gt;"",E37&lt;&gt;"",NOT(ISNUMBER(F37))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="34" t="n">
@@ -4026,6 +4165,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J38" s="36">
+        <f>IF(AND(B38&lt;&gt;"",E38&lt;&gt;"",NOT(ISNUMBER(F38))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="34" t="n">
@@ -4066,6 +4209,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J39" s="36">
+        <f>IF(AND(B39&lt;&gt;"",E39&lt;&gt;"",NOT(ISNUMBER(F39))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="34" t="n">
@@ -4106,6 +4253,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J40" s="36">
+        <f>IF(AND(B40&lt;&gt;"",E40&lt;&gt;"",NOT(ISNUMBER(F40))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="34" t="n">
@@ -4146,6 +4297,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J41" s="36">
+        <f>IF(AND(B41&lt;&gt;"",E41&lt;&gt;"",NOT(ISNUMBER(F41))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="34" t="n">
@@ -4186,6 +4341,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J42" s="36">
+        <f>IF(AND(B42&lt;&gt;"",E42&lt;&gt;"",NOT(ISNUMBER(F42))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="34" t="n">
@@ -4226,6 +4385,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J43" s="36">
+        <f>IF(AND(B43&lt;&gt;"",E43&lt;&gt;"",NOT(ISNUMBER(F43))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="34" t="n">
@@ -4266,6 +4429,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J44" s="36">
+        <f>IF(AND(B44&lt;&gt;"",E44&lt;&gt;"",NOT(ISNUMBER(F44))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="34" t="n">
@@ -4306,6 +4473,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J45" s="36">
+        <f>IF(AND(B45&lt;&gt;"",E45&lt;&gt;"",NOT(ISNUMBER(F45))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="34" t="n">
@@ -4346,6 +4517,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J46" s="36">
+        <f>IF(AND(B46&lt;&gt;"",E46&lt;&gt;"",NOT(ISNUMBER(F46))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="34" t="n">
@@ -4386,6 +4561,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J47" s="36">
+        <f>IF(AND(B47&lt;&gt;"",E47&lt;&gt;"",NOT(ISNUMBER(F47))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="34" t="n">
@@ -4426,6 +4605,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J48" s="36">
+        <f>IF(AND(B48&lt;&gt;"",E48&lt;&gt;"",NOT(ISNUMBER(F48))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="34" t="n">
@@ -4466,6 +4649,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J49" s="36">
+        <f>IF(AND(B49&lt;&gt;"",E49&lt;&gt;"",NOT(ISNUMBER(F49))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="34" t="n">
@@ -4506,6 +4693,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J50" s="36">
+        <f>IF(AND(B50&lt;&gt;"",E50&lt;&gt;"",NOT(ISNUMBER(F50))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="34" t="n">
@@ -4546,6 +4737,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J51" s="36">
+        <f>IF(AND(B51&lt;&gt;"",E51&lt;&gt;"",NOT(ISNUMBER(F51))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="34" t="n">
@@ -4586,6 +4781,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J52" s="36">
+        <f>IF(AND(B52&lt;&gt;"",E52&lt;&gt;"",NOT(ISNUMBER(F52))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="34" t="n">
@@ -4626,6 +4825,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J53" s="36">
+        <f>IF(AND(B53&lt;&gt;"",E53&lt;&gt;"",NOT(ISNUMBER(F53))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="34" t="n">
@@ -4666,6 +4869,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J54" s="36">
+        <f>IF(AND(B54&lt;&gt;"",E54&lt;&gt;"",NOT(ISNUMBER(F54))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="34" t="n">
@@ -4706,6 +4913,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J55" s="36">
+        <f>IF(AND(B55&lt;&gt;"",E55&lt;&gt;"",NOT(ISNUMBER(F55))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="34" t="n">
@@ -4746,6 +4957,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J56" s="36">
+        <f>IF(AND(B56&lt;&gt;"",E56&lt;&gt;"",NOT(ISNUMBER(F56))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="34" t="n">
@@ -4786,6 +5001,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J57" s="36">
+        <f>IF(AND(B57&lt;&gt;"",E57&lt;&gt;"",NOT(ISNUMBER(F57))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="34" t="n">
@@ -4826,6 +5045,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J58" s="36">
+        <f>IF(AND(B58&lt;&gt;"",E58&lt;&gt;"",NOT(ISNUMBER(F58))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="34" t="n">
@@ -4866,6 +5089,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J59" s="36">
+        <f>IF(AND(B59&lt;&gt;"",E59&lt;&gt;"",NOT(ISNUMBER(F59))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="34" t="n">
@@ -4906,6 +5133,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J60" s="36">
+        <f>IF(AND(B60&lt;&gt;"",E60&lt;&gt;"",NOT(ISNUMBER(F60))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="34" t="n">
@@ -4946,6 +5177,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J61" s="36">
+        <f>IF(AND(B61&lt;&gt;"",E61&lt;&gt;"",NOT(ISNUMBER(F61))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="34" t="n">
@@ -4986,6 +5221,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J62" s="36">
+        <f>IF(AND(B62&lt;&gt;"",E62&lt;&gt;"",NOT(ISNUMBER(F62))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="34" t="n">
@@ -5026,6 +5265,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J63" s="36">
+        <f>IF(AND(B63&lt;&gt;"",E63&lt;&gt;"",NOT(ISNUMBER(F63))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="34" t="n">
@@ -5066,6 +5309,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J64" s="36">
+        <f>IF(AND(B64&lt;&gt;"",E64&lt;&gt;"",NOT(ISNUMBER(F64))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="34" t="n">
@@ -5106,6 +5353,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J65" s="36">
+        <f>IF(AND(B65&lt;&gt;"",E65&lt;&gt;"",NOT(ISNUMBER(F65))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="34" t="n">
@@ -5146,6 +5397,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J66" s="36">
+        <f>IF(AND(B66&lt;&gt;"",E66&lt;&gt;"",NOT(ISNUMBER(F66))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="34" t="n">
@@ -5186,6 +5441,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J67" s="36">
+        <f>IF(AND(B67&lt;&gt;"",E67&lt;&gt;"",NOT(ISNUMBER(F67))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="34" t="n">
@@ -5226,6 +5485,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J68" s="36">
+        <f>IF(AND(B68&lt;&gt;"",E68&lt;&gt;"",NOT(ISNUMBER(F68))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="34" t="n">
@@ -5266,6 +5529,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J69" s="36">
+        <f>IF(AND(B69&lt;&gt;"",E69&lt;&gt;"",NOT(ISNUMBER(F69))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="34" t="n">
@@ -5306,6 +5573,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J70" s="36">
+        <f>IF(AND(B70&lt;&gt;"",E70&lt;&gt;"",NOT(ISNUMBER(F70))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="34" t="n">
@@ -5346,6 +5617,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J71" s="36">
+        <f>IF(AND(B71&lt;&gt;"",E71&lt;&gt;"",NOT(ISNUMBER(F71))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="34" t="n">
@@ -5386,6 +5661,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J72" s="36">
+        <f>IF(AND(B72&lt;&gt;"",E72&lt;&gt;"",NOT(ISNUMBER(F72))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="34" t="n">
@@ -5426,6 +5705,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J73" s="36">
+        <f>IF(AND(B73&lt;&gt;"",E73&lt;&gt;"",NOT(ISNUMBER(F73))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="34" t="n">
@@ -5466,6 +5749,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J74" s="36">
+        <f>IF(AND(B74&lt;&gt;"",E74&lt;&gt;"",NOT(ISNUMBER(F74))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="34" t="n">
@@ -5506,6 +5793,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J75" s="36">
+        <f>IF(AND(B75&lt;&gt;"",E75&lt;&gt;"",NOT(ISNUMBER(F75))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="34" t="n">
@@ -5546,6 +5837,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J76" s="36">
+        <f>IF(AND(B76&lt;&gt;"",E76&lt;&gt;"",NOT(ISNUMBER(F76))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="34" t="n">
@@ -5586,6 +5881,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J77" s="36">
+        <f>IF(AND(B77&lt;&gt;"",E77&lt;&gt;"",NOT(ISNUMBER(F77))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="34" t="n">
@@ -5626,6 +5925,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J78" s="36">
+        <f>IF(AND(B78&lt;&gt;"",E78&lt;&gt;"",NOT(ISNUMBER(F78))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="34" t="n">
@@ -5666,6 +5969,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J79" s="36">
+        <f>IF(AND(B79&lt;&gt;"",E79&lt;&gt;"",NOT(ISNUMBER(F79))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="34" t="n">
@@ -5706,6 +6013,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J80" s="36">
+        <f>IF(AND(B80&lt;&gt;"",E80&lt;&gt;"",NOT(ISNUMBER(F80))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="34" t="n">
@@ -5746,6 +6057,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J81" s="36">
+        <f>IF(AND(B81&lt;&gt;"",E81&lt;&gt;"",NOT(ISNUMBER(F81))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="34" t="n">
@@ -5786,6 +6101,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J82" s="36">
+        <f>IF(AND(B82&lt;&gt;"",E82&lt;&gt;"",NOT(ISNUMBER(F82))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="34" t="n">
@@ -5826,6 +6145,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J83" s="36">
+        <f>IF(AND(B83&lt;&gt;"",E83&lt;&gt;"",NOT(ISNUMBER(F83))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="34" t="n">
@@ -5866,6 +6189,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J84" s="36">
+        <f>IF(AND(B84&lt;&gt;"",E84&lt;&gt;"",NOT(ISNUMBER(F84))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="34" t="n">
@@ -5906,6 +6233,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J85" s="36">
+        <f>IF(AND(B85&lt;&gt;"",E85&lt;&gt;"",NOT(ISNUMBER(F85))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="34" t="n">
@@ -5946,6 +6277,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J86" s="36">
+        <f>IF(AND(B86&lt;&gt;"",E86&lt;&gt;"",NOT(ISNUMBER(F86))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="34" t="n">
@@ -5986,6 +6321,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J87" s="36">
+        <f>IF(AND(B87&lt;&gt;"",E87&lt;&gt;"",NOT(ISNUMBER(F87))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="34" t="n">
@@ -6026,6 +6365,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J88" s="36">
+        <f>IF(AND(B88&lt;&gt;"",E88&lt;&gt;"",NOT(ISNUMBER(F88))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="34" t="n">
@@ -6066,6 +6409,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J89" s="36">
+        <f>IF(AND(B89&lt;&gt;"",E89&lt;&gt;"",NOT(ISNUMBER(F89))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="34" t="n">
@@ -6106,6 +6453,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J90" s="36">
+        <f>IF(AND(B90&lt;&gt;"",E90&lt;&gt;"",NOT(ISNUMBER(F90))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="34" t="n">
@@ -6146,6 +6497,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J91" s="36">
+        <f>IF(AND(B91&lt;&gt;"",E91&lt;&gt;"",NOT(ISNUMBER(F91))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="34" t="n">
@@ -6186,6 +6541,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J92" s="36">
+        <f>IF(AND(B92&lt;&gt;"",E92&lt;&gt;"",NOT(ISNUMBER(F92))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="34" t="n">
@@ -6226,6 +6585,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J93" s="36">
+        <f>IF(AND(B93&lt;&gt;"",E93&lt;&gt;"",NOT(ISNUMBER(F93))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="34" t="n">
@@ -6266,6 +6629,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J94" s="36">
+        <f>IF(AND(B94&lt;&gt;"",E94&lt;&gt;"",NOT(ISNUMBER(F94))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="34" t="n">
@@ -6306,6 +6673,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J95" s="36">
+        <f>IF(AND(B95&lt;&gt;"",E95&lt;&gt;"",NOT(ISNUMBER(F95))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="34" t="n">
@@ -6346,6 +6717,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J96" s="36">
+        <f>IF(AND(B96&lt;&gt;"",E96&lt;&gt;"",NOT(ISNUMBER(F96))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="34" t="n">
@@ -6386,6 +6761,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J97" s="36">
+        <f>IF(AND(B97&lt;&gt;"",E97&lt;&gt;"",NOT(ISNUMBER(F97))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="34" t="n">
@@ -6426,6 +6805,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J98" s="36">
+        <f>IF(AND(B98&lt;&gt;"",E98&lt;&gt;"",NOT(ISNUMBER(F98))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="34" t="n">
@@ -6466,6 +6849,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J99" s="36">
+        <f>IF(AND(B99&lt;&gt;"",E99&lt;&gt;"",NOT(ISNUMBER(F99))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="34" t="n">
@@ -6506,6 +6893,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J100" s="36">
+        <f>IF(AND(B100&lt;&gt;"",E100&lt;&gt;"",NOT(ISNUMBER(F100))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="34" t="n">
@@ -6546,6 +6937,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J101" s="36">
+        <f>IF(AND(B101&lt;&gt;"",E101&lt;&gt;"",NOT(ISNUMBER(F101))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="34" t="n">
@@ -6586,6 +6981,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J102" s="36">
+        <f>IF(AND(B102&lt;&gt;"",E102&lt;&gt;"",NOT(ISNUMBER(F102))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="34" t="n">
@@ -6626,6 +7025,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J103" s="36">
+        <f>IF(AND(B103&lt;&gt;"",E103&lt;&gt;"",NOT(ISNUMBER(F103))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="34" t="n">
@@ -6666,6 +7069,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J104" s="36">
+        <f>IF(AND(B104&lt;&gt;"",E104&lt;&gt;"",NOT(ISNUMBER(F104))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="34" t="n">
@@ -6706,6 +7113,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J105" s="36">
+        <f>IF(AND(B105&lt;&gt;"",E105&lt;&gt;"",NOT(ISNUMBER(F105))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="34" t="n">
@@ -6746,6 +7157,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J106" s="36">
+        <f>IF(AND(B106&lt;&gt;"",E106&lt;&gt;"",NOT(ISNUMBER(F106))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="34" t="n">
@@ -6786,6 +7201,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J107" s="36">
+        <f>IF(AND(B107&lt;&gt;"",E107&lt;&gt;"",NOT(ISNUMBER(F107))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="34" t="n">
@@ -6826,6 +7245,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J108" s="36">
+        <f>IF(AND(B108&lt;&gt;"",E108&lt;&gt;"",NOT(ISNUMBER(F108))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="34" t="n">
@@ -6866,6 +7289,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J109" s="36">
+        <f>IF(AND(B109&lt;&gt;"",E109&lt;&gt;"",NOT(ISNUMBER(F109))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="34" t="n">
@@ -6906,6 +7333,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J110" s="36">
+        <f>IF(AND(B110&lt;&gt;"",E110&lt;&gt;"",NOT(ISNUMBER(F110))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="34" t="n">
@@ -6946,6 +7377,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J111" s="36">
+        <f>IF(AND(B111&lt;&gt;"",E111&lt;&gt;"",NOT(ISNUMBER(F111))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="34" t="n">
@@ -6986,6 +7421,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J112" s="36">
+        <f>IF(AND(B112&lt;&gt;"",E112&lt;&gt;"",NOT(ISNUMBER(F112))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="34" t="n">
@@ -7026,6 +7465,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J113" s="36">
+        <f>IF(AND(B113&lt;&gt;"",E113&lt;&gt;"",NOT(ISNUMBER(F113))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="34" t="n">
@@ -7066,6 +7509,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J114" s="36">
+        <f>IF(AND(B114&lt;&gt;"",E114&lt;&gt;"",NOT(ISNUMBER(F114))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="34" t="n">
@@ -7106,6 +7553,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J115" s="36">
+        <f>IF(AND(B115&lt;&gt;"",E115&lt;&gt;"",NOT(ISNUMBER(F115))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="34" t="n">
@@ -7146,6 +7597,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J116" s="36">
+        <f>IF(AND(B116&lt;&gt;"",E116&lt;&gt;"",NOT(ISNUMBER(F116))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="34" t="n">
@@ -7186,6 +7641,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J117" s="36">
+        <f>IF(AND(B117&lt;&gt;"",E117&lt;&gt;"",NOT(ISNUMBER(F117))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="34" t="n">
@@ -7226,6 +7685,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J118" s="36">
+        <f>IF(AND(B118&lt;&gt;"",E118&lt;&gt;"",NOT(ISNUMBER(F118))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="34" t="n">
@@ -7266,6 +7729,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J119" s="36">
+        <f>IF(AND(B119&lt;&gt;"",E119&lt;&gt;"",NOT(ISNUMBER(F119))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="34" t="n">
@@ -7306,6 +7773,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J120" s="36">
+        <f>IF(AND(B120&lt;&gt;"",E120&lt;&gt;"",NOT(ISNUMBER(F120))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="34" t="n">
@@ -7346,6 +7817,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J121" s="36">
+        <f>IF(AND(B121&lt;&gt;"",E121&lt;&gt;"",NOT(ISNUMBER(F121))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="34" t="n">
@@ -7386,6 +7861,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J122" s="36">
+        <f>IF(AND(B122&lt;&gt;"",E122&lt;&gt;"",NOT(ISNUMBER(F122))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="34" t="n">
@@ -7426,6 +7905,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J123" s="36">
+        <f>IF(AND(B123&lt;&gt;"",E123&lt;&gt;"",NOT(ISNUMBER(F123))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="34" t="n">
@@ -7466,6 +7949,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J124" s="36">
+        <f>IF(AND(B124&lt;&gt;"",E124&lt;&gt;"",NOT(ISNUMBER(F124))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="34" t="n">
@@ -7506,6 +7993,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J125" s="36">
+        <f>IF(AND(B125&lt;&gt;"",E125&lt;&gt;"",NOT(ISNUMBER(F125))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="34" t="n">
@@ -7546,6 +8037,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J126" s="36">
+        <f>IF(AND(B126&lt;&gt;"",E126&lt;&gt;"",NOT(ISNUMBER(F126))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="34" t="n">
@@ -7586,6 +8081,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J127" s="36">
+        <f>IF(AND(B127&lt;&gt;"",E127&lt;&gt;"",NOT(ISNUMBER(F127))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="34" t="n">
@@ -7626,6 +8125,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J128" s="36">
+        <f>IF(AND(B128&lt;&gt;"",E128&lt;&gt;"",NOT(ISNUMBER(F128))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="34" t="n">
@@ -7666,6 +8169,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J129" s="36">
+        <f>IF(AND(B129&lt;&gt;"",E129&lt;&gt;"",NOT(ISNUMBER(F129))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="34" t="n">
@@ -7706,6 +8213,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J130" s="36">
+        <f>IF(AND(B130&lt;&gt;"",E130&lt;&gt;"",NOT(ISNUMBER(F130))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="34" t="n">
@@ -7746,6 +8257,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J131" s="36">
+        <f>IF(AND(B131&lt;&gt;"",E131&lt;&gt;"",NOT(ISNUMBER(F131))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="34" t="n">
@@ -7786,6 +8301,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J132" s="36">
+        <f>IF(AND(B132&lt;&gt;"",E132&lt;&gt;"",NOT(ISNUMBER(F132))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="34" t="n">
@@ -7826,6 +8345,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J133" s="36">
+        <f>IF(AND(B133&lt;&gt;"",E133&lt;&gt;"",NOT(ISNUMBER(F133))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="34" t="n">
@@ -7866,6 +8389,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J134" s="36">
+        <f>IF(AND(B134&lt;&gt;"",E134&lt;&gt;"",NOT(ISNUMBER(F134))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="34" t="n">
@@ -7906,6 +8433,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J135" s="36">
+        <f>IF(AND(B135&lt;&gt;"",E135&lt;&gt;"",NOT(ISNUMBER(F135))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="34" t="n">
@@ -7946,6 +8477,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J136" s="36">
+        <f>IF(AND(B136&lt;&gt;"",E136&lt;&gt;"",NOT(ISNUMBER(F136))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="34" t="n">
@@ -7986,6 +8521,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J137" s="36">
+        <f>IF(AND(B137&lt;&gt;"",E137&lt;&gt;"",NOT(ISNUMBER(F137))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="34" t="n">
@@ -8026,6 +8565,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J138" s="36">
+        <f>IF(AND(B138&lt;&gt;"",E138&lt;&gt;"",NOT(ISNUMBER(F138))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="34" t="n">
@@ -8066,6 +8609,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J139" s="36">
+        <f>IF(AND(B139&lt;&gt;"",E139&lt;&gt;"",NOT(ISNUMBER(F139))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="34" t="n">
@@ -8106,6 +8653,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J140" s="36">
+        <f>IF(AND(B140&lt;&gt;"",E140&lt;&gt;"",NOT(ISNUMBER(F140))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="34" t="n">
@@ -8146,6 +8697,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J141" s="36">
+        <f>IF(AND(B141&lt;&gt;"",E141&lt;&gt;"",NOT(ISNUMBER(F141))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="34" t="n">
@@ -8186,6 +8741,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J142" s="36">
+        <f>IF(AND(B142&lt;&gt;"",E142&lt;&gt;"",NOT(ISNUMBER(F142))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="34" t="n">
@@ -8226,6 +8785,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J143" s="36">
+        <f>IF(AND(B143&lt;&gt;"",E143&lt;&gt;"",NOT(ISNUMBER(F143))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="34" t="n">
@@ -8266,6 +8829,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J144" s="36">
+        <f>IF(AND(B144&lt;&gt;"",E144&lt;&gt;"",NOT(ISNUMBER(F144))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="34" t="n">
@@ -8306,6 +8873,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J145" s="36">
+        <f>IF(AND(B145&lt;&gt;"",E145&lt;&gt;"",NOT(ISNUMBER(F145))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="34" t="n">
@@ -8346,6 +8917,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J146" s="36">
+        <f>IF(AND(B146&lt;&gt;"",E146&lt;&gt;"",NOT(ISNUMBER(F146))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="34" t="n">
@@ -8386,6 +8961,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J147" s="36">
+        <f>IF(AND(B147&lt;&gt;"",E147&lt;&gt;"",NOT(ISNUMBER(F147))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="34" t="n">
@@ -8426,6 +9005,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J148" s="36">
+        <f>IF(AND(B148&lt;&gt;"",E148&lt;&gt;"",NOT(ISNUMBER(F148))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="34" t="n">
@@ -8466,6 +9049,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J149" s="36">
+        <f>IF(AND(B149&lt;&gt;"",E149&lt;&gt;"",NOT(ISNUMBER(F149))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="34" t="n">
@@ -8506,6 +9093,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J150" s="36">
+        <f>IF(AND(B150&lt;&gt;"",E150&lt;&gt;"",NOT(ISNUMBER(F150))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="34" t="n">
@@ -8546,6 +9137,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J151" s="36">
+        <f>IF(AND(B151&lt;&gt;"",E151&lt;&gt;"",NOT(ISNUMBER(F151))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="34" t="n">
@@ -8586,6 +9181,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J152" s="36">
+        <f>IF(AND(B152&lt;&gt;"",E152&lt;&gt;"",NOT(ISNUMBER(F152))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="34" t="n">
@@ -8626,6 +9225,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J153" s="36">
+        <f>IF(AND(B153&lt;&gt;"",E153&lt;&gt;"",NOT(ISNUMBER(F153))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="34" t="n">
@@ -8666,6 +9269,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J154" s="36">
+        <f>IF(AND(B154&lt;&gt;"",E154&lt;&gt;"",NOT(ISNUMBER(F154))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="34" t="n">
@@ -8706,6 +9313,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J155" s="36">
+        <f>IF(AND(B155&lt;&gt;"",E155&lt;&gt;"",NOT(ISNUMBER(F155))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="34" t="n">
@@ -8746,6 +9357,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J156" s="36">
+        <f>IF(AND(B156&lt;&gt;"",E156&lt;&gt;"",NOT(ISNUMBER(F156))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="34" t="n">
@@ -8786,6 +9401,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J157" s="36">
+        <f>IF(AND(B157&lt;&gt;"",E157&lt;&gt;"",NOT(ISNUMBER(F157))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="34" t="n">
@@ -8826,6 +9445,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J158" s="36">
+        <f>IF(AND(B158&lt;&gt;"",E158&lt;&gt;"",NOT(ISNUMBER(F158))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="34" t="n">
@@ -8866,6 +9489,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J159" s="36">
+        <f>IF(AND(B159&lt;&gt;"",E159&lt;&gt;"",NOT(ISNUMBER(F159))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="34" t="n">
@@ -8906,6 +9533,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J160" s="36">
+        <f>IF(AND(B160&lt;&gt;"",E160&lt;&gt;"",NOT(ISNUMBER(F160))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="34" t="n">
@@ -8946,6 +9577,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J161" s="36">
+        <f>IF(AND(B161&lt;&gt;"",E161&lt;&gt;"",NOT(ISNUMBER(F161))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="34" t="n">
@@ -8986,6 +9621,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J162" s="36">
+        <f>IF(AND(B162&lt;&gt;"",E162&lt;&gt;"",NOT(ISNUMBER(F162))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="34" t="n">
@@ -9026,6 +9665,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J163" s="36">
+        <f>IF(AND(B163&lt;&gt;"",E163&lt;&gt;"",NOT(ISNUMBER(F163))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="34" t="n">
@@ -9066,6 +9709,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J164" s="36">
+        <f>IF(AND(B164&lt;&gt;"",E164&lt;&gt;"",NOT(ISNUMBER(F164))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="34" t="n">
@@ -9106,6 +9753,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J165" s="36">
+        <f>IF(AND(B165&lt;&gt;"",E165&lt;&gt;"",NOT(ISNUMBER(F165))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="34" t="n">
@@ -9146,6 +9797,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J166" s="36">
+        <f>IF(AND(B166&lt;&gt;"",E166&lt;&gt;"",NOT(ISNUMBER(F166))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="34" t="n">
@@ -9186,6 +9841,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J167" s="36">
+        <f>IF(AND(B167&lt;&gt;"",E167&lt;&gt;"",NOT(ISNUMBER(F167))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="34" t="n">
@@ -9226,6 +9885,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J168" s="36">
+        <f>IF(AND(B168&lt;&gt;"",E168&lt;&gt;"",NOT(ISNUMBER(F168))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="34" t="n">
@@ -9266,6 +9929,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J169" s="36">
+        <f>IF(AND(B169&lt;&gt;"",E169&lt;&gt;"",NOT(ISNUMBER(F169))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="34" t="n">
@@ -9306,6 +9973,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J170" s="36">
+        <f>IF(AND(B170&lt;&gt;"",E170&lt;&gt;"",NOT(ISNUMBER(F170))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="34" t="n">
@@ -9346,6 +10017,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J171" s="36">
+        <f>IF(AND(B171&lt;&gt;"",E171&lt;&gt;"",NOT(ISNUMBER(F171))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="34" t="n">
@@ -9386,6 +10061,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J172" s="36">
+        <f>IF(AND(B172&lt;&gt;"",E172&lt;&gt;"",NOT(ISNUMBER(F172))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="34" t="n">
@@ -9426,6 +10105,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J173" s="36">
+        <f>IF(AND(B173&lt;&gt;"",E173&lt;&gt;"",NOT(ISNUMBER(F173))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="34" t="n">
@@ -9466,6 +10149,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J174" s="36">
+        <f>IF(AND(B174&lt;&gt;"",E174&lt;&gt;"",NOT(ISNUMBER(F174))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="34" t="n">
@@ -9506,6 +10193,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J175" s="36">
+        <f>IF(AND(B175&lt;&gt;"",E175&lt;&gt;"",NOT(ISNUMBER(F175))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="34" t="n">
@@ -9546,6 +10237,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J176" s="36">
+        <f>IF(AND(B176&lt;&gt;"",E176&lt;&gt;"",NOT(ISNUMBER(F176))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="34" t="n">
@@ -9586,6 +10281,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J177" s="36">
+        <f>IF(AND(B177&lt;&gt;"",E177&lt;&gt;"",NOT(ISNUMBER(F177))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="34" t="n">
@@ -9626,6 +10325,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J178" s="36">
+        <f>IF(AND(B178&lt;&gt;"",E178&lt;&gt;"",NOT(ISNUMBER(F178))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="34" t="n">
@@ -9666,6 +10369,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J179" s="36">
+        <f>IF(AND(B179&lt;&gt;"",E179&lt;&gt;"",NOT(ISNUMBER(F179))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="34" t="n">
@@ -9706,6 +10413,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J180" s="36">
+        <f>IF(AND(B180&lt;&gt;"",E180&lt;&gt;"",NOT(ISNUMBER(F180))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="34" t="n">
@@ -9746,6 +10457,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J181" s="36">
+        <f>IF(AND(B181&lt;&gt;"",E181&lt;&gt;"",NOT(ISNUMBER(F181))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="34" t="n">
@@ -9786,6 +10501,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J182" s="36">
+        <f>IF(AND(B182&lt;&gt;"",E182&lt;&gt;"",NOT(ISNUMBER(F182))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="34" t="n">
@@ -9826,6 +10545,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J183" s="36">
+        <f>IF(AND(B183&lt;&gt;"",E183&lt;&gt;"",NOT(ISNUMBER(F183))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="34" t="n">
@@ -9866,6 +10589,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J184" s="36">
+        <f>IF(AND(B184&lt;&gt;"",E184&lt;&gt;"",NOT(ISNUMBER(F184))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="34" t="n">
@@ -9906,6 +10633,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J185" s="36">
+        <f>IF(AND(B185&lt;&gt;"",E185&lt;&gt;"",NOT(ISNUMBER(F185))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="34" t="n">
@@ -9946,6 +10677,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J186" s="36">
+        <f>IF(AND(B186&lt;&gt;"",E186&lt;&gt;"",NOT(ISNUMBER(F186))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="34" t="n">
@@ -9986,6 +10721,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J187" s="36">
+        <f>IF(AND(B187&lt;&gt;"",E187&lt;&gt;"",NOT(ISNUMBER(F187))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="34" t="n">
@@ -10026,6 +10765,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J188" s="36">
+        <f>IF(AND(B188&lt;&gt;"",E188&lt;&gt;"",NOT(ISNUMBER(F188))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="34" t="n">
@@ -10066,6 +10809,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J189" s="36">
+        <f>IF(AND(B189&lt;&gt;"",E189&lt;&gt;"",NOT(ISNUMBER(F189))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="34" t="n">
@@ -10106,6 +10853,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J190" s="36">
+        <f>IF(AND(B190&lt;&gt;"",E190&lt;&gt;"",NOT(ISNUMBER(F190))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="34" t="n">
@@ -10146,6 +10897,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J191" s="36">
+        <f>IF(AND(B191&lt;&gt;"",E191&lt;&gt;"",NOT(ISNUMBER(F191))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="34" t="n">
@@ -10186,6 +10941,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J192" s="36">
+        <f>IF(AND(B192&lt;&gt;"",E192&lt;&gt;"",NOT(ISNUMBER(F192))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="34" t="n">
@@ -10226,6 +10985,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J193" s="36">
+        <f>IF(AND(B193&lt;&gt;"",E193&lt;&gt;"",NOT(ISNUMBER(F193))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="34" t="n">
@@ -10266,6 +11029,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J194" s="36">
+        <f>IF(AND(B194&lt;&gt;"",E194&lt;&gt;"",NOT(ISNUMBER(F194))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="34" t="n">
@@ -10306,6 +11073,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J195" s="36">
+        <f>IF(AND(B195&lt;&gt;"",E195&lt;&gt;"",NOT(ISNUMBER(F195))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="34" t="n">
@@ -10346,6 +11117,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J196" s="36">
+        <f>IF(AND(B196&lt;&gt;"",E196&lt;&gt;"",NOT(ISNUMBER(F196))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="34" t="n">
@@ -10386,6 +11161,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J197" s="36">
+        <f>IF(AND(B197&lt;&gt;"",E197&lt;&gt;"",NOT(ISNUMBER(F197))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="34" t="n">
@@ -10426,6 +11205,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J198" s="36">
+        <f>IF(AND(B198&lt;&gt;"",E198&lt;&gt;"",NOT(ISNUMBER(F198))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="34" t="n">
@@ -10466,6 +11249,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J199" s="36">
+        <f>IF(AND(B199&lt;&gt;"",E199&lt;&gt;"",NOT(ISNUMBER(F199))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="34" t="n">
@@ -10506,6 +11293,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J200" s="36">
+        <f>IF(AND(B200&lt;&gt;"",E200&lt;&gt;"",NOT(ISNUMBER(F200))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="34" t="n">
@@ -10546,6 +11337,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J201" s="36">
+        <f>IF(AND(B201&lt;&gt;"",E201&lt;&gt;"",NOT(ISNUMBER(F201))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="34" t="n">
@@ -10586,6 +11381,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J202" s="36">
+        <f>IF(AND(B202&lt;&gt;"",E202&lt;&gt;"",NOT(ISNUMBER(F202))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="34" t="n">
@@ -10626,6 +11425,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J203" s="36">
+        <f>IF(AND(B203&lt;&gt;"",E203&lt;&gt;"",NOT(ISNUMBER(F203))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="34" t="n">
@@ -10666,6 +11469,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J204" s="36">
+        <f>IF(AND(B204&lt;&gt;"",E204&lt;&gt;"",NOT(ISNUMBER(F204))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="34" t="n">
@@ -10706,6 +11513,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J205" s="36">
+        <f>IF(AND(B205&lt;&gt;"",E205&lt;&gt;"",NOT(ISNUMBER(F205))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="34" t="n">
@@ -10746,6 +11557,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J206" s="36">
+        <f>IF(AND(B206&lt;&gt;"",E206&lt;&gt;"",NOT(ISNUMBER(F206))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="34" t="n">
@@ -10786,6 +11601,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J207" s="36">
+        <f>IF(AND(B207&lt;&gt;"",E207&lt;&gt;"",NOT(ISNUMBER(F207))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="34" t="n">
@@ -10826,6 +11645,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J208" s="36">
+        <f>IF(AND(B208&lt;&gt;"",E208&lt;&gt;"",NOT(ISNUMBER(F208))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="34" t="n">
@@ -10866,6 +11689,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J209" s="36">
+        <f>IF(AND(B209&lt;&gt;"",E209&lt;&gt;"",NOT(ISNUMBER(F209))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="34" t="n">
@@ -10906,6 +11733,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J210" s="36">
+        <f>IF(AND(B210&lt;&gt;"",E210&lt;&gt;"",NOT(ISNUMBER(F210))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="34" t="n">
@@ -10946,6 +11777,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J211" s="36">
+        <f>IF(AND(B211&lt;&gt;"",E211&lt;&gt;"",NOT(ISNUMBER(F211))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="34" t="n">
@@ -10986,6 +11821,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J212" s="36">
+        <f>IF(AND(B212&lt;&gt;"",E212&lt;&gt;"",NOT(ISNUMBER(F212))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="34" t="n">
@@ -11026,6 +11865,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J213" s="36">
+        <f>IF(AND(B213&lt;&gt;"",E213&lt;&gt;"",NOT(ISNUMBER(F213))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="34" t="n">
@@ -11066,6 +11909,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J214" s="36">
+        <f>IF(AND(B214&lt;&gt;"",E214&lt;&gt;"",NOT(ISNUMBER(F214))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="34" t="n">
@@ -11106,6 +11953,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J215" s="36">
+        <f>IF(AND(B215&lt;&gt;"",E215&lt;&gt;"",NOT(ISNUMBER(F215))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="34" t="n">
@@ -11146,6 +11997,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J216" s="36">
+        <f>IF(AND(B216&lt;&gt;"",E216&lt;&gt;"",NOT(ISNUMBER(F216))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="34" t="n">
@@ -11186,6 +12041,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J217" s="36">
+        <f>IF(AND(B217&lt;&gt;"",E217&lt;&gt;"",NOT(ISNUMBER(F217))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="34" t="n">
@@ -11226,6 +12085,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J218" s="36">
+        <f>IF(AND(B218&lt;&gt;"",E218&lt;&gt;"",NOT(ISNUMBER(F218))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="34" t="n">
@@ -11266,6 +12129,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J219" s="36">
+        <f>IF(AND(B219&lt;&gt;"",E219&lt;&gt;"",NOT(ISNUMBER(F219))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="34" t="n">
@@ -11306,6 +12173,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J220" s="36">
+        <f>IF(AND(B220&lt;&gt;"",E220&lt;&gt;"",NOT(ISNUMBER(F220))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="34" t="n">
@@ -11346,6 +12217,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J221" s="36">
+        <f>IF(AND(B221&lt;&gt;"",E221&lt;&gt;"",NOT(ISNUMBER(F221))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="34" t="n">
@@ -11386,6 +12261,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J222" s="36">
+        <f>IF(AND(B222&lt;&gt;"",E222&lt;&gt;"",NOT(ISNUMBER(F222))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="34" t="n">
@@ -11426,6 +12305,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J223" s="36">
+        <f>IF(AND(B223&lt;&gt;"",E223&lt;&gt;"",NOT(ISNUMBER(F223))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="34" t="n">
@@ -11466,6 +12349,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J224" s="36">
+        <f>IF(AND(B224&lt;&gt;"",E224&lt;&gt;"",NOT(ISNUMBER(F224))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="34" t="n">
@@ -11506,6 +12393,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J225" s="36">
+        <f>IF(AND(B225&lt;&gt;"",E225&lt;&gt;"",NOT(ISNUMBER(F225))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="34" t="n">
@@ -11546,6 +12437,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J226" s="36">
+        <f>IF(AND(B226&lt;&gt;"",E226&lt;&gt;"",NOT(ISNUMBER(F226))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="34" t="n">
@@ -11586,6 +12481,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J227" s="36">
+        <f>IF(AND(B227&lt;&gt;"",E227&lt;&gt;"",NOT(ISNUMBER(F227))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="34" t="n">
@@ -11626,6 +12525,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J228" s="36">
+        <f>IF(AND(B228&lt;&gt;"",E228&lt;&gt;"",NOT(ISNUMBER(F228))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="34" t="n">
@@ -11666,6 +12569,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J229" s="36">
+        <f>IF(AND(B229&lt;&gt;"",E229&lt;&gt;"",NOT(ISNUMBER(F229))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="34" t="n">
@@ -11706,6 +12613,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J230" s="36">
+        <f>IF(AND(B230&lt;&gt;"",E230&lt;&gt;"",NOT(ISNUMBER(F230))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="34" t="n">
@@ -11746,6 +12657,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J231" s="36">
+        <f>IF(AND(B231&lt;&gt;"",E231&lt;&gt;"",NOT(ISNUMBER(F231))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="34" t="n">
@@ -11786,6 +12701,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J232" s="36">
+        <f>IF(AND(B232&lt;&gt;"",E232&lt;&gt;"",NOT(ISNUMBER(F232))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="34" t="n">
@@ -11826,6 +12745,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J233" s="36">
+        <f>IF(AND(B233&lt;&gt;"",E233&lt;&gt;"",NOT(ISNUMBER(F233))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="34" t="n">
@@ -11866,6 +12789,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J234" s="36">
+        <f>IF(AND(B234&lt;&gt;"",E234&lt;&gt;"",NOT(ISNUMBER(F234))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="34" t="n">
@@ -11906,6 +12833,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J235" s="36">
+        <f>IF(AND(B235&lt;&gt;"",E235&lt;&gt;"",NOT(ISNUMBER(F235))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="34" t="n">
@@ -11946,6 +12877,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J236" s="36">
+        <f>IF(AND(B236&lt;&gt;"",E236&lt;&gt;"",NOT(ISNUMBER(F236))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="34" t="n">
@@ -11986,6 +12921,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J237" s="36">
+        <f>IF(AND(B237&lt;&gt;"",E237&lt;&gt;"",NOT(ISNUMBER(F237))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="34" t="n">
@@ -12026,6 +12965,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J238" s="36">
+        <f>IF(AND(B238&lt;&gt;"",E238&lt;&gt;"",NOT(ISNUMBER(F238))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="34" t="n">
@@ -12066,6 +13009,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J239" s="36">
+        <f>IF(AND(B239&lt;&gt;"",E239&lt;&gt;"",NOT(ISNUMBER(F239))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="34" t="n">
@@ -12106,6 +13053,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J240" s="36">
+        <f>IF(AND(B240&lt;&gt;"",E240&lt;&gt;"",NOT(ISNUMBER(F240))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="34" t="n">
@@ -12146,6 +13097,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J241" s="36">
+        <f>IF(AND(B241&lt;&gt;"",E241&lt;&gt;"",NOT(ISNUMBER(F241))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="34" t="n">
@@ -12186,6 +13141,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J242" s="36">
+        <f>IF(AND(B242&lt;&gt;"",E242&lt;&gt;"",NOT(ISNUMBER(F242))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="34" t="n">
@@ -12226,6 +13185,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J243" s="36">
+        <f>IF(AND(B243&lt;&gt;"",E243&lt;&gt;"",NOT(ISNUMBER(F243))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="34" t="n">
@@ -12266,6 +13229,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J244" s="36">
+        <f>IF(AND(B244&lt;&gt;"",E244&lt;&gt;"",NOT(ISNUMBER(F244))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="34" t="n">
@@ -12306,6 +13273,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J245" s="36">
+        <f>IF(AND(B245&lt;&gt;"",E245&lt;&gt;"",NOT(ISNUMBER(F245))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="34" t="n">
@@ -12346,6 +13317,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J246" s="36">
+        <f>IF(AND(B246&lt;&gt;"",E246&lt;&gt;"",NOT(ISNUMBER(F246))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="34" t="n">
@@ -12386,6 +13361,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J247" s="36">
+        <f>IF(AND(B247&lt;&gt;"",E247&lt;&gt;"",NOT(ISNUMBER(F247))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="34" t="n">
@@ -12426,6 +13405,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J248" s="36">
+        <f>IF(AND(B248&lt;&gt;"",E248&lt;&gt;"",NOT(ISNUMBER(F248))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="34" t="n">
@@ -12466,6 +13449,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J249" s="36">
+        <f>IF(AND(B249&lt;&gt;"",E249&lt;&gt;"",NOT(ISNUMBER(F249))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="34" t="n">
@@ -12506,6 +13493,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J250" s="36">
+        <f>IF(AND(B250&lt;&gt;"",E250&lt;&gt;"",NOT(ISNUMBER(F250))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="34" t="n">
@@ -12546,6 +13537,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J251" s="36">
+        <f>IF(AND(B251&lt;&gt;"",E251&lt;&gt;"",NOT(ISNUMBER(F251))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="34" t="n">
@@ -12586,6 +13581,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J252" s="36">
+        <f>IF(AND(B252&lt;&gt;"",E252&lt;&gt;"",NOT(ISNUMBER(F252))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="34" t="n">
@@ -12626,6 +13625,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J253" s="36">
+        <f>IF(AND(B253&lt;&gt;"",E253&lt;&gt;"",NOT(ISNUMBER(F253))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="34" t="n">
@@ -12666,6 +13669,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J254" s="36">
+        <f>IF(AND(B254&lt;&gt;"",E254&lt;&gt;"",NOT(ISNUMBER(F254))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="34" t="n">
@@ -12706,6 +13713,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J255" s="36">
+        <f>IF(AND(B255&lt;&gt;"",E255&lt;&gt;"",NOT(ISNUMBER(F255))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="34" t="n">
@@ -12746,6 +13757,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J256" s="36">
+        <f>IF(AND(B256&lt;&gt;"",E256&lt;&gt;"",NOT(ISNUMBER(F256))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="34" t="n">
@@ -12786,6 +13801,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J257" s="36">
+        <f>IF(AND(B257&lt;&gt;"",E257&lt;&gt;"",NOT(ISNUMBER(F257))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="34" t="n">
@@ -12826,6 +13845,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J258" s="36">
+        <f>IF(AND(B258&lt;&gt;"",E258&lt;&gt;"",NOT(ISNUMBER(F258))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="34" t="n">
@@ -12866,6 +13889,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J259" s="36">
+        <f>IF(AND(B259&lt;&gt;"",E259&lt;&gt;"",NOT(ISNUMBER(F259))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="34" t="n">
@@ -12906,6 +13933,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J260" s="36">
+        <f>IF(AND(B260&lt;&gt;"",E260&lt;&gt;"",NOT(ISNUMBER(F260))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="34" t="n">
@@ -12946,6 +13977,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J261" s="36">
+        <f>IF(AND(B261&lt;&gt;"",E261&lt;&gt;"",NOT(ISNUMBER(F261))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="34" t="n">
@@ -12986,6 +14021,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J262" s="36">
+        <f>IF(AND(B262&lt;&gt;"",E262&lt;&gt;"",NOT(ISNUMBER(F262))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="34" t="n">
@@ -13026,6 +14065,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J263" s="36">
+        <f>IF(AND(B263&lt;&gt;"",E263&lt;&gt;"",NOT(ISNUMBER(F263))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="34" t="n">
@@ -13066,6 +14109,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J264" s="36">
+        <f>IF(AND(B264&lt;&gt;"",E264&lt;&gt;"",NOT(ISNUMBER(F264))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="34" t="n">
@@ -13106,6 +14153,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J265" s="36">
+        <f>IF(AND(B265&lt;&gt;"",E265&lt;&gt;"",NOT(ISNUMBER(F265))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="34" t="n">
@@ -13146,6 +14197,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J266" s="36">
+        <f>IF(AND(B266&lt;&gt;"",E266&lt;&gt;"",NOT(ISNUMBER(F266))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="34" t="n">
@@ -13186,6 +14241,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J267" s="36">
+        <f>IF(AND(B267&lt;&gt;"",E267&lt;&gt;"",NOT(ISNUMBER(F267))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="34" t="n">
@@ -13226,6 +14285,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J268" s="36">
+        <f>IF(AND(B268&lt;&gt;"",E268&lt;&gt;"",NOT(ISNUMBER(F268))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="34" t="n">
@@ -13266,6 +14329,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J269" s="36">
+        <f>IF(AND(B269&lt;&gt;"",E269&lt;&gt;"",NOT(ISNUMBER(F269))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="34" t="n">
@@ -13306,6 +14373,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J270" s="36">
+        <f>IF(AND(B270&lt;&gt;"",E270&lt;&gt;"",NOT(ISNUMBER(F270))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="34" t="n">
@@ -13346,6 +14417,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J271" s="36">
+        <f>IF(AND(B271&lt;&gt;"",E271&lt;&gt;"",NOT(ISNUMBER(F271))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="34" t="n">
@@ -13386,6 +14461,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J272" s="36">
+        <f>IF(AND(B272&lt;&gt;"",E272&lt;&gt;"",NOT(ISNUMBER(F272))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="34" t="n">
@@ -13426,6 +14505,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J273" s="36">
+        <f>IF(AND(B273&lt;&gt;"",E273&lt;&gt;"",NOT(ISNUMBER(F273))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="34" t="n">
@@ -13466,6 +14549,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J274" s="36">
+        <f>IF(AND(B274&lt;&gt;"",E274&lt;&gt;"",NOT(ISNUMBER(F274))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="34" t="n">
@@ -13506,6 +14593,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J275" s="36">
+        <f>IF(AND(B275&lt;&gt;"",E275&lt;&gt;"",NOT(ISNUMBER(F275))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="34" t="n">
@@ -13546,6 +14637,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J276" s="36">
+        <f>IF(AND(B276&lt;&gt;"",E276&lt;&gt;"",NOT(ISNUMBER(F276))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="34" t="n">
@@ -13586,6 +14681,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J277" s="36">
+        <f>IF(AND(B277&lt;&gt;"",E277&lt;&gt;"",NOT(ISNUMBER(F277))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="34" t="n">
@@ -13626,6 +14725,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J278" s="36">
+        <f>IF(AND(B278&lt;&gt;"",E278&lt;&gt;"",NOT(ISNUMBER(F278))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="34" t="n">
@@ -13666,6 +14769,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J279" s="36">
+        <f>IF(AND(B279&lt;&gt;"",E279&lt;&gt;"",NOT(ISNUMBER(F279))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="34" t="n">
@@ -13706,6 +14813,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J280" s="36">
+        <f>IF(AND(B280&lt;&gt;"",E280&lt;&gt;"",NOT(ISNUMBER(F280))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="34" t="n">
@@ -13746,6 +14857,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J281" s="36">
+        <f>IF(AND(B281&lt;&gt;"",E281&lt;&gt;"",NOT(ISNUMBER(F281))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="34" t="n">
@@ -13786,6 +14901,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J282" s="36">
+        <f>IF(AND(B282&lt;&gt;"",E282&lt;&gt;"",NOT(ISNUMBER(F282))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="34" t="n">
@@ -13826,6 +14945,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J283" s="36">
+        <f>IF(AND(B283&lt;&gt;"",E283&lt;&gt;"",NOT(ISNUMBER(F283))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="34" t="n">
@@ -13866,6 +14989,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J284" s="36">
+        <f>IF(AND(B284&lt;&gt;"",E284&lt;&gt;"",NOT(ISNUMBER(F284))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="34" t="n">
@@ -13906,6 +15033,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J285" s="36">
+        <f>IF(AND(B285&lt;&gt;"",E285&lt;&gt;"",NOT(ISNUMBER(F285))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="34" t="n">
@@ -13946,6 +15077,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J286" s="36">
+        <f>IF(AND(B286&lt;&gt;"",E286&lt;&gt;"",NOT(ISNUMBER(F286))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="34" t="n">
@@ -13986,6 +15121,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J287" s="36">
+        <f>IF(AND(B287&lt;&gt;"",E287&lt;&gt;"",NOT(ISNUMBER(F287))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="34" t="n">
@@ -14026,6 +15165,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J288" s="36">
+        <f>IF(AND(B288&lt;&gt;"",E288&lt;&gt;"",NOT(ISNUMBER(F288))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="34" t="n">
@@ -14066,6 +15209,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J289" s="36">
+        <f>IF(AND(B289&lt;&gt;"",E289&lt;&gt;"",NOT(ISNUMBER(F289))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="34" t="n">
@@ -14106,6 +15253,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J290" s="36">
+        <f>IF(AND(B290&lt;&gt;"",E290&lt;&gt;"",NOT(ISNUMBER(F290))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="34" t="n">
@@ -14146,6 +15297,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J291" s="36">
+        <f>IF(AND(B291&lt;&gt;"",E291&lt;&gt;"",NOT(ISNUMBER(F291))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="34" t="n">
@@ -14186,6 +15341,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J292" s="36">
+        <f>IF(AND(B292&lt;&gt;"",E292&lt;&gt;"",NOT(ISNUMBER(F292))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="34" t="n">
@@ -14226,6 +15385,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J293" s="36">
+        <f>IF(AND(B293&lt;&gt;"",E293&lt;&gt;"",NOT(ISNUMBER(F293))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="34" t="n">
@@ -14266,6 +15429,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J294" s="36">
+        <f>IF(AND(B294&lt;&gt;"",E294&lt;&gt;"",NOT(ISNUMBER(F294))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="34" t="n">
@@ -14306,6 +15473,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J295" s="36">
+        <f>IF(AND(B295&lt;&gt;"",E295&lt;&gt;"",NOT(ISNUMBER(F295))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="34" t="n">
@@ -14346,6 +15517,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J296" s="36">
+        <f>IF(AND(B296&lt;&gt;"",E296&lt;&gt;"",NOT(ISNUMBER(F296))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="34" t="n">
@@ -14386,6 +15561,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J297" s="36">
+        <f>IF(AND(B297&lt;&gt;"",E297&lt;&gt;"",NOT(ISNUMBER(F297))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="34" t="n">
@@ -14426,6 +15605,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J298" s="36">
+        <f>IF(AND(B298&lt;&gt;"",E298&lt;&gt;"",NOT(ISNUMBER(F298))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="34" t="n">
@@ -14466,6 +15649,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J299" s="36">
+        <f>IF(AND(B299&lt;&gt;"",E299&lt;&gt;"",NOT(ISNUMBER(F299))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="34" t="n">
@@ -14506,6 +15693,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J300" s="36">
+        <f>IF(AND(B300&lt;&gt;"",E300&lt;&gt;"",NOT(ISNUMBER(F300))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="34" t="n">
@@ -14546,6 +15737,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J301" s="36">
+        <f>IF(AND(B301&lt;&gt;"",E301&lt;&gt;"",NOT(ISNUMBER(F301))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="34" t="n">
@@ -14586,6 +15781,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J302" s="36">
+        <f>IF(AND(B302&lt;&gt;"",E302&lt;&gt;"",NOT(ISNUMBER(F302))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="34" t="n">
@@ -14626,6 +15825,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J303" s="36">
+        <f>IF(AND(B303&lt;&gt;"",E303&lt;&gt;"",NOT(ISNUMBER(F303))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="34" t="n">
@@ -14666,6 +15869,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J304" s="36">
+        <f>IF(AND(B304&lt;&gt;"",E304&lt;&gt;"",NOT(ISNUMBER(F304))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="34" t="n">
@@ -14706,6 +15913,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J305" s="36">
+        <f>IF(AND(B305&lt;&gt;"",E305&lt;&gt;"",NOT(ISNUMBER(F305))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="34" t="n">
@@ -14746,6 +15957,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J306" s="36">
+        <f>IF(AND(B306&lt;&gt;"",E306&lt;&gt;"",NOT(ISNUMBER(F306))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="34" t="n">
@@ -14786,6 +16001,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J307" s="36">
+        <f>IF(AND(B307&lt;&gt;"",E307&lt;&gt;"",NOT(ISNUMBER(F307))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="34" t="n">
@@ -14826,6 +16045,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J308" s="36">
+        <f>IF(AND(B308&lt;&gt;"",E308&lt;&gt;"",NOT(ISNUMBER(F308))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="34" t="n">
@@ -14866,6 +16089,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J309" s="36">
+        <f>IF(AND(B309&lt;&gt;"",E309&lt;&gt;"",NOT(ISNUMBER(F309))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="34" t="n">
@@ -14906,6 +16133,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J310" s="36">
+        <f>IF(AND(B310&lt;&gt;"",E310&lt;&gt;"",NOT(ISNUMBER(F310))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="34" t="n">
@@ -14946,6 +16177,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J311" s="36">
+        <f>IF(AND(B311&lt;&gt;"",E311&lt;&gt;"",NOT(ISNUMBER(F311))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="34" t="n">
@@ -14986,6 +16221,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J312" s="36">
+        <f>IF(AND(B312&lt;&gt;"",E312&lt;&gt;"",NOT(ISNUMBER(F312))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="34" t="n">
@@ -15026,6 +16265,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J313" s="36">
+        <f>IF(AND(B313&lt;&gt;"",E313&lt;&gt;"",NOT(ISNUMBER(F313))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="34" t="n">
@@ -15066,6 +16309,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J314" s="36">
+        <f>IF(AND(B314&lt;&gt;"",E314&lt;&gt;"",NOT(ISNUMBER(F314))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="34" t="n">
@@ -15106,6 +16353,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J315" s="36">
+        <f>IF(AND(B315&lt;&gt;"",E315&lt;&gt;"",NOT(ISNUMBER(F315))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="34" t="n">
@@ -15146,6 +16397,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J316" s="36">
+        <f>IF(AND(B316&lt;&gt;"",E316&lt;&gt;"",NOT(ISNUMBER(F316))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="34" t="n">
@@ -15186,6 +16441,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J317" s="36">
+        <f>IF(AND(B317&lt;&gt;"",E317&lt;&gt;"",NOT(ISNUMBER(F317))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="34" t="n">
@@ -15226,6 +16485,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J318" s="36">
+        <f>IF(AND(B318&lt;&gt;"",E318&lt;&gt;"",NOT(ISNUMBER(F318))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="34" t="n">
@@ -15266,6 +16529,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J319" s="36">
+        <f>IF(AND(B319&lt;&gt;"",E319&lt;&gt;"",NOT(ISNUMBER(F319))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="34" t="n">
@@ -15306,6 +16573,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J320" s="36">
+        <f>IF(AND(B320&lt;&gt;"",E320&lt;&gt;"",NOT(ISNUMBER(F320))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="34" t="n">
@@ -15346,6 +16617,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J321" s="36">
+        <f>IF(AND(B321&lt;&gt;"",E321&lt;&gt;"",NOT(ISNUMBER(F321))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="34" t="n">
@@ -15386,6 +16661,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J322" s="36">
+        <f>IF(AND(B322&lt;&gt;"",E322&lt;&gt;"",NOT(ISNUMBER(F322))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="34" t="n">
@@ -15426,6 +16705,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J323" s="36">
+        <f>IF(AND(B323&lt;&gt;"",E323&lt;&gt;"",NOT(ISNUMBER(F323))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="34" t="n">
@@ -15466,6 +16749,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J324" s="36">
+        <f>IF(AND(B324&lt;&gt;"",E324&lt;&gt;"",NOT(ISNUMBER(F324))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="34" t="n">
@@ -15506,6 +16793,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J325" s="36">
+        <f>IF(AND(B325&lt;&gt;"",E325&lt;&gt;"",NOT(ISNUMBER(F325))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="34" t="n">
@@ -15546,6 +16837,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J326" s="36">
+        <f>IF(AND(B326&lt;&gt;"",E326&lt;&gt;"",NOT(ISNUMBER(F326))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="34" t="n">
@@ -15586,6 +16881,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J327" s="36">
+        <f>IF(AND(B327&lt;&gt;"",E327&lt;&gt;"",NOT(ISNUMBER(F327))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="34" t="n">
@@ -15626,6 +16925,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J328" s="36">
+        <f>IF(AND(B328&lt;&gt;"",E328&lt;&gt;"",NOT(ISNUMBER(F328))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="34" t="n">
@@ -15666,6 +16969,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J329" s="36">
+        <f>IF(AND(B329&lt;&gt;"",E329&lt;&gt;"",NOT(ISNUMBER(F329))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="34" t="n">
@@ -15706,6 +17013,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J330" s="36">
+        <f>IF(AND(B330&lt;&gt;"",E330&lt;&gt;"",NOT(ISNUMBER(F330))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="34" t="n">
@@ -15746,6 +17057,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J331" s="36">
+        <f>IF(AND(B331&lt;&gt;"",E331&lt;&gt;"",NOT(ISNUMBER(F331))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="34" t="n">
@@ -15786,6 +17101,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J332" s="36">
+        <f>IF(AND(B332&lt;&gt;"",E332&lt;&gt;"",NOT(ISNUMBER(F332))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="34" t="n">
@@ -15826,6 +17145,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J333" s="36">
+        <f>IF(AND(B333&lt;&gt;"",E333&lt;&gt;"",NOT(ISNUMBER(F333))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="34" t="n">
@@ -15866,6 +17189,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J334" s="36">
+        <f>IF(AND(B334&lt;&gt;"",E334&lt;&gt;"",NOT(ISNUMBER(F334))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="34" t="n">
@@ -15906,6 +17233,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J335" s="36">
+        <f>IF(AND(B335&lt;&gt;"",E335&lt;&gt;"",NOT(ISNUMBER(F335))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="34" t="n">
@@ -15946,6 +17277,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J336" s="36">
+        <f>IF(AND(B336&lt;&gt;"",E336&lt;&gt;"",NOT(ISNUMBER(F336))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="34" t="n">
@@ -15986,6 +17321,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J337" s="36">
+        <f>IF(AND(B337&lt;&gt;"",E337&lt;&gt;"",NOT(ISNUMBER(F337))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="34" t="n">
@@ -16026,6 +17365,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J338" s="36">
+        <f>IF(AND(B338&lt;&gt;"",E338&lt;&gt;"",NOT(ISNUMBER(F338))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="34" t="n">
@@ -16066,6 +17409,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J339" s="36">
+        <f>IF(AND(B339&lt;&gt;"",E339&lt;&gt;"",NOT(ISNUMBER(F339))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="34" t="n">
@@ -16106,6 +17453,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J340" s="36">
+        <f>IF(AND(B340&lt;&gt;"",E340&lt;&gt;"",NOT(ISNUMBER(F340))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="34" t="n">
@@ -16146,6 +17497,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J341" s="36">
+        <f>IF(AND(B341&lt;&gt;"",E341&lt;&gt;"",NOT(ISNUMBER(F341))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="34" t="n">
@@ -16186,6 +17541,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J342" s="36">
+        <f>IF(AND(B342&lt;&gt;"",E342&lt;&gt;"",NOT(ISNUMBER(F342))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="34" t="n">
@@ -16226,6 +17585,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J343" s="36">
+        <f>IF(AND(B343&lt;&gt;"",E343&lt;&gt;"",NOT(ISNUMBER(F343))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="34" t="n">
@@ -16266,6 +17629,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J344" s="36">
+        <f>IF(AND(B344&lt;&gt;"",E344&lt;&gt;"",NOT(ISNUMBER(F344))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="34" t="n">
@@ -16306,6 +17673,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J345" s="36">
+        <f>IF(AND(B345&lt;&gt;"",E345&lt;&gt;"",NOT(ISNUMBER(F345))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="34" t="n">
@@ -16346,6 +17717,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J346" s="36">
+        <f>IF(AND(B346&lt;&gt;"",E346&lt;&gt;"",NOT(ISNUMBER(F346))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="34" t="n">
@@ -16386,6 +17761,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J347" s="36">
+        <f>IF(AND(B347&lt;&gt;"",E347&lt;&gt;"",NOT(ISNUMBER(F347))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="34" t="n">
@@ -16426,6 +17805,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J348" s="36">
+        <f>IF(AND(B348&lt;&gt;"",E348&lt;&gt;"",NOT(ISNUMBER(F348))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="34" t="n">
@@ -16466,6 +17849,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J349" s="36">
+        <f>IF(AND(B349&lt;&gt;"",E349&lt;&gt;"",NOT(ISNUMBER(F349))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="34" t="n">
@@ -16506,6 +17893,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J350" s="36">
+        <f>IF(AND(B350&lt;&gt;"",E350&lt;&gt;"",NOT(ISNUMBER(F350))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="34" t="n">
@@ -16546,6 +17937,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J351" s="36">
+        <f>IF(AND(B351&lt;&gt;"",E351&lt;&gt;"",NOT(ISNUMBER(F351))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="34" t="n">
@@ -16586,6 +17981,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J352" s="36">
+        <f>IF(AND(B352&lt;&gt;"",E352&lt;&gt;"",NOT(ISNUMBER(F352))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="34" t="n">
@@ -16626,6 +18025,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J353" s="36">
+        <f>IF(AND(B353&lt;&gt;"",E353&lt;&gt;"",NOT(ISNUMBER(F353))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="34" t="n">
@@ -16666,6 +18069,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J354" s="36">
+        <f>IF(AND(B354&lt;&gt;"",E354&lt;&gt;"",NOT(ISNUMBER(F354))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="34" t="n">
@@ -16706,6 +18113,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J355" s="36">
+        <f>IF(AND(B355&lt;&gt;"",E355&lt;&gt;"",NOT(ISNUMBER(F355))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="34" t="n">
@@ -16746,6 +18157,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J356" s="36">
+        <f>IF(AND(B356&lt;&gt;"",E356&lt;&gt;"",NOT(ISNUMBER(F356))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="34" t="n">
@@ -16786,6 +18201,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J357" s="36">
+        <f>IF(AND(B357&lt;&gt;"",E357&lt;&gt;"",NOT(ISNUMBER(F357))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="34" t="n">
@@ -16826,6 +18245,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J358" s="36">
+        <f>IF(AND(B358&lt;&gt;"",E358&lt;&gt;"",NOT(ISNUMBER(F358))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="34" t="n">
@@ -16866,6 +18289,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J359" s="36">
+        <f>IF(AND(B359&lt;&gt;"",E359&lt;&gt;"",NOT(ISNUMBER(F359))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="34" t="n">
@@ -16906,6 +18333,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J360" s="36">
+        <f>IF(AND(B360&lt;&gt;"",E360&lt;&gt;"",NOT(ISNUMBER(F360))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="34" t="n">
@@ -16946,6 +18377,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J361" s="36">
+        <f>IF(AND(B361&lt;&gt;"",E361&lt;&gt;"",NOT(ISNUMBER(F361))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="34" t="n">
@@ -16986,6 +18421,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J362" s="36">
+        <f>IF(AND(B362&lt;&gt;"",E362&lt;&gt;"",NOT(ISNUMBER(F362))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="34" t="n">
@@ -17026,6 +18465,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J363" s="36">
+        <f>IF(AND(B363&lt;&gt;"",E363&lt;&gt;"",NOT(ISNUMBER(F363))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="34" t="n">
@@ -17066,6 +18509,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J364" s="36">
+        <f>IF(AND(B364&lt;&gt;"",E364&lt;&gt;"",NOT(ISNUMBER(F364))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="34" t="n">
@@ -17106,6 +18553,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J365" s="36">
+        <f>IF(AND(B365&lt;&gt;"",E365&lt;&gt;"",NOT(ISNUMBER(F365))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="34" t="n">
@@ -17146,6 +18597,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J366" s="36">
+        <f>IF(AND(B366&lt;&gt;"",E366&lt;&gt;"",NOT(ISNUMBER(F366))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="34" t="n">
@@ -17186,6 +18641,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J367" s="36">
+        <f>IF(AND(B367&lt;&gt;"",E367&lt;&gt;"",NOT(ISNUMBER(F367))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="34" t="n">
@@ -17226,6 +18685,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J368" s="36">
+        <f>IF(AND(B368&lt;&gt;"",E368&lt;&gt;"",NOT(ISNUMBER(F368))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="34" t="n">
@@ -17266,6 +18729,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J369" s="36">
+        <f>IF(AND(B369&lt;&gt;"",E369&lt;&gt;"",NOT(ISNUMBER(F369))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="34" t="n">
@@ -17306,6 +18773,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J370" s="36">
+        <f>IF(AND(B370&lt;&gt;"",E370&lt;&gt;"",NOT(ISNUMBER(F370))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="34" t="n">
@@ -17346,6 +18817,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J371" s="36">
+        <f>IF(AND(B371&lt;&gt;"",E371&lt;&gt;"",NOT(ISNUMBER(F371))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="34" t="n">
@@ -17386,6 +18861,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J372" s="36">
+        <f>IF(AND(B372&lt;&gt;"",E372&lt;&gt;"",NOT(ISNUMBER(F372))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="34" t="n">
@@ -17426,6 +18905,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J373" s="36">
+        <f>IF(AND(B373&lt;&gt;"",E373&lt;&gt;"",NOT(ISNUMBER(F373))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="34" t="n">
@@ -17466,6 +18949,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J374" s="36">
+        <f>IF(AND(B374&lt;&gt;"",E374&lt;&gt;"",NOT(ISNUMBER(F374))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="34" t="n">
@@ -17506,6 +18993,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J375" s="36">
+        <f>IF(AND(B375&lt;&gt;"",E375&lt;&gt;"",NOT(ISNUMBER(F375))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="34" t="n">
@@ -17546,6 +19037,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J376" s="36">
+        <f>IF(AND(B376&lt;&gt;"",E376&lt;&gt;"",NOT(ISNUMBER(F376))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="34" t="n">
@@ -17586,6 +19081,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J377" s="36">
+        <f>IF(AND(B377&lt;&gt;"",E377&lt;&gt;"",NOT(ISNUMBER(F377))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="34" t="n">
@@ -17626,6 +19125,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J378" s="36">
+        <f>IF(AND(B378&lt;&gt;"",E378&lt;&gt;"",NOT(ISNUMBER(F378))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="34" t="n">
@@ -17666,6 +19169,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J379" s="36">
+        <f>IF(AND(B379&lt;&gt;"",E379&lt;&gt;"",NOT(ISNUMBER(F379))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="34" t="n">
@@ -17706,6 +19213,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J380" s="36">
+        <f>IF(AND(B380&lt;&gt;"",E380&lt;&gt;"",NOT(ISNUMBER(F380))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="34" t="n">
@@ -17746,6 +19257,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J381" s="36">
+        <f>IF(AND(B381&lt;&gt;"",E381&lt;&gt;"",NOT(ISNUMBER(F381))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="34" t="n">
@@ -17786,6 +19301,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J382" s="36">
+        <f>IF(AND(B382&lt;&gt;"",E382&lt;&gt;"",NOT(ISNUMBER(F382))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="34" t="n">
@@ -17826,6 +19345,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J383" s="36">
+        <f>IF(AND(B383&lt;&gt;"",E383&lt;&gt;"",NOT(ISNUMBER(F383))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="34" t="n">
@@ -17866,6 +19389,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J384" s="36">
+        <f>IF(AND(B384&lt;&gt;"",E384&lt;&gt;"",NOT(ISNUMBER(F384))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="34" t="n">
@@ -17906,6 +19433,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J385" s="36">
+        <f>IF(AND(B385&lt;&gt;"",E385&lt;&gt;"",NOT(ISNUMBER(F385))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="34" t="n">
@@ -17946,6 +19477,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J386" s="36">
+        <f>IF(AND(B386&lt;&gt;"",E386&lt;&gt;"",NOT(ISNUMBER(F386))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="34" t="n">
@@ -17986,6 +19521,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J387" s="36">
+        <f>IF(AND(B387&lt;&gt;"",E387&lt;&gt;"",NOT(ISNUMBER(F387))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="34" t="n">
@@ -18026,6 +19565,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J388" s="36">
+        <f>IF(AND(B388&lt;&gt;"",E388&lt;&gt;"",NOT(ISNUMBER(F388))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="34" t="n">
@@ -18066,6 +19609,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J389" s="36">
+        <f>IF(AND(B389&lt;&gt;"",E389&lt;&gt;"",NOT(ISNUMBER(F389))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="34" t="n">
@@ -18106,6 +19653,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J390" s="36">
+        <f>IF(AND(B390&lt;&gt;"",E390&lt;&gt;"",NOT(ISNUMBER(F390))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="34" t="n">
@@ -18146,6 +19697,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J391" s="36">
+        <f>IF(AND(B391&lt;&gt;"",E391&lt;&gt;"",NOT(ISNUMBER(F391))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="34" t="n">
@@ -18186,6 +19741,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J392" s="36">
+        <f>IF(AND(B392&lt;&gt;"",E392&lt;&gt;"",NOT(ISNUMBER(F392))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="34" t="n">
@@ -18226,6 +19785,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J393" s="36">
+        <f>IF(AND(B393&lt;&gt;"",E393&lt;&gt;"",NOT(ISNUMBER(F393))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="34" t="n">
@@ -18266,6 +19829,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J394" s="36">
+        <f>IF(AND(B394&lt;&gt;"",E394&lt;&gt;"",NOT(ISNUMBER(F394))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="34" t="n">
@@ -18306,6 +19873,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J395" s="36">
+        <f>IF(AND(B395&lt;&gt;"",E395&lt;&gt;"",NOT(ISNUMBER(F395))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="34" t="n">
@@ -18346,6 +19917,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J396" s="36">
+        <f>IF(AND(B396&lt;&gt;"",E396&lt;&gt;"",NOT(ISNUMBER(F396))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="34" t="n">
@@ -18386,6 +19961,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J397" s="36">
+        <f>IF(AND(B397&lt;&gt;"",E397&lt;&gt;"",NOT(ISNUMBER(F397))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="34" t="n">
@@ -18426,6 +20005,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J398" s="36">
+        <f>IF(AND(B398&lt;&gt;"",E398&lt;&gt;"",NOT(ISNUMBER(F398))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="34" t="n">
@@ -18466,6 +20049,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J399" s="36">
+        <f>IF(AND(B399&lt;&gt;"",E399&lt;&gt;"",NOT(ISNUMBER(F399))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="34" t="n">
@@ -18506,6 +20093,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J400" s="36">
+        <f>IF(AND(B400&lt;&gt;"",E400&lt;&gt;"",NOT(ISNUMBER(F400))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="34" t="n">
@@ -18546,6 +20137,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J401" s="36">
+        <f>IF(AND(B401&lt;&gt;"",E401&lt;&gt;"",NOT(ISNUMBER(F401))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="34" t="n">
@@ -18586,6 +20181,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J402" s="36">
+        <f>IF(AND(B402&lt;&gt;"",E402&lt;&gt;"",NOT(ISNUMBER(F402))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="34" t="n">
@@ -18626,6 +20225,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J403" s="36">
+        <f>IF(AND(B403&lt;&gt;"",E403&lt;&gt;"",NOT(ISNUMBER(F403))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="34" t="n">
@@ -18666,6 +20269,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J404" s="36">
+        <f>IF(AND(B404&lt;&gt;"",E404&lt;&gt;"",NOT(ISNUMBER(F404))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="34" t="n">
@@ -18706,6 +20313,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J405" s="36">
+        <f>IF(AND(B405&lt;&gt;"",E405&lt;&gt;"",NOT(ISNUMBER(F405))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="34" t="n">
@@ -18746,6 +20357,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J406" s="36">
+        <f>IF(AND(B406&lt;&gt;"",E406&lt;&gt;"",NOT(ISNUMBER(F406))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="34" t="n">
@@ -18786,6 +20401,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J407" s="36">
+        <f>IF(AND(B407&lt;&gt;"",E407&lt;&gt;"",NOT(ISNUMBER(F407))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="34" t="n">
@@ -18826,6 +20445,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J408" s="36">
+        <f>IF(AND(B408&lt;&gt;"",E408&lt;&gt;"",NOT(ISNUMBER(F408))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="34" t="n">
@@ -18866,6 +20489,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J409" s="36">
+        <f>IF(AND(B409&lt;&gt;"",E409&lt;&gt;"",NOT(ISNUMBER(F409))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="34" t="n">
@@ -18906,6 +20533,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J410" s="36">
+        <f>IF(AND(B410&lt;&gt;"",E410&lt;&gt;"",NOT(ISNUMBER(F410))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="34" t="n">
@@ -18946,6 +20577,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J411" s="36">
+        <f>IF(AND(B411&lt;&gt;"",E411&lt;&gt;"",NOT(ISNUMBER(F411))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="34" t="n">
@@ -18986,6 +20621,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J412" s="36">
+        <f>IF(AND(B412&lt;&gt;"",E412&lt;&gt;"",NOT(ISNUMBER(F412))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="34" t="n">
@@ -19026,6 +20665,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J413" s="36">
+        <f>IF(AND(B413&lt;&gt;"",E413&lt;&gt;"",NOT(ISNUMBER(F413))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="34" t="n">
@@ -19066,6 +20709,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J414" s="36">
+        <f>IF(AND(B414&lt;&gt;"",E414&lt;&gt;"",NOT(ISNUMBER(F414))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="34" t="n">
@@ -19106,6 +20753,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J415" s="36">
+        <f>IF(AND(B415&lt;&gt;"",E415&lt;&gt;"",NOT(ISNUMBER(F415))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="34" t="n">
@@ -19146,6 +20797,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J416" s="36">
+        <f>IF(AND(B416&lt;&gt;"",E416&lt;&gt;"",NOT(ISNUMBER(F416))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="34" t="n">
@@ -19186,6 +20841,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J417" s="36">
+        <f>IF(AND(B417&lt;&gt;"",E417&lt;&gt;"",NOT(ISNUMBER(F417))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="34" t="n">
@@ -19226,6 +20885,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J418" s="36">
+        <f>IF(AND(B418&lt;&gt;"",E418&lt;&gt;"",NOT(ISNUMBER(F418))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="34" t="n">
@@ -19266,6 +20929,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J419" s="36">
+        <f>IF(AND(B419&lt;&gt;"",E419&lt;&gt;"",NOT(ISNUMBER(F419))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="34" t="n">
@@ -19306,6 +20973,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J420" s="36">
+        <f>IF(AND(B420&lt;&gt;"",E420&lt;&gt;"",NOT(ISNUMBER(F420))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="34" t="n">
@@ -19346,6 +21017,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J421" s="36">
+        <f>IF(AND(B421&lt;&gt;"",E421&lt;&gt;"",NOT(ISNUMBER(F421))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="34" t="n">
@@ -19386,6 +21061,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J422" s="36">
+        <f>IF(AND(B422&lt;&gt;"",E422&lt;&gt;"",NOT(ISNUMBER(F422))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="34" t="n">
@@ -19426,6 +21105,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J423" s="36">
+        <f>IF(AND(B423&lt;&gt;"",E423&lt;&gt;"",NOT(ISNUMBER(F423))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="34" t="n">
@@ -19466,6 +21149,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J424" s="36">
+        <f>IF(AND(B424&lt;&gt;"",E424&lt;&gt;"",NOT(ISNUMBER(F424))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="34" t="n">
@@ -19506,6 +21193,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J425" s="36">
+        <f>IF(AND(B425&lt;&gt;"",E425&lt;&gt;"",NOT(ISNUMBER(F425))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="34" t="n">
@@ -19546,6 +21237,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J426" s="36">
+        <f>IF(AND(B426&lt;&gt;"",E426&lt;&gt;"",NOT(ISNUMBER(F426))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="34" t="n">
@@ -19586,6 +21281,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J427" s="36">
+        <f>IF(AND(B427&lt;&gt;"",E427&lt;&gt;"",NOT(ISNUMBER(F427))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="34" t="n">
@@ -19626,6 +21325,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J428" s="36">
+        <f>IF(AND(B428&lt;&gt;"",E428&lt;&gt;"",NOT(ISNUMBER(F428))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="34" t="n">
@@ -19666,6 +21369,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J429" s="36">
+        <f>IF(AND(B429&lt;&gt;"",E429&lt;&gt;"",NOT(ISNUMBER(F429))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="34" t="n">
@@ -19706,6 +21413,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J430" s="36">
+        <f>IF(AND(B430&lt;&gt;"",E430&lt;&gt;"",NOT(ISNUMBER(F430))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="34" t="n">
@@ -19746,6 +21457,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J431" s="36">
+        <f>IF(AND(B431&lt;&gt;"",E431&lt;&gt;"",NOT(ISNUMBER(F431))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="34" t="n">
@@ -19786,6 +21501,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J432" s="36">
+        <f>IF(AND(B432&lt;&gt;"",E432&lt;&gt;"",NOT(ISNUMBER(F432))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="34" t="n">
@@ -19826,6 +21545,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J433" s="36">
+        <f>IF(AND(B433&lt;&gt;"",E433&lt;&gt;"",NOT(ISNUMBER(F433))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="34" t="n">
@@ -19866,6 +21589,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J434" s="36">
+        <f>IF(AND(B434&lt;&gt;"",E434&lt;&gt;"",NOT(ISNUMBER(F434))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="34" t="n">
@@ -19906,6 +21633,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J435" s="36">
+        <f>IF(AND(B435&lt;&gt;"",E435&lt;&gt;"",NOT(ISNUMBER(F435))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="34" t="n">
@@ -19946,6 +21677,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J436" s="36">
+        <f>IF(AND(B436&lt;&gt;"",E436&lt;&gt;"",NOT(ISNUMBER(F436))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="34" t="n">
@@ -19986,6 +21721,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J437" s="36">
+        <f>IF(AND(B437&lt;&gt;"",E437&lt;&gt;"",NOT(ISNUMBER(F437))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="34" t="n">
@@ -20026,6 +21765,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J438" s="36">
+        <f>IF(AND(B438&lt;&gt;"",E438&lt;&gt;"",NOT(ISNUMBER(F438))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="34" t="n">
@@ -20066,6 +21809,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J439" s="36">
+        <f>IF(AND(B439&lt;&gt;"",E439&lt;&gt;"",NOT(ISNUMBER(F439))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="34" t="n">
@@ -20106,6 +21853,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J440" s="36">
+        <f>IF(AND(B440&lt;&gt;"",E440&lt;&gt;"",NOT(ISNUMBER(F440))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="34" t="n">
@@ -20146,6 +21897,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J441" s="36">
+        <f>IF(AND(B441&lt;&gt;"",E441&lt;&gt;"",NOT(ISNUMBER(F441))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="34" t="n">
@@ -20186,6 +21941,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J442" s="36">
+        <f>IF(AND(B442&lt;&gt;"",E442&lt;&gt;"",NOT(ISNUMBER(F442))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="34" t="n">
@@ -20226,6 +21985,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J443" s="36">
+        <f>IF(AND(B443&lt;&gt;"",E443&lt;&gt;"",NOT(ISNUMBER(F443))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="34" t="n">
@@ -20266,6 +22029,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J444" s="36">
+        <f>IF(AND(B444&lt;&gt;"",E444&lt;&gt;"",NOT(ISNUMBER(F444))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="34" t="n">
@@ -20306,6 +22073,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J445" s="36">
+        <f>IF(AND(B445&lt;&gt;"",E445&lt;&gt;"",NOT(ISNUMBER(F445))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="34" t="n">
@@ -20346,6 +22117,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J446" s="36">
+        <f>IF(AND(B446&lt;&gt;"",E446&lt;&gt;"",NOT(ISNUMBER(F446))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="34" t="n">
@@ -20386,6 +22161,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J447" s="36">
+        <f>IF(AND(B447&lt;&gt;"",E447&lt;&gt;"",NOT(ISNUMBER(F447))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="34" t="n">
@@ -20426,6 +22205,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J448" s="36">
+        <f>IF(AND(B448&lt;&gt;"",E448&lt;&gt;"",NOT(ISNUMBER(F448))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="34" t="n">
@@ -20466,6 +22249,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J449" s="36">
+        <f>IF(AND(B449&lt;&gt;"",E449&lt;&gt;"",NOT(ISNUMBER(F449))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="34" t="n">
@@ -20506,6 +22293,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J450" s="36">
+        <f>IF(AND(B450&lt;&gt;"",E450&lt;&gt;"",NOT(ISNUMBER(F450))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="34" t="n">
@@ -20546,6 +22337,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J451" s="36">
+        <f>IF(AND(B451&lt;&gt;"",E451&lt;&gt;"",NOT(ISNUMBER(F451))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="34" t="n">
@@ -20586,6 +22381,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J452" s="36">
+        <f>IF(AND(B452&lt;&gt;"",E452&lt;&gt;"",NOT(ISNUMBER(F452))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="34" t="n">
@@ -20626,6 +22425,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J453" s="36">
+        <f>IF(AND(B453&lt;&gt;"",E453&lt;&gt;"",NOT(ISNUMBER(F453))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="34" t="n">
@@ -20666,6 +22469,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J454" s="36">
+        <f>IF(AND(B454&lt;&gt;"",E454&lt;&gt;"",NOT(ISNUMBER(F454))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="34" t="n">
@@ -20706,6 +22513,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J455" s="36">
+        <f>IF(AND(B455&lt;&gt;"",E455&lt;&gt;"",NOT(ISNUMBER(F455))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="34" t="n">
@@ -20746,6 +22557,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J456" s="36">
+        <f>IF(AND(B456&lt;&gt;"",E456&lt;&gt;"",NOT(ISNUMBER(F456))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="34" t="n">
@@ -20786,6 +22601,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J457" s="36">
+        <f>IF(AND(B457&lt;&gt;"",E457&lt;&gt;"",NOT(ISNUMBER(F457))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="34" t="n">
@@ -20826,6 +22645,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J458" s="36">
+        <f>IF(AND(B458&lt;&gt;"",E458&lt;&gt;"",NOT(ISNUMBER(F458))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="34" t="n">
@@ -20866,6 +22689,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J459" s="36">
+        <f>IF(AND(B459&lt;&gt;"",E459&lt;&gt;"",NOT(ISNUMBER(F459))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="34" t="n">
@@ -20906,6 +22733,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J460" s="36">
+        <f>IF(AND(B460&lt;&gt;"",E460&lt;&gt;"",NOT(ISNUMBER(F460))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="34" t="n">
@@ -20946,6 +22777,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J461" s="36">
+        <f>IF(AND(B461&lt;&gt;"",E461&lt;&gt;"",NOT(ISNUMBER(F461))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="34" t="n">
@@ -20986,6 +22821,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J462" s="36">
+        <f>IF(AND(B462&lt;&gt;"",E462&lt;&gt;"",NOT(ISNUMBER(F462))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="34" t="n">
@@ -21026,6 +22865,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J463" s="36">
+        <f>IF(AND(B463&lt;&gt;"",E463&lt;&gt;"",NOT(ISNUMBER(F463))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="34" t="n">
@@ -21066,6 +22909,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J464" s="36">
+        <f>IF(AND(B464&lt;&gt;"",E464&lt;&gt;"",NOT(ISNUMBER(F464))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="34" t="n">
@@ -21106,6 +22953,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J465" s="36">
+        <f>IF(AND(B465&lt;&gt;"",E465&lt;&gt;"",NOT(ISNUMBER(F465))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="34" t="n">
@@ -21146,6 +22997,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J466" s="36">
+        <f>IF(AND(B466&lt;&gt;"",E466&lt;&gt;"",NOT(ISNUMBER(F466))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="34" t="n">
@@ -21186,6 +23041,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J467" s="36">
+        <f>IF(AND(B467&lt;&gt;"",E467&lt;&gt;"",NOT(ISNUMBER(F467))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="34" t="n">
@@ -21226,6 +23085,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J468" s="36">
+        <f>IF(AND(B468&lt;&gt;"",E468&lt;&gt;"",NOT(ISNUMBER(F468))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="34" t="n">
@@ -21266,6 +23129,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J469" s="36">
+        <f>IF(AND(B469&lt;&gt;"",E469&lt;&gt;"",NOT(ISNUMBER(F469))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="34" t="n">
@@ -21306,6 +23173,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J470" s="36">
+        <f>IF(AND(B470&lt;&gt;"",E470&lt;&gt;"",NOT(ISNUMBER(F470))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="34" t="n">
@@ -21346,6 +23217,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J471" s="36">
+        <f>IF(AND(B471&lt;&gt;"",E471&lt;&gt;"",NOT(ISNUMBER(F471))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="34" t="n">
@@ -21386,6 +23261,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J472" s="36">
+        <f>IF(AND(B472&lt;&gt;"",E472&lt;&gt;"",NOT(ISNUMBER(F472))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="34" t="n">
@@ -21426,6 +23305,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J473" s="36">
+        <f>IF(AND(B473&lt;&gt;"",E473&lt;&gt;"",NOT(ISNUMBER(F473))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="34" t="n">
@@ -21466,6 +23349,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J474" s="36">
+        <f>IF(AND(B474&lt;&gt;"",E474&lt;&gt;"",NOT(ISNUMBER(F474))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="34" t="n">
@@ -21506,6 +23393,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J475" s="36">
+        <f>IF(AND(B475&lt;&gt;"",E475&lt;&gt;"",NOT(ISNUMBER(F475))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="34" t="n">
@@ -21546,6 +23437,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J476" s="36">
+        <f>IF(AND(B476&lt;&gt;"",E476&lt;&gt;"",NOT(ISNUMBER(F476))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="34" t="n">
@@ -21586,6 +23481,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J477" s="36">
+        <f>IF(AND(B477&lt;&gt;"",E477&lt;&gt;"",NOT(ISNUMBER(F477))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="34" t="n">
@@ -21626,6 +23525,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J478" s="36">
+        <f>IF(AND(B478&lt;&gt;"",E478&lt;&gt;"",NOT(ISNUMBER(F478))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="34" t="n">
@@ -21666,6 +23569,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J479" s="36">
+        <f>IF(AND(B479&lt;&gt;"",E479&lt;&gt;"",NOT(ISNUMBER(F479))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="34" t="n">
@@ -21706,6 +23613,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J480" s="36">
+        <f>IF(AND(B480&lt;&gt;"",E480&lt;&gt;"",NOT(ISNUMBER(F480))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="34" t="n">
@@ -21746,6 +23657,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J481" s="36">
+        <f>IF(AND(B481&lt;&gt;"",E481&lt;&gt;"",NOT(ISNUMBER(F481))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="34" t="n">
@@ -21786,6 +23701,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J482" s="36">
+        <f>IF(AND(B482&lt;&gt;"",E482&lt;&gt;"",NOT(ISNUMBER(F482))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="34" t="n">
@@ -21826,6 +23745,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J483" s="36">
+        <f>IF(AND(B483&lt;&gt;"",E483&lt;&gt;"",NOT(ISNUMBER(F483))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="34" t="n">
@@ -21866,6 +23789,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J484" s="36">
+        <f>IF(AND(B484&lt;&gt;"",E484&lt;&gt;"",NOT(ISNUMBER(F484))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="34" t="n">
@@ -21906,6 +23833,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J485" s="36">
+        <f>IF(AND(B485&lt;&gt;"",E485&lt;&gt;"",NOT(ISNUMBER(F485))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="34" t="n">
@@ -21946,6 +23877,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J486" s="36">
+        <f>IF(AND(B486&lt;&gt;"",E486&lt;&gt;"",NOT(ISNUMBER(F486))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="34" t="n">
@@ -21986,6 +23921,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J487" s="36">
+        <f>IF(AND(B487&lt;&gt;"",E487&lt;&gt;"",NOT(ISNUMBER(F487))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="34" t="n">
@@ -22026,6 +23965,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J488" s="36">
+        <f>IF(AND(B488&lt;&gt;"",E488&lt;&gt;"",NOT(ISNUMBER(F488))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="34" t="n">
@@ -22066,6 +24009,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J489" s="36">
+        <f>IF(AND(B489&lt;&gt;"",E489&lt;&gt;"",NOT(ISNUMBER(F489))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="34" t="n">
@@ -22106,6 +24053,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J490" s="36">
+        <f>IF(AND(B490&lt;&gt;"",E490&lt;&gt;"",NOT(ISNUMBER(F490))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="34" t="n">
@@ -22146,6 +24097,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J491" s="36">
+        <f>IF(AND(B491&lt;&gt;"",E491&lt;&gt;"",NOT(ISNUMBER(F491))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="34" t="n">
@@ -22186,6 +24141,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J492" s="36">
+        <f>IF(AND(B492&lt;&gt;"",E492&lt;&gt;"",NOT(ISNUMBER(F492))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="34" t="n">
@@ -22226,6 +24185,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J493" s="36">
+        <f>IF(AND(B493&lt;&gt;"",E493&lt;&gt;"",NOT(ISNUMBER(F493))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="34" t="n">
@@ -22266,6 +24229,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J494" s="36">
+        <f>IF(AND(B494&lt;&gt;"",E494&lt;&gt;"",NOT(ISNUMBER(F494))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="34" t="n">
@@ -22306,6 +24273,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J495" s="36">
+        <f>IF(AND(B495&lt;&gt;"",E495&lt;&gt;"",NOT(ISNUMBER(F495))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="34" t="n">
@@ -22346,6 +24317,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J496" s="36">
+        <f>IF(AND(B496&lt;&gt;"",E496&lt;&gt;"",NOT(ISNUMBER(F496))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="34" t="n">
@@ -22386,6 +24361,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J497" s="36">
+        <f>IF(AND(B497&lt;&gt;"",E497&lt;&gt;"",NOT(ISNUMBER(F497))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="34" t="n">
@@ -22426,6 +24405,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J498" s="36">
+        <f>IF(AND(B498&lt;&gt;"",E498&lt;&gt;"",NOT(ISNUMBER(F498))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="34" t="n">
@@ -22466,6 +24449,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J499" s="36">
+        <f>IF(AND(B499&lt;&gt;"",E499&lt;&gt;"",NOT(ISNUMBER(F499))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="34" t="n">
@@ -22506,6 +24493,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J500" s="36">
+        <f>IF(AND(B500&lt;&gt;"",E500&lt;&gt;"",NOT(ISNUMBER(F500))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="34" t="n">
@@ -22546,6 +24537,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J501" s="36">
+        <f>IF(AND(B501&lt;&gt;"",E501&lt;&gt;"",NOT(ISNUMBER(F501))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="34" t="n">
@@ -22586,6 +24581,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J502" s="36">
+        <f>IF(AND(B502&lt;&gt;"",E502&lt;&gt;"",NOT(ISNUMBER(F502))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="34" t="n">
@@ -22626,6 +24625,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J503" s="36">
+        <f>IF(AND(B503&lt;&gt;"",E503&lt;&gt;"",NOT(ISNUMBER(F503))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="34" t="n">
@@ -22666,6 +24669,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J504" s="36">
+        <f>IF(AND(B504&lt;&gt;"",E504&lt;&gt;"",NOT(ISNUMBER(F504))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="34" t="n">
@@ -22706,6 +24713,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J505" s="36">
+        <f>IF(AND(B505&lt;&gt;"",E505&lt;&gt;"",NOT(ISNUMBER(F505))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="34" t="n">
@@ -22746,6 +24757,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J506" s="36">
+        <f>IF(AND(B506&lt;&gt;"",E506&lt;&gt;"",NOT(ISNUMBER(F506))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="34" t="n">
@@ -22786,6 +24801,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J507" s="36">
+        <f>IF(AND(B507&lt;&gt;"",E507&lt;&gt;"",NOT(ISNUMBER(F507))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="34" t="n">
@@ -22826,6 +24845,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J508" s="36">
+        <f>IF(AND(B508&lt;&gt;"",E508&lt;&gt;"",NOT(ISNUMBER(F508))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="34" t="n">
@@ -22866,6 +24889,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J509" s="36">
+        <f>IF(AND(B509&lt;&gt;"",E509&lt;&gt;"",NOT(ISNUMBER(F509))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="34" t="n">
@@ -22906,6 +24933,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J510" s="36">
+        <f>IF(AND(B510&lt;&gt;"",E510&lt;&gt;"",NOT(ISNUMBER(F510))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="34" t="n">
@@ -22946,6 +24977,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J511" s="36">
+        <f>IF(AND(B511&lt;&gt;"",E511&lt;&gt;"",NOT(ISNUMBER(F511))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="34" t="n">
@@ -22986,6 +25021,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J512" s="36">
+        <f>IF(AND(B512&lt;&gt;"",E512&lt;&gt;"",NOT(ISNUMBER(F512))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="34" t="n">
@@ -23026,6 +25065,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J513" s="36">
+        <f>IF(AND(B513&lt;&gt;"",E513&lt;&gt;"",NOT(ISNUMBER(F513))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="34" t="n">
@@ -23066,6 +25109,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J514" s="36">
+        <f>IF(AND(B514&lt;&gt;"",E514&lt;&gt;"",NOT(ISNUMBER(F514))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="34" t="n">
@@ -23106,6 +25153,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J515" s="36">
+        <f>IF(AND(B515&lt;&gt;"",E515&lt;&gt;"",NOT(ISNUMBER(F515))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="34" t="n">
@@ -23146,6 +25197,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J516" s="36">
+        <f>IF(AND(B516&lt;&gt;"",E516&lt;&gt;"",NOT(ISNUMBER(F516))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="34" t="n">
@@ -23186,6 +25241,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J517" s="36">
+        <f>IF(AND(B517&lt;&gt;"",E517&lt;&gt;"",NOT(ISNUMBER(F517))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="34" t="n">
@@ -23226,6 +25285,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J518" s="36">
+        <f>IF(AND(B518&lt;&gt;"",E518&lt;&gt;"",NOT(ISNUMBER(F518))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="34" t="n">
@@ -23266,6 +25329,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J519" s="36">
+        <f>IF(AND(B519&lt;&gt;"",E519&lt;&gt;"",NOT(ISNUMBER(F519))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="34" t="n">
@@ -23306,6 +25373,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J520" s="36">
+        <f>IF(AND(B520&lt;&gt;"",E520&lt;&gt;"",NOT(ISNUMBER(F520))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="34" t="n">
@@ -23346,6 +25417,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J521" s="36">
+        <f>IF(AND(B521&lt;&gt;"",E521&lt;&gt;"",NOT(ISNUMBER(F521))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="34" t="n">
@@ -23386,6 +25461,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J522" s="36">
+        <f>IF(AND(B522&lt;&gt;"",E522&lt;&gt;"",NOT(ISNUMBER(F522))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="34" t="n">
@@ -23426,6 +25505,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J523" s="36">
+        <f>IF(AND(B523&lt;&gt;"",E523&lt;&gt;"",NOT(ISNUMBER(F523))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="34" t="n">
@@ -23466,6 +25549,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J524" s="36">
+        <f>IF(AND(B524&lt;&gt;"",E524&lt;&gt;"",NOT(ISNUMBER(F524))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="34" t="n">
@@ -23506,6 +25593,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J525" s="36">
+        <f>IF(AND(B525&lt;&gt;"",E525&lt;&gt;"",NOT(ISNUMBER(F525))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="34" t="n">
@@ -23546,6 +25637,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J526" s="36">
+        <f>IF(AND(B526&lt;&gt;"",E526&lt;&gt;"",NOT(ISNUMBER(F526))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="34" t="n">
@@ -23586,6 +25681,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J527" s="36">
+        <f>IF(AND(B527&lt;&gt;"",E527&lt;&gt;"",NOT(ISNUMBER(F527))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="34" t="n">
@@ -23626,6 +25725,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J528" s="36">
+        <f>IF(AND(B528&lt;&gt;"",E528&lt;&gt;"",NOT(ISNUMBER(F528))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="34" t="n">
@@ -23666,6 +25769,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J529" s="36">
+        <f>IF(AND(B529&lt;&gt;"",E529&lt;&gt;"",NOT(ISNUMBER(F529))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="34" t="n">
@@ -23706,6 +25813,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J530" s="36">
+        <f>IF(AND(B530&lt;&gt;"",E530&lt;&gt;"",NOT(ISNUMBER(F530))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="34" t="n">
@@ -23746,6 +25857,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J531" s="36">
+        <f>IF(AND(B531&lt;&gt;"",E531&lt;&gt;"",NOT(ISNUMBER(F531))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="34" t="n">
@@ -23786,6 +25901,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J532" s="36">
+        <f>IF(AND(B532&lt;&gt;"",E532&lt;&gt;"",NOT(ISNUMBER(F532))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="34" t="n">
@@ -23826,6 +25945,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J533" s="36">
+        <f>IF(AND(B533&lt;&gt;"",E533&lt;&gt;"",NOT(ISNUMBER(F533))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="34" t="n">
@@ -23866,6 +25989,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J534" s="36">
+        <f>IF(AND(B534&lt;&gt;"",E534&lt;&gt;"",NOT(ISNUMBER(F534))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="34" t="n">
@@ -23906,6 +26033,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J535" s="36">
+        <f>IF(AND(B535&lt;&gt;"",E535&lt;&gt;"",NOT(ISNUMBER(F535))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="34" t="n">
@@ -23946,6 +26077,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J536" s="36">
+        <f>IF(AND(B536&lt;&gt;"",E536&lt;&gt;"",NOT(ISNUMBER(F536))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="34" t="n">
@@ -23986,6 +26121,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J537" s="36">
+        <f>IF(AND(B537&lt;&gt;"",E537&lt;&gt;"",NOT(ISNUMBER(F537))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="34" t="n">
@@ -24026,6 +26165,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J538" s="36">
+        <f>IF(AND(B538&lt;&gt;"",E538&lt;&gt;"",NOT(ISNUMBER(F538))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="34" t="n">
@@ -24066,6 +26209,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J539" s="36">
+        <f>IF(AND(B539&lt;&gt;"",E539&lt;&gt;"",NOT(ISNUMBER(F539))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="34" t="n">
@@ -24106,6 +26253,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J540" s="36">
+        <f>IF(AND(B540&lt;&gt;"",E540&lt;&gt;"",NOT(ISNUMBER(F540))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="34" t="n">
@@ -24146,6 +26297,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J541" s="36">
+        <f>IF(AND(B541&lt;&gt;"",E541&lt;&gt;"",NOT(ISNUMBER(F541))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="34" t="n">
@@ -24186,6 +26341,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J542" s="36">
+        <f>IF(AND(B542&lt;&gt;"",E542&lt;&gt;"",NOT(ISNUMBER(F542))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="34" t="n">
@@ -24226,6 +26385,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J543" s="36">
+        <f>IF(AND(B543&lt;&gt;"",E543&lt;&gt;"",NOT(ISNUMBER(F543))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="34" t="n">
@@ -24266,6 +26429,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J544" s="36">
+        <f>IF(AND(B544&lt;&gt;"",E544&lt;&gt;"",NOT(ISNUMBER(F544))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="34" t="n">
@@ -24306,6 +26473,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J545" s="36">
+        <f>IF(AND(B545&lt;&gt;"",E545&lt;&gt;"",NOT(ISNUMBER(F545))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="34" t="n">
@@ -24346,6 +26517,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J546" s="36">
+        <f>IF(AND(B546&lt;&gt;"",E546&lt;&gt;"",NOT(ISNUMBER(F546))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="34" t="n">
@@ -24386,6 +26561,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J547" s="36">
+        <f>IF(AND(B547&lt;&gt;"",E547&lt;&gt;"",NOT(ISNUMBER(F547))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="34" t="n">
@@ -24426,6 +26605,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J548" s="36">
+        <f>IF(AND(B548&lt;&gt;"",E548&lt;&gt;"",NOT(ISNUMBER(F548))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="34" t="n">
@@ -24466,6 +26649,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J549" s="36">
+        <f>IF(AND(B549&lt;&gt;"",E549&lt;&gt;"",NOT(ISNUMBER(F549))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="34" t="n">
@@ -24506,6 +26693,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J550" s="36">
+        <f>IF(AND(B550&lt;&gt;"",E550&lt;&gt;"",NOT(ISNUMBER(F550))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="34" t="n">
@@ -24546,6 +26737,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J551" s="36">
+        <f>IF(AND(B551&lt;&gt;"",E551&lt;&gt;"",NOT(ISNUMBER(F551))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="34" t="n">
@@ -24586,6 +26781,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J552" s="36">
+        <f>IF(AND(B552&lt;&gt;"",E552&lt;&gt;"",NOT(ISNUMBER(F552))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="34" t="n">
@@ -24626,6 +26825,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J553" s="36">
+        <f>IF(AND(B553&lt;&gt;"",E553&lt;&gt;"",NOT(ISNUMBER(F553))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="34" t="n">
@@ -24666,6 +26869,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J554" s="36">
+        <f>IF(AND(B554&lt;&gt;"",E554&lt;&gt;"",NOT(ISNUMBER(F554))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="34" t="n">
@@ -24706,6 +26913,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J555" s="36">
+        <f>IF(AND(B555&lt;&gt;"",E555&lt;&gt;"",NOT(ISNUMBER(F555))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="34" t="n">
@@ -24746,6 +26957,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J556" s="36">
+        <f>IF(AND(B556&lt;&gt;"",E556&lt;&gt;"",NOT(ISNUMBER(F556))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="34" t="n">
@@ -24786,6 +27001,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J557" s="36">
+        <f>IF(AND(B557&lt;&gt;"",E557&lt;&gt;"",NOT(ISNUMBER(F557))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="34" t="n">
@@ -24826,6 +27045,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J558" s="36">
+        <f>IF(AND(B558&lt;&gt;"",E558&lt;&gt;"",NOT(ISNUMBER(F558))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="34" t="n">
@@ -24866,6 +27089,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J559" s="36">
+        <f>IF(AND(B559&lt;&gt;"",E559&lt;&gt;"",NOT(ISNUMBER(F559))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="34" t="n">
@@ -24906,6 +27133,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J560" s="36">
+        <f>IF(AND(B560&lt;&gt;"",E560&lt;&gt;"",NOT(ISNUMBER(F560))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="34" t="n">
@@ -24946,6 +27177,10 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="J561" s="36">
+        <f>IF(AND(B561&lt;&gt;"",E561&lt;&gt;"",NOT(ISNUMBER(F561))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="34" t="n">
@@ -24986,6 +27221,10 @@
           <t>Não</t>
         </is>
       </c>
+      <c r="J562" s="36">
+        <f>IF(AND(B562&lt;&gt;"",E562&lt;&gt;"",NOT(ISNUMBER(F562))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="34" t="n">
@@ -25025,6 +27264,10 @@
         <is>
           <t>Não</t>
         </is>
+      </c>
+      <c r="J563" s="36">
+        <f>IF(AND(B563&lt;&gt;"",E563&lt;&gt;"",NOT(ISNUMBER(F563))),1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="564">
@@ -25046,6 +27289,10 @@
         <v/>
       </c>
       <c r="I564" s="31" t="n"/>
+      <c r="J564" s="36">
+        <f>IF(AND(B564&lt;&gt;"",E564&lt;&gt;"",NOT(ISNUMBER(F564))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="34" t="n"/>
@@ -25066,6 +27313,10 @@
         <v/>
       </c>
       <c r="I565" s="31" t="n"/>
+      <c r="J565" s="36">
+        <f>IF(AND(B565&lt;&gt;"",E565&lt;&gt;"",NOT(ISNUMBER(F565))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="34" t="n"/>
@@ -25086,6 +27337,10 @@
         <v/>
       </c>
       <c r="I566" s="31" t="n"/>
+      <c r="J566" s="36">
+        <f>IF(AND(B566&lt;&gt;"",E566&lt;&gt;"",NOT(ISNUMBER(F566))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="34" t="n"/>
@@ -25106,6 +27361,10 @@
         <v/>
       </c>
       <c r="I567" s="31" t="n"/>
+      <c r="J567" s="36">
+        <f>IF(AND(B567&lt;&gt;"",E567&lt;&gt;"",NOT(ISNUMBER(F567))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="34" t="n"/>
@@ -25126,6 +27385,10 @@
         <v/>
       </c>
       <c r="I568" s="31" t="n"/>
+      <c r="J568" s="36">
+        <f>IF(AND(B568&lt;&gt;"",E568&lt;&gt;"",NOT(ISNUMBER(F568))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="34" t="n"/>
@@ -25146,6 +27409,10 @@
         <v/>
       </c>
       <c r="I569" s="31" t="n"/>
+      <c r="J569" s="36">
+        <f>IF(AND(B569&lt;&gt;"",E569&lt;&gt;"",NOT(ISNUMBER(F569))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="34" t="n"/>
@@ -25166,6 +27433,10 @@
         <v/>
       </c>
       <c r="I570" s="31" t="n"/>
+      <c r="J570" s="36">
+        <f>IF(AND(B570&lt;&gt;"",E570&lt;&gt;"",NOT(ISNUMBER(F570))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="34" t="n"/>
@@ -25186,6 +27457,10 @@
         <v/>
       </c>
       <c r="I571" s="31" t="n"/>
+      <c r="J571" s="36">
+        <f>IF(AND(B571&lt;&gt;"",E571&lt;&gt;"",NOT(ISNUMBER(F571))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="34" t="n"/>
@@ -25206,6 +27481,10 @@
         <v/>
       </c>
       <c r="I572" s="31" t="n"/>
+      <c r="J572" s="36">
+        <f>IF(AND(B572&lt;&gt;"",E572&lt;&gt;"",NOT(ISNUMBER(F572))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="34" t="n"/>
@@ -25226,6 +27505,10 @@
         <v/>
       </c>
       <c r="I573" s="31" t="n"/>
+      <c r="J573" s="36">
+        <f>IF(AND(B573&lt;&gt;"",E573&lt;&gt;"",NOT(ISNUMBER(F573))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="34" t="n"/>
@@ -25246,6 +27529,10 @@
         <v/>
       </c>
       <c r="I574" s="31" t="n"/>
+      <c r="J574" s="36">
+        <f>IF(AND(B574&lt;&gt;"",E574&lt;&gt;"",NOT(ISNUMBER(F574))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="34" t="n"/>
@@ -25266,6 +27553,10 @@
         <v/>
       </c>
       <c r="I575" s="31" t="n"/>
+      <c r="J575" s="36">
+        <f>IF(AND(B575&lt;&gt;"",E575&lt;&gt;"",NOT(ISNUMBER(F575))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="34" t="n"/>
@@ -25286,6 +27577,10 @@
         <v/>
       </c>
       <c r="I576" s="31" t="n"/>
+      <c r="J576" s="36">
+        <f>IF(AND(B576&lt;&gt;"",E576&lt;&gt;"",NOT(ISNUMBER(F576))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="34" t="n"/>
@@ -25306,6 +27601,10 @@
         <v/>
       </c>
       <c r="I577" s="31" t="n"/>
+      <c r="J577" s="36">
+        <f>IF(AND(B577&lt;&gt;"",E577&lt;&gt;"",NOT(ISNUMBER(F577))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="34" t="n"/>
@@ -25326,6 +27625,10 @@
         <v/>
       </c>
       <c r="I578" s="31" t="n"/>
+      <c r="J578" s="36">
+        <f>IF(AND(B578&lt;&gt;"",E578&lt;&gt;"",NOT(ISNUMBER(F578))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="34" t="n"/>
@@ -25346,6 +27649,10 @@
         <v/>
       </c>
       <c r="I579" s="31" t="n"/>
+      <c r="J579" s="36">
+        <f>IF(AND(B579&lt;&gt;"",E579&lt;&gt;"",NOT(ISNUMBER(F579))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="34" t="n"/>
@@ -25366,6 +27673,10 @@
         <v/>
       </c>
       <c r="I580" s="31" t="n"/>
+      <c r="J580" s="36">
+        <f>IF(AND(B580&lt;&gt;"",E580&lt;&gt;"",NOT(ISNUMBER(F580))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="34" t="n"/>
@@ -25386,6 +27697,10 @@
         <v/>
       </c>
       <c r="I581" s="31" t="n"/>
+      <c r="J581" s="36">
+        <f>IF(AND(B581&lt;&gt;"",E581&lt;&gt;"",NOT(ISNUMBER(F581))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="34" t="n"/>
@@ -25406,6 +27721,10 @@
         <v/>
       </c>
       <c r="I582" s="31" t="n"/>
+      <c r="J582" s="36">
+        <f>IF(AND(B582&lt;&gt;"",E582&lt;&gt;"",NOT(ISNUMBER(F582))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="34" t="n"/>
@@ -25426,6 +27745,10 @@
         <v/>
       </c>
       <c r="I583" s="31" t="n"/>
+      <c r="J583" s="36">
+        <f>IF(AND(B583&lt;&gt;"",E583&lt;&gt;"",NOT(ISNUMBER(F583))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="34" t="n"/>
@@ -25446,6 +27769,10 @@
         <v/>
       </c>
       <c r="I584" s="31" t="n"/>
+      <c r="J584" s="36">
+        <f>IF(AND(B584&lt;&gt;"",E584&lt;&gt;"",NOT(ISNUMBER(F584))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="34" t="n"/>
@@ -25466,6 +27793,10 @@
         <v/>
       </c>
       <c r="I585" s="31" t="n"/>
+      <c r="J585" s="36">
+        <f>IF(AND(B585&lt;&gt;"",E585&lt;&gt;"",NOT(ISNUMBER(F585))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="34" t="n"/>
@@ -25486,6 +27817,10 @@
         <v/>
       </c>
       <c r="I586" s="31" t="n"/>
+      <c r="J586" s="36">
+        <f>IF(AND(B586&lt;&gt;"",E586&lt;&gt;"",NOT(ISNUMBER(F586))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="34" t="n"/>
@@ -25506,6 +27841,10 @@
         <v/>
       </c>
       <c r="I587" s="31" t="n"/>
+      <c r="J587" s="36">
+        <f>IF(AND(B587&lt;&gt;"",E587&lt;&gt;"",NOT(ISNUMBER(F587))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="34" t="n"/>
@@ -25526,6 +27865,10 @@
         <v/>
       </c>
       <c r="I588" s="31" t="n"/>
+      <c r="J588" s="36">
+        <f>IF(AND(B588&lt;&gt;"",E588&lt;&gt;"",NOT(ISNUMBER(F588))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="34" t="n"/>
@@ -25546,6 +27889,10 @@
         <v/>
       </c>
       <c r="I589" s="31" t="n"/>
+      <c r="J589" s="36">
+        <f>IF(AND(B589&lt;&gt;"",E589&lt;&gt;"",NOT(ISNUMBER(F589))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="34" t="n"/>
@@ -25566,6 +27913,10 @@
         <v/>
       </c>
       <c r="I590" s="31" t="n"/>
+      <c r="J590" s="36">
+        <f>IF(AND(B590&lt;&gt;"",E590&lt;&gt;"",NOT(ISNUMBER(F590))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="34" t="n"/>
@@ -25586,6 +27937,10 @@
         <v/>
       </c>
       <c r="I591" s="31" t="n"/>
+      <c r="J591" s="36">
+        <f>IF(AND(B591&lt;&gt;"",E591&lt;&gt;"",NOT(ISNUMBER(F591))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="34" t="n"/>
@@ -25606,6 +27961,10 @@
         <v/>
       </c>
       <c r="I592" s="31" t="n"/>
+      <c r="J592" s="36">
+        <f>IF(AND(B592&lt;&gt;"",E592&lt;&gt;"",NOT(ISNUMBER(F592))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="34" t="n"/>
@@ -25626,6 +27985,10 @@
         <v/>
       </c>
       <c r="I593" s="31" t="n"/>
+      <c r="J593" s="36">
+        <f>IF(AND(B593&lt;&gt;"",E593&lt;&gt;"",NOT(ISNUMBER(F593))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="34" t="n"/>
@@ -25646,6 +28009,10 @@
         <v/>
       </c>
       <c r="I594" s="31" t="n"/>
+      <c r="J594" s="36">
+        <f>IF(AND(B594&lt;&gt;"",E594&lt;&gt;"",NOT(ISNUMBER(F594))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="34" t="n"/>
@@ -25666,6 +28033,10 @@
         <v/>
       </c>
       <c r="I595" s="31" t="n"/>
+      <c r="J595" s="36">
+        <f>IF(AND(B595&lt;&gt;"",E595&lt;&gt;"",NOT(ISNUMBER(F595))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="34" t="n"/>
@@ -25686,6 +28057,10 @@
         <v/>
       </c>
       <c r="I596" s="31" t="n"/>
+      <c r="J596" s="36">
+        <f>IF(AND(B596&lt;&gt;"",E596&lt;&gt;"",NOT(ISNUMBER(F596))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="34" t="n"/>
@@ -25706,6 +28081,10 @@
         <v/>
       </c>
       <c r="I597" s="31" t="n"/>
+      <c r="J597" s="36">
+        <f>IF(AND(B597&lt;&gt;"",E597&lt;&gt;"",NOT(ISNUMBER(F597))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="34" t="n"/>
@@ -25726,6 +28105,10 @@
         <v/>
       </c>
       <c r="I598" s="31" t="n"/>
+      <c r="J598" s="36">
+        <f>IF(AND(B598&lt;&gt;"",E598&lt;&gt;"",NOT(ISNUMBER(F598))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="34" t="n"/>
@@ -25746,6 +28129,10 @@
         <v/>
       </c>
       <c r="I599" s="31" t="n"/>
+      <c r="J599" s="36">
+        <f>IF(AND(B599&lt;&gt;"",E599&lt;&gt;"",NOT(ISNUMBER(F599))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="34" t="n"/>
@@ -25766,6 +28153,10 @@
         <v/>
       </c>
       <c r="I600" s="31" t="n"/>
+      <c r="J600" s="36">
+        <f>IF(AND(B600&lt;&gt;"",E600&lt;&gt;"",NOT(ISNUMBER(F600))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="34" t="n"/>
@@ -25786,6 +28177,10 @@
         <v/>
       </c>
       <c r="I601" s="31" t="n"/>
+      <c r="J601" s="36">
+        <f>IF(AND(B601&lt;&gt;"",E601&lt;&gt;"",NOT(ISNUMBER(F601))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="34" t="n"/>
@@ -25806,6 +28201,10 @@
         <v/>
       </c>
       <c r="I602" s="31" t="n"/>
+      <c r="J602" s="36">
+        <f>IF(AND(B602&lt;&gt;"",E602&lt;&gt;"",NOT(ISNUMBER(F602))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="34" t="n"/>
@@ -25826,6 +28225,10 @@
         <v/>
       </c>
       <c r="I603" s="31" t="n"/>
+      <c r="J603" s="36">
+        <f>IF(AND(B603&lt;&gt;"",E603&lt;&gt;"",NOT(ISNUMBER(F603))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="34" t="n"/>
@@ -25846,6 +28249,10 @@
         <v/>
       </c>
       <c r="I604" s="31" t="n"/>
+      <c r="J604" s="36">
+        <f>IF(AND(B604&lt;&gt;"",E604&lt;&gt;"",NOT(ISNUMBER(F604))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="34" t="n"/>
@@ -25866,6 +28273,10 @@
         <v/>
       </c>
       <c r="I605" s="31" t="n"/>
+      <c r="J605" s="36">
+        <f>IF(AND(B605&lt;&gt;"",E605&lt;&gt;"",NOT(ISNUMBER(F605))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="34" t="n"/>
@@ -25886,6 +28297,10 @@
         <v/>
       </c>
       <c r="I606" s="31" t="n"/>
+      <c r="J606" s="36">
+        <f>IF(AND(B606&lt;&gt;"",E606&lt;&gt;"",NOT(ISNUMBER(F606))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="34" t="n"/>
@@ -25906,6 +28321,10 @@
         <v/>
       </c>
       <c r="I607" s="31" t="n"/>
+      <c r="J607" s="36">
+        <f>IF(AND(B607&lt;&gt;"",E607&lt;&gt;"",NOT(ISNUMBER(F607))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="34" t="n"/>
@@ -25926,6 +28345,10 @@
         <v/>
       </c>
       <c r="I608" s="31" t="n"/>
+      <c r="J608" s="36">
+        <f>IF(AND(B608&lt;&gt;"",E608&lt;&gt;"",NOT(ISNUMBER(F608))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="34" t="n"/>
@@ -25946,6 +28369,10 @@
         <v/>
       </c>
       <c r="I609" s="31" t="n"/>
+      <c r="J609" s="36">
+        <f>IF(AND(B609&lt;&gt;"",E609&lt;&gt;"",NOT(ISNUMBER(F609))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="34" t="n"/>
@@ -25966,6 +28393,10 @@
         <v/>
       </c>
       <c r="I610" s="31" t="n"/>
+      <c r="J610" s="36">
+        <f>IF(AND(B610&lt;&gt;"",E610&lt;&gt;"",NOT(ISNUMBER(F610))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="34" t="n"/>
@@ -25986,6 +28417,10 @@
         <v/>
       </c>
       <c r="I611" s="31" t="n"/>
+      <c r="J611" s="36">
+        <f>IF(AND(B611&lt;&gt;"",E611&lt;&gt;"",NOT(ISNUMBER(F611))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="34" t="n"/>
@@ -26006,6 +28441,10 @@
         <v/>
       </c>
       <c r="I612" s="31" t="n"/>
+      <c r="J612" s="36">
+        <f>IF(AND(B612&lt;&gt;"",E612&lt;&gt;"",NOT(ISNUMBER(F612))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="34" t="n"/>
@@ -26026,6 +28465,10 @@
         <v/>
       </c>
       <c r="I613" s="31" t="n"/>
+      <c r="J613" s="36">
+        <f>IF(AND(B613&lt;&gt;"",E613&lt;&gt;"",NOT(ISNUMBER(F613))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="34" t="n"/>
@@ -26046,6 +28489,10 @@
         <v/>
       </c>
       <c r="I614" s="31" t="n"/>
+      <c r="J614" s="36">
+        <f>IF(AND(B614&lt;&gt;"",E614&lt;&gt;"",NOT(ISNUMBER(F614))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="34" t="n"/>
@@ -26066,6 +28513,10 @@
         <v/>
       </c>
       <c r="I615" s="31" t="n"/>
+      <c r="J615" s="36">
+        <f>IF(AND(B615&lt;&gt;"",E615&lt;&gt;"",NOT(ISNUMBER(F615))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="34" t="n"/>
@@ -26086,6 +28537,10 @@
         <v/>
       </c>
       <c r="I616" s="31" t="n"/>
+      <c r="J616" s="36">
+        <f>IF(AND(B616&lt;&gt;"",E616&lt;&gt;"",NOT(ISNUMBER(F616))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="34" t="n"/>
@@ -26106,6 +28561,10 @@
         <v/>
       </c>
       <c r="I617" s="31" t="n"/>
+      <c r="J617" s="36">
+        <f>IF(AND(B617&lt;&gt;"",E617&lt;&gt;"",NOT(ISNUMBER(F617))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="34" t="n"/>
@@ -26126,6 +28585,10 @@
         <v/>
       </c>
       <c r="I618" s="31" t="n"/>
+      <c r="J618" s="36">
+        <f>IF(AND(B618&lt;&gt;"",E618&lt;&gt;"",NOT(ISNUMBER(F618))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="34" t="n"/>
@@ -26146,6 +28609,10 @@
         <v/>
       </c>
       <c r="I619" s="31" t="n"/>
+      <c r="J619" s="36">
+        <f>IF(AND(B619&lt;&gt;"",E619&lt;&gt;"",NOT(ISNUMBER(F619))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="34" t="n"/>
@@ -26166,6 +28633,10 @@
         <v/>
       </c>
       <c r="I620" s="31" t="n"/>
+      <c r="J620" s="36">
+        <f>IF(AND(B620&lt;&gt;"",E620&lt;&gt;"",NOT(ISNUMBER(F620))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="34" t="n"/>
@@ -26186,6 +28657,10 @@
         <v/>
       </c>
       <c r="I621" s="31" t="n"/>
+      <c r="J621" s="36">
+        <f>IF(AND(B621&lt;&gt;"",E621&lt;&gt;"",NOT(ISNUMBER(F621))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="34" t="n"/>
@@ -26206,6 +28681,10 @@
         <v/>
       </c>
       <c r="I622" s="31" t="n"/>
+      <c r="J622" s="36">
+        <f>IF(AND(B622&lt;&gt;"",E622&lt;&gt;"",NOT(ISNUMBER(F622))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="34" t="n"/>
@@ -26226,6 +28705,10 @@
         <v/>
       </c>
       <c r="I623" s="31" t="n"/>
+      <c r="J623" s="36">
+        <f>IF(AND(B623&lt;&gt;"",E623&lt;&gt;"",NOT(ISNUMBER(F623))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="34" t="n"/>
@@ -26246,6 +28729,10 @@
         <v/>
       </c>
       <c r="I624" s="31" t="n"/>
+      <c r="J624" s="36">
+        <f>IF(AND(B624&lt;&gt;"",E624&lt;&gt;"",NOT(ISNUMBER(F624))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="34" t="n"/>
@@ -26266,6 +28753,10 @@
         <v/>
       </c>
       <c r="I625" s="31" t="n"/>
+      <c r="J625" s="36">
+        <f>IF(AND(B625&lt;&gt;"",E625&lt;&gt;"",NOT(ISNUMBER(F625))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="34" t="n"/>
@@ -26286,6 +28777,10 @@
         <v/>
       </c>
       <c r="I626" s="31" t="n"/>
+      <c r="J626" s="36">
+        <f>IF(AND(B626&lt;&gt;"",E626&lt;&gt;"",NOT(ISNUMBER(F626))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="34" t="n"/>
@@ -26306,6 +28801,10 @@
         <v/>
       </c>
       <c r="I627" s="31" t="n"/>
+      <c r="J627" s="36">
+        <f>IF(AND(B627&lt;&gt;"",E627&lt;&gt;"",NOT(ISNUMBER(F627))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="34" t="n"/>
@@ -26326,6 +28825,10 @@
         <v/>
       </c>
       <c r="I628" s="31" t="n"/>
+      <c r="J628" s="36">
+        <f>IF(AND(B628&lt;&gt;"",E628&lt;&gt;"",NOT(ISNUMBER(F628))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="34" t="n"/>
@@ -26346,6 +28849,10 @@
         <v/>
       </c>
       <c r="I629" s="31" t="n"/>
+      <c r="J629" s="36">
+        <f>IF(AND(B629&lt;&gt;"",E629&lt;&gt;"",NOT(ISNUMBER(F629))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="34" t="n"/>
@@ -26366,6 +28873,10 @@
         <v/>
       </c>
       <c r="I630" s="31" t="n"/>
+      <c r="J630" s="36">
+        <f>IF(AND(B630&lt;&gt;"",E630&lt;&gt;"",NOT(ISNUMBER(F630))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="34" t="n"/>
@@ -26386,6 +28897,10 @@
         <v/>
       </c>
       <c r="I631" s="31" t="n"/>
+      <c r="J631" s="36">
+        <f>IF(AND(B631&lt;&gt;"",E631&lt;&gt;"",NOT(ISNUMBER(F631))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="34" t="n"/>
@@ -26406,6 +28921,10 @@
         <v/>
       </c>
       <c r="I632" s="31" t="n"/>
+      <c r="J632" s="36">
+        <f>IF(AND(B632&lt;&gt;"",E632&lt;&gt;"",NOT(ISNUMBER(F632))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="34" t="n"/>
@@ -26426,6 +28945,10 @@
         <v/>
       </c>
       <c r="I633" s="31" t="n"/>
+      <c r="J633" s="36">
+        <f>IF(AND(B633&lt;&gt;"",E633&lt;&gt;"",NOT(ISNUMBER(F633))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="34" t="n"/>
@@ -26446,6 +28969,10 @@
         <v/>
       </c>
       <c r="I634" s="31" t="n"/>
+      <c r="J634" s="36">
+        <f>IF(AND(B634&lt;&gt;"",E634&lt;&gt;"",NOT(ISNUMBER(F634))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="34" t="n"/>
@@ -26466,6 +28993,10 @@
         <v/>
       </c>
       <c r="I635" s="31" t="n"/>
+      <c r="J635" s="36">
+        <f>IF(AND(B635&lt;&gt;"",E635&lt;&gt;"",NOT(ISNUMBER(F635))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="34" t="n"/>
@@ -26486,6 +29017,10 @@
         <v/>
       </c>
       <c r="I636" s="31" t="n"/>
+      <c r="J636" s="36">
+        <f>IF(AND(B636&lt;&gt;"",E636&lt;&gt;"",NOT(ISNUMBER(F636))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="34" t="n"/>
@@ -26506,6 +29041,10 @@
         <v/>
       </c>
       <c r="I637" s="31" t="n"/>
+      <c r="J637" s="36">
+        <f>IF(AND(B637&lt;&gt;"",E637&lt;&gt;"",NOT(ISNUMBER(F637))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="34" t="n"/>
@@ -26526,6 +29065,10 @@
         <v/>
       </c>
       <c r="I638" s="31" t="n"/>
+      <c r="J638" s="36">
+        <f>IF(AND(B638&lt;&gt;"",E638&lt;&gt;"",NOT(ISNUMBER(F638))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="34" t="n"/>
@@ -26546,6 +29089,10 @@
         <v/>
       </c>
       <c r="I639" s="31" t="n"/>
+      <c r="J639" s="36">
+        <f>IF(AND(B639&lt;&gt;"",E639&lt;&gt;"",NOT(ISNUMBER(F639))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="34" t="n"/>
@@ -26566,6 +29113,10 @@
         <v/>
       </c>
       <c r="I640" s="31" t="n"/>
+      <c r="J640" s="36">
+        <f>IF(AND(B640&lt;&gt;"",E640&lt;&gt;"",NOT(ISNUMBER(F640))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="34" t="n"/>
@@ -26586,6 +29137,10 @@
         <v/>
       </c>
       <c r="I641" s="31" t="n"/>
+      <c r="J641" s="36">
+        <f>IF(AND(B641&lt;&gt;"",E641&lt;&gt;"",NOT(ISNUMBER(F641))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="34" t="n"/>
@@ -26606,6 +29161,10 @@
         <v/>
       </c>
       <c r="I642" s="31" t="n"/>
+      <c r="J642" s="36">
+        <f>IF(AND(B642&lt;&gt;"",E642&lt;&gt;"",NOT(ISNUMBER(F642))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="34" t="n"/>
@@ -26626,6 +29185,10 @@
         <v/>
       </c>
       <c r="I643" s="31" t="n"/>
+      <c r="J643" s="36">
+        <f>IF(AND(B643&lt;&gt;"",E643&lt;&gt;"",NOT(ISNUMBER(F643))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="34" t="n"/>
@@ -26646,6 +29209,10 @@
         <v/>
       </c>
       <c r="I644" s="31" t="n"/>
+      <c r="J644" s="36">
+        <f>IF(AND(B644&lt;&gt;"",E644&lt;&gt;"",NOT(ISNUMBER(F644))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="34" t="n"/>
@@ -26666,6 +29233,10 @@
         <v/>
       </c>
       <c r="I645" s="31" t="n"/>
+      <c r="J645" s="36">
+        <f>IF(AND(B645&lt;&gt;"",E645&lt;&gt;"",NOT(ISNUMBER(F645))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="34" t="n"/>
@@ -26686,6 +29257,10 @@
         <v/>
       </c>
       <c r="I646" s="31" t="n"/>
+      <c r="J646" s="36">
+        <f>IF(AND(B646&lt;&gt;"",E646&lt;&gt;"",NOT(ISNUMBER(F646))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="34" t="n"/>
@@ -26706,6 +29281,10 @@
         <v/>
       </c>
       <c r="I647" s="31" t="n"/>
+      <c r="J647" s="36">
+        <f>IF(AND(B647&lt;&gt;"",E647&lt;&gt;"",NOT(ISNUMBER(F647))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="34" t="n"/>
@@ -26726,6 +29305,10 @@
         <v/>
       </c>
       <c r="I648" s="31" t="n"/>
+      <c r="J648" s="36">
+        <f>IF(AND(B648&lt;&gt;"",E648&lt;&gt;"",NOT(ISNUMBER(F648))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="34" t="n"/>
@@ -26746,6 +29329,10 @@
         <v/>
       </c>
       <c r="I649" s="31" t="n"/>
+      <c r="J649" s="36">
+        <f>IF(AND(B649&lt;&gt;"",E649&lt;&gt;"",NOT(ISNUMBER(F649))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="34" t="n"/>
@@ -26766,6 +29353,10 @@
         <v/>
       </c>
       <c r="I650" s="31" t="n"/>
+      <c r="J650" s="36">
+        <f>IF(AND(B650&lt;&gt;"",E650&lt;&gt;"",NOT(ISNUMBER(F650))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="34" t="n"/>
@@ -26786,6 +29377,10 @@
         <v/>
       </c>
       <c r="I651" s="31" t="n"/>
+      <c r="J651" s="36">
+        <f>IF(AND(B651&lt;&gt;"",E651&lt;&gt;"",NOT(ISNUMBER(F651))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="34" t="n"/>
@@ -26806,6 +29401,10 @@
         <v/>
       </c>
       <c r="I652" s="31" t="n"/>
+      <c r="J652" s="36">
+        <f>IF(AND(B652&lt;&gt;"",E652&lt;&gt;"",NOT(ISNUMBER(F652))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="34" t="n"/>
@@ -26826,6 +29425,10 @@
         <v/>
       </c>
       <c r="I653" s="31" t="n"/>
+      <c r="J653" s="36">
+        <f>IF(AND(B653&lt;&gt;"",E653&lt;&gt;"",NOT(ISNUMBER(F653))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="34" t="n"/>
@@ -26846,6 +29449,10 @@
         <v/>
       </c>
       <c r="I654" s="31" t="n"/>
+      <c r="J654" s="36">
+        <f>IF(AND(B654&lt;&gt;"",E654&lt;&gt;"",NOT(ISNUMBER(F654))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="34" t="n"/>
@@ -26866,6 +29473,10 @@
         <v/>
       </c>
       <c r="I655" s="31" t="n"/>
+      <c r="J655" s="36">
+        <f>IF(AND(B655&lt;&gt;"",E655&lt;&gt;"",NOT(ISNUMBER(F655))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="34" t="n"/>
@@ -26886,6 +29497,10 @@
         <v/>
       </c>
       <c r="I656" s="31" t="n"/>
+      <c r="J656" s="36">
+        <f>IF(AND(B656&lt;&gt;"",E656&lt;&gt;"",NOT(ISNUMBER(F656))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="34" t="n"/>
@@ -26906,6 +29521,10 @@
         <v/>
       </c>
       <c r="I657" s="31" t="n"/>
+      <c r="J657" s="36">
+        <f>IF(AND(B657&lt;&gt;"",E657&lt;&gt;"",NOT(ISNUMBER(F657))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="34" t="n"/>
@@ -26926,6 +29545,10 @@
         <v/>
       </c>
       <c r="I658" s="31" t="n"/>
+      <c r="J658" s="36">
+        <f>IF(AND(B658&lt;&gt;"",E658&lt;&gt;"",NOT(ISNUMBER(F658))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="34" t="n"/>
@@ -26946,6 +29569,10 @@
         <v/>
       </c>
       <c r="I659" s="31" t="n"/>
+      <c r="J659" s="36">
+        <f>IF(AND(B659&lt;&gt;"",E659&lt;&gt;"",NOT(ISNUMBER(F659))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="34" t="n"/>
@@ -26966,6 +29593,10 @@
         <v/>
       </c>
       <c r="I660" s="31" t="n"/>
+      <c r="J660" s="36">
+        <f>IF(AND(B660&lt;&gt;"",E660&lt;&gt;"",NOT(ISNUMBER(F660))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="34" t="n"/>
@@ -26986,6 +29617,10 @@
         <v/>
       </c>
       <c r="I661" s="31" t="n"/>
+      <c r="J661" s="36">
+        <f>IF(AND(B661&lt;&gt;"",E661&lt;&gt;"",NOT(ISNUMBER(F661))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="34" t="n"/>
@@ -27006,6 +29641,10 @@
         <v/>
       </c>
       <c r="I662" s="31" t="n"/>
+      <c r="J662" s="36">
+        <f>IF(AND(B662&lt;&gt;"",E662&lt;&gt;"",NOT(ISNUMBER(F662))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="34" t="n"/>
@@ -27026,6 +29665,10 @@
         <v/>
       </c>
       <c r="I663" s="31" t="n"/>
+      <c r="J663" s="36">
+        <f>IF(AND(B663&lt;&gt;"",E663&lt;&gt;"",NOT(ISNUMBER(F663))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="34" t="n"/>
@@ -27046,6 +29689,10 @@
         <v/>
       </c>
       <c r="I664" s="31" t="n"/>
+      <c r="J664" s="36">
+        <f>IF(AND(B664&lt;&gt;"",E664&lt;&gt;"",NOT(ISNUMBER(F664))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="34" t="n"/>
@@ -27066,6 +29713,10 @@
         <v/>
       </c>
       <c r="I665" s="31" t="n"/>
+      <c r="J665" s="36">
+        <f>IF(AND(B665&lt;&gt;"",E665&lt;&gt;"",NOT(ISNUMBER(F665))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="34" t="n"/>
@@ -27086,6 +29737,10 @@
         <v/>
       </c>
       <c r="I666" s="31" t="n"/>
+      <c r="J666" s="36">
+        <f>IF(AND(B666&lt;&gt;"",E666&lt;&gt;"",NOT(ISNUMBER(F666))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="34" t="n"/>
@@ -27106,6 +29761,10 @@
         <v/>
       </c>
       <c r="I667" s="31" t="n"/>
+      <c r="J667" s="36">
+        <f>IF(AND(B667&lt;&gt;"",E667&lt;&gt;"",NOT(ISNUMBER(F667))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="34" t="n"/>
@@ -27126,6 +29785,10 @@
         <v/>
       </c>
       <c r="I668" s="31" t="n"/>
+      <c r="J668" s="36">
+        <f>IF(AND(B668&lt;&gt;"",E668&lt;&gt;"",NOT(ISNUMBER(F668))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="34" t="n"/>
@@ -27146,6 +29809,10 @@
         <v/>
       </c>
       <c r="I669" s="31" t="n"/>
+      <c r="J669" s="36">
+        <f>IF(AND(B669&lt;&gt;"",E669&lt;&gt;"",NOT(ISNUMBER(F669))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="34" t="n"/>
@@ -27166,6 +29833,10 @@
         <v/>
       </c>
       <c r="I670" s="31" t="n"/>
+      <c r="J670" s="36">
+        <f>IF(AND(B670&lt;&gt;"",E670&lt;&gt;"",NOT(ISNUMBER(F670))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="34" t="n"/>
@@ -27186,6 +29857,10 @@
         <v/>
       </c>
       <c r="I671" s="31" t="n"/>
+      <c r="J671" s="36">
+        <f>IF(AND(B671&lt;&gt;"",E671&lt;&gt;"",NOT(ISNUMBER(F671))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="34" t="n"/>
@@ -27206,6 +29881,10 @@
         <v/>
       </c>
       <c r="I672" s="31" t="n"/>
+      <c r="J672" s="36">
+        <f>IF(AND(B672&lt;&gt;"",E672&lt;&gt;"",NOT(ISNUMBER(F672))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="34" t="n"/>
@@ -27226,6 +29905,10 @@
         <v/>
       </c>
       <c r="I673" s="31" t="n"/>
+      <c r="J673" s="36">
+        <f>IF(AND(B673&lt;&gt;"",E673&lt;&gt;"",NOT(ISNUMBER(F673))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" s="34" t="n"/>
@@ -27246,6 +29929,10 @@
         <v/>
       </c>
       <c r="I674" s="31" t="n"/>
+      <c r="J674" s="36">
+        <f>IF(AND(B674&lt;&gt;"",E674&lt;&gt;"",NOT(ISNUMBER(F674))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="34" t="n"/>
@@ -27266,6 +29953,10 @@
         <v/>
       </c>
       <c r="I675" s="31" t="n"/>
+      <c r="J675" s="36">
+        <f>IF(AND(B675&lt;&gt;"",E675&lt;&gt;"",NOT(ISNUMBER(F675))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" s="34" t="n"/>
@@ -27286,6 +29977,10 @@
         <v/>
       </c>
       <c r="I676" s="31" t="n"/>
+      <c r="J676" s="36">
+        <f>IF(AND(B676&lt;&gt;"",E676&lt;&gt;"",NOT(ISNUMBER(F676))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="34" t="n"/>
@@ -27306,6 +30001,10 @@
         <v/>
       </c>
       <c r="I677" s="31" t="n"/>
+      <c r="J677" s="36">
+        <f>IF(AND(B677&lt;&gt;"",E677&lt;&gt;"",NOT(ISNUMBER(F677))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" s="34" t="n"/>
@@ -27326,6 +30025,10 @@
         <v/>
       </c>
       <c r="I678" s="31" t="n"/>
+      <c r="J678" s="36">
+        <f>IF(AND(B678&lt;&gt;"",E678&lt;&gt;"",NOT(ISNUMBER(F678))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" s="34" t="n"/>
@@ -27346,6 +30049,10 @@
         <v/>
       </c>
       <c r="I679" s="31" t="n"/>
+      <c r="J679" s="36">
+        <f>IF(AND(B679&lt;&gt;"",E679&lt;&gt;"",NOT(ISNUMBER(F679))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" s="34" t="n"/>
@@ -27366,6 +30073,10 @@
         <v/>
       </c>
       <c r="I680" s="31" t="n"/>
+      <c r="J680" s="36">
+        <f>IF(AND(B680&lt;&gt;"",E680&lt;&gt;"",NOT(ISNUMBER(F680))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="34" t="n"/>
@@ -27386,6 +30097,10 @@
         <v/>
       </c>
       <c r="I681" s="31" t="n"/>
+      <c r="J681" s="36">
+        <f>IF(AND(B681&lt;&gt;"",E681&lt;&gt;"",NOT(ISNUMBER(F681))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="34" t="n"/>
@@ -27406,6 +30121,10 @@
         <v/>
       </c>
       <c r="I682" s="31" t="n"/>
+      <c r="J682" s="36">
+        <f>IF(AND(B682&lt;&gt;"",E682&lt;&gt;"",NOT(ISNUMBER(F682))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="34" t="n"/>
@@ -27426,6 +30145,10 @@
         <v/>
       </c>
       <c r="I683" s="31" t="n"/>
+      <c r="J683" s="36">
+        <f>IF(AND(B683&lt;&gt;"",E683&lt;&gt;"",NOT(ISNUMBER(F683))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="34" t="n"/>
@@ -27446,6 +30169,10 @@
         <v/>
       </c>
       <c r="I684" s="31" t="n"/>
+      <c r="J684" s="36">
+        <f>IF(AND(B684&lt;&gt;"",E684&lt;&gt;"",NOT(ISNUMBER(F684))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" s="34" t="n"/>
@@ -27466,6 +30193,10 @@
         <v/>
       </c>
       <c r="I685" s="31" t="n"/>
+      <c r="J685" s="36">
+        <f>IF(AND(B685&lt;&gt;"",E685&lt;&gt;"",NOT(ISNUMBER(F685))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="34" t="n"/>
@@ -27486,6 +30217,10 @@
         <v/>
       </c>
       <c r="I686" s="31" t="n"/>
+      <c r="J686" s="36">
+        <f>IF(AND(B686&lt;&gt;"",E686&lt;&gt;"",NOT(ISNUMBER(F686))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" s="34" t="n"/>
@@ -27506,6 +30241,10 @@
         <v/>
       </c>
       <c r="I687" s="31" t="n"/>
+      <c r="J687" s="36">
+        <f>IF(AND(B687&lt;&gt;"",E687&lt;&gt;"",NOT(ISNUMBER(F687))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" s="34" t="n"/>
@@ -27526,6 +30265,10 @@
         <v/>
       </c>
       <c r="I688" s="31" t="n"/>
+      <c r="J688" s="36">
+        <f>IF(AND(B688&lt;&gt;"",E688&lt;&gt;"",NOT(ISNUMBER(F688))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" s="34" t="n"/>
@@ -27546,6 +30289,10 @@
         <v/>
       </c>
       <c r="I689" s="31" t="n"/>
+      <c r="J689" s="36">
+        <f>IF(AND(B689&lt;&gt;"",E689&lt;&gt;"",NOT(ISNUMBER(F689))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="34" t="n"/>
@@ -27566,6 +30313,10 @@
         <v/>
       </c>
       <c r="I690" s="31" t="n"/>
+      <c r="J690" s="36">
+        <f>IF(AND(B690&lt;&gt;"",E690&lt;&gt;"",NOT(ISNUMBER(F690))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" s="34" t="n"/>
@@ -27586,6 +30337,10 @@
         <v/>
       </c>
       <c r="I691" s="31" t="n"/>
+      <c r="J691" s="36">
+        <f>IF(AND(B691&lt;&gt;"",E691&lt;&gt;"",NOT(ISNUMBER(F691))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" s="34" t="n"/>
@@ -27606,6 +30361,10 @@
         <v/>
       </c>
       <c r="I692" s="31" t="n"/>
+      <c r="J692" s="36">
+        <f>IF(AND(B692&lt;&gt;"",E692&lt;&gt;"",NOT(ISNUMBER(F692))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" s="34" t="n"/>
@@ -27626,6 +30385,10 @@
         <v/>
       </c>
       <c r="I693" s="31" t="n"/>
+      <c r="J693" s="36">
+        <f>IF(AND(B693&lt;&gt;"",E693&lt;&gt;"",NOT(ISNUMBER(F693))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="34" t="n"/>
@@ -27646,6 +30409,10 @@
         <v/>
       </c>
       <c r="I694" s="31" t="n"/>
+      <c r="J694" s="36">
+        <f>IF(AND(B694&lt;&gt;"",E694&lt;&gt;"",NOT(ISNUMBER(F694))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" s="34" t="n"/>
@@ -27666,6 +30433,10 @@
         <v/>
       </c>
       <c r="I695" s="31" t="n"/>
+      <c r="J695" s="36">
+        <f>IF(AND(B695&lt;&gt;"",E695&lt;&gt;"",NOT(ISNUMBER(F695))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="34" t="n"/>
@@ -27686,6 +30457,10 @@
         <v/>
       </c>
       <c r="I696" s="31" t="n"/>
+      <c r="J696" s="36">
+        <f>IF(AND(B696&lt;&gt;"",E696&lt;&gt;"",NOT(ISNUMBER(F696))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="34" t="n"/>
@@ -27706,6 +30481,10 @@
         <v/>
       </c>
       <c r="I697" s="31" t="n"/>
+      <c r="J697" s="36">
+        <f>IF(AND(B697&lt;&gt;"",E697&lt;&gt;"",NOT(ISNUMBER(F697))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" s="34" t="n"/>
@@ -27726,6 +30505,10 @@
         <v/>
       </c>
       <c r="I698" s="31" t="n"/>
+      <c r="J698" s="36">
+        <f>IF(AND(B698&lt;&gt;"",E698&lt;&gt;"",NOT(ISNUMBER(F698))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="34" t="n"/>
@@ -27746,6 +30529,10 @@
         <v/>
       </c>
       <c r="I699" s="31" t="n"/>
+      <c r="J699" s="36">
+        <f>IF(AND(B699&lt;&gt;"",E699&lt;&gt;"",NOT(ISNUMBER(F699))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" s="34" t="n"/>
@@ -27766,6 +30553,10 @@
         <v/>
       </c>
       <c r="I700" s="31" t="n"/>
+      <c r="J700" s="36">
+        <f>IF(AND(B700&lt;&gt;"",E700&lt;&gt;"",NOT(ISNUMBER(F700))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="34" t="n"/>
@@ -27786,6 +30577,10 @@
         <v/>
       </c>
       <c r="I701" s="31" t="n"/>
+      <c r="J701" s="36">
+        <f>IF(AND(B701&lt;&gt;"",E701&lt;&gt;"",NOT(ISNUMBER(F701))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="34" t="n"/>
@@ -27806,6 +30601,10 @@
         <v/>
       </c>
       <c r="I702" s="31" t="n"/>
+      <c r="J702" s="36">
+        <f>IF(AND(B702&lt;&gt;"",E702&lt;&gt;"",NOT(ISNUMBER(F702))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="34" t="n"/>
@@ -27826,6 +30625,10 @@
         <v/>
       </c>
       <c r="I703" s="31" t="n"/>
+      <c r="J703" s="36">
+        <f>IF(AND(B703&lt;&gt;"",E703&lt;&gt;"",NOT(ISNUMBER(F703))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="34" t="n"/>
@@ -27846,6 +30649,10 @@
         <v/>
       </c>
       <c r="I704" s="31" t="n"/>
+      <c r="J704" s="36">
+        <f>IF(AND(B704&lt;&gt;"",E704&lt;&gt;"",NOT(ISNUMBER(F704))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="34" t="n"/>
@@ -27866,6 +30673,10 @@
         <v/>
       </c>
       <c r="I705" s="31" t="n"/>
+      <c r="J705" s="36">
+        <f>IF(AND(B705&lt;&gt;"",E705&lt;&gt;"",NOT(ISNUMBER(F705))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="34" t="n"/>
@@ -27886,6 +30697,10 @@
         <v/>
       </c>
       <c r="I706" s="31" t="n"/>
+      <c r="J706" s="36">
+        <f>IF(AND(B706&lt;&gt;"",E706&lt;&gt;"",NOT(ISNUMBER(F706))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="34" t="n"/>
@@ -27906,6 +30721,10 @@
         <v/>
       </c>
       <c r="I707" s="31" t="n"/>
+      <c r="J707" s="36">
+        <f>IF(AND(B707&lt;&gt;"",E707&lt;&gt;"",NOT(ISNUMBER(F707))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="34" t="n"/>
@@ -27926,6 +30745,10 @@
         <v/>
       </c>
       <c r="I708" s="31" t="n"/>
+      <c r="J708" s="36">
+        <f>IF(AND(B708&lt;&gt;"",E708&lt;&gt;"",NOT(ISNUMBER(F708))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="34" t="n"/>
@@ -27946,6 +30769,10 @@
         <v/>
       </c>
       <c r="I709" s="31" t="n"/>
+      <c r="J709" s="36">
+        <f>IF(AND(B709&lt;&gt;"",E709&lt;&gt;"",NOT(ISNUMBER(F709))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="34" t="n"/>
@@ -27966,6 +30793,10 @@
         <v/>
       </c>
       <c r="I710" s="31" t="n"/>
+      <c r="J710" s="36">
+        <f>IF(AND(B710&lt;&gt;"",E710&lt;&gt;"",NOT(ISNUMBER(F710))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" s="34" t="n"/>
@@ -27986,6 +30817,10 @@
         <v/>
       </c>
       <c r="I711" s="31" t="n"/>
+      <c r="J711" s="36">
+        <f>IF(AND(B711&lt;&gt;"",E711&lt;&gt;"",NOT(ISNUMBER(F711))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" s="34" t="n"/>
@@ -28006,6 +30841,10 @@
         <v/>
       </c>
       <c r="I712" s="31" t="n"/>
+      <c r="J712" s="36">
+        <f>IF(AND(B712&lt;&gt;"",E712&lt;&gt;"",NOT(ISNUMBER(F712))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="34" t="n"/>
@@ -28026,6 +30865,10 @@
         <v/>
       </c>
       <c r="I713" s="31" t="n"/>
+      <c r="J713" s="36">
+        <f>IF(AND(B713&lt;&gt;"",E713&lt;&gt;"",NOT(ISNUMBER(F713))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="34" t="n"/>
@@ -28046,6 +30889,10 @@
         <v/>
       </c>
       <c r="I714" s="31" t="n"/>
+      <c r="J714" s="36">
+        <f>IF(AND(B714&lt;&gt;"",E714&lt;&gt;"",NOT(ISNUMBER(F714))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" s="34" t="n"/>
@@ -28066,6 +30913,10 @@
         <v/>
       </c>
       <c r="I715" s="31" t="n"/>
+      <c r="J715" s="36">
+        <f>IF(AND(B715&lt;&gt;"",E715&lt;&gt;"",NOT(ISNUMBER(F715))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="34" t="n"/>
@@ -28086,6 +30937,10 @@
         <v/>
       </c>
       <c r="I716" s="31" t="n"/>
+      <c r="J716" s="36">
+        <f>IF(AND(B716&lt;&gt;"",E716&lt;&gt;"",NOT(ISNUMBER(F716))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" s="34" t="n"/>
@@ -28106,6 +30961,10 @@
         <v/>
       </c>
       <c r="I717" s="31" t="n"/>
+      <c r="J717" s="36">
+        <f>IF(AND(B717&lt;&gt;"",E717&lt;&gt;"",NOT(ISNUMBER(F717))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" s="34" t="n"/>
@@ -28126,6 +30985,10 @@
         <v/>
       </c>
       <c r="I718" s="31" t="n"/>
+      <c r="J718" s="36">
+        <f>IF(AND(B718&lt;&gt;"",E718&lt;&gt;"",NOT(ISNUMBER(F718))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" s="34" t="n"/>
@@ -28146,6 +31009,10 @@
         <v/>
       </c>
       <c r="I719" s="31" t="n"/>
+      <c r="J719" s="36">
+        <f>IF(AND(B719&lt;&gt;"",E719&lt;&gt;"",NOT(ISNUMBER(F719))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" s="34" t="n"/>
@@ -28166,6 +31033,10 @@
         <v/>
       </c>
       <c r="I720" s="31" t="n"/>
+      <c r="J720" s="36">
+        <f>IF(AND(B720&lt;&gt;"",E720&lt;&gt;"",NOT(ISNUMBER(F720))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="34" t="n"/>
@@ -28186,6 +31057,10 @@
         <v/>
       </c>
       <c r="I721" s="31" t="n"/>
+      <c r="J721" s="36">
+        <f>IF(AND(B721&lt;&gt;"",E721&lt;&gt;"",NOT(ISNUMBER(F721))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" s="34" t="n"/>
@@ -28206,6 +31081,10 @@
         <v/>
       </c>
       <c r="I722" s="31" t="n"/>
+      <c r="J722" s="36">
+        <f>IF(AND(B722&lt;&gt;"",E722&lt;&gt;"",NOT(ISNUMBER(F722))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" s="34" t="n"/>
@@ -28226,6 +31105,10 @@
         <v/>
       </c>
       <c r="I723" s="31" t="n"/>
+      <c r="J723" s="36">
+        <f>IF(AND(B723&lt;&gt;"",E723&lt;&gt;"",NOT(ISNUMBER(F723))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="34" t="n"/>
@@ -28246,6 +31129,10 @@
         <v/>
       </c>
       <c r="I724" s="31" t="n"/>
+      <c r="J724" s="36">
+        <f>IF(AND(B724&lt;&gt;"",E724&lt;&gt;"",NOT(ISNUMBER(F724))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725" s="34" t="n"/>
@@ -28266,6 +31153,10 @@
         <v/>
       </c>
       <c r="I725" s="31" t="n"/>
+      <c r="J725" s="36">
+        <f>IF(AND(B725&lt;&gt;"",E725&lt;&gt;"",NOT(ISNUMBER(F725))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726" s="34" t="n"/>
@@ -28286,6 +31177,10 @@
         <v/>
       </c>
       <c r="I726" s="31" t="n"/>
+      <c r="J726" s="36">
+        <f>IF(AND(B726&lt;&gt;"",E726&lt;&gt;"",NOT(ISNUMBER(F726))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" s="34" t="n"/>
@@ -28306,6 +31201,10 @@
         <v/>
       </c>
       <c r="I727" s="31" t="n"/>
+      <c r="J727" s="36">
+        <f>IF(AND(B727&lt;&gt;"",E727&lt;&gt;"",NOT(ISNUMBER(F727))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="34" t="n"/>
@@ -28326,6 +31225,10 @@
         <v/>
       </c>
       <c r="I728" s="31" t="n"/>
+      <c r="J728" s="36">
+        <f>IF(AND(B728&lt;&gt;"",E728&lt;&gt;"",NOT(ISNUMBER(F728))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" s="34" t="n"/>
@@ -28346,6 +31249,10 @@
         <v/>
       </c>
       <c r="I729" s="31" t="n"/>
+      <c r="J729" s="36">
+        <f>IF(AND(B729&lt;&gt;"",E729&lt;&gt;"",NOT(ISNUMBER(F729))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="34" t="n"/>
@@ -28366,6 +31273,10 @@
         <v/>
       </c>
       <c r="I730" s="31" t="n"/>
+      <c r="J730" s="36">
+        <f>IF(AND(B730&lt;&gt;"",E730&lt;&gt;"",NOT(ISNUMBER(F730))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="34" t="n"/>
@@ -28386,6 +31297,10 @@
         <v/>
       </c>
       <c r="I731" s="31" t="n"/>
+      <c r="J731" s="36">
+        <f>IF(AND(B731&lt;&gt;"",E731&lt;&gt;"",NOT(ISNUMBER(F731))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="34" t="n"/>
@@ -28406,6 +31321,10 @@
         <v/>
       </c>
       <c r="I732" s="31" t="n"/>
+      <c r="J732" s="36">
+        <f>IF(AND(B732&lt;&gt;"",E732&lt;&gt;"",NOT(ISNUMBER(F732))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="34" t="n"/>
@@ -28426,6 +31345,10 @@
         <v/>
       </c>
       <c r="I733" s="31" t="n"/>
+      <c r="J733" s="36">
+        <f>IF(AND(B733&lt;&gt;"",E733&lt;&gt;"",NOT(ISNUMBER(F733))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="34" t="n"/>
@@ -28446,6 +31369,10 @@
         <v/>
       </c>
       <c r="I734" s="31" t="n"/>
+      <c r="J734" s="36">
+        <f>IF(AND(B734&lt;&gt;"",E734&lt;&gt;"",NOT(ISNUMBER(F734))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="34" t="n"/>
@@ -28466,6 +31393,10 @@
         <v/>
       </c>
       <c r="I735" s="31" t="n"/>
+      <c r="J735" s="36">
+        <f>IF(AND(B735&lt;&gt;"",E735&lt;&gt;"",NOT(ISNUMBER(F735))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="34" t="n"/>
@@ -28486,6 +31417,10 @@
         <v/>
       </c>
       <c r="I736" s="31" t="n"/>
+      <c r="J736" s="36">
+        <f>IF(AND(B736&lt;&gt;"",E736&lt;&gt;"",NOT(ISNUMBER(F736))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" s="34" t="n"/>
@@ -28506,6 +31441,10 @@
         <v/>
       </c>
       <c r="I737" s="31" t="n"/>
+      <c r="J737" s="36">
+        <f>IF(AND(B737&lt;&gt;"",E737&lt;&gt;"",NOT(ISNUMBER(F737))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" s="34" t="n"/>
@@ -28526,6 +31465,10 @@
         <v/>
       </c>
       <c r="I738" s="31" t="n"/>
+      <c r="J738" s="36">
+        <f>IF(AND(B738&lt;&gt;"",E738&lt;&gt;"",NOT(ISNUMBER(F738))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="34" t="n"/>
@@ -28546,6 +31489,10 @@
         <v/>
       </c>
       <c r="I739" s="31" t="n"/>
+      <c r="J739" s="36">
+        <f>IF(AND(B739&lt;&gt;"",E739&lt;&gt;"",NOT(ISNUMBER(F739))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="34" t="n"/>
@@ -28566,6 +31513,10 @@
         <v/>
       </c>
       <c r="I740" s="31" t="n"/>
+      <c r="J740" s="36">
+        <f>IF(AND(B740&lt;&gt;"",E740&lt;&gt;"",NOT(ISNUMBER(F740))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="34" t="n"/>
@@ -28586,6 +31537,10 @@
         <v/>
       </c>
       <c r="I741" s="31" t="n"/>
+      <c r="J741" s="36">
+        <f>IF(AND(B741&lt;&gt;"",E741&lt;&gt;"",NOT(ISNUMBER(F741))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="34" t="n"/>
@@ -28606,6 +31561,10 @@
         <v/>
       </c>
       <c r="I742" s="31" t="n"/>
+      <c r="J742" s="36">
+        <f>IF(AND(B742&lt;&gt;"",E742&lt;&gt;"",NOT(ISNUMBER(F742))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="34" t="n"/>
@@ -28626,6 +31585,10 @@
         <v/>
       </c>
       <c r="I743" s="31" t="n"/>
+      <c r="J743" s="36">
+        <f>IF(AND(B743&lt;&gt;"",E743&lt;&gt;"",NOT(ISNUMBER(F743))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="34" t="n"/>
@@ -28646,6 +31609,10 @@
         <v/>
       </c>
       <c r="I744" s="31" t="n"/>
+      <c r="J744" s="36">
+        <f>IF(AND(B744&lt;&gt;"",E744&lt;&gt;"",NOT(ISNUMBER(F744))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="34" t="n"/>
@@ -28666,6 +31633,10 @@
         <v/>
       </c>
       <c r="I745" s="31" t="n"/>
+      <c r="J745" s="36">
+        <f>IF(AND(B745&lt;&gt;"",E745&lt;&gt;"",NOT(ISNUMBER(F745))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="34" t="n"/>
@@ -28686,6 +31657,10 @@
         <v/>
       </c>
       <c r="I746" s="31" t="n"/>
+      <c r="J746" s="36">
+        <f>IF(AND(B746&lt;&gt;"",E746&lt;&gt;"",NOT(ISNUMBER(F746))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747" s="34" t="n"/>
@@ -28706,6 +31681,10 @@
         <v/>
       </c>
       <c r="I747" s="31" t="n"/>
+      <c r="J747" s="36">
+        <f>IF(AND(B747&lt;&gt;"",E747&lt;&gt;"",NOT(ISNUMBER(F747))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" s="34" t="n"/>
@@ -28726,6 +31705,10 @@
         <v/>
       </c>
       <c r="I748" s="31" t="n"/>
+      <c r="J748" s="36">
+        <f>IF(AND(B748&lt;&gt;"",E748&lt;&gt;"",NOT(ISNUMBER(F748))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="34" t="n"/>
@@ -28746,6 +31729,10 @@
         <v/>
       </c>
       <c r="I749" s="31" t="n"/>
+      <c r="J749" s="36">
+        <f>IF(AND(B749&lt;&gt;"",E749&lt;&gt;"",NOT(ISNUMBER(F749))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750" s="34" t="n"/>
@@ -28766,6 +31753,10 @@
         <v/>
       </c>
       <c r="I750" s="31" t="n"/>
+      <c r="J750" s="36">
+        <f>IF(AND(B750&lt;&gt;"",E750&lt;&gt;"",NOT(ISNUMBER(F750))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" s="34" t="n"/>
@@ -28786,6 +31777,10 @@
         <v/>
       </c>
       <c r="I751" s="31" t="n"/>
+      <c r="J751" s="36">
+        <f>IF(AND(B751&lt;&gt;"",E751&lt;&gt;"",NOT(ISNUMBER(F751))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="34" t="n"/>
@@ -28806,6 +31801,10 @@
         <v/>
       </c>
       <c r="I752" s="31" t="n"/>
+      <c r="J752" s="36">
+        <f>IF(AND(B752&lt;&gt;"",E752&lt;&gt;"",NOT(ISNUMBER(F752))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="34" t="n"/>
@@ -28826,6 +31825,10 @@
         <v/>
       </c>
       <c r="I753" s="31" t="n"/>
+      <c r="J753" s="36">
+        <f>IF(AND(B753&lt;&gt;"",E753&lt;&gt;"",NOT(ISNUMBER(F753))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="34" t="n"/>
@@ -28846,6 +31849,10 @@
         <v/>
       </c>
       <c r="I754" s="31" t="n"/>
+      <c r="J754" s="36">
+        <f>IF(AND(B754&lt;&gt;"",E754&lt;&gt;"",NOT(ISNUMBER(F754))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="34" t="n"/>
@@ -28866,6 +31873,10 @@
         <v/>
       </c>
       <c r="I755" s="31" t="n"/>
+      <c r="J755" s="36">
+        <f>IF(AND(B755&lt;&gt;"",E755&lt;&gt;"",NOT(ISNUMBER(F755))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="34" t="n"/>
@@ -28886,6 +31897,10 @@
         <v/>
       </c>
       <c r="I756" s="31" t="n"/>
+      <c r="J756" s="36">
+        <f>IF(AND(B756&lt;&gt;"",E756&lt;&gt;"",NOT(ISNUMBER(F756))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="34" t="n"/>
@@ -28906,6 +31921,10 @@
         <v/>
       </c>
       <c r="I757" s="31" t="n"/>
+      <c r="J757" s="36">
+        <f>IF(AND(B757&lt;&gt;"",E757&lt;&gt;"",NOT(ISNUMBER(F757))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="34" t="n"/>
@@ -28926,6 +31945,10 @@
         <v/>
       </c>
       <c r="I758" s="31" t="n"/>
+      <c r="J758" s="36">
+        <f>IF(AND(B758&lt;&gt;"",E758&lt;&gt;"",NOT(ISNUMBER(F758))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="34" t="n"/>
@@ -28946,6 +31969,10 @@
         <v/>
       </c>
       <c r="I759" s="31" t="n"/>
+      <c r="J759" s="36">
+        <f>IF(AND(B759&lt;&gt;"",E759&lt;&gt;"",NOT(ISNUMBER(F759))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" s="34" t="n"/>
@@ -28966,6 +31993,10 @@
         <v/>
       </c>
       <c r="I760" s="31" t="n"/>
+      <c r="J760" s="36">
+        <f>IF(AND(B760&lt;&gt;"",E760&lt;&gt;"",NOT(ISNUMBER(F760))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="34" t="n"/>
@@ -28986,6 +32017,10 @@
         <v/>
       </c>
       <c r="I761" s="31" t="n"/>
+      <c r="J761" s="36">
+        <f>IF(AND(B761&lt;&gt;"",E761&lt;&gt;"",NOT(ISNUMBER(F761))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="34" t="n"/>
@@ -29006,6 +32041,10 @@
         <v/>
       </c>
       <c r="I762" s="31" t="n"/>
+      <c r="J762" s="36">
+        <f>IF(AND(B762&lt;&gt;"",E762&lt;&gt;"",NOT(ISNUMBER(F762))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763" s="34" t="n"/>
@@ -29026,6 +32065,10 @@
         <v/>
       </c>
       <c r="I763" s="31" t="n"/>
+      <c r="J763" s="36">
+        <f>IF(AND(B763&lt;&gt;"",E763&lt;&gt;"",NOT(ISNUMBER(F763))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764" s="34" t="n"/>
@@ -29046,6 +32089,10 @@
         <v/>
       </c>
       <c r="I764" s="31" t="n"/>
+      <c r="J764" s="36">
+        <f>IF(AND(B764&lt;&gt;"",E764&lt;&gt;"",NOT(ISNUMBER(F764))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765" s="34" t="n"/>
@@ -29066,6 +32113,10 @@
         <v/>
       </c>
       <c r="I765" s="31" t="n"/>
+      <c r="J765" s="36">
+        <f>IF(AND(B765&lt;&gt;"",E765&lt;&gt;"",NOT(ISNUMBER(F765))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="34" t="n"/>
@@ -29086,6 +32137,10 @@
         <v/>
       </c>
       <c r="I766" s="31" t="n"/>
+      <c r="J766" s="36">
+        <f>IF(AND(B766&lt;&gt;"",E766&lt;&gt;"",NOT(ISNUMBER(F766))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="34" t="n"/>
@@ -29106,6 +32161,10 @@
         <v/>
       </c>
       <c r="I767" s="31" t="n"/>
+      <c r="J767" s="36">
+        <f>IF(AND(B767&lt;&gt;"",E767&lt;&gt;"",NOT(ISNUMBER(F767))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="34" t="n"/>
@@ -29126,6 +32185,10 @@
         <v/>
       </c>
       <c r="I768" s="31" t="n"/>
+      <c r="J768" s="36">
+        <f>IF(AND(B768&lt;&gt;"",E768&lt;&gt;"",NOT(ISNUMBER(F768))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769" s="34" t="n"/>
@@ -29146,6 +32209,10 @@
         <v/>
       </c>
       <c r="I769" s="31" t="n"/>
+      <c r="J769" s="36">
+        <f>IF(AND(B769&lt;&gt;"",E769&lt;&gt;"",NOT(ISNUMBER(F769))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" s="34" t="n"/>
@@ -29166,6 +32233,10 @@
         <v/>
       </c>
       <c r="I770" s="31" t="n"/>
+      <c r="J770" s="36">
+        <f>IF(AND(B770&lt;&gt;"",E770&lt;&gt;"",NOT(ISNUMBER(F770))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="34" t="n"/>
@@ -29186,6 +32257,10 @@
         <v/>
       </c>
       <c r="I771" s="31" t="n"/>
+      <c r="J771" s="36">
+        <f>IF(AND(B771&lt;&gt;"",E771&lt;&gt;"",NOT(ISNUMBER(F771))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" s="34" t="n"/>
@@ -29206,6 +32281,10 @@
         <v/>
       </c>
       <c r="I772" s="31" t="n"/>
+      <c r="J772" s="36">
+        <f>IF(AND(B772&lt;&gt;"",E772&lt;&gt;"",NOT(ISNUMBER(F772))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="34" t="n"/>
@@ -29226,6 +32305,10 @@
         <v/>
       </c>
       <c r="I773" s="31" t="n"/>
+      <c r="J773" s="36">
+        <f>IF(AND(B773&lt;&gt;"",E773&lt;&gt;"",NOT(ISNUMBER(F773))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" s="34" t="n"/>
@@ -29246,6 +32329,10 @@
         <v/>
       </c>
       <c r="I774" s="31" t="n"/>
+      <c r="J774" s="36">
+        <f>IF(AND(B774&lt;&gt;"",E774&lt;&gt;"",NOT(ISNUMBER(F774))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" s="34" t="n"/>
@@ -29266,6 +32353,10 @@
         <v/>
       </c>
       <c r="I775" s="31" t="n"/>
+      <c r="J775" s="36">
+        <f>IF(AND(B775&lt;&gt;"",E775&lt;&gt;"",NOT(ISNUMBER(F775))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="34" t="n"/>
@@ -29286,6 +32377,10 @@
         <v/>
       </c>
       <c r="I776" s="31" t="n"/>
+      <c r="J776" s="36">
+        <f>IF(AND(B776&lt;&gt;"",E776&lt;&gt;"",NOT(ISNUMBER(F776))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777" s="34" t="n"/>
@@ -29306,6 +32401,10 @@
         <v/>
       </c>
       <c r="I777" s="31" t="n"/>
+      <c r="J777" s="36">
+        <f>IF(AND(B777&lt;&gt;"",E777&lt;&gt;"",NOT(ISNUMBER(F777))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" s="34" t="n"/>
@@ -29326,6 +32425,10 @@
         <v/>
       </c>
       <c r="I778" s="31" t="n"/>
+      <c r="J778" s="36">
+        <f>IF(AND(B778&lt;&gt;"",E778&lt;&gt;"",NOT(ISNUMBER(F778))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779" s="34" t="n"/>
@@ -29346,6 +32449,10 @@
         <v/>
       </c>
       <c r="I779" s="31" t="n"/>
+      <c r="J779" s="36">
+        <f>IF(AND(B779&lt;&gt;"",E779&lt;&gt;"",NOT(ISNUMBER(F779))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" s="34" t="n"/>
@@ -29366,6 +32473,10 @@
         <v/>
       </c>
       <c r="I780" s="31" t="n"/>
+      <c r="J780" s="36">
+        <f>IF(AND(B780&lt;&gt;"",E780&lt;&gt;"",NOT(ISNUMBER(F780))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" s="34" t="n"/>
@@ -29386,6 +32497,10 @@
         <v/>
       </c>
       <c r="I781" s="31" t="n"/>
+      <c r="J781" s="36">
+        <f>IF(AND(B781&lt;&gt;"",E781&lt;&gt;"",NOT(ISNUMBER(F781))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782" s="34" t="n"/>
@@ -29406,6 +32521,10 @@
         <v/>
       </c>
       <c r="I782" s="31" t="n"/>
+      <c r="J782" s="36">
+        <f>IF(AND(B782&lt;&gt;"",E782&lt;&gt;"",NOT(ISNUMBER(F782))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="783">
       <c r="A783" s="34" t="n"/>
@@ -29426,6 +32545,10 @@
         <v/>
       </c>
       <c r="I783" s="31" t="n"/>
+      <c r="J783" s="36">
+        <f>IF(AND(B783&lt;&gt;"",E783&lt;&gt;"",NOT(ISNUMBER(F783))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="784">
       <c r="A784" s="34" t="n"/>
@@ -29446,6 +32569,10 @@
         <v/>
       </c>
       <c r="I784" s="31" t="n"/>
+      <c r="J784" s="36">
+        <f>IF(AND(B784&lt;&gt;"",E784&lt;&gt;"",NOT(ISNUMBER(F784))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="785">
       <c r="A785" s="34" t="n"/>
@@ -29466,6 +32593,10 @@
         <v/>
       </c>
       <c r="I785" s="31" t="n"/>
+      <c r="J785" s="36">
+        <f>IF(AND(B785&lt;&gt;"",E785&lt;&gt;"",NOT(ISNUMBER(F785))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786" s="34" t="n"/>
@@ -29486,6 +32617,10 @@
         <v/>
       </c>
       <c r="I786" s="31" t="n"/>
+      <c r="J786" s="36">
+        <f>IF(AND(B786&lt;&gt;"",E786&lt;&gt;"",NOT(ISNUMBER(F786))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" s="34" t="n"/>
@@ -29506,6 +32641,10 @@
         <v/>
       </c>
       <c r="I787" s="31" t="n"/>
+      <c r="J787" s="36">
+        <f>IF(AND(B787&lt;&gt;"",E787&lt;&gt;"",NOT(ISNUMBER(F787))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788" s="34" t="n"/>
@@ -29526,6 +32665,10 @@
         <v/>
       </c>
       <c r="I788" s="31" t="n"/>
+      <c r="J788" s="36">
+        <f>IF(AND(B788&lt;&gt;"",E788&lt;&gt;"",NOT(ISNUMBER(F788))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" s="34" t="n"/>
@@ -29546,6 +32689,10 @@
         <v/>
       </c>
       <c r="I789" s="31" t="n"/>
+      <c r="J789" s="36">
+        <f>IF(AND(B789&lt;&gt;"",E789&lt;&gt;"",NOT(ISNUMBER(F789))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" s="34" t="n"/>
@@ -29566,6 +32713,10 @@
         <v/>
       </c>
       <c r="I790" s="31" t="n"/>
+      <c r="J790" s="36">
+        <f>IF(AND(B790&lt;&gt;"",E790&lt;&gt;"",NOT(ISNUMBER(F790))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" s="34" t="n"/>
@@ -29586,6 +32737,10 @@
         <v/>
       </c>
       <c r="I791" s="31" t="n"/>
+      <c r="J791" s="36">
+        <f>IF(AND(B791&lt;&gt;"",E791&lt;&gt;"",NOT(ISNUMBER(F791))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792" s="34" t="n"/>
@@ -29606,6 +32761,10 @@
         <v/>
       </c>
       <c r="I792" s="31" t="n"/>
+      <c r="J792" s="36">
+        <f>IF(AND(B792&lt;&gt;"",E792&lt;&gt;"",NOT(ISNUMBER(F792))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793" s="34" t="n"/>
@@ -29626,6 +32785,10 @@
         <v/>
       </c>
       <c r="I793" s="31" t="n"/>
+      <c r="J793" s="36">
+        <f>IF(AND(B793&lt;&gt;"",E793&lt;&gt;"",NOT(ISNUMBER(F793))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="794">
       <c r="A794" s="34" t="n"/>
@@ -29646,6 +32809,10 @@
         <v/>
       </c>
       <c r="I794" s="31" t="n"/>
+      <c r="J794" s="36">
+        <f>IF(AND(B794&lt;&gt;"",E794&lt;&gt;"",NOT(ISNUMBER(F794))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795" s="34" t="n"/>
@@ -29666,6 +32833,10 @@
         <v/>
       </c>
       <c r="I795" s="31" t="n"/>
+      <c r="J795" s="36">
+        <f>IF(AND(B795&lt;&gt;"",E795&lt;&gt;"",NOT(ISNUMBER(F795))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" s="34" t="n"/>
@@ -29686,6 +32857,10 @@
         <v/>
       </c>
       <c r="I796" s="31" t="n"/>
+      <c r="J796" s="36">
+        <f>IF(AND(B796&lt;&gt;"",E796&lt;&gt;"",NOT(ISNUMBER(F796))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797" s="34" t="n"/>
@@ -29706,6 +32881,10 @@
         <v/>
       </c>
       <c r="I797" s="31" t="n"/>
+      <c r="J797" s="36">
+        <f>IF(AND(B797&lt;&gt;"",E797&lt;&gt;"",NOT(ISNUMBER(F797))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" s="34" t="n"/>
@@ -29726,6 +32905,10 @@
         <v/>
       </c>
       <c r="I798" s="31" t="n"/>
+      <c r="J798" s="36">
+        <f>IF(AND(B798&lt;&gt;"",E798&lt;&gt;"",NOT(ISNUMBER(F798))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="799">
       <c r="A799" s="34" t="n"/>
@@ -29746,6 +32929,10 @@
         <v/>
       </c>
       <c r="I799" s="31" t="n"/>
+      <c r="J799" s="36">
+        <f>IF(AND(B799&lt;&gt;"",E799&lt;&gt;"",NOT(ISNUMBER(F799))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800" s="34" t="n"/>
@@ -29766,6 +32953,10 @@
         <v/>
       </c>
       <c r="I800" s="31" t="n"/>
+      <c r="J800" s="36">
+        <f>IF(AND(B800&lt;&gt;"",E800&lt;&gt;"",NOT(ISNUMBER(F800))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" s="34" t="n"/>
@@ -29786,6 +32977,10 @@
         <v/>
       </c>
       <c r="I801" s="31" t="n"/>
+      <c r="J801" s="36">
+        <f>IF(AND(B801&lt;&gt;"",E801&lt;&gt;"",NOT(ISNUMBER(F801))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" s="34" t="n"/>
@@ -29806,6 +33001,10 @@
         <v/>
       </c>
       <c r="I802" s="31" t="n"/>
+      <c r="J802" s="36">
+        <f>IF(AND(B802&lt;&gt;"",E802&lt;&gt;"",NOT(ISNUMBER(F802))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="34" t="n"/>
@@ -29826,6 +33025,10 @@
         <v/>
       </c>
       <c r="I803" s="31" t="n"/>
+      <c r="J803" s="36">
+        <f>IF(AND(B803&lt;&gt;"",E803&lt;&gt;"",NOT(ISNUMBER(F803))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="34" t="n"/>
@@ -29846,6 +33049,10 @@
         <v/>
       </c>
       <c r="I804" s="31" t="n"/>
+      <c r="J804" s="36">
+        <f>IF(AND(B804&lt;&gt;"",E804&lt;&gt;"",NOT(ISNUMBER(F804))),1,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/09-horas-e-custo-por-projeto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/09-horas-e-custo-por-projeto.xlsx
@@ -1087,7 +1087,7 @@
     </row>
     <row r="7">
       <c r="A7" s="17">
-        <f>IF(SUM(Horas!$J$5:$J$804)=0,"","Atenção: "&amp;SUM(Horas!$J$5:$J$804)&amp;" lançamento(s) de hora sem custo-hora (cadastro incompleto em Config). O custo desses lançamentos não está contado: o custo real é MAIOR e a margem real é MENOR do que qualquer soma parcial, por isso custo e margem dos projetos e pessoas afetados aparecem como 'cadastro incompleto' até você completar o custo mensal e as horas disponíveis da pessoa.")</f>
+        <f>IF(SUM(Horas!$J$5:$J$804)=0,"","Atenção: "&amp;SUM(Horas!$J$5:$J$804)&amp;" lançamento(s) de hora sem custo-hora (cadastro incompleto em Config). "&amp;"O custo desses lançamentos não está contado: o custo real é MAIOR e a margem real é MENOR do que qualquer soma parcial, "&amp;"por isso custo e margem dos projetos e pessoas afetados aparecem como 'cadastro incompleto' até você completar o custo mensal e as horas disponíveis da pessoa.")</f>
         <v/>
       </c>
     </row>
